--- a/NBS FINAL delivery/03_Excel_Deliveries/9_NBS_Accounts_Domestic_and_GNI.xlsx
+++ b/NBS FINAL delivery/03_Excel_Deliveries/9_NBS_Accounts_Domestic_and_GNI.xlsx
@@ -512,7 +512,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>2026-08-17T02:00:37.393929+00:00</t>
+          <t>2026-08-28T13:31:58.420547+00:00</t>
         </is>
       </c>
     </row>
@@ -637,13 +637,13 @@
         </is>
       </c>
       <c r="C2" s="6" t="n">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="D2" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E2" s="7" t="n">
-        <v>0</v>
+        <v>1104600.78</v>
       </c>
       <c r="F2" s="7" t="n">
         <v>39968.25</v>
@@ -652,19 +652,19 @@
         <v>0</v>
       </c>
       <c r="H2" s="7" t="n">
-        <v>39968.25</v>
+        <v>1144569.03</v>
       </c>
       <c r="I2" s="6" t="n">
-        <v>59952375</v>
+        <v>1716853545</v>
       </c>
       <c r="L2" s="6" t="n">
-        <v>457600000</v>
+        <v>465920000</v>
       </c>
       <c r="M2" s="7" t="n">
-        <v>305066.67</v>
+        <v>310613.33</v>
       </c>
       <c r="N2" s="6" t="n">
-        <v>-397647625</v>
+        <v>1250933545</v>
       </c>
     </row>
     <row r="3">
@@ -679,13 +679,13 @@
         </is>
       </c>
       <c r="C3" s="6" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="D3" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E3" s="7" t="n">
-        <v>0</v>
+        <v>166386.42</v>
       </c>
       <c r="F3" s="7" t="n">
         <v>18481.94</v>
@@ -694,19 +694,19 @@
         <v>0</v>
       </c>
       <c r="H3" s="7" t="n">
-        <v>18481.94</v>
+        <v>184868.36</v>
       </c>
       <c r="I3" s="6" t="n">
-        <v>27722910</v>
+        <v>277302540</v>
       </c>
       <c r="L3" s="6" t="n">
-        <v>72800000</v>
+        <v>81120000</v>
       </c>
       <c r="M3" s="7" t="n">
-        <v>48533.33</v>
+        <v>54080</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>-45077090</v>
+        <v>196182540</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         </is>
       </c>
       <c r="C4" s="6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D4" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E4" s="7" t="n">
-        <v>0</v>
+        <v>3015.54</v>
       </c>
       <c r="F4" s="7" t="n">
         <v>31.93</v>
@@ -736,19 +736,19 @@
         <v>0</v>
       </c>
       <c r="H4" s="7" t="n">
-        <v>31.93</v>
+        <v>3047.47</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>47895</v>
+        <v>4571205</v>
       </c>
       <c r="L4" s="6" t="n">
-        <v>31200000</v>
+        <v>33280000</v>
       </c>
       <c r="M4" s="7" t="n">
-        <v>20800</v>
+        <v>22186.67</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>-31152105</v>
+        <v>-28708795</v>
       </c>
     </row>
     <row r="5">
@@ -763,13 +763,13 @@
         </is>
       </c>
       <c r="C5" s="6" t="n">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="D5" s="7" t="n">
         <v>1158908.69</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>0</v>
+        <v>1229039.28</v>
       </c>
       <c r="F5" s="7" t="n">
         <v>42745.73</v>
@@ -778,19 +778,19 @@
         <v>347672.68</v>
       </c>
       <c r="H5" s="7" t="n">
-        <v>1549326.98</v>
+        <v>2778366.26</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>2323990470</v>
+        <v>4167549390</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>653120000</v>
+        <v>659360000</v>
       </c>
       <c r="M5" s="7" t="n">
-        <v>435413.33</v>
+        <v>439573.33</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>1670870470</v>
+        <v>3508189390</v>
       </c>
     </row>
     <row r="6">
@@ -811,7 +811,7 @@
         <v>448918.99</v>
       </c>
       <c r="E6" s="7" t="n">
-        <v>0</v>
+        <v>281265.84</v>
       </c>
       <c r="F6" s="7" t="n">
         <v>18974.45</v>
@@ -820,10 +820,10 @@
         <v>134675.71</v>
       </c>
       <c r="H6" s="7" t="n">
-        <v>602569.08</v>
+        <v>883834.92</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>903853620</v>
+        <v>1325752380</v>
       </c>
       <c r="L6" s="6" t="n">
         <v>147680000</v>
@@ -832,7 +832,7 @@
         <v>98453.33</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>756173620</v>
+        <v>1178072380</v>
       </c>
     </row>
     <row r="7">
@@ -853,7 +853,7 @@
         <v>1829.85</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>0</v>
+        <v>3130.74</v>
       </c>
       <c r="F7" s="7" t="n">
         <v>32.55</v>
@@ -862,10 +862,10 @@
         <v>548.96</v>
       </c>
       <c r="H7" s="7" t="n">
-        <v>2411.35</v>
+        <v>5542.09</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>3617025</v>
+        <v>8313135</v>
       </c>
       <c r="L7" s="6" t="n">
         <v>70720000</v>
@@ -874,7 +874,7 @@
         <v>47146.67</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>-67102975</v>
+        <v>-62406865</v>
       </c>
     </row>
     <row r="8">
@@ -889,13 +889,13 @@
         </is>
       </c>
       <c r="C8" s="6" t="n">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="D8" s="7" t="n">
         <v>1648929.32</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>0</v>
+        <v>1352730.6</v>
       </c>
       <c r="F8" s="7" t="n">
         <v>55865.5</v>
@@ -904,19 +904,19 @@
         <v>494678.84</v>
       </c>
       <c r="H8" s="7" t="n">
-        <v>2199473.73</v>
+        <v>3552204.33</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>3299210595</v>
+        <v>5328306495</v>
       </c>
       <c r="L8" s="6" t="n">
-        <v>721760000</v>
+        <v>723840000</v>
       </c>
       <c r="M8" s="7" t="n">
-        <v>481173.33</v>
+        <v>482560</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>2577450595</v>
+        <v>4604466495</v>
       </c>
     </row>
     <row r="9">
@@ -937,7 +937,7 @@
         <v>476500.37</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>0</v>
+        <v>293377.68</v>
       </c>
       <c r="F9" s="7" t="n">
         <v>19688.62</v>
@@ -946,10 +946,10 @@
         <v>142950.09</v>
       </c>
       <c r="H9" s="7" t="n">
-        <v>639139.0600000001</v>
+        <v>932516.74</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>958708590</v>
+        <v>1398775110</v>
       </c>
       <c r="L9" s="6" t="n">
         <v>174720000</v>
@@ -958,7 +958,7 @@
         <v>116480</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>783988590</v>
+        <v>1224055110</v>
       </c>
     </row>
     <row r="10">
@@ -979,7 +979,7 @@
         <v>1292.33</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>0</v>
+        <v>3258</v>
       </c>
       <c r="F10" s="7" t="n">
         <v>59.64</v>
@@ -988,10 +988,10 @@
         <v>387.68</v>
       </c>
       <c r="H10" s="7" t="n">
-        <v>1739.69</v>
+        <v>4997.69</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>2609535</v>
+        <v>7496535</v>
       </c>
       <c r="L10" s="6" t="n">
         <v>81120000</v>
@@ -1000,7 +1000,7 @@
         <v>54080</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>-78510465</v>
+        <v>-73623465</v>
       </c>
     </row>
     <row r="11">
@@ -1015,13 +1015,13 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D11" s="7" t="n">
         <v>1979440.3</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>0</v>
+        <v>1895427.36</v>
       </c>
       <c r="F11" s="7" t="n">
         <v>66819.48</v>
@@ -1030,19 +1030,19 @@
         <v>593831.9300000001</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>2640091.91</v>
+        <v>4535519.28</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>3960137865</v>
+        <v>6803278920</v>
       </c>
       <c r="L11" s="6" t="n">
-        <v>734240000</v>
+        <v>736320000</v>
       </c>
       <c r="M11" s="7" t="n">
-        <v>489493.33</v>
+        <v>490880</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>3225897865</v>
+        <v>6066958920</v>
       </c>
     </row>
     <row r="12">
@@ -1063,7 +1063,7 @@
         <v>532221.88</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>0</v>
+        <v>306765.18</v>
       </c>
       <c r="F12" s="7" t="n">
         <v>20756.08</v>
@@ -1072,10 +1072,10 @@
         <v>159666.63</v>
       </c>
       <c r="H12" s="7" t="n">
-        <v>712644.5</v>
+        <v>1019409.68</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>1068966750</v>
+        <v>1529114520</v>
       </c>
       <c r="L12" s="6" t="n">
         <v>176800000</v>
@@ -1084,7 +1084,7 @@
         <v>117866.67</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>892166750</v>
+        <v>1352314520</v>
       </c>
     </row>
     <row r="13">
@@ -1105,7 +1105,7 @@
         <v>1391.37</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>0</v>
+        <v>3420</v>
       </c>
       <c r="F13" s="7" t="n">
         <v>75.93000000000001</v>
@@ -1114,10 +1114,10 @@
         <v>417.45</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>1884.71</v>
+        <v>5304.71</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>2827065</v>
+        <v>7957065</v>
       </c>
       <c r="L13" s="6" t="n">
         <v>85280000</v>
@@ -1126,7 +1126,7 @@
         <v>56853.33</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>-82452935</v>
+        <v>-77322935</v>
       </c>
     </row>
     <row r="14">
@@ -1141,13 +1141,13 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="D14" s="7" t="n">
         <v>1927024.69</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>0</v>
+        <v>2070249.48</v>
       </c>
       <c r="F14" s="7" t="n">
         <v>77246.02</v>
@@ -1156,19 +1156,19 @@
         <v>578107.4399999999</v>
       </c>
       <c r="H14" s="7" t="n">
-        <v>2582378.01</v>
+        <v>4652627.5</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>3873567015</v>
+        <v>6978941250</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>748800000</v>
+        <v>750880000</v>
       </c>
       <c r="M14" s="7" t="n">
-        <v>499200</v>
+        <v>500586.67</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>3124767015</v>
+        <v>6228061250</v>
       </c>
     </row>
     <row r="15">
@@ -1189,7 +1189,7 @@
         <v>630712.8199999999</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>0</v>
+        <v>318280.5</v>
       </c>
       <c r="F15" s="7" t="n">
         <v>21736.2</v>
@@ -1198,10 +1198,10 @@
         <v>189213.84</v>
       </c>
       <c r="H15" s="7" t="n">
-        <v>841662.86</v>
+        <v>1159943.36</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>1262494290</v>
+        <v>1739915040</v>
       </c>
       <c r="L15" s="6" t="n">
         <v>178880000</v>
@@ -1210,7 +1210,7 @@
         <v>119253.33</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>1083614290</v>
+        <v>1561035040</v>
       </c>
     </row>
     <row r="16">
@@ -1231,7 +1231,7 @@
         <v>1225.57</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>0</v>
+        <v>3546</v>
       </c>
       <c r="F16" s="7" t="n">
         <v>99.13</v>
@@ -1240,10 +1240,10 @@
         <v>367.67</v>
       </c>
       <c r="H16" s="7" t="n">
-        <v>1692.39</v>
+        <v>5238.39</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>2538585</v>
+        <v>7857585</v>
       </c>
       <c r="L16" s="6" t="n">
         <v>87360000</v>
@@ -1252,7 +1252,7 @@
         <v>58240</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>-84821415</v>
+        <v>-79502415</v>
       </c>
     </row>
     <row r="17">
@@ -1267,13 +1267,13 @@
         </is>
       </c>
       <c r="C17" s="6" t="n">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="D17" s="7" t="n">
         <v>2265971.02</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>0</v>
+        <v>2314536.66</v>
       </c>
       <c r="F17" s="7" t="n">
         <v>89097.19</v>
@@ -1282,19 +1282,19 @@
         <v>679791.3</v>
       </c>
       <c r="H17" s="7" t="n">
-        <v>3034859.44</v>
+        <v>5349396.1</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>4552289160</v>
+        <v>8024094150</v>
       </c>
       <c r="L17" s="6" t="n">
-        <v>800800000</v>
+        <v>802880000</v>
       </c>
       <c r="M17" s="7" t="n">
-        <v>533866.67</v>
+        <v>535253.33</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>3751489160</v>
+        <v>7221214150</v>
       </c>
     </row>
     <row r="18">
@@ -1315,7 +1315,7 @@
         <v>707531.3199999999</v>
       </c>
       <c r="E18" s="7" t="n">
-        <v>0</v>
+        <v>333415.08</v>
       </c>
       <c r="F18" s="7" t="n">
         <v>22720.03</v>
@@ -1324,10 +1324,10 @@
         <v>212259.44</v>
       </c>
       <c r="H18" s="7" t="n">
-        <v>942510.84</v>
+        <v>1275925.92</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>1413766260</v>
+        <v>1913888880</v>
       </c>
       <c r="L18" s="6" t="n">
         <v>193440000</v>
@@ -1336,7 +1336,7 @@
         <v>128960</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>1220326260</v>
+        <v>1720448880</v>
       </c>
     </row>
     <row r="19">
@@ -1357,7 +1357,7 @@
         <v>1596.1</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>0</v>
+        <v>3672</v>
       </c>
       <c r="F19" s="7" t="n">
         <v>123.07</v>
@@ -1366,10 +1366,10 @@
         <v>478.78</v>
       </c>
       <c r="H19" s="7" t="n">
-        <v>2197.98</v>
+        <v>5869.98</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>3296970</v>
+        <v>8804970</v>
       </c>
       <c r="L19" s="6" t="n">
         <v>91520000</v>
@@ -1378,7 +1378,7 @@
         <v>61013.33</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>-88223030</v>
+        <v>-82715030</v>
       </c>
     </row>
     <row r="20">
@@ -1393,13 +1393,13 @@
         </is>
       </c>
       <c r="C20" s="6" t="n">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="D20" s="7" t="n">
         <v>2581135.11</v>
       </c>
       <c r="E20" s="7" t="n">
-        <v>0</v>
+        <v>2926911.96</v>
       </c>
       <c r="F20" s="7" t="n">
         <v>104788.44</v>
@@ -1408,19 +1408,19 @@
         <v>774340.54</v>
       </c>
       <c r="H20" s="7" t="n">
-        <v>3460264.22</v>
+        <v>6387176.18</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>5190396330</v>
+        <v>9580764270</v>
       </c>
       <c r="L20" s="6" t="n">
-        <v>846560000</v>
+        <v>848640000</v>
       </c>
       <c r="M20" s="7" t="n">
-        <v>564373.33</v>
+        <v>565760</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>4343836330</v>
+        <v>8732124270</v>
       </c>
     </row>
     <row r="21">
@@ -1441,7 +1441,7 @@
         <v>728865.5699999999</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>0</v>
+        <v>355220.82</v>
       </c>
       <c r="F21" s="7" t="n">
         <v>23878.73</v>
@@ -1450,10 +1450,10 @@
         <v>218659.68</v>
       </c>
       <c r="H21" s="7" t="n">
-        <v>971404.0600000001</v>
+        <v>1326624.88</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>1457106090</v>
+        <v>1989937320</v>
       </c>
       <c r="L21" s="6" t="n">
         <v>197600000</v>
@@ -1462,7 +1462,7 @@
         <v>131733.33</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>1259506090</v>
+        <v>1792337320</v>
       </c>
     </row>
     <row r="22">
@@ -1483,7 +1483,7 @@
         <v>1283.81</v>
       </c>
       <c r="E22" s="7" t="n">
-        <v>0</v>
+        <v>3798</v>
       </c>
       <c r="F22" s="7" t="n">
         <v>140.97</v>
@@ -1492,10 +1492,10 @@
         <v>385.17</v>
       </c>
       <c r="H22" s="7" t="n">
-        <v>1809.95</v>
+        <v>5607.95</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>2714925</v>
+        <v>8411925</v>
       </c>
       <c r="L22" s="6" t="n">
         <v>97760000</v>
@@ -1504,7 +1504,7 @@
         <v>65173.33</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>-95045075</v>
+        <v>-89348075</v>
       </c>
     </row>
     <row r="23">
@@ -1519,13 +1519,13 @@
         </is>
       </c>
       <c r="C23" s="6" t="n">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="D23" s="7" t="n">
         <v>2279842.09</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>0</v>
+        <v>3429953.46</v>
       </c>
       <c r="F23" s="7" t="n">
         <v>120783.98</v>
@@ -1534,19 +1534,19 @@
         <v>683952.67</v>
       </c>
       <c r="H23" s="7" t="n">
-        <v>3084578.86</v>
+        <v>6514532.31</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>4626868290</v>
+        <v>9771798465</v>
       </c>
       <c r="L23" s="6" t="n">
-        <v>871520000</v>
+        <v>873600000</v>
       </c>
       <c r="M23" s="7" t="n">
-        <v>581013.33</v>
+        <v>582400</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>3755348290</v>
+        <v>8898198465</v>
       </c>
     </row>
     <row r="24">
@@ -1567,7 +1567,7 @@
         <v>1017953.85</v>
       </c>
       <c r="E24" s="7" t="n">
-        <v>0</v>
+        <v>431344.62</v>
       </c>
       <c r="F24" s="7" t="n">
         <v>24846.67</v>
@@ -1576,10 +1576,10 @@
         <v>305386.13</v>
       </c>
       <c r="H24" s="7" t="n">
-        <v>1348186.59</v>
+        <v>1779531.21</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>2022279885</v>
+        <v>2669296815</v>
       </c>
       <c r="L24" s="6" t="n">
         <v>203840000</v>
@@ -1588,7 +1588,7 @@
         <v>135893.33</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>1818439885</v>
+        <v>2465456815</v>
       </c>
     </row>
     <row r="25">
@@ -1609,7 +1609,7 @@
         <v>1385.46</v>
       </c>
       <c r="E25" s="7" t="n">
-        <v>0</v>
+        <v>3906</v>
       </c>
       <c r="F25" s="7" t="n">
         <v>151.16</v>
@@ -1618,10 +1618,10 @@
         <v>415.66</v>
       </c>
       <c r="H25" s="7" t="n">
-        <v>1952.23</v>
+        <v>5858.23</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>2928345</v>
+        <v>8787345</v>
       </c>
       <c r="L25" s="6" t="n">
         <v>97760000</v>
@@ -1630,7 +1630,7 @@
         <v>65173.33</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>-94831655</v>
+        <v>-88972655</v>
       </c>
     </row>
     <row r="26">
@@ -1645,13 +1645,13 @@
         </is>
       </c>
       <c r="C26" s="6" t="n">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="D26" s="7" t="n">
         <v>2698296.15</v>
       </c>
       <c r="E26" s="7" t="n">
-        <v>0</v>
+        <v>4114455.48</v>
       </c>
       <c r="F26" s="7" t="n">
         <v>135947.53</v>
@@ -1660,25 +1660,25 @@
         <v>809489.02</v>
       </c>
       <c r="H26" s="7" t="n">
-        <v>3643732.44</v>
+        <v>7758187.91</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>5465598660</v>
+        <v>11637281865</v>
       </c>
       <c r="J26" s="7" t="n">
-        <v>138285.94</v>
+        <v>328607.72</v>
       </c>
       <c r="K26" s="7" t="n">
-        <v>3505446.52</v>
+        <v>7429580.39</v>
       </c>
       <c r="L26" s="6" t="n">
-        <v>884000000</v>
+        <v>886080000</v>
       </c>
       <c r="M26" s="7" t="n">
-        <v>589333.33</v>
+        <v>590720</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>4581598660</v>
+        <v>10751201865</v>
       </c>
     </row>
     <row r="27">
@@ -1699,7 +1699,7 @@
         <v>958995.3199999999</v>
       </c>
       <c r="E27" s="7" t="n">
-        <v>0</v>
+        <v>446386.32</v>
       </c>
       <c r="F27" s="7" t="n">
         <v>25717.39</v>
@@ -1708,16 +1708,16 @@
         <v>287698.63</v>
       </c>
       <c r="H27" s="7" t="n">
-        <v>1272411.36</v>
+        <v>1718797.68</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>1908617040</v>
+        <v>2578196520</v>
       </c>
       <c r="J27" s="7" t="n">
-        <v>33340.69</v>
+        <v>45581.34</v>
       </c>
       <c r="K27" s="7" t="n">
-        <v>1239070.66</v>
+        <v>1673216.31</v>
       </c>
       <c r="L27" s="6" t="n">
         <v>210080000</v>
@@ -1726,7 +1726,7 @@
         <v>140053.33</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>1698537040</v>
+        <v>2368116520</v>
       </c>
     </row>
     <row r="28">
@@ -1747,7 +1747,7 @@
         <v>1884.11</v>
       </c>
       <c r="E28" s="7" t="n">
-        <v>0</v>
+        <v>3996</v>
       </c>
       <c r="F28" s="7" t="n">
         <v>162.62</v>
@@ -1756,16 +1756,16 @@
         <v>565.21</v>
       </c>
       <c r="H28" s="7" t="n">
-        <v>2611.98</v>
+        <v>6607.98</v>
       </c>
       <c r="I28" s="6" t="n">
-        <v>3917970</v>
+        <v>9911970</v>
       </c>
       <c r="J28" s="7" t="n">
-        <v>203.37</v>
+        <v>487.66</v>
       </c>
       <c r="K28" s="7" t="n">
-        <v>2408.59</v>
+        <v>6120.3</v>
       </c>
       <c r="L28" s="6" t="n">
         <v>99840000</v>
@@ -1774,7 +1774,7 @@
         <v>66560</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>-95922030</v>
+        <v>-89928030</v>
       </c>
     </row>
     <row r="29">
@@ -1789,13 +1789,13 @@
         </is>
       </c>
       <c r="C29" s="6" t="n">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="D29" s="7" t="n">
         <v>2896002.93</v>
       </c>
       <c r="E29" s="7" t="n">
-        <v>0</v>
+        <v>4794182.28</v>
       </c>
       <c r="F29" s="7" t="n">
         <v>150010.07</v>
@@ -1804,25 +1804,25 @@
         <v>868800.98</v>
       </c>
       <c r="H29" s="7" t="n">
-        <v>3914814.01</v>
+        <v>8708996.279999999</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>5872221015</v>
+        <v>13063494420</v>
       </c>
       <c r="J29" s="7" t="n">
-        <v>148914.69</v>
+        <v>354035.69</v>
       </c>
       <c r="K29" s="7" t="n">
-        <v>3765899.33</v>
+        <v>8354960.59</v>
       </c>
       <c r="L29" s="6" t="n">
-        <v>902720000</v>
+        <v>904800000</v>
       </c>
       <c r="M29" s="7" t="n">
-        <v>601813.33</v>
+        <v>603200</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>4969501015</v>
+        <v>12158694420</v>
       </c>
     </row>
     <row r="30">
@@ -1843,7 +1843,7 @@
         <v>1563473.58</v>
       </c>
       <c r="E30" s="7" t="n">
-        <v>0</v>
+        <v>459349.02</v>
       </c>
       <c r="F30" s="7" t="n">
         <v>26624.46</v>
@@ -1852,16 +1852,16 @@
         <v>469042.06</v>
       </c>
       <c r="H30" s="7" t="n">
-        <v>2059140.13</v>
+        <v>2518489.15</v>
       </c>
       <c r="I30" s="6" t="n">
-        <v>3088710195</v>
+        <v>3777733725</v>
       </c>
       <c r="J30" s="7" t="n">
-        <v>24631.3</v>
+        <v>33878.15</v>
       </c>
       <c r="K30" s="7" t="n">
-        <v>2034508.8</v>
+        <v>2484611.02</v>
       </c>
       <c r="L30" s="6" t="n">
         <v>212160000</v>
@@ -1870,7 +1870,7 @@
         <v>141440</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>2876550195</v>
+        <v>3565573725</v>
       </c>
     </row>
     <row r="31">
@@ -1891,7 +1891,7 @@
         <v>1768.15</v>
       </c>
       <c r="E31" s="7" t="n">
-        <v>0</v>
+        <v>4086</v>
       </c>
       <c r="F31" s="7" t="n">
         <v>172.48</v>
@@ -1900,16 +1900,16 @@
         <v>530.4400000000001</v>
       </c>
       <c r="H31" s="7" t="n">
-        <v>2471.07</v>
+        <v>6557.07</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>3706605</v>
+        <v>9835605</v>
       </c>
       <c r="J31" s="7" t="n">
-        <v>228.51</v>
+        <v>571.87</v>
       </c>
       <c r="K31" s="7" t="n">
-        <v>2242.57</v>
+        <v>5985.21</v>
       </c>
       <c r="L31" s="6" t="n">
         <v>104000000</v>
@@ -1918,7 +1918,7 @@
         <v>69333.33</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>-100293395</v>
+        <v>-94164395</v>
       </c>
     </row>
     <row r="32">
@@ -1939,7 +1939,7 @@
         <v>4526301.09</v>
       </c>
       <c r="E32" s="7" t="n">
-        <v>1429385.51</v>
+        <v>1473544.91</v>
       </c>
       <c r="F32" s="7" t="n">
         <v>164363.14</v>
@@ -1948,16 +1948,16 @@
         <v>1357890.32</v>
       </c>
       <c r="H32" s="7" t="n">
-        <v>7477940.09</v>
+        <v>7522099.49</v>
       </c>
       <c r="I32" s="6" t="n">
-        <v>11216910135</v>
+        <v>11283149235</v>
       </c>
       <c r="J32" s="7" t="n">
-        <v>251916.89</v>
+        <v>253481.35</v>
       </c>
       <c r="K32" s="7" t="n">
-        <v>7226023.16</v>
+        <v>7268618.1</v>
       </c>
       <c r="L32" s="6" t="n">
         <v>911040000</v>
@@ -1966,7 +1966,7 @@
         <v>607360</v>
       </c>
       <c r="N32" s="6" t="n">
-        <v>10305870135</v>
+        <v>10372109235</v>
       </c>
     </row>
     <row r="33">
@@ -1987,7 +1987,7 @@
         <v>1337179.69</v>
       </c>
       <c r="E33" s="7" t="n">
-        <v>20277.61</v>
+        <v>95157.61</v>
       </c>
       <c r="F33" s="7" t="n">
         <v>27589.82</v>
@@ -1996,16 +1996,16 @@
         <v>401153.89</v>
       </c>
       <c r="H33" s="7" t="n">
-        <v>1786200.98</v>
+        <v>1861080.98</v>
       </c>
       <c r="I33" s="6" t="n">
-        <v>2679301470</v>
+        <v>2791621470</v>
       </c>
       <c r="J33" s="7" t="n">
-        <v>40120.77</v>
+        <v>44928.49</v>
       </c>
       <c r="K33" s="7" t="n">
-        <v>1746080.19</v>
+        <v>1816152.46</v>
       </c>
       <c r="L33" s="6" t="n">
         <v>218400000</v>
@@ -2014,7 +2014,7 @@
         <v>145600</v>
       </c>
       <c r="N33" s="6" t="n">
-        <v>2460901470</v>
+        <v>2573221470</v>
       </c>
     </row>
     <row r="34">
@@ -2083,7 +2083,7 @@
         <v>5167783.04</v>
       </c>
       <c r="E35" s="7" t="n">
-        <v>5978069.28</v>
+        <v>6012947.88</v>
       </c>
       <c r="F35" s="7" t="n">
         <v>179743.67</v>
@@ -2092,16 +2092,16 @@
         <v>1550334.92</v>
       </c>
       <c r="H35" s="7" t="n">
-        <v>12875930.91</v>
+        <v>12910809.51</v>
       </c>
       <c r="I35" s="6" t="n">
-        <v>19313896365</v>
+        <v>19366214265</v>
       </c>
       <c r="J35" s="7" t="n">
-        <v>790704.88</v>
+        <v>793494.8100000001</v>
       </c>
       <c r="K35" s="7" t="n">
-        <v>12085225.89</v>
+        <v>12117314.57</v>
       </c>
       <c r="L35" s="6" t="n">
         <v>938080000</v>
@@ -2110,7 +2110,7 @@
         <v>625386.67</v>
       </c>
       <c r="N35" s="6" t="n">
-        <v>18375816365</v>
+        <v>18428134265</v>
       </c>
     </row>
     <row r="36">
@@ -2227,7 +2227,7 @@
         <v>5990704.91</v>
       </c>
       <c r="E38" s="7" t="n">
-        <v>5192973.19</v>
+        <v>5194013.59</v>
       </c>
       <c r="F38" s="7" t="n">
         <v>194162.12</v>
@@ -2236,16 +2236,16 @@
         <v>1797211.59</v>
       </c>
       <c r="H38" s="7" t="n">
-        <v>13175051.86</v>
+        <v>13176092.26</v>
       </c>
       <c r="I38" s="6" t="n">
-        <v>19762577790</v>
+        <v>19764138390</v>
       </c>
       <c r="J38" s="7" t="n">
-        <v>779294.16</v>
+        <v>779549.12</v>
       </c>
       <c r="K38" s="7" t="n">
-        <v>12395757.48</v>
+        <v>12396542.91</v>
       </c>
       <c r="L38" s="6" t="n">
         <v>950560000</v>
@@ -2254,7 +2254,7 @@
         <v>633706.67</v>
       </c>
       <c r="N38" s="6" t="n">
-        <v>18812017790</v>
+        <v>18813578390</v>
       </c>
     </row>
     <row r="39">
@@ -2275,7 +2275,7 @@
         <v>1526592.02</v>
       </c>
       <c r="E39" s="7" t="n">
-        <v>680022.62</v>
+        <v>684055.88</v>
       </c>
       <c r="F39" s="7" t="n">
         <v>29730.81</v>
@@ -2284,16 +2284,16 @@
         <v>457977.63</v>
       </c>
       <c r="H39" s="7" t="n">
-        <v>2694323.12</v>
+        <v>2698356.38</v>
       </c>
       <c r="I39" s="6" t="n">
-        <v>4041484680</v>
+        <v>4047534570</v>
       </c>
       <c r="J39" s="7" t="n">
-        <v>84765.21000000001</v>
+        <v>85951.84</v>
       </c>
       <c r="K39" s="7" t="n">
-        <v>2609557.86</v>
+        <v>2612404.49</v>
       </c>
       <c r="L39" s="6" t="n">
         <v>222560000</v>
@@ -2302,7 +2302,7 @@
         <v>148373.33</v>
       </c>
       <c r="N39" s="6" t="n">
-        <v>3818924680</v>
+        <v>3824974570</v>
       </c>
     </row>
     <row r="40">
@@ -2323,7 +2323,7 @@
         <v>5977.23</v>
       </c>
       <c r="E40" s="7" t="n">
-        <v>0</v>
+        <v>4248</v>
       </c>
       <c r="F40" s="7" t="n">
         <v>196.3</v>
@@ -2332,16 +2332,16 @@
         <v>1793.2</v>
       </c>
       <c r="H40" s="7" t="n">
-        <v>7966.7</v>
+        <v>12214.7</v>
       </c>
       <c r="I40" s="6" t="n">
-        <v>11950050</v>
+        <v>18322050</v>
       </c>
       <c r="J40" s="7" t="n">
-        <v>2070.02</v>
+        <v>2261.11</v>
       </c>
       <c r="K40" s="7" t="n">
-        <v>5896.74</v>
+        <v>9953.65</v>
       </c>
       <c r="L40" s="6" t="n">
         <v>114400000</v>
@@ -2350,7 +2350,7 @@
         <v>76266.67</v>
       </c>
       <c r="N40" s="6" t="n">
-        <v>-102449950</v>
+        <v>-96077950</v>
       </c>
     </row>
     <row r="41">
@@ -2371,7 +2371,7 @@
         <v>6787044.27</v>
       </c>
       <c r="E41" s="7" t="n">
-        <v>5627349.44</v>
+        <v>5769328.04</v>
       </c>
       <c r="F41" s="7" t="n">
         <v>201947.05</v>
@@ -2380,16 +2380,16 @@
         <v>2036113.31</v>
       </c>
       <c r="H41" s="7" t="n">
-        <v>14652454.13</v>
+        <v>14794432.73</v>
       </c>
       <c r="I41" s="6" t="n">
-        <v>21978681195</v>
+        <v>22191649095</v>
       </c>
       <c r="J41" s="7" t="n">
-        <v>913262.08</v>
+        <v>916703.4399999999</v>
       </c>
       <c r="K41" s="7" t="n">
-        <v>13739191.99</v>
+        <v>13877729.24</v>
       </c>
       <c r="L41" s="6" t="n">
         <v>958880000</v>
@@ -2398,7 +2398,7 @@
         <v>639253.33</v>
       </c>
       <c r="N41" s="6" t="n">
-        <v>21019801195</v>
+        <v>21232769095</v>
       </c>
     </row>
     <row r="42">
@@ -2467,7 +2467,7 @@
         <v>5727.34</v>
       </c>
       <c r="E43" s="7" t="n">
-        <v>0</v>
+        <v>4248</v>
       </c>
       <c r="F43" s="7" t="n">
         <v>200.19</v>
@@ -2476,16 +2476,16 @@
         <v>1718.23</v>
       </c>
       <c r="H43" s="7" t="n">
-        <v>7645.69</v>
+        <v>11893.69</v>
       </c>
       <c r="I43" s="6" t="n">
-        <v>11468535</v>
+        <v>17840535</v>
       </c>
       <c r="J43" s="7" t="n">
-        <v>1953.62</v>
+        <v>2159.57</v>
       </c>
       <c r="K43" s="7" t="n">
-        <v>5692.1</v>
+        <v>9734.15</v>
       </c>
       <c r="L43" s="6" t="n">
         <v>122720000</v>
@@ -2494,7 +2494,7 @@
         <v>81813.33</v>
       </c>
       <c r="N43" s="6" t="n">
-        <v>-111251465</v>
+        <v>-104879465</v>
       </c>
     </row>
     <row r="44">
@@ -2515,7 +2515,7 @@
         <v>7910499.2</v>
       </c>
       <c r="E44" s="7" t="n">
-        <v>7271589.56</v>
+        <v>7409300.36</v>
       </c>
       <c r="F44" s="7" t="n">
         <v>208194.32</v>
@@ -2524,16 +2524,16 @@
         <v>2373149.74</v>
       </c>
       <c r="H44" s="7" t="n">
-        <v>17763432.86</v>
+        <v>17901143.66</v>
       </c>
       <c r="I44" s="6" t="n">
-        <v>26645149290</v>
+        <v>26851715490</v>
       </c>
       <c r="J44" s="7" t="n">
-        <v>1003636.94</v>
+        <v>1016551.9</v>
       </c>
       <c r="K44" s="7" t="n">
-        <v>16759795.95</v>
+        <v>16884591.79</v>
       </c>
       <c r="L44" s="6" t="n">
         <v>981760000</v>
@@ -2542,7 +2542,7 @@
         <v>654506.67</v>
       </c>
       <c r="N44" s="6" t="n">
-        <v>25663389290</v>
+        <v>25869955490</v>
       </c>
     </row>
     <row r="45">
@@ -2611,7 +2611,7 @@
         <v>6173.38</v>
       </c>
       <c r="E46" s="7" t="n">
-        <v>0</v>
+        <v>4230</v>
       </c>
       <c r="F46" s="7" t="n">
         <v>202.26</v>
@@ -2620,16 +2620,16 @@
         <v>1851.98</v>
       </c>
       <c r="H46" s="7" t="n">
-        <v>8227.66</v>
+        <v>12457.66</v>
       </c>
       <c r="I46" s="6" t="n">
-        <v>12341490</v>
+        <v>18686490</v>
       </c>
       <c r="J46" s="7" t="n">
-        <v>1967.58</v>
+        <v>2152.9</v>
       </c>
       <c r="K46" s="7" t="n">
-        <v>6260.13</v>
+        <v>10304.81</v>
       </c>
       <c r="L46" s="6" t="n">
         <v>122720000</v>
@@ -2638,7 +2638,7 @@
         <v>81813.33</v>
       </c>
       <c r="N46" s="6" t="n">
-        <v>-110378510</v>
+        <v>-104033510</v>
       </c>
     </row>
     <row r="47">
@@ -2659,7 +2659,7 @@
         <v>8820132.970000001</v>
       </c>
       <c r="E47" s="7" t="n">
-        <v>7349693.33</v>
+        <v>7380880.13</v>
       </c>
       <c r="F47" s="7" t="n">
         <v>213439.62</v>
@@ -2668,16 +2668,16 @@
         <v>2646039.91</v>
       </c>
       <c r="H47" s="7" t="n">
-        <v>19029305.89</v>
+        <v>19060492.69</v>
       </c>
       <c r="I47" s="6" t="n">
-        <v>28543958835</v>
+        <v>28590739035</v>
       </c>
       <c r="J47" s="7" t="n">
-        <v>1349930.18</v>
+        <v>1355032.39</v>
       </c>
       <c r="K47" s="7" t="n">
-        <v>17679375.73</v>
+        <v>17705460.33</v>
       </c>
       <c r="L47" s="6" t="n">
         <v>994240000</v>
@@ -2686,7 +2686,7 @@
         <v>662826.67</v>
       </c>
       <c r="N47" s="6" t="n">
-        <v>27549718835</v>
+        <v>27596499035</v>
       </c>
     </row>
     <row r="48">
@@ -2707,7 +2707,7 @@
         <v>1806877.16</v>
       </c>
       <c r="E48" s="7" t="n">
-        <v>860761.24</v>
+        <v>926034.1</v>
       </c>
       <c r="F48" s="7" t="n">
         <v>32203.02</v>
@@ -2716,16 +2716,16 @@
         <v>542063.13</v>
       </c>
       <c r="H48" s="7" t="n">
-        <v>3241904.65</v>
+        <v>3307177.51</v>
       </c>
       <c r="I48" s="6" t="n">
-        <v>4862856975</v>
+        <v>4960766265</v>
       </c>
       <c r="J48" s="7" t="n">
-        <v>176091.23</v>
+        <v>179947.32</v>
       </c>
       <c r="K48" s="7" t="n">
-        <v>3065813.27</v>
+        <v>3127230.05</v>
       </c>
       <c r="L48" s="6" t="n">
         <v>230880000</v>
@@ -2734,7 +2734,7 @@
         <v>153920</v>
       </c>
       <c r="N48" s="6" t="n">
-        <v>4631976975</v>
+        <v>4729886265</v>
       </c>
     </row>
     <row r="49">
@@ -2755,7 +2755,7 @@
         <v>5401.29</v>
       </c>
       <c r="E49" s="7" t="n">
-        <v>0</v>
+        <v>4230</v>
       </c>
       <c r="F49" s="7" t="n">
         <v>204.05</v>
@@ -2764,16 +2764,16 @@
         <v>1620.41</v>
       </c>
       <c r="H49" s="7" t="n">
-        <v>7225.7</v>
+        <v>11455.7</v>
       </c>
       <c r="I49" s="6" t="n">
-        <v>10838550</v>
+        <v>17183550</v>
       </c>
       <c r="J49" s="7" t="n">
-        <v>2311.78</v>
+        <v>2564.05</v>
       </c>
       <c r="K49" s="7" t="n">
-        <v>4913.9</v>
+        <v>8891.629999999999</v>
       </c>
       <c r="L49" s="6" t="n">
         <v>120640000</v>
@@ -2782,7 +2782,7 @@
         <v>80426.67</v>
       </c>
       <c r="N49" s="6" t="n">
-        <v>-109801450</v>
+        <v>-103456450</v>
       </c>
     </row>
     <row r="50">
@@ -2803,7 +2803,7 @@
         <v>10242978.78</v>
       </c>
       <c r="E50" s="7" t="n">
-        <v>7126255.69</v>
+        <v>7293928.57</v>
       </c>
       <c r="F50" s="7" t="n">
         <v>218092</v>
@@ -2812,16 +2812,16 @@
         <v>3072893.64</v>
       </c>
       <c r="H50" s="7" t="n">
-        <v>20660220.16</v>
+        <v>20827893.04</v>
       </c>
       <c r="I50" s="6" t="n">
-        <v>30990330240</v>
+        <v>31241839560</v>
       </c>
       <c r="J50" s="7" t="n">
-        <v>1973826.21</v>
+        <v>2004716.06</v>
       </c>
       <c r="K50" s="7" t="n">
-        <v>18686393.98</v>
+        <v>18823177.03</v>
       </c>
       <c r="L50" s="6" t="n">
         <v>1006720000</v>
@@ -2830,7 +2830,7 @@
         <v>671146.67</v>
       </c>
       <c r="N50" s="6" t="n">
-        <v>29983610240</v>
+        <v>30235119560</v>
       </c>
     </row>
     <row r="51">
@@ -2851,7 +2851,7 @@
         <v>2368422.53</v>
       </c>
       <c r="E51" s="7" t="n">
-        <v>783463.89</v>
+        <v>783465.15</v>
       </c>
       <c r="F51" s="7" t="n">
         <v>32825.93</v>
@@ -2860,16 +2860,16 @@
         <v>710526.73</v>
       </c>
       <c r="H51" s="7" t="n">
-        <v>3895239.11</v>
+        <v>3895240.37</v>
       </c>
       <c r="I51" s="6" t="n">
-        <v>5842858665</v>
+        <v>5842860555</v>
       </c>
       <c r="J51" s="7" t="n">
-        <v>225279.49</v>
+        <v>225279.99</v>
       </c>
       <c r="K51" s="7" t="n">
-        <v>3669959.55</v>
+        <v>3669960.3</v>
       </c>
       <c r="L51" s="6" t="n">
         <v>228800000</v>
@@ -2878,7 +2878,7 @@
         <v>152533.33</v>
       </c>
       <c r="N51" s="6" t="n">
-        <v>5614058665</v>
+        <v>5614060555</v>
       </c>
     </row>
     <row r="52">
@@ -2899,7 +2899,7 @@
         <v>7092.08</v>
       </c>
       <c r="E52" s="7" t="n">
-        <v>0</v>
+        <v>4230</v>
       </c>
       <c r="F52" s="7" t="n">
         <v>205.87</v>
@@ -2908,16 +2908,16 @@
         <v>2127.64</v>
       </c>
       <c r="H52" s="7" t="n">
-        <v>9425.549999999999</v>
+        <v>13655.55</v>
       </c>
       <c r="I52" s="6" t="n">
-        <v>14138325</v>
+        <v>20483325</v>
       </c>
       <c r="J52" s="7" t="n">
-        <v>4043.65</v>
+        <v>4379.57</v>
       </c>
       <c r="K52" s="7" t="n">
-        <v>5381.85</v>
+        <v>9275.92</v>
       </c>
       <c r="L52" s="6" t="n">
         <v>126880000</v>
@@ -2926,7 +2926,7 @@
         <v>84586.67</v>
       </c>
       <c r="N52" s="6" t="n">
-        <v>-112741675</v>
+        <v>-106396675</v>
       </c>
     </row>
     <row r="53">
@@ -2947,7 +2947,7 @@
         <v>12253435.18</v>
       </c>
       <c r="E53" s="7" t="n">
-        <v>8462946.359999999</v>
+        <v>8560851.960000001</v>
       </c>
       <c r="F53" s="7" t="n">
         <v>222615.46</v>
@@ -2956,16 +2956,16 @@
         <v>3676030.57</v>
       </c>
       <c r="H53" s="7" t="n">
-        <v>24615027.41</v>
+        <v>24712933.01</v>
       </c>
       <c r="I53" s="6" t="n">
-        <v>36922541115</v>
+        <v>37069399515</v>
       </c>
       <c r="J53" s="7" t="n">
-        <v>2884322.24</v>
+        <v>2917764.97</v>
       </c>
       <c r="K53" s="7" t="n">
-        <v>21730705.21</v>
+        <v>21795168.08</v>
       </c>
       <c r="L53" s="6" t="n">
         <v>1027520000</v>
@@ -2974,7 +2974,7 @@
         <v>685013.33</v>
       </c>
       <c r="N53" s="6" t="n">
-        <v>35895021115</v>
+        <v>36041879515</v>
       </c>
     </row>
     <row r="54">
@@ -2995,7 +2995,7 @@
         <v>2837075.09</v>
       </c>
       <c r="E54" s="7" t="n">
-        <v>1392268</v>
+        <v>1401377.26</v>
       </c>
       <c r="F54" s="7" t="n">
         <v>33473.33</v>
@@ -3004,16 +3004,16 @@
         <v>851122.53</v>
       </c>
       <c r="H54" s="7" t="n">
-        <v>5113938.99</v>
+        <v>5123048.25</v>
       </c>
       <c r="I54" s="6" t="n">
-        <v>7670908485</v>
+        <v>7684572375</v>
       </c>
       <c r="J54" s="7" t="n">
-        <v>277400.88</v>
+        <v>278034.05</v>
       </c>
       <c r="K54" s="7" t="n">
-        <v>4836538.19</v>
+        <v>4845014.27</v>
       </c>
       <c r="L54" s="6" t="n">
         <v>235040000</v>
@@ -3022,7 +3022,7 @@
         <v>156693.33</v>
       </c>
       <c r="N54" s="6" t="n">
-        <v>7435868485</v>
+        <v>7449532375</v>
       </c>
     </row>
     <row r="55">
@@ -3043,7 +3043,7 @@
         <v>8940.93</v>
       </c>
       <c r="E55" s="7" t="n">
-        <v>0</v>
+        <v>4212</v>
       </c>
       <c r="F55" s="7" t="n">
         <v>207.36</v>
@@ -3052,16 +3052,16 @@
         <v>2682.28</v>
       </c>
       <c r="H55" s="7" t="n">
-        <v>11830.55</v>
+        <v>16042.55</v>
       </c>
       <c r="I55" s="6" t="n">
-        <v>17745825</v>
+        <v>24063825</v>
       </c>
       <c r="J55" s="7" t="n">
-        <v>6201.1</v>
+        <v>6584.32</v>
       </c>
       <c r="K55" s="7" t="n">
-        <v>5629.39</v>
+        <v>9458.17</v>
       </c>
       <c r="L55" s="6" t="n">
         <v>131040000</v>
@@ -3070,7 +3070,7 @@
         <v>87360</v>
       </c>
       <c r="N55" s="6" t="n">
-        <v>-113294175</v>
+        <v>-106976175</v>
       </c>
     </row>
     <row r="56">
@@ -3091,7 +3091,7 @@
         <v>11573147.47</v>
       </c>
       <c r="E56" s="7" t="n">
-        <v>6913023.96</v>
+        <v>7266855.36</v>
       </c>
       <c r="F56" s="7" t="n">
         <v>227250.03</v>
@@ -3100,16 +3100,16 @@
         <v>3471944.24</v>
       </c>
       <c r="H56" s="7" t="n">
-        <v>22185365.85</v>
+        <v>22539197.26</v>
       </c>
       <c r="I56" s="6" t="n">
-        <v>33278048775</v>
+        <v>33808795890</v>
       </c>
       <c r="J56" s="7" t="n">
-        <v>3272638.77</v>
+        <v>3412566.07</v>
       </c>
       <c r="K56" s="7" t="n">
-        <v>18912726.85</v>
+        <v>19126630.94</v>
       </c>
       <c r="L56" s="6" t="n">
         <v>1025440000</v>
@@ -3118,7 +3118,7 @@
         <v>683626.67</v>
       </c>
       <c r="N56" s="6" t="n">
-        <v>32252608775</v>
+        <v>32783355890</v>
       </c>
     </row>
     <row r="57">
@@ -3139,7 +3139,7 @@
         <v>2736178.63</v>
       </c>
       <c r="E57" s="7" t="n">
-        <v>1236297.59</v>
+        <v>1274313.59</v>
       </c>
       <c r="F57" s="7" t="n">
         <v>34184.81</v>
@@ -3148,16 +3148,16 @@
         <v>820853.59</v>
       </c>
       <c r="H57" s="7" t="n">
-        <v>4827514.55</v>
+        <v>4865530.55</v>
       </c>
       <c r="I57" s="6" t="n">
-        <v>7241271825</v>
+        <v>7298295825</v>
       </c>
       <c r="J57" s="7" t="n">
-        <v>374743</v>
+        <v>376076.7</v>
       </c>
       <c r="K57" s="7" t="n">
-        <v>4452771.53</v>
+        <v>4489453.82</v>
       </c>
       <c r="L57" s="6" t="n">
         <v>235040000</v>
@@ -3166,7 +3166,7 @@
         <v>156693.33</v>
       </c>
       <c r="N57" s="6" t="n">
-        <v>7006231825</v>
+        <v>7063255825</v>
       </c>
     </row>
     <row r="58">
@@ -3187,7 +3187,7 @@
         <v>11249.43</v>
       </c>
       <c r="E58" s="7" t="n">
-        <v>0</v>
+        <v>4212</v>
       </c>
       <c r="F58" s="7" t="n">
         <v>209.38</v>
@@ -3196,16 +3196,16 @@
         <v>3374.82</v>
       </c>
       <c r="H58" s="7" t="n">
-        <v>14833.61</v>
+        <v>19045.61</v>
       </c>
       <c r="I58" s="6" t="n">
-        <v>22250415</v>
+        <v>28568415</v>
       </c>
       <c r="J58" s="7" t="n">
-        <v>9779.030000000001</v>
+        <v>10308.59</v>
       </c>
       <c r="K58" s="7" t="n">
-        <v>5054.54</v>
+        <v>8736.99</v>
       </c>
       <c r="L58" s="6" t="n">
         <v>131040000</v>
@@ -3214,7 +3214,7 @@
         <v>87360</v>
       </c>
       <c r="N58" s="6" t="n">
-        <v>-108789585</v>
+        <v>-102471585</v>
       </c>
     </row>
     <row r="59">
@@ -3235,7 +3235,7 @@
         <v>12081945.7</v>
       </c>
       <c r="E59" s="7" t="n">
-        <v>6846568.98</v>
+        <v>7236747.06</v>
       </c>
       <c r="F59" s="7" t="n">
         <v>232074.24</v>
@@ -3244,16 +3244,16 @@
         <v>3624583.79</v>
       </c>
       <c r="H59" s="7" t="n">
-        <v>22785172.65</v>
+        <v>23175350.74</v>
       </c>
       <c r="I59" s="6" t="n">
-        <v>34177758975</v>
+        <v>34763026110</v>
       </c>
       <c r="J59" s="7" t="n">
-        <v>4538754.16</v>
+        <v>4692191.48</v>
       </c>
       <c r="K59" s="7" t="n">
-        <v>18246418.63</v>
+        <v>18483159.41</v>
       </c>
       <c r="L59" s="6" t="n">
         <v>1031680000</v>
@@ -3262,7 +3262,7 @@
         <v>687786.67</v>
       </c>
       <c r="N59" s="6" t="n">
-        <v>33146078975</v>
+        <v>33731346110</v>
       </c>
     </row>
     <row r="60">
@@ -3331,7 +3331,7 @@
         <v>18270.18</v>
       </c>
       <c r="E61" s="7" t="n">
-        <v>0</v>
+        <v>4194</v>
       </c>
       <c r="F61" s="7" t="n">
         <v>211.24</v>
@@ -3340,16 +3340,16 @@
         <v>5481.04</v>
       </c>
       <c r="H61" s="7" t="n">
-        <v>23962.5</v>
+        <v>28156.5</v>
       </c>
       <c r="I61" s="6" t="n">
-        <v>35943750</v>
+        <v>42234750</v>
       </c>
       <c r="J61" s="7" t="n">
-        <v>17528.46</v>
+        <v>18260.35</v>
       </c>
       <c r="K61" s="7" t="n">
-        <v>6434.12</v>
+        <v>9896.219999999999</v>
       </c>
       <c r="L61" s="6" t="n">
         <v>131040000</v>
@@ -3358,7 +3358,7 @@
         <v>87360</v>
       </c>
       <c r="N61" s="6" t="n">
-        <v>-95096250</v>
+        <v>-88805250</v>
       </c>
     </row>
     <row r="62">
@@ -3379,7 +3379,7 @@
         <v>11850520.38</v>
       </c>
       <c r="E62" s="7" t="n">
-        <v>6422032.72</v>
+        <v>7631315.2</v>
       </c>
       <c r="F62" s="7" t="n">
         <v>237674.94</v>
@@ -3388,16 +3388,16 @@
         <v>3555156.21</v>
       </c>
       <c r="H62" s="7" t="n">
-        <v>22065384.31</v>
+        <v>23274666.79</v>
       </c>
       <c r="I62" s="6" t="n">
-        <v>33098076465</v>
+        <v>34912000185</v>
       </c>
       <c r="J62" s="7" t="n">
-        <v>4438229.81</v>
+        <v>4774270.2</v>
       </c>
       <c r="K62" s="7" t="n">
-        <v>17627154.55</v>
+        <v>18500396.57</v>
       </c>
       <c r="L62" s="6" t="n">
         <v>1044160000</v>
@@ -3406,7 +3406,7 @@
         <v>696106.67</v>
       </c>
       <c r="N62" s="6" t="n">
-        <v>32053916465</v>
+        <v>33867840185</v>
       </c>
     </row>
     <row r="63">
@@ -3427,7 +3427,7 @@
         <v>2913889.95</v>
       </c>
       <c r="E63" s="7" t="n">
-        <v>1123427.06</v>
+        <v>1244797.46</v>
       </c>
       <c r="F63" s="7" t="n">
         <v>35864.78</v>
@@ -3436,16 +3436,16 @@
         <v>874166.98</v>
       </c>
       <c r="H63" s="7" t="n">
-        <v>4947348.75</v>
+        <v>5068719.15</v>
       </c>
       <c r="I63" s="6" t="n">
-        <v>7421023125</v>
+        <v>7603078725</v>
       </c>
       <c r="J63" s="7" t="n">
-        <v>572479.5600000001</v>
+        <v>589364</v>
       </c>
       <c r="K63" s="7" t="n">
-        <v>4374869.19</v>
+        <v>4479355.17</v>
       </c>
       <c r="L63" s="6" t="n">
         <v>235040000</v>
@@ -3454,7 +3454,7 @@
         <v>156693.33</v>
       </c>
       <c r="N63" s="6" t="n">
-        <v>7185983125</v>
+        <v>7368038725</v>
       </c>
     </row>
     <row r="64">
@@ -3475,7 +3475,7 @@
         <v>18350.59</v>
       </c>
       <c r="E64" s="7" t="n">
-        <v>0</v>
+        <v>4194</v>
       </c>
       <c r="F64" s="7" t="n">
         <v>213.12</v>
@@ -3484,16 +3484,16 @@
         <v>5505.19</v>
       </c>
       <c r="H64" s="7" t="n">
-        <v>24068.9</v>
+        <v>28262.9</v>
       </c>
       <c r="I64" s="6" t="n">
-        <v>36103350</v>
+        <v>42394350</v>
       </c>
       <c r="J64" s="7" t="n">
-        <v>16490.85</v>
+        <v>17218.12</v>
       </c>
       <c r="K64" s="7" t="n">
-        <v>7578.02</v>
+        <v>11044.75</v>
       </c>
       <c r="L64" s="6" t="n">
         <v>143520000</v>
@@ -3502,7 +3502,7 @@
         <v>95680</v>
       </c>
       <c r="N64" s="6" t="n">
-        <v>-107416650</v>
+        <v>-101125650</v>
       </c>
     </row>
     <row r="65">
@@ -3523,7 +3523,7 @@
         <v>13194146.48</v>
       </c>
       <c r="E65" s="7" t="n">
-        <v>7961972.99</v>
+        <v>8291318.81</v>
       </c>
       <c r="F65" s="7" t="n">
         <v>243618.46</v>
@@ -3532,16 +3532,16 @@
         <v>3958244</v>
       </c>
       <c r="H65" s="7" t="n">
-        <v>25357981.71</v>
+        <v>25687327.53</v>
       </c>
       <c r="I65" s="6" t="n">
-        <v>38036972565</v>
+        <v>38530991295</v>
       </c>
       <c r="J65" s="7" t="n">
-        <v>6288791.48</v>
+        <v>6432925.12</v>
       </c>
       <c r="K65" s="7" t="n">
-        <v>19069190.33</v>
+        <v>19254402.53</v>
       </c>
       <c r="L65" s="6" t="n">
         <v>1058720000</v>
@@ -3550,7 +3550,7 @@
         <v>705813.33</v>
       </c>
       <c r="N65" s="6" t="n">
-        <v>36978252565</v>
+        <v>37472271295</v>
       </c>
     </row>
     <row r="66">
@@ -3571,7 +3571,7 @@
         <v>3040159.31</v>
       </c>
       <c r="E66" s="7" t="n">
-        <v>1273277.79</v>
+        <v>1278214.65</v>
       </c>
       <c r="F66" s="7" t="n">
         <v>36607.29</v>
@@ -3580,16 +3580,16 @@
         <v>912047.78</v>
       </c>
       <c r="H66" s="7" t="n">
-        <v>5262092.25</v>
+        <v>5267029.11</v>
       </c>
       <c r="I66" s="6" t="n">
-        <v>7893138375</v>
+        <v>7900543665</v>
       </c>
       <c r="J66" s="7" t="n">
-        <v>831350.87</v>
+        <v>832518.2</v>
       </c>
       <c r="K66" s="7" t="n">
-        <v>4430741.39</v>
+        <v>4434510.92</v>
       </c>
       <c r="L66" s="6" t="n">
         <v>237120000</v>
@@ -3598,7 +3598,7 @@
         <v>158080</v>
       </c>
       <c r="N66" s="6" t="n">
-        <v>7656018375</v>
+        <v>7663423665</v>
       </c>
     </row>
     <row r="67">
@@ -3619,7 +3619,7 @@
         <v>25170.04</v>
       </c>
       <c r="E67" s="7" t="n">
-        <v>0</v>
+        <v>4194</v>
       </c>
       <c r="F67" s="7" t="n">
         <v>214.47</v>
@@ -3628,16 +3628,16 @@
         <v>7551.02</v>
       </c>
       <c r="H67" s="7" t="n">
-        <v>32935.56</v>
+        <v>37129.56</v>
       </c>
       <c r="I67" s="6" t="n">
-        <v>49403340</v>
+        <v>55694340</v>
       </c>
       <c r="J67" s="7" t="n">
-        <v>19819.56</v>
+        <v>20712.55</v>
       </c>
       <c r="K67" s="7" t="n">
-        <v>13116.01</v>
+        <v>16417.02</v>
       </c>
       <c r="L67" s="6" t="n">
         <v>143520000</v>
@@ -3646,7 +3646,7 @@
         <v>95680</v>
       </c>
       <c r="N67" s="6" t="n">
-        <v>-94116660</v>
+        <v>-87825660</v>
       </c>
     </row>
     <row r="68">
@@ -3667,7 +3667,7 @@
         <v>13260604.91</v>
       </c>
       <c r="E68" s="7" t="n">
-        <v>9819674.48</v>
+        <v>10717223.78</v>
       </c>
       <c r="F68" s="7" t="n">
         <v>249498.18</v>
@@ -3676,16 +3676,16 @@
         <v>3978181.47</v>
       </c>
       <c r="H68" s="7" t="n">
-        <v>27307959.27</v>
+        <v>28205508.57</v>
       </c>
       <c r="I68" s="6" t="n">
-        <v>40961938905</v>
+        <v>42308262855</v>
       </c>
       <c r="J68" s="7" t="n">
-        <v>7659234.58</v>
+        <v>7964790.86</v>
       </c>
       <c r="K68" s="7" t="n">
-        <v>19648724.61</v>
+        <v>20240717.64</v>
       </c>
       <c r="L68" s="6" t="n">
         <v>1062880000</v>
@@ -3694,7 +3694,7 @@
         <v>708586.67</v>
       </c>
       <c r="N68" s="6" t="n">
-        <v>39899058905</v>
+        <v>41245382855</v>
       </c>
     </row>
     <row r="69">
@@ -3715,7 +3715,7 @@
         <v>4203926.92</v>
       </c>
       <c r="E69" s="7" t="n">
-        <v>997645.17</v>
+        <v>1585771.77</v>
       </c>
       <c r="F69" s="7" t="n">
         <v>37322.83</v>
@@ -3724,16 +3724,16 @@
         <v>1261178.07</v>
       </c>
       <c r="H69" s="7" t="n">
-        <v>6500073.06</v>
+        <v>7088199.66</v>
       </c>
       <c r="I69" s="6" t="n">
-        <v>9750109590</v>
+        <v>10632299490</v>
       </c>
       <c r="J69" s="7" t="n">
-        <v>786195.45</v>
+        <v>916223.87</v>
       </c>
       <c r="K69" s="7" t="n">
-        <v>5713877.64</v>
+        <v>6171975.79</v>
       </c>
       <c r="L69" s="6" t="n">
         <v>237120000</v>
@@ -3742,7 +3742,7 @@
         <v>158080</v>
       </c>
       <c r="N69" s="6" t="n">
-        <v>9512989590</v>
+        <v>10395179490</v>
       </c>
     </row>
     <row r="70">
@@ -3763,7 +3763,7 @@
         <v>26528.96</v>
       </c>
       <c r="E70" s="7" t="n">
-        <v>497.29</v>
+        <v>4720.09</v>
       </c>
       <c r="F70" s="7" t="n">
         <v>216.14</v>
@@ -3772,16 +3772,16 @@
         <v>7958.67</v>
       </c>
       <c r="H70" s="7" t="n">
-        <v>35201.02</v>
+        <v>39423.82</v>
       </c>
       <c r="I70" s="6" t="n">
-        <v>52801530</v>
+        <v>59135730</v>
       </c>
       <c r="J70" s="7" t="n">
-        <v>19801.56</v>
+        <v>20720.87</v>
       </c>
       <c r="K70" s="7" t="n">
-        <v>15399.49</v>
+        <v>18702.97</v>
       </c>
       <c r="L70" s="6" t="n">
         <v>147680000</v>
@@ -3790,7 +3790,7 @@
         <v>98453.33</v>
       </c>
       <c r="N70" s="6" t="n">
-        <v>-94878470</v>
+        <v>-88544270</v>
       </c>
     </row>
     <row r="71">
@@ -3805,13 +3805,13 @@
         </is>
       </c>
       <c r="C71" s="6" t="n">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="D71" s="7" t="n">
         <v>14151253.03</v>
       </c>
       <c r="E71" s="7" t="n">
-        <v>9879497.98</v>
+        <v>10375971.28</v>
       </c>
       <c r="F71" s="7" t="n">
         <v>252130.39</v>
@@ -3820,25 +3820,25 @@
         <v>4245375.88</v>
       </c>
       <c r="H71" s="7" t="n">
-        <v>28528257.5</v>
+        <v>29024730.8</v>
       </c>
       <c r="I71" s="6" t="n">
-        <v>42792386250</v>
+        <v>43537096200</v>
       </c>
       <c r="J71" s="7" t="n">
-        <v>9250919.93</v>
+        <v>9455708.109999999</v>
       </c>
       <c r="K71" s="7" t="n">
-        <v>19277337.61</v>
+        <v>19569022.74</v>
       </c>
       <c r="L71" s="6" t="n">
-        <v>1064960000</v>
+        <v>1067040000</v>
       </c>
       <c r="M71" s="7" t="n">
-        <v>709973.33</v>
+        <v>711360</v>
       </c>
       <c r="N71" s="6" t="n">
-        <v>41727426250</v>
+        <v>42470056200</v>
       </c>
     </row>
     <row r="72">
@@ -3859,7 +3859,7 @@
         <v>4113507.56</v>
       </c>
       <c r="E72" s="7" t="n">
-        <v>1369854.2</v>
+        <v>1381734.02</v>
       </c>
       <c r="F72" s="7" t="n">
         <v>38061.11</v>
@@ -3868,16 +3868,16 @@
         <v>1234052.25</v>
       </c>
       <c r="H72" s="7" t="n">
-        <v>6755475.15</v>
+        <v>6767354.96</v>
       </c>
       <c r="I72" s="6" t="n">
-        <v>10133212725</v>
+        <v>10151032440</v>
       </c>
       <c r="J72" s="7" t="n">
-        <v>1151899.24</v>
+        <v>1156457.29</v>
       </c>
       <c r="K72" s="7" t="n">
-        <v>5603575.95</v>
+        <v>5610897.73</v>
       </c>
       <c r="L72" s="6" t="n">
         <v>243360000</v>
@@ -3886,7 +3886,7 @@
         <v>162240</v>
       </c>
       <c r="N72" s="6" t="n">
-        <v>9889852725</v>
+        <v>9907672440</v>
       </c>
     </row>
     <row r="73">
@@ -3907,7 +3907,7 @@
         <v>34885.37</v>
       </c>
       <c r="E73" s="7" t="n">
-        <v>678.75</v>
+        <v>4879.59</v>
       </c>
       <c r="F73" s="7" t="n">
         <v>217.47</v>
@@ -3916,16 +3916,16 @@
         <v>10465.58</v>
       </c>
       <c r="H73" s="7" t="n">
-        <v>46247.17</v>
+        <v>50448.01</v>
       </c>
       <c r="I73" s="6" t="n">
-        <v>69370755</v>
+        <v>75672015</v>
       </c>
       <c r="J73" s="7" t="n">
-        <v>26934.09</v>
+        <v>28144.33</v>
       </c>
       <c r="K73" s="7" t="n">
-        <v>19313.13</v>
+        <v>22303.73</v>
       </c>
       <c r="L73" s="6" t="n">
         <v>149760000</v>
@@ -3934,7 +3934,7 @@
         <v>99840</v>
       </c>
       <c r="N73" s="6" t="n">
-        <v>-80389245</v>
+        <v>-74087985</v>
       </c>
     </row>
     <row r="74">
@@ -3955,7 +3955,7 @@
         <v>13118835.33</v>
       </c>
       <c r="E74" s="7" t="n">
-        <v>9225754.85</v>
+        <v>9413014.25</v>
       </c>
       <c r="F74" s="7" t="n">
         <v>260117.63</v>
@@ -3964,16 +3964,16 @@
         <v>3935650.6</v>
       </c>
       <c r="H74" s="7" t="n">
-        <v>26540358.29</v>
+        <v>26727617.69</v>
       </c>
       <c r="I74" s="6" t="n">
-        <v>39810537435</v>
+        <v>40091426535</v>
       </c>
       <c r="J74" s="7" t="n">
-        <v>9946436.460000001</v>
+        <v>10016790.61</v>
       </c>
       <c r="K74" s="7" t="n">
-        <v>16593921.92</v>
+        <v>16710827.2</v>
       </c>
       <c r="L74" s="6" t="n">
         <v>1071200000</v>
@@ -3982,7 +3982,7 @@
         <v>714133.33</v>
       </c>
       <c r="N74" s="6" t="n">
-        <v>38739337435</v>
+        <v>39020226535</v>
       </c>
     </row>
     <row r="75">
@@ -4003,7 +4003,7 @@
         <v>3909212.81</v>
       </c>
       <c r="E75" s="7" t="n">
-        <v>1465414.96</v>
+        <v>1507711.54</v>
       </c>
       <c r="F75" s="7" t="n">
         <v>38903.52</v>
@@ -4012,16 +4012,16 @@
         <v>1172763.82</v>
       </c>
       <c r="H75" s="7" t="n">
-        <v>6586295.16</v>
+        <v>6628591.74</v>
       </c>
       <c r="I75" s="6" t="n">
-        <v>9879442740</v>
+        <v>9942887610</v>
       </c>
       <c r="J75" s="7" t="n">
-        <v>1242019.22</v>
+        <v>1245902.37</v>
       </c>
       <c r="K75" s="7" t="n">
-        <v>5344275.9</v>
+        <v>5382689.34</v>
       </c>
       <c r="L75" s="6" t="n">
         <v>245440000</v>
@@ -4030,7 +4030,7 @@
         <v>163626.67</v>
       </c>
       <c r="N75" s="6" t="n">
-        <v>9634002740</v>
+        <v>9697447610</v>
       </c>
     </row>
     <row r="76">
@@ -4051,7 +4051,7 @@
         <v>27331.39</v>
       </c>
       <c r="E76" s="7" t="n">
-        <v>1069.66</v>
+        <v>5245.66</v>
       </c>
       <c r="F76" s="7" t="n">
         <v>218.73</v>
@@ -4060,16 +4060,16 @@
         <v>8199.379999999999</v>
       </c>
       <c r="H76" s="7" t="n">
-        <v>36819.11</v>
+        <v>40995.11</v>
       </c>
       <c r="I76" s="6" t="n">
-        <v>55228665</v>
+        <v>61492665</v>
       </c>
       <c r="J76" s="7" t="n">
-        <v>24805.57</v>
+        <v>26148.27</v>
       </c>
       <c r="K76" s="7" t="n">
-        <v>12013.57</v>
+        <v>14846.87</v>
       </c>
       <c r="L76" s="6" t="n">
         <v>153920000</v>
@@ -4078,7 +4078,7 @@
         <v>102613.33</v>
       </c>
       <c r="N76" s="6" t="n">
-        <v>-98691335</v>
+        <v>-92427335</v>
       </c>
     </row>
     <row r="77">
@@ -4099,7 +4099,7 @@
         <v>15182768.98</v>
       </c>
       <c r="E77" s="7" t="n">
-        <v>10682560.48</v>
+        <v>10814981.08</v>
       </c>
       <c r="F77" s="7" t="n">
         <v>256445.55</v>
@@ -4108,16 +4108,16 @@
         <v>4554830.77</v>
       </c>
       <c r="H77" s="7" t="n">
-        <v>30676605.57</v>
+        <v>30809026.17</v>
       </c>
       <c r="I77" s="6" t="n">
-        <v>46014908355</v>
+        <v>46213539255</v>
       </c>
       <c r="J77" s="7" t="n">
-        <v>11720416.83</v>
+        <v>11812007.17</v>
       </c>
       <c r="K77" s="7" t="n">
-        <v>18956188.63</v>
+        <v>18997018.88</v>
       </c>
       <c r="L77" s="6" t="n">
         <v>1081600000</v>
@@ -4126,7 +4126,7 @@
         <v>721066.67</v>
       </c>
       <c r="N77" s="6" t="n">
-        <v>44933308355</v>
+        <v>45131939255</v>
       </c>
     </row>
     <row r="78">
@@ -4147,7 +4147,7 @@
         <v>4299541.82</v>
       </c>
       <c r="E78" s="7" t="n">
-        <v>1652270.35</v>
+        <v>1672610.71</v>
       </c>
       <c r="F78" s="7" t="n">
         <v>39844.21</v>
@@ -4156,16 +4156,16 @@
         <v>1289862.59</v>
       </c>
       <c r="H78" s="7" t="n">
-        <v>7281518.89</v>
+        <v>7301859.25</v>
       </c>
       <c r="I78" s="6" t="n">
-        <v>10922278335</v>
+        <v>10952788875</v>
       </c>
       <c r="J78" s="7" t="n">
-        <v>1593825.8</v>
+        <v>1600983.14</v>
       </c>
       <c r="K78" s="7" t="n">
-        <v>5687693.08</v>
+        <v>5700876.11</v>
       </c>
       <c r="L78" s="6" t="n">
         <v>247520000</v>
@@ -4174,7 +4174,7 @@
         <v>165013.33</v>
       </c>
       <c r="N78" s="6" t="n">
-        <v>10674758335</v>
+        <v>10705268875</v>
       </c>
     </row>
     <row r="79">
@@ -4243,7 +4243,7 @@
         <v>15309950.01</v>
       </c>
       <c r="E80" s="7" t="n">
-        <v>10330350.69</v>
+        <v>11079605.01</v>
       </c>
       <c r="F80" s="7" t="n">
         <v>261005.57</v>
@@ -4252,16 +4252,16 @@
         <v>4592984.88</v>
       </c>
       <c r="H80" s="7" t="n">
-        <v>30494291.03</v>
+        <v>31243545.35</v>
       </c>
       <c r="I80" s="6" t="n">
-        <v>45741436545</v>
+        <v>46865318025</v>
       </c>
       <c r="J80" s="7" t="n">
-        <v>11718050.58</v>
+        <v>12101706.85</v>
       </c>
       <c r="K80" s="7" t="n">
-        <v>18776240.4</v>
+        <v>19141838.48</v>
       </c>
       <c r="L80" s="6" t="n">
         <v>1085760000</v>
@@ -4270,7 +4270,7 @@
         <v>723840</v>
       </c>
       <c r="N80" s="6" t="n">
-        <v>44655676545</v>
+        <v>45779558025</v>
       </c>
     </row>
     <row r="81">
@@ -4291,7 +4291,7 @@
         <v>4218312.56</v>
       </c>
       <c r="E81" s="7" t="n">
-        <v>1438585.99</v>
+        <v>1456067.77</v>
       </c>
       <c r="F81" s="7" t="n">
         <v>41013.07</v>
@@ -4300,16 +4300,16 @@
         <v>1265493.79</v>
       </c>
       <c r="H81" s="7" t="n">
-        <v>6963405.45</v>
+        <v>6980887.23</v>
       </c>
       <c r="I81" s="6" t="n">
-        <v>10445108175</v>
+        <v>10471330845</v>
       </c>
       <c r="J81" s="7" t="n">
-        <v>1423241.25</v>
+        <v>1432474.88</v>
       </c>
       <c r="K81" s="7" t="n">
-        <v>5540164.18</v>
+        <v>5548412.36</v>
       </c>
       <c r="L81" s="6" t="n">
         <v>249600000</v>
@@ -4318,7 +4318,7 @@
         <v>166400</v>
       </c>
       <c r="N81" s="6" t="n">
-        <v>10195508175</v>
+        <v>10221730845</v>
       </c>
     </row>
     <row r="82">
@@ -4339,7 +4339,7 @@
         <v>48506.32</v>
       </c>
       <c r="E82" s="7" t="n">
-        <v>2173.01</v>
+        <v>2273.09</v>
       </c>
       <c r="F82" s="7" t="n">
         <v>222.54</v>
@@ -4348,16 +4348,16 @@
         <v>14551.91</v>
       </c>
       <c r="H82" s="7" t="n">
-        <v>65453.81</v>
+        <v>65553.89</v>
       </c>
       <c r="I82" s="6" t="n">
-        <v>98180715</v>
+        <v>98330835</v>
       </c>
       <c r="J82" s="7" t="n">
-        <v>38689.62</v>
+        <v>38709.21</v>
       </c>
       <c r="K82" s="7" t="n">
-        <v>26764.28</v>
+        <v>26844.79</v>
       </c>
       <c r="L82" s="6" t="n">
         <v>162240000</v>
@@ -4366,7 +4366,7 @@
         <v>108160</v>
       </c>
       <c r="N82" s="6" t="n">
-        <v>-64059285</v>
+        <v>-63909165</v>
       </c>
     </row>
     <row r="83">
@@ -4387,7 +4387,7 @@
         <v>16355772.25</v>
       </c>
       <c r="E83" s="7" t="n">
-        <v>10739101.07</v>
+        <v>10828323.47</v>
       </c>
       <c r="F83" s="7" t="n">
         <v>231584.72</v>
@@ -4396,16 +4396,16 @@
         <v>4906731.66</v>
       </c>
       <c r="H83" s="7" t="n">
-        <v>32233189.71</v>
+        <v>32322412.13</v>
       </c>
       <c r="I83" s="6" t="n">
-        <v>48349784565</v>
+        <v>48483618195</v>
       </c>
       <c r="J83" s="7" t="n">
-        <v>13644764.66</v>
+        <v>13708469.17</v>
       </c>
       <c r="K83" s="7" t="n">
-        <v>18588425.21</v>
+        <v>18613943.09</v>
       </c>
       <c r="L83" s="6" t="n">
         <v>1087840000</v>
@@ -4414,7 +4414,7 @@
         <v>725226.67</v>
       </c>
       <c r="N83" s="6" t="n">
-        <v>47261944565</v>
+        <v>47395778195</v>
       </c>
     </row>
     <row r="84">
@@ -4435,7 +4435,7 @@
         <v>4528391.73</v>
       </c>
       <c r="E84" s="7" t="n">
-        <v>1341609.6</v>
+        <v>1374573</v>
       </c>
       <c r="F84" s="7" t="n">
         <v>42071.49</v>
@@ -4444,16 +4444,16 @@
         <v>1358517.5</v>
       </c>
       <c r="H84" s="7" t="n">
-        <v>7270590.39</v>
+        <v>7303553.79</v>
       </c>
       <c r="I84" s="6" t="n">
-        <v>10905885585</v>
+        <v>10955330685</v>
       </c>
       <c r="J84" s="7" t="n">
-        <v>1849054.27</v>
+        <v>1859108.97</v>
       </c>
       <c r="K84" s="7" t="n">
-        <v>5421536.07</v>
+        <v>5444444.76</v>
       </c>
       <c r="L84" s="6" t="n">
         <v>249600000</v>
@@ -4462,7 +4462,7 @@
         <v>166400</v>
       </c>
       <c r="N84" s="6" t="n">
-        <v>10656285585</v>
+        <v>10705730685</v>
       </c>
     </row>
     <row r="85">
@@ -4483,7 +4483,7 @@
         <v>159336.18</v>
       </c>
       <c r="E85" s="7" t="n">
-        <v>9464.059999999999</v>
+        <v>10864.46</v>
       </c>
       <c r="F85" s="7" t="n">
         <v>224.99</v>
@@ -4492,16 +4492,16 @@
         <v>47800.89</v>
       </c>
       <c r="H85" s="7" t="n">
-        <v>216826.06</v>
+        <v>218226.46</v>
       </c>
       <c r="I85" s="6" t="n">
-        <v>325239090</v>
+        <v>327339690</v>
       </c>
       <c r="J85" s="7" t="n">
-        <v>106504.77</v>
+        <v>107552.08</v>
       </c>
       <c r="K85" s="7" t="n">
-        <v>110321.22</v>
+        <v>110674.31</v>
       </c>
       <c r="L85" s="6" t="n">
         <v>164320000</v>
@@ -4510,7 +4510,7 @@
         <v>109546.67</v>
       </c>
       <c r="N85" s="6" t="n">
-        <v>160919090</v>
+        <v>163019690</v>
       </c>
     </row>
     <row r="86">
@@ -4531,7 +4531,7 @@
         <v>17584131.8</v>
       </c>
       <c r="E86" s="7" t="n">
-        <v>9150137.300000001</v>
+        <v>9892007.66</v>
       </c>
       <c r="F86" s="7" t="n">
         <v>234917.91</v>
@@ -4540,16 +4540,16 @@
         <v>5275239.43</v>
       </c>
       <c r="H86" s="7" t="n">
-        <v>32244426.55</v>
+        <v>32986296.91</v>
       </c>
       <c r="I86" s="6" t="n">
-        <v>48366639825</v>
+        <v>49479445365</v>
       </c>
       <c r="J86" s="7" t="n">
-        <v>13243081.93</v>
+        <v>13605442.1</v>
       </c>
       <c r="K86" s="7" t="n">
-        <v>19001344.56</v>
+        <v>19380854.73</v>
       </c>
       <c r="L86" s="6" t="n">
         <v>1089920000</v>
@@ -4558,7 +4558,7 @@
         <v>726613.33</v>
       </c>
       <c r="N86" s="6" t="n">
-        <v>47276719825</v>
+        <v>48389525365</v>
       </c>
     </row>
     <row r="87">
@@ -4579,7 +4579,7 @@
         <v>4996053.88</v>
       </c>
       <c r="E87" s="7" t="n">
-        <v>1319342.43</v>
+        <v>1355487.69</v>
       </c>
       <c r="F87" s="7" t="n">
         <v>42956.71</v>
@@ -4588,16 +4588,16 @@
         <v>1498816.15</v>
       </c>
       <c r="H87" s="7" t="n">
-        <v>7857169.14</v>
+        <v>7893314.4</v>
       </c>
       <c r="I87" s="6" t="n">
-        <v>11785753710</v>
+        <v>11839971600</v>
       </c>
       <c r="J87" s="7" t="n">
-        <v>2063675.3</v>
+        <v>2078246.77</v>
       </c>
       <c r="K87" s="7" t="n">
-        <v>5793493.89</v>
+        <v>5815067.68</v>
       </c>
       <c r="L87" s="6" t="n">
         <v>251680000</v>
@@ -4606,7 +4606,7 @@
         <v>167786.67</v>
       </c>
       <c r="N87" s="6" t="n">
-        <v>11534073710</v>
+        <v>11588291600</v>
       </c>
     </row>
     <row r="88">
@@ -4627,7 +4627,7 @@
         <v>155305.4</v>
       </c>
       <c r="E88" s="7" t="n">
-        <v>2763.91</v>
+        <v>2767.87</v>
       </c>
       <c r="F88" s="7" t="n">
         <v>228.8</v>
@@ -4636,16 +4636,16 @@
         <v>46591.62</v>
       </c>
       <c r="H88" s="7" t="n">
-        <v>204889.73</v>
+        <v>204893.69</v>
       </c>
       <c r="I88" s="6" t="n">
-        <v>307334595</v>
+        <v>307340535</v>
       </c>
       <c r="J88" s="7" t="n">
-        <v>96081.52</v>
+        <v>96083.57000000001</v>
       </c>
       <c r="K88" s="7" t="n">
-        <v>108808.24</v>
+        <v>108810.15</v>
       </c>
       <c r="L88" s="6" t="n">
         <v>166400000</v>
@@ -4654,7 +4654,7 @@
         <v>110933.33</v>
       </c>
       <c r="N88" s="6" t="n">
-        <v>140934595</v>
+        <v>140940535</v>
       </c>
     </row>
     <row r="89">
@@ -4675,7 +4675,7 @@
         <v>20096219.7</v>
       </c>
       <c r="E89" s="7" t="n">
-        <v>10329267.26</v>
+        <v>10423694.54</v>
       </c>
       <c r="F89" s="7" t="n">
         <v>278845.02</v>
@@ -4684,16 +4684,16 @@
         <v>6028865.88</v>
       </c>
       <c r="H89" s="7" t="n">
-        <v>36733197.75</v>
+        <v>36827625.03</v>
       </c>
       <c r="I89" s="6" t="n">
-        <v>55099796625</v>
+        <v>55241437545</v>
       </c>
       <c r="J89" s="7" t="n">
-        <v>14895540.74</v>
+        <v>14967718.59</v>
       </c>
       <c r="K89" s="7" t="n">
-        <v>21837657.02</v>
+        <v>21859906.46</v>
       </c>
       <c r="L89" s="6" t="n">
         <v>1089920000</v>
@@ -4702,7 +4702,7 @@
         <v>726613.33</v>
       </c>
       <c r="N89" s="6" t="n">
-        <v>54009876625</v>
+        <v>54151517545</v>
       </c>
     </row>
     <row r="90">
@@ -4723,7 +4723,7 @@
         <v>5422294.97</v>
       </c>
       <c r="E90" s="7" t="n">
-        <v>1322345.57</v>
+        <v>1363401.41</v>
       </c>
       <c r="F90" s="7" t="n">
         <v>43801.23</v>
@@ -4732,16 +4732,16 @@
         <v>1626688.46</v>
       </c>
       <c r="H90" s="7" t="n">
-        <v>8415130.199999999</v>
+        <v>8456186.039999999</v>
       </c>
       <c r="I90" s="6" t="n">
-        <v>12622695300</v>
+        <v>12684279060</v>
       </c>
       <c r="J90" s="7" t="n">
-        <v>2054774.96</v>
+        <v>2070905.94</v>
       </c>
       <c r="K90" s="7" t="n">
-        <v>6360355.24</v>
+        <v>6385280.1</v>
       </c>
       <c r="L90" s="6" t="n">
         <v>251680000</v>
@@ -4750,7 +4750,7 @@
         <v>167786.67</v>
       </c>
       <c r="N90" s="6" t="n">
-        <v>12371015300</v>
+        <v>12432599060</v>
       </c>
     </row>
     <row r="91">
@@ -4771,7 +4771,7 @@
         <v>140860.71</v>
       </c>
       <c r="E91" s="7" t="n">
-        <v>42250.19</v>
+        <v>42254.51</v>
       </c>
       <c r="F91" s="7" t="n">
         <v>237.96</v>
@@ -4780,16 +4780,16 @@
         <v>42258.21</v>
       </c>
       <c r="H91" s="7" t="n">
-        <v>225607.07</v>
+        <v>225611.39</v>
       </c>
       <c r="I91" s="6" t="n">
-        <v>338410605</v>
+        <v>338417085</v>
       </c>
       <c r="J91" s="7" t="n">
-        <v>90903.00999999999</v>
+        <v>90905.56</v>
       </c>
       <c r="K91" s="7" t="n">
-        <v>134704.06</v>
+        <v>134705.83</v>
       </c>
       <c r="L91" s="6" t="n">
         <v>170560000</v>
@@ -4798,7 +4798,7 @@
         <v>113706.67</v>
       </c>
       <c r="N91" s="6" t="n">
-        <v>167850605</v>
+        <v>167857085</v>
       </c>
     </row>
     <row r="92">
@@ -4819,7 +4819,7 @@
         <v>20967697.37</v>
       </c>
       <c r="E92" s="7" t="n">
-        <v>4712947.23</v>
+        <v>5575295.55</v>
       </c>
       <c r="F92" s="7" t="n">
         <v>280694.12</v>
@@ -4828,16 +4828,16 @@
         <v>6290309.18</v>
       </c>
       <c r="H92" s="7" t="n">
-        <v>32251647.9</v>
+        <v>33113996.21</v>
       </c>
       <c r="I92" s="6" t="n">
-        <v>48377471850</v>
+        <v>49670994315</v>
       </c>
       <c r="J92" s="7" t="n">
-        <v>13102334.5</v>
+        <v>13447287.91</v>
       </c>
       <c r="K92" s="7" t="n">
-        <v>19149313.23</v>
+        <v>19666708.15</v>
       </c>
       <c r="L92" s="6" t="n">
         <v>1089920000</v>
@@ -4846,7 +4846,7 @@
         <v>726613.33</v>
       </c>
       <c r="N92" s="6" t="n">
-        <v>47287551850</v>
+        <v>48581074315</v>
       </c>
     </row>
     <row r="93">
@@ -4867,7 +4867,7 @@
         <v>5393736.03</v>
       </c>
       <c r="E93" s="7" t="n">
-        <v>439969.21</v>
+        <v>725499.25</v>
       </c>
       <c r="F93" s="7" t="n">
         <v>44130.18</v>
@@ -4876,16 +4876,16 @@
         <v>1618120.81</v>
       </c>
       <c r="H93" s="7" t="n">
-        <v>7495956.23</v>
+        <v>7781486.27</v>
       </c>
       <c r="I93" s="6" t="n">
-        <v>11243934345</v>
+        <v>11672229405</v>
       </c>
       <c r="J93" s="7" t="n">
-        <v>1274508.93</v>
+        <v>1328476.22</v>
       </c>
       <c r="K93" s="7" t="n">
-        <v>6221447.31</v>
+        <v>6453010.11</v>
       </c>
       <c r="L93" s="6" t="n">
         <v>251680000</v>
@@ -4894,7 +4894,7 @@
         <v>167786.67</v>
       </c>
       <c r="N93" s="6" t="n">
-        <v>10992254345</v>
+        <v>11420549405</v>
       </c>
     </row>
     <row r="94">

--- a/NBS FINAL delivery/03_Excel_Deliveries/9_NBS_Accounts_Domestic_and_GNI.xlsx
+++ b/NBS FINAL delivery/03_Excel_Deliveries/9_NBS_Accounts_Domestic_and_GNI.xlsx
@@ -512,7 +512,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28T13:31:58.420547+00:00</t>
+          <t>2026-08-28T18:49:53.220713+00:00</t>
         </is>
       </c>
     </row>
@@ -643,7 +643,7 @@
         <v>0</v>
       </c>
       <c r="E2" s="7" t="n">
-        <v>1104600.78</v>
+        <v>996128.98</v>
       </c>
       <c r="F2" s="7" t="n">
         <v>39968.25</v>
@@ -652,10 +652,10 @@
         <v>0</v>
       </c>
       <c r="H2" s="7" t="n">
-        <v>1144569.03</v>
+        <v>1036097.22</v>
       </c>
       <c r="I2" s="6" t="n">
-        <v>1716853545</v>
+        <v>1554145830</v>
       </c>
       <c r="L2" s="6" t="n">
         <v>465920000</v>
@@ -664,7 +664,7 @@
         <v>310613.33</v>
       </c>
       <c r="N2" s="6" t="n">
-        <v>1250933545</v>
+        <v>1088225830</v>
       </c>
     </row>
     <row r="3">
@@ -685,7 +685,7 @@
         <v>0</v>
       </c>
       <c r="E3" s="7" t="n">
-        <v>166386.42</v>
+        <v>150047.27</v>
       </c>
       <c r="F3" s="7" t="n">
         <v>18481.94</v>
@@ -694,10 +694,10 @@
         <v>0</v>
       </c>
       <c r="H3" s="7" t="n">
-        <v>184868.36</v>
+        <v>168529.23</v>
       </c>
       <c r="I3" s="6" t="n">
-        <v>277302540</v>
+        <v>252793845</v>
       </c>
       <c r="L3" s="6" t="n">
         <v>81120000</v>
@@ -706,7 +706,7 @@
         <v>54080</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>196182540</v>
+        <v>171673845</v>
       </c>
     </row>
     <row r="4">
@@ -727,7 +727,7 @@
         <v>0</v>
       </c>
       <c r="E4" s="7" t="n">
-        <v>3015.54</v>
+        <v>2719.41</v>
       </c>
       <c r="F4" s="7" t="n">
         <v>31.93</v>
@@ -736,10 +736,10 @@
         <v>0</v>
       </c>
       <c r="H4" s="7" t="n">
-        <v>3047.47</v>
+        <v>2751.34</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>4571205</v>
+        <v>4127010</v>
       </c>
       <c r="L4" s="6" t="n">
         <v>33280000</v>
@@ -748,7 +748,7 @@
         <v>22186.67</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>-28708795</v>
+        <v>-29152990</v>
       </c>
     </row>
     <row r="5">
@@ -769,7 +769,7 @@
         <v>1158908.69</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>1229039.28</v>
+        <v>1087027.9</v>
       </c>
       <c r="F5" s="7" t="n">
         <v>42745.73</v>
@@ -778,10 +778,10 @@
         <v>347672.68</v>
       </c>
       <c r="H5" s="7" t="n">
-        <v>2778366.26</v>
+        <v>2636354.87</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>4167549390</v>
+        <v>3954532305</v>
       </c>
       <c r="L5" s="6" t="n">
         <v>659360000</v>
@@ -790,7 +790,7 @@
         <v>439573.33</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>3508189390</v>
+        <v>3295172305</v>
       </c>
     </row>
     <row r="6">
@@ -811,7 +811,7 @@
         <v>448918.99</v>
       </c>
       <c r="E6" s="7" t="n">
-        <v>281265.84</v>
+        <v>248766.49</v>
       </c>
       <c r="F6" s="7" t="n">
         <v>18974.45</v>
@@ -820,10 +820,10 @@
         <v>134675.71</v>
       </c>
       <c r="H6" s="7" t="n">
-        <v>883834.92</v>
+        <v>851335.59</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>1325752380</v>
+        <v>1277003385</v>
       </c>
       <c r="L6" s="6" t="n">
         <v>147680000</v>
@@ -832,7 +832,7 @@
         <v>98453.33</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>1178072380</v>
+        <v>1129323385</v>
       </c>
     </row>
     <row r="7">
@@ -853,7 +853,7 @@
         <v>1829.85</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>3130.74</v>
+        <v>2768.99</v>
       </c>
       <c r="F7" s="7" t="n">
         <v>32.55</v>
@@ -862,10 +862,10 @@
         <v>548.96</v>
       </c>
       <c r="H7" s="7" t="n">
-        <v>5542.09</v>
+        <v>5180.35</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>8313135</v>
+        <v>7770525</v>
       </c>
       <c r="L7" s="6" t="n">
         <v>70720000</v>
@@ -874,7 +874,7 @@
         <v>47146.67</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>-62406865</v>
+        <v>-62949475</v>
       </c>
     </row>
     <row r="8">
@@ -895,7 +895,7 @@
         <v>1648929.32</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>1352730.6</v>
+        <v>1172961.73</v>
       </c>
       <c r="F8" s="7" t="n">
         <v>55865.5</v>
@@ -904,10 +904,10 @@
         <v>494678.84</v>
       </c>
       <c r="H8" s="7" t="n">
-        <v>3552204.33</v>
+        <v>3372435.46</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>5328306495</v>
+        <v>5058653190</v>
       </c>
       <c r="L8" s="6" t="n">
         <v>723840000</v>
@@ -916,7 +916,7 @@
         <v>482560</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>4604466495</v>
+        <v>4334813190</v>
       </c>
     </row>
     <row r="9">
@@ -937,7 +937,7 @@
         <v>476500.37</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>293377.68</v>
+        <v>254389.76</v>
       </c>
       <c r="F9" s="7" t="n">
         <v>19688.62</v>
@@ -946,10 +946,10 @@
         <v>142950.09</v>
       </c>
       <c r="H9" s="7" t="n">
-        <v>932516.74</v>
+        <v>893528.8</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>1398775110</v>
+        <v>1340293200</v>
       </c>
       <c r="L9" s="6" t="n">
         <v>174720000</v>
@@ -958,7 +958,7 @@
         <v>116480</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>1224055110</v>
+        <v>1165573200</v>
       </c>
     </row>
     <row r="10">
@@ -979,7 +979,7 @@
         <v>1292.33</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>3258</v>
+        <v>2825.03</v>
       </c>
       <c r="F10" s="7" t="n">
         <v>59.64</v>
@@ -988,10 +988,10 @@
         <v>387.68</v>
       </c>
       <c r="H10" s="7" t="n">
-        <v>4997.69</v>
+        <v>4564.73</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>7496535</v>
+        <v>6847095</v>
       </c>
       <c r="L10" s="6" t="n">
         <v>81120000</v>
@@ -1000,7 +1000,7 @@
         <v>54080</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>-73623465</v>
+        <v>-74272905</v>
       </c>
     </row>
     <row r="11">
@@ -1021,7 +1021,7 @@
         <v>1979440.3</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>1895427.36</v>
+        <v>1610658.32</v>
       </c>
       <c r="F11" s="7" t="n">
         <v>66819.48</v>
@@ -1030,10 +1030,10 @@
         <v>593831.9300000001</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>4535519.28</v>
+        <v>4250750.22</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>6803278920</v>
+        <v>6376125330</v>
       </c>
       <c r="L11" s="6" t="n">
         <v>736320000</v>
@@ -1042,7 +1042,7 @@
         <v>490880</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>6066958920</v>
+        <v>5639805330</v>
       </c>
     </row>
     <row r="12">
@@ -1063,7 +1063,7 @@
         <v>532221.88</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>306765.18</v>
+        <v>260676.75</v>
       </c>
       <c r="F12" s="7" t="n">
         <v>20756.08</v>
@@ -1072,10 +1072,10 @@
         <v>159666.63</v>
       </c>
       <c r="H12" s="7" t="n">
-        <v>1019409.68</v>
+        <v>973321.28</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>1529114520</v>
+        <v>1459981920</v>
       </c>
       <c r="L12" s="6" t="n">
         <v>176800000</v>
@@ -1084,7 +1084,7 @@
         <v>117866.67</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>1352314520</v>
+        <v>1283181920</v>
       </c>
     </row>
     <row r="13">
@@ -1105,7 +1105,7 @@
         <v>1391.37</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>3420</v>
+        <v>2906.18</v>
       </c>
       <c r="F13" s="7" t="n">
         <v>75.93000000000001</v>
@@ -1114,10 +1114,10 @@
         <v>417.45</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>5304.71</v>
+        <v>4790.89</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>7957065</v>
+        <v>7186335</v>
       </c>
       <c r="L13" s="6" t="n">
         <v>85280000</v>
@@ -1126,7 +1126,7 @@
         <v>56853.33</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>-77322935</v>
+        <v>-78093665</v>
       </c>
     </row>
     <row r="14">
@@ -1147,7 +1147,7 @@
         <v>1927024.69</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>2070249.48</v>
+        <v>1723303.26</v>
       </c>
       <c r="F14" s="7" t="n">
         <v>77246.02</v>
@@ -1156,10 +1156,10 @@
         <v>578107.4399999999</v>
       </c>
       <c r="H14" s="7" t="n">
-        <v>4652627.5</v>
+        <v>4305681.34</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>6978941250</v>
+        <v>6458522010</v>
       </c>
       <c r="L14" s="6" t="n">
         <v>750880000</v>
@@ -1168,7 +1168,7 @@
         <v>500586.67</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>6228061250</v>
+        <v>5707642010</v>
       </c>
     </row>
     <row r="15">
@@ -1189,7 +1189,7 @@
         <v>630712.8199999999</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>318280.5</v>
+        <v>264940.94</v>
       </c>
       <c r="F15" s="7" t="n">
         <v>21736.2</v>
@@ -1198,10 +1198,10 @@
         <v>189213.84</v>
       </c>
       <c r="H15" s="7" t="n">
-        <v>1159943.36</v>
+        <v>1106603.78</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>1739915040</v>
+        <v>1659905670</v>
       </c>
       <c r="L15" s="6" t="n">
         <v>178880000</v>
@@ -1210,7 +1210,7 @@
         <v>119253.33</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>1561035040</v>
+        <v>1481025670</v>
       </c>
     </row>
     <row r="16">
@@ -1231,7 +1231,7 @@
         <v>1225.57</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>3546</v>
+        <v>2951.74</v>
       </c>
       <c r="F16" s="7" t="n">
         <v>99.13</v>
@@ -1240,10 +1240,10 @@
         <v>367.67</v>
       </c>
       <c r="H16" s="7" t="n">
-        <v>5238.39</v>
+        <v>4644.12</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>7857585</v>
+        <v>6966180</v>
       </c>
       <c r="L16" s="6" t="n">
         <v>87360000</v>
@@ -1252,7 +1252,7 @@
         <v>58240</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>-79502415</v>
+        <v>-80393820</v>
       </c>
     </row>
     <row r="17">
@@ -1273,7 +1273,7 @@
         <v>2265971.02</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>2314536.66</v>
+        <v>1886501.7</v>
       </c>
       <c r="F17" s="7" t="n">
         <v>89097.19</v>
@@ -1282,10 +1282,10 @@
         <v>679791.3</v>
       </c>
       <c r="H17" s="7" t="n">
-        <v>5349396.1</v>
+        <v>4921361.17</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>8024094150</v>
+        <v>7382041755</v>
       </c>
       <c r="L17" s="6" t="n">
         <v>802880000</v>
@@ -1294,7 +1294,7 @@
         <v>535253.33</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>7221214150</v>
+        <v>6579161755</v>
       </c>
     </row>
     <row r="18">
@@ -1315,7 +1315,7 @@
         <v>707531.3199999999</v>
       </c>
       <c r="E18" s="7" t="n">
-        <v>333415.08</v>
+        <v>271755.52</v>
       </c>
       <c r="F18" s="7" t="n">
         <v>22720.03</v>
@@ -1324,10 +1324,10 @@
         <v>212259.44</v>
       </c>
       <c r="H18" s="7" t="n">
-        <v>1275925.92</v>
+        <v>1214266.36</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>1913888880</v>
+        <v>1821399540</v>
       </c>
       <c r="L18" s="6" t="n">
         <v>193440000</v>
@@ -1336,7 +1336,7 @@
         <v>128960</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>1720448880</v>
+        <v>1627959540</v>
       </c>
     </row>
     <row r="19">
@@ -1357,7 +1357,7 @@
         <v>1596.1</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>3672</v>
+        <v>2992.92</v>
       </c>
       <c r="F19" s="7" t="n">
         <v>123.07</v>
@@ -1366,10 +1366,10 @@
         <v>478.78</v>
       </c>
       <c r="H19" s="7" t="n">
-        <v>5869.98</v>
+        <v>5190.91</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>8804970</v>
+        <v>7786365</v>
       </c>
       <c r="L19" s="6" t="n">
         <v>91520000</v>
@@ -1378,7 +1378,7 @@
         <v>61013.33</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>-82715030</v>
+        <v>-83733635</v>
       </c>
     </row>
     <row r="20">
@@ -1399,7 +1399,7 @@
         <v>2581135.11</v>
       </c>
       <c r="E20" s="7" t="n">
-        <v>2926911.96</v>
+        <v>2334856.21</v>
       </c>
       <c r="F20" s="7" t="n">
         <v>104788.44</v>
@@ -1408,10 +1408,10 @@
         <v>774340.54</v>
       </c>
       <c r="H20" s="7" t="n">
-        <v>6387176.18</v>
+        <v>5795120.34</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>9580764270</v>
+        <v>8692680510</v>
       </c>
       <c r="L20" s="6" t="n">
         <v>848640000</v>
@@ -1420,7 +1420,7 @@
         <v>565760</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>8732124270</v>
+        <v>7844040510</v>
       </c>
     </row>
     <row r="21">
@@ -1441,7 +1441,7 @@
         <v>728865.5699999999</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>355220.82</v>
+        <v>283366.77</v>
       </c>
       <c r="F21" s="7" t="n">
         <v>23878.73</v>
@@ -1450,10 +1450,10 @@
         <v>218659.68</v>
       </c>
       <c r="H21" s="7" t="n">
-        <v>1326624.88</v>
+        <v>1254770.84</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>1989937320</v>
+        <v>1882156260</v>
       </c>
       <c r="L21" s="6" t="n">
         <v>197600000</v>
@@ -1462,7 +1462,7 @@
         <v>131733.33</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>1792337320</v>
+        <v>1684556260</v>
       </c>
     </row>
     <row r="22">
@@ -1483,7 +1483,7 @@
         <v>1283.81</v>
       </c>
       <c r="E22" s="7" t="n">
-        <v>3798</v>
+        <v>3029.74</v>
       </c>
       <c r="F22" s="7" t="n">
         <v>140.97</v>
@@ -1492,10 +1492,10 @@
         <v>385.17</v>
       </c>
       <c r="H22" s="7" t="n">
-        <v>5607.95</v>
+        <v>4839.69</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>8411925</v>
+        <v>7259535</v>
       </c>
       <c r="L22" s="6" t="n">
         <v>97760000</v>
@@ -1504,7 +1504,7 @@
         <v>65173.33</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>-89348075</v>
+        <v>-90500465</v>
       </c>
     </row>
     <row r="23">
@@ -1525,7 +1525,7 @@
         <v>2279842.09</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>3429953.46</v>
+        <v>2676644.25</v>
       </c>
       <c r="F23" s="7" t="n">
         <v>120783.98</v>
@@ -1534,10 +1534,10 @@
         <v>683952.67</v>
       </c>
       <c r="H23" s="7" t="n">
-        <v>6514532.31</v>
+        <v>5761223.06</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>9771798465</v>
+        <v>8641834590</v>
       </c>
       <c r="L23" s="6" t="n">
         <v>873600000</v>
@@ -1546,7 +1546,7 @@
         <v>582400</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>8898198465</v>
+        <v>7768234590</v>
       </c>
     </row>
     <row r="24">
@@ -1567,7 +1567,7 @@
         <v>1017953.85</v>
       </c>
       <c r="E24" s="7" t="n">
-        <v>431344.62</v>
+        <v>336609.85</v>
       </c>
       <c r="F24" s="7" t="n">
         <v>24846.67</v>
@@ -1576,10 +1576,10 @@
         <v>305386.13</v>
       </c>
       <c r="H24" s="7" t="n">
-        <v>1779531.21</v>
+        <v>1684796.48</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>2669296815</v>
+        <v>2527194720</v>
       </c>
       <c r="L24" s="6" t="n">
         <v>203840000</v>
@@ -1588,7 +1588,7 @@
         <v>135893.33</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>2465456815</v>
+        <v>2323354720</v>
       </c>
     </row>
     <row r="25">
@@ -1609,7 +1609,7 @@
         <v>1385.46</v>
       </c>
       <c r="E25" s="7" t="n">
-        <v>3906</v>
+        <v>3048.14</v>
       </c>
       <c r="F25" s="7" t="n">
         <v>151.16</v>
@@ -1618,10 +1618,10 @@
         <v>415.66</v>
       </c>
       <c r="H25" s="7" t="n">
-        <v>5858.23</v>
+        <v>5000.37</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>8787345</v>
+        <v>7500555</v>
       </c>
       <c r="L25" s="6" t="n">
         <v>97760000</v>
@@ -1630,7 +1630,7 @@
         <v>65173.33</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>-88972655</v>
+        <v>-90259445</v>
       </c>
     </row>
     <row r="26">
@@ -1651,7 +1651,7 @@
         <v>2698296.15</v>
       </c>
       <c r="E26" s="7" t="n">
-        <v>4114455.48</v>
+        <v>3139439.22</v>
       </c>
       <c r="F26" s="7" t="n">
         <v>135947.53</v>
@@ -1660,16 +1660,16 @@
         <v>809489.02</v>
       </c>
       <c r="H26" s="7" t="n">
-        <v>7758187.91</v>
+        <v>6783171.76</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>11637281865</v>
+        <v>10174757640</v>
       </c>
       <c r="J26" s="7" t="n">
-        <v>328607.72</v>
+        <v>283506.52</v>
       </c>
       <c r="K26" s="7" t="n">
-        <v>7429580.39</v>
+        <v>6499665.28</v>
       </c>
       <c r="L26" s="6" t="n">
         <v>886080000</v>
@@ -1678,7 +1678,7 @@
         <v>590720</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>10751201865</v>
+        <v>9288677640</v>
       </c>
     </row>
     <row r="27">
@@ -1699,7 +1699,7 @@
         <v>958995.3199999999</v>
       </c>
       <c r="E27" s="7" t="n">
-        <v>446386.32</v>
+        <v>340604.64</v>
       </c>
       <c r="F27" s="7" t="n">
         <v>25717.39</v>
@@ -1708,16 +1708,16 @@
         <v>287698.63</v>
       </c>
       <c r="H27" s="7" t="n">
-        <v>1718797.68</v>
+        <v>1613016.02</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>2578196520</v>
+        <v>2419524030</v>
       </c>
       <c r="J27" s="7" t="n">
-        <v>45581.34</v>
+        <v>42680.65</v>
       </c>
       <c r="K27" s="7" t="n">
-        <v>1673216.31</v>
+        <v>1570335.38</v>
       </c>
       <c r="L27" s="6" t="n">
         <v>210080000</v>
@@ -1726,7 +1726,7 @@
         <v>140053.33</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>2368116520</v>
+        <v>2209444030</v>
       </c>
     </row>
     <row r="28">
@@ -1747,7 +1747,7 @@
         <v>1884.11</v>
       </c>
       <c r="E28" s="7" t="n">
-        <v>3996</v>
+        <v>3049.05</v>
       </c>
       <c r="F28" s="7" t="n">
         <v>162.62</v>
@@ -1756,16 +1756,16 @@
         <v>565.21</v>
       </c>
       <c r="H28" s="7" t="n">
-        <v>6607.98</v>
+        <v>5661.04</v>
       </c>
       <c r="I28" s="6" t="n">
-        <v>9911970</v>
+        <v>8491560</v>
       </c>
       <c r="J28" s="7" t="n">
-        <v>487.66</v>
+        <v>420.29</v>
       </c>
       <c r="K28" s="7" t="n">
-        <v>6120.3</v>
+        <v>5240.73</v>
       </c>
       <c r="L28" s="6" t="n">
         <v>99840000</v>
@@ -1774,7 +1774,7 @@
         <v>66560</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>-89928030</v>
+        <v>-91348440</v>
       </c>
     </row>
     <row r="29">
@@ -1795,7 +1795,7 @@
         <v>2896002.93</v>
       </c>
       <c r="E29" s="7" t="n">
-        <v>4794182.28</v>
+        <v>3574925.78</v>
       </c>
       <c r="F29" s="7" t="n">
         <v>150010.07</v>
@@ -1804,16 +1804,16 @@
         <v>868800.98</v>
       </c>
       <c r="H29" s="7" t="n">
-        <v>8708996.279999999</v>
+        <v>7489739.84</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>13063494420</v>
+        <v>11234609760</v>
       </c>
       <c r="J29" s="7" t="n">
-        <v>354035.69</v>
+        <v>301869.36</v>
       </c>
       <c r="K29" s="7" t="n">
-        <v>8354960.59</v>
+        <v>7187870.59</v>
       </c>
       <c r="L29" s="6" t="n">
         <v>904800000</v>
@@ -1822,7 +1822,7 @@
         <v>603200</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>12158694420</v>
+        <v>10329809760</v>
       </c>
     </row>
     <row r="30">
@@ -1843,7 +1843,7 @@
         <v>1563473.58</v>
       </c>
       <c r="E30" s="7" t="n">
-        <v>459349.02</v>
+        <v>342527.37</v>
       </c>
       <c r="F30" s="7" t="n">
         <v>26624.46</v>
@@ -1852,16 +1852,16 @@
         <v>469042.06</v>
       </c>
       <c r="H30" s="7" t="n">
-        <v>2518489.15</v>
+        <v>2401667.52</v>
       </c>
       <c r="I30" s="6" t="n">
-        <v>3777733725</v>
+        <v>3602501280</v>
       </c>
       <c r="J30" s="7" t="n">
-        <v>33878.15</v>
+        <v>31526.46</v>
       </c>
       <c r="K30" s="7" t="n">
-        <v>2484611.02</v>
+        <v>2370141.02</v>
       </c>
       <c r="L30" s="6" t="n">
         <v>212160000</v>
@@ -1870,7 +1870,7 @@
         <v>141440</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>3565573725</v>
+        <v>3390341280</v>
       </c>
     </row>
     <row r="31">
@@ -1891,7 +1891,7 @@
         <v>1768.15</v>
       </c>
       <c r="E31" s="7" t="n">
-        <v>4086</v>
+        <v>3046.85</v>
       </c>
       <c r="F31" s="7" t="n">
         <v>172.48</v>
@@ -1900,16 +1900,16 @@
         <v>530.4400000000001</v>
       </c>
       <c r="H31" s="7" t="n">
-        <v>6557.07</v>
+        <v>5517.91</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>9835605</v>
+        <v>8276865</v>
       </c>
       <c r="J31" s="7" t="n">
-        <v>571.87</v>
+        <v>484.55</v>
       </c>
       <c r="K31" s="7" t="n">
-        <v>5985.21</v>
+        <v>5033.38</v>
       </c>
       <c r="L31" s="6" t="n">
         <v>104000000</v>
@@ -1918,7 +1918,7 @@
         <v>69333.33</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>-94164395</v>
+        <v>-95723135</v>
       </c>
     </row>
     <row r="32">
@@ -1939,7 +1939,7 @@
         <v>4526301.09</v>
       </c>
       <c r="E32" s="7" t="n">
-        <v>1473544.91</v>
+        <v>3922000.16</v>
       </c>
       <c r="F32" s="7" t="n">
         <v>164363.14</v>
@@ -1948,16 +1948,16 @@
         <v>1357890.32</v>
       </c>
       <c r="H32" s="7" t="n">
-        <v>7522099.49</v>
+        <v>9970554.699999999</v>
       </c>
       <c r="I32" s="6" t="n">
-        <v>11283149235</v>
+        <v>14955832050</v>
       </c>
       <c r="J32" s="7" t="n">
-        <v>253481.35</v>
+        <v>432005.99</v>
       </c>
       <c r="K32" s="7" t="n">
-        <v>7268618.1</v>
+        <v>9538548.76</v>
       </c>
       <c r="L32" s="6" t="n">
         <v>911040000</v>
@@ -1966,7 +1966,7 @@
         <v>607360</v>
       </c>
       <c r="N32" s="6" t="n">
-        <v>10372109235</v>
+        <v>14044792050</v>
       </c>
     </row>
     <row r="33">
@@ -1987,7 +1987,7 @@
         <v>1337179.69</v>
       </c>
       <c r="E33" s="7" t="n">
-        <v>95157.61</v>
+        <v>347325.59</v>
       </c>
       <c r="F33" s="7" t="n">
         <v>27589.82</v>
@@ -1996,16 +1996,16 @@
         <v>401153.89</v>
       </c>
       <c r="H33" s="7" t="n">
-        <v>1861080.98</v>
+        <v>2113248.95</v>
       </c>
       <c r="I33" s="6" t="n">
-        <v>2791621470</v>
+        <v>3169873425</v>
       </c>
       <c r="J33" s="7" t="n">
-        <v>44928.49</v>
+        <v>48727.13</v>
       </c>
       <c r="K33" s="7" t="n">
-        <v>1816152.46</v>
+        <v>2064521.83</v>
       </c>
       <c r="L33" s="6" t="n">
         <v>218400000</v>
@@ -2014,7 +2014,7 @@
         <v>145600</v>
       </c>
       <c r="N33" s="6" t="n">
-        <v>2573221470</v>
+        <v>2951473425</v>
       </c>
     </row>
     <row r="34">
@@ -2035,7 +2035,7 @@
         <v>2230.37</v>
       </c>
       <c r="E34" s="7" t="n">
-        <v>37.07</v>
+        <v>3054.63</v>
       </c>
       <c r="F34" s="7" t="n">
         <v>182.61</v>
@@ -2044,16 +2044,16 @@
         <v>669.12</v>
       </c>
       <c r="H34" s="7" t="n">
-        <v>3119.22</v>
+        <v>6136.78</v>
       </c>
       <c r="I34" s="6" t="n">
-        <v>4678830</v>
+        <v>9205170</v>
       </c>
       <c r="J34" s="7" t="n">
-        <v>539.22</v>
+        <v>2048</v>
       </c>
       <c r="K34" s="7" t="n">
-        <v>2580</v>
+        <v>4088.78</v>
       </c>
       <c r="L34" s="6" t="n">
         <v>108160000</v>
@@ -2062,7 +2062,7 @@
         <v>72106.67</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>-103481170</v>
+        <v>-98954830</v>
       </c>
     </row>
     <row r="35">
@@ -2083,7 +2083,7 @@
         <v>5167783.04</v>
       </c>
       <c r="E35" s="7" t="n">
-        <v>6012947.88</v>
+        <v>6025842.92</v>
       </c>
       <c r="F35" s="7" t="n">
         <v>179743.67</v>
@@ -2092,16 +2092,16 @@
         <v>1550334.92</v>
       </c>
       <c r="H35" s="7" t="n">
-        <v>12910809.51</v>
+        <v>12923704.55</v>
       </c>
       <c r="I35" s="6" t="n">
-        <v>19366214265</v>
+        <v>19385556825</v>
       </c>
       <c r="J35" s="7" t="n">
-        <v>793494.8100000001</v>
+        <v>795675.61</v>
       </c>
       <c r="K35" s="7" t="n">
-        <v>12117314.57</v>
+        <v>12128028.8</v>
       </c>
       <c r="L35" s="6" t="n">
         <v>938080000</v>
@@ -2110,7 +2110,7 @@
         <v>625386.67</v>
       </c>
       <c r="N35" s="6" t="n">
-        <v>18428134265</v>
+        <v>18447476825</v>
       </c>
     </row>
     <row r="36">
@@ -2131,7 +2131,7 @@
         <v>1649056.45</v>
       </c>
       <c r="E36" s="7" t="n">
-        <v>513146.37</v>
+        <v>516517.11</v>
       </c>
       <c r="F36" s="7" t="n">
         <v>28516.67</v>
@@ -2140,16 +2140,16 @@
         <v>494716.91</v>
       </c>
       <c r="H36" s="7" t="n">
-        <v>2685436.39</v>
+        <v>2688807.14</v>
       </c>
       <c r="I36" s="6" t="n">
-        <v>4028154585</v>
+        <v>4033210710</v>
       </c>
       <c r="J36" s="7" t="n">
-        <v>60781.31</v>
+        <v>61076.62</v>
       </c>
       <c r="K36" s="7" t="n">
-        <v>2624655.09</v>
+        <v>2627730.51</v>
       </c>
       <c r="L36" s="6" t="n">
         <v>218400000</v>
@@ -2158,7 +2158,7 @@
         <v>145600</v>
       </c>
       <c r="N36" s="6" t="n">
-        <v>3809754585</v>
+        <v>3814810710</v>
       </c>
     </row>
     <row r="37">
@@ -2227,7 +2227,7 @@
         <v>5990704.91</v>
       </c>
       <c r="E38" s="7" t="n">
-        <v>5194013.59</v>
+        <v>5205248.74</v>
       </c>
       <c r="F38" s="7" t="n">
         <v>194162.12</v>
@@ -2236,16 +2236,16 @@
         <v>1797211.59</v>
       </c>
       <c r="H38" s="7" t="n">
-        <v>13176092.26</v>
+        <v>13187327.41</v>
       </c>
       <c r="I38" s="6" t="n">
-        <v>19764138390</v>
+        <v>19780991115</v>
       </c>
       <c r="J38" s="7" t="n">
-        <v>779549.12</v>
+        <v>783885.59</v>
       </c>
       <c r="K38" s="7" t="n">
-        <v>12396542.91</v>
+        <v>12403441.6</v>
       </c>
       <c r="L38" s="6" t="n">
         <v>950560000</v>
@@ -2254,7 +2254,7 @@
         <v>633706.67</v>
       </c>
       <c r="N38" s="6" t="n">
-        <v>18813578390</v>
+        <v>18830431115</v>
       </c>
     </row>
     <row r="39">
@@ -2275,7 +2275,7 @@
         <v>1526592.02</v>
       </c>
       <c r="E39" s="7" t="n">
-        <v>684055.88</v>
+        <v>682820.25</v>
       </c>
       <c r="F39" s="7" t="n">
         <v>29730.81</v>
@@ -2284,16 +2284,16 @@
         <v>457977.63</v>
       </c>
       <c r="H39" s="7" t="n">
-        <v>2698356.38</v>
+        <v>2697120.75</v>
       </c>
       <c r="I39" s="6" t="n">
-        <v>4047534570</v>
+        <v>4045681125</v>
       </c>
       <c r="J39" s="7" t="n">
-        <v>85951.84</v>
+        <v>85588.31</v>
       </c>
       <c r="K39" s="7" t="n">
-        <v>2612404.49</v>
+        <v>2611532.4</v>
       </c>
       <c r="L39" s="6" t="n">
         <v>222560000</v>
@@ -2302,7 +2302,7 @@
         <v>148373.33</v>
       </c>
       <c r="N39" s="6" t="n">
-        <v>3824974570</v>
+        <v>3823121125</v>
       </c>
     </row>
     <row r="40">
@@ -2323,7 +2323,7 @@
         <v>5977.23</v>
       </c>
       <c r="E40" s="7" t="n">
-        <v>4248</v>
+        <v>2946.58</v>
       </c>
       <c r="F40" s="7" t="n">
         <v>196.3</v>
@@ -2332,16 +2332,16 @@
         <v>1793.2</v>
       </c>
       <c r="H40" s="7" t="n">
-        <v>12214.7</v>
+        <v>10913.28</v>
       </c>
       <c r="I40" s="6" t="n">
-        <v>18322050</v>
+        <v>16369920</v>
       </c>
       <c r="J40" s="7" t="n">
-        <v>2261.11</v>
+        <v>2202.57</v>
       </c>
       <c r="K40" s="7" t="n">
-        <v>9953.65</v>
+        <v>8710.77</v>
       </c>
       <c r="L40" s="6" t="n">
         <v>114400000</v>
@@ -2350,7 +2350,7 @@
         <v>76266.67</v>
       </c>
       <c r="N40" s="6" t="n">
-        <v>-96077950</v>
+        <v>-98030080</v>
       </c>
     </row>
     <row r="41">
@@ -2371,7 +2371,7 @@
         <v>6787044.27</v>
       </c>
       <c r="E41" s="7" t="n">
-        <v>5769328.04</v>
+        <v>5745823.71</v>
       </c>
       <c r="F41" s="7" t="n">
         <v>201947.05</v>
@@ -2380,16 +2380,16 @@
         <v>2036113.31</v>
       </c>
       <c r="H41" s="7" t="n">
-        <v>14794432.73</v>
+        <v>14770928.4</v>
       </c>
       <c r="I41" s="6" t="n">
-        <v>22191649095</v>
+        <v>22156392600</v>
       </c>
       <c r="J41" s="7" t="n">
-        <v>916703.4399999999</v>
+        <v>922799.16</v>
       </c>
       <c r="K41" s="7" t="n">
-        <v>13877729.24</v>
+        <v>13848129.18</v>
       </c>
       <c r="L41" s="6" t="n">
         <v>958880000</v>
@@ -2398,7 +2398,7 @@
         <v>639253.33</v>
       </c>
       <c r="N41" s="6" t="n">
-        <v>21232769095</v>
+        <v>21197512600</v>
       </c>
     </row>
     <row r="42">
@@ -2419,7 +2419,7 @@
         <v>1510912.47</v>
       </c>
       <c r="E42" s="7" t="n">
-        <v>692094.36</v>
+        <v>692126.26</v>
       </c>
       <c r="F42" s="7" t="n">
         <v>30670.68</v>
@@ -2428,16 +2428,16 @@
         <v>453273.77</v>
       </c>
       <c r="H42" s="7" t="n">
-        <v>2686951.29</v>
+        <v>2686983.19</v>
       </c>
       <c r="I42" s="6" t="n">
-        <v>4030426935</v>
+        <v>4030474785</v>
       </c>
       <c r="J42" s="7" t="n">
-        <v>122556.15</v>
+        <v>122563.74</v>
       </c>
       <c r="K42" s="7" t="n">
-        <v>2564395.19</v>
+        <v>2564419.51</v>
       </c>
       <c r="L42" s="6" t="n">
         <v>222560000</v>
@@ -2446,7 +2446,7 @@
         <v>148373.33</v>
       </c>
       <c r="N42" s="6" t="n">
-        <v>3807866935</v>
+        <v>3807914785</v>
       </c>
     </row>
     <row r="43">
@@ -2467,7 +2467,7 @@
         <v>5727.34</v>
       </c>
       <c r="E43" s="7" t="n">
-        <v>4248</v>
+        <v>2872.89</v>
       </c>
       <c r="F43" s="7" t="n">
         <v>200.19</v>
@@ -2476,16 +2476,16 @@
         <v>1718.23</v>
       </c>
       <c r="H43" s="7" t="n">
-        <v>11893.69</v>
+        <v>10518.59</v>
       </c>
       <c r="I43" s="6" t="n">
-        <v>17840535</v>
+        <v>15777885</v>
       </c>
       <c r="J43" s="7" t="n">
-        <v>2159.57</v>
+        <v>2092.9</v>
       </c>
       <c r="K43" s="7" t="n">
-        <v>9734.15</v>
+        <v>8425.709999999999</v>
       </c>
       <c r="L43" s="6" t="n">
         <v>122720000</v>
@@ -2494,7 +2494,7 @@
         <v>81813.33</v>
       </c>
       <c r="N43" s="6" t="n">
-        <v>-104879465</v>
+        <v>-106942115</v>
       </c>
     </row>
     <row r="44">
@@ -2515,7 +2515,7 @@
         <v>7910499.2</v>
       </c>
       <c r="E44" s="7" t="n">
-        <v>7409300.36</v>
+        <v>7416785.27</v>
       </c>
       <c r="F44" s="7" t="n">
         <v>208194.32</v>
@@ -2524,16 +2524,16 @@
         <v>2373149.74</v>
       </c>
       <c r="H44" s="7" t="n">
-        <v>17901143.66</v>
+        <v>17908628.58</v>
       </c>
       <c r="I44" s="6" t="n">
-        <v>26851715490</v>
+        <v>26862942870</v>
       </c>
       <c r="J44" s="7" t="n">
-        <v>1016551.9</v>
+        <v>1022202.52</v>
       </c>
       <c r="K44" s="7" t="n">
-        <v>16884591.79</v>
+        <v>16886426.07</v>
       </c>
       <c r="L44" s="6" t="n">
         <v>981760000</v>
@@ -2542,7 +2542,7 @@
         <v>654506.67</v>
       </c>
       <c r="N44" s="6" t="n">
-        <v>25869955490</v>
+        <v>25881182870</v>
       </c>
     </row>
     <row r="45">
@@ -2563,7 +2563,7 @@
         <v>1798208.88</v>
       </c>
       <c r="E45" s="7" t="n">
-        <v>728165.14</v>
+        <v>773565.98</v>
       </c>
       <c r="F45" s="7" t="n">
         <v>31487.49</v>
@@ -2572,16 +2572,16 @@
         <v>539462.67</v>
       </c>
       <c r="H45" s="7" t="n">
-        <v>3097324.14</v>
+        <v>3142724.98</v>
       </c>
       <c r="I45" s="6" t="n">
-        <v>4645986210</v>
+        <v>4714087470</v>
       </c>
       <c r="J45" s="7" t="n">
-        <v>117449.69</v>
+        <v>122286.86</v>
       </c>
       <c r="K45" s="7" t="n">
-        <v>2979874.45</v>
+        <v>3020438.11</v>
       </c>
       <c r="L45" s="6" t="n">
         <v>226720000</v>
@@ -2590,7 +2590,7 @@
         <v>151146.67</v>
       </c>
       <c r="N45" s="6" t="n">
-        <v>4419266210</v>
+        <v>4487367470</v>
       </c>
     </row>
     <row r="46">
@@ -2611,7 +2611,7 @@
         <v>6173.38</v>
       </c>
       <c r="E46" s="7" t="n">
-        <v>4230</v>
+        <v>2787.34</v>
       </c>
       <c r="F46" s="7" t="n">
         <v>202.26</v>
@@ -2620,16 +2620,16 @@
         <v>1851.98</v>
       </c>
       <c r="H46" s="7" t="n">
-        <v>12457.66</v>
+        <v>11015</v>
       </c>
       <c r="I46" s="6" t="n">
-        <v>18686490</v>
+        <v>16522500</v>
       </c>
       <c r="J46" s="7" t="n">
-        <v>2152.9</v>
+        <v>2089.69</v>
       </c>
       <c r="K46" s="7" t="n">
-        <v>10304.81</v>
+        <v>8925.360000000001</v>
       </c>
       <c r="L46" s="6" t="n">
         <v>122720000</v>
@@ -2638,7 +2638,7 @@
         <v>81813.33</v>
       </c>
       <c r="N46" s="6" t="n">
-        <v>-104033510</v>
+        <v>-106197500</v>
       </c>
     </row>
     <row r="47">
@@ -2659,7 +2659,7 @@
         <v>8820132.970000001</v>
       </c>
       <c r="E47" s="7" t="n">
-        <v>7380880.13</v>
+        <v>7369801.54</v>
       </c>
       <c r="F47" s="7" t="n">
         <v>213439.62</v>
@@ -2668,16 +2668,16 @@
         <v>2646039.91</v>
       </c>
       <c r="H47" s="7" t="n">
-        <v>19060492.69</v>
+        <v>19049414.09</v>
       </c>
       <c r="I47" s="6" t="n">
-        <v>28590739035</v>
+        <v>28574121135</v>
       </c>
       <c r="J47" s="7" t="n">
-        <v>1355032.39</v>
+        <v>1353247.79</v>
       </c>
       <c r="K47" s="7" t="n">
-        <v>17705460.33</v>
+        <v>17696166.33</v>
       </c>
       <c r="L47" s="6" t="n">
         <v>994240000</v>
@@ -2686,7 +2686,7 @@
         <v>662826.67</v>
       </c>
       <c r="N47" s="6" t="n">
-        <v>27596499035</v>
+        <v>27579881135</v>
       </c>
     </row>
     <row r="48">
@@ -2707,7 +2707,7 @@
         <v>1806877.16</v>
       </c>
       <c r="E48" s="7" t="n">
-        <v>926034.1</v>
+        <v>902640.3100000001</v>
       </c>
       <c r="F48" s="7" t="n">
         <v>32203.02</v>
@@ -2716,16 +2716,16 @@
         <v>542063.13</v>
       </c>
       <c r="H48" s="7" t="n">
-        <v>3307177.51</v>
+        <v>3283783.72</v>
       </c>
       <c r="I48" s="6" t="n">
-        <v>4960766265</v>
+        <v>4925675580</v>
       </c>
       <c r="J48" s="7" t="n">
-        <v>179947.32</v>
+        <v>178565.3</v>
       </c>
       <c r="K48" s="7" t="n">
-        <v>3127230.05</v>
+        <v>3105218.27</v>
       </c>
       <c r="L48" s="6" t="n">
         <v>230880000</v>
@@ -2734,7 +2734,7 @@
         <v>153920</v>
       </c>
       <c r="N48" s="6" t="n">
-        <v>4729886265</v>
+        <v>4694795580</v>
       </c>
     </row>
     <row r="49">
@@ -2755,7 +2755,7 @@
         <v>5401.29</v>
       </c>
       <c r="E49" s="7" t="n">
-        <v>4230</v>
+        <v>2713.97</v>
       </c>
       <c r="F49" s="7" t="n">
         <v>204.05</v>
@@ -2764,16 +2764,16 @@
         <v>1620.41</v>
       </c>
       <c r="H49" s="7" t="n">
-        <v>11455.7</v>
+        <v>9939.67</v>
       </c>
       <c r="I49" s="6" t="n">
-        <v>17183550</v>
+        <v>14909505</v>
       </c>
       <c r="J49" s="7" t="n">
-        <v>2564.05</v>
+        <v>2473.64</v>
       </c>
       <c r="K49" s="7" t="n">
-        <v>8891.629999999999</v>
+        <v>7466.01</v>
       </c>
       <c r="L49" s="6" t="n">
         <v>120640000</v>
@@ -2782,7 +2782,7 @@
         <v>80426.67</v>
       </c>
       <c r="N49" s="6" t="n">
-        <v>-103456450</v>
+        <v>-105730495</v>
       </c>
     </row>
     <row r="50">
@@ -2803,7 +2803,7 @@
         <v>10242978.78</v>
       </c>
       <c r="E50" s="7" t="n">
-        <v>7293928.57</v>
+        <v>7113309.54</v>
       </c>
       <c r="F50" s="7" t="n">
         <v>218092</v>
@@ -2812,16 +2812,16 @@
         <v>3072893.64</v>
       </c>
       <c r="H50" s="7" t="n">
-        <v>20827893.04</v>
+        <v>20647274.01</v>
       </c>
       <c r="I50" s="6" t="n">
-        <v>31241839560</v>
+        <v>30970911015</v>
       </c>
       <c r="J50" s="7" t="n">
-        <v>2004716.06</v>
+        <v>1973748.86</v>
       </c>
       <c r="K50" s="7" t="n">
-        <v>18823177.03</v>
+        <v>18673525.17</v>
       </c>
       <c r="L50" s="6" t="n">
         <v>1006720000</v>
@@ -2830,7 +2830,7 @@
         <v>671146.67</v>
       </c>
       <c r="N50" s="6" t="n">
-        <v>30235119560</v>
+        <v>29964191015</v>
       </c>
     </row>
     <row r="51">
@@ -2851,7 +2851,7 @@
         <v>2368422.53</v>
       </c>
       <c r="E51" s="7" t="n">
-        <v>783465.15</v>
+        <v>783464.6800000001</v>
       </c>
       <c r="F51" s="7" t="n">
         <v>32825.93</v>
@@ -2860,16 +2860,16 @@
         <v>710526.73</v>
       </c>
       <c r="H51" s="7" t="n">
-        <v>3895240.37</v>
+        <v>3895239.9</v>
       </c>
       <c r="I51" s="6" t="n">
-        <v>5842860555</v>
+        <v>5842859850</v>
       </c>
       <c r="J51" s="7" t="n">
-        <v>225279.99</v>
+        <v>225279.8</v>
       </c>
       <c r="K51" s="7" t="n">
-        <v>3669960.3</v>
+        <v>3669960.02</v>
       </c>
       <c r="L51" s="6" t="n">
         <v>228800000</v>
@@ -2878,7 +2878,7 @@
         <v>152533.33</v>
       </c>
       <c r="N51" s="6" t="n">
-        <v>5614060555</v>
+        <v>5614059850</v>
       </c>
     </row>
     <row r="52">
@@ -2899,7 +2899,7 @@
         <v>7092.08</v>
       </c>
       <c r="E52" s="7" t="n">
-        <v>4230</v>
+        <v>2640.59</v>
       </c>
       <c r="F52" s="7" t="n">
         <v>205.87</v>
@@ -2908,16 +2908,16 @@
         <v>2127.64</v>
       </c>
       <c r="H52" s="7" t="n">
-        <v>13655.55</v>
+        <v>12066.14</v>
       </c>
       <c r="I52" s="6" t="n">
-        <v>20483325</v>
+        <v>18099210</v>
       </c>
       <c r="J52" s="7" t="n">
-        <v>4379.57</v>
+        <v>4253.35</v>
       </c>
       <c r="K52" s="7" t="n">
-        <v>9275.92</v>
+        <v>7812.74</v>
       </c>
       <c r="L52" s="6" t="n">
         <v>126880000</v>
@@ -2926,7 +2926,7 @@
         <v>84586.67</v>
       </c>
       <c r="N52" s="6" t="n">
-        <v>-106396675</v>
+        <v>-108780790</v>
       </c>
     </row>
     <row r="53">
@@ -2947,7 +2947,7 @@
         <v>12253435.18</v>
       </c>
       <c r="E53" s="7" t="n">
-        <v>8560851.960000001</v>
+        <v>8523117.140000001</v>
       </c>
       <c r="F53" s="7" t="n">
         <v>222615.46</v>
@@ -2956,16 +2956,16 @@
         <v>3676030.57</v>
       </c>
       <c r="H53" s="7" t="n">
-        <v>24712933.01</v>
+        <v>24675198.18</v>
       </c>
       <c r="I53" s="6" t="n">
-        <v>37069399515</v>
+        <v>37012797270</v>
       </c>
       <c r="J53" s="7" t="n">
-        <v>2917764.97</v>
+        <v>2904548.75</v>
       </c>
       <c r="K53" s="7" t="n">
-        <v>21795168.08</v>
+        <v>21770649.48</v>
       </c>
       <c r="L53" s="6" t="n">
         <v>1027520000</v>
@@ -2974,7 +2974,7 @@
         <v>685013.33</v>
       </c>
       <c r="N53" s="6" t="n">
-        <v>36041879515</v>
+        <v>35985277270</v>
       </c>
     </row>
     <row r="54">
@@ -2995,7 +2995,7 @@
         <v>2837075.09</v>
       </c>
       <c r="E54" s="7" t="n">
-        <v>1401377.26</v>
+        <v>1397796.47</v>
       </c>
       <c r="F54" s="7" t="n">
         <v>33473.33</v>
@@ -3004,16 +3004,16 @@
         <v>851122.53</v>
       </c>
       <c r="H54" s="7" t="n">
-        <v>5123048.25</v>
+        <v>5119467.45</v>
       </c>
       <c r="I54" s="6" t="n">
-        <v>7684572375</v>
+        <v>7679201175</v>
       </c>
       <c r="J54" s="7" t="n">
-        <v>278034.05</v>
+        <v>277785.15</v>
       </c>
       <c r="K54" s="7" t="n">
-        <v>4845014.27</v>
+        <v>4841682.38</v>
       </c>
       <c r="L54" s="6" t="n">
         <v>235040000</v>
@@ -3022,7 +3022,7 @@
         <v>156693.33</v>
       </c>
       <c r="N54" s="6" t="n">
-        <v>7449532375</v>
+        <v>7444161175</v>
       </c>
     </row>
     <row r="55">
@@ -3043,7 +3043,7 @@
         <v>8940.93</v>
       </c>
       <c r="E55" s="7" t="n">
-        <v>4212</v>
+        <v>2556.29</v>
       </c>
       <c r="F55" s="7" t="n">
         <v>207.36</v>
@@ -3052,16 +3052,16 @@
         <v>2682.28</v>
       </c>
       <c r="H55" s="7" t="n">
-        <v>16042.55</v>
+        <v>14386.84</v>
       </c>
       <c r="I55" s="6" t="n">
-        <v>24063825</v>
+        <v>21580260</v>
       </c>
       <c r="J55" s="7" t="n">
-        <v>6584.32</v>
+        <v>6433.68</v>
       </c>
       <c r="K55" s="7" t="n">
-        <v>9458.17</v>
+        <v>7953.1</v>
       </c>
       <c r="L55" s="6" t="n">
         <v>131040000</v>
@@ -3070,7 +3070,7 @@
         <v>87360</v>
       </c>
       <c r="N55" s="6" t="n">
-        <v>-106976175</v>
+        <v>-109459740</v>
       </c>
     </row>
     <row r="56">
@@ -3091,7 +3091,7 @@
         <v>11573147.47</v>
       </c>
       <c r="E56" s="7" t="n">
-        <v>7266855.36</v>
+        <v>7121667.29</v>
       </c>
       <c r="F56" s="7" t="n">
         <v>227250.03</v>
@@ -3100,16 +3100,16 @@
         <v>3471944.24</v>
       </c>
       <c r="H56" s="7" t="n">
-        <v>22539197.26</v>
+        <v>22394009.16</v>
       </c>
       <c r="I56" s="6" t="n">
-        <v>33808795890</v>
+        <v>33591013740</v>
       </c>
       <c r="J56" s="7" t="n">
-        <v>3412566.07</v>
+        <v>3355142.06</v>
       </c>
       <c r="K56" s="7" t="n">
-        <v>19126630.94</v>
+        <v>19038866.91</v>
       </c>
       <c r="L56" s="6" t="n">
         <v>1025440000</v>
@@ -3118,7 +3118,7 @@
         <v>683626.67</v>
       </c>
       <c r="N56" s="6" t="n">
-        <v>32783355890</v>
+        <v>32565573740</v>
       </c>
     </row>
     <row r="57">
@@ -3139,7 +3139,7 @@
         <v>2736178.63</v>
       </c>
       <c r="E57" s="7" t="n">
-        <v>1274313.59</v>
+        <v>1274189.45</v>
       </c>
       <c r="F57" s="7" t="n">
         <v>34184.81</v>
@@ -3148,16 +3148,16 @@
         <v>820853.59</v>
       </c>
       <c r="H57" s="7" t="n">
-        <v>4865530.55</v>
+        <v>4865406.41</v>
       </c>
       <c r="I57" s="6" t="n">
-        <v>7298295825</v>
+        <v>7298109615</v>
       </c>
       <c r="J57" s="7" t="n">
-        <v>376076.7</v>
+        <v>375943.42</v>
       </c>
       <c r="K57" s="7" t="n">
-        <v>4489453.82</v>
+        <v>4489462.98</v>
       </c>
       <c r="L57" s="6" t="n">
         <v>235040000</v>
@@ -3166,7 +3166,7 @@
         <v>156693.33</v>
       </c>
       <c r="N57" s="6" t="n">
-        <v>7063255825</v>
+        <v>7063069615</v>
       </c>
     </row>
     <row r="58">
@@ -3187,7 +3187,7 @@
         <v>11249.43</v>
       </c>
       <c r="E58" s="7" t="n">
-        <v>4212</v>
+        <v>2483.23</v>
       </c>
       <c r="F58" s="7" t="n">
         <v>209.38</v>
@@ -3196,16 +3196,16 @@
         <v>3374.82</v>
       </c>
       <c r="H58" s="7" t="n">
-        <v>19045.61</v>
+        <v>17316.83</v>
       </c>
       <c r="I58" s="6" t="n">
-        <v>28568415</v>
+        <v>25975245</v>
       </c>
       <c r="J58" s="7" t="n">
-        <v>10308.59</v>
+        <v>10091.24</v>
       </c>
       <c r="K58" s="7" t="n">
-        <v>8736.99</v>
+        <v>7225.56</v>
       </c>
       <c r="L58" s="6" t="n">
         <v>131040000</v>
@@ -3214,7 +3214,7 @@
         <v>87360</v>
       </c>
       <c r="N58" s="6" t="n">
-        <v>-102471585</v>
+        <v>-105064755</v>
       </c>
     </row>
     <row r="59">
@@ -3235,7 +3235,7 @@
         <v>12081945.7</v>
       </c>
       <c r="E59" s="7" t="n">
-        <v>7236747.06</v>
+        <v>7069903.73</v>
       </c>
       <c r="F59" s="7" t="n">
         <v>232074.24</v>
@@ -3244,16 +3244,16 @@
         <v>3624583.79</v>
       </c>
       <c r="H59" s="7" t="n">
-        <v>23175350.74</v>
+        <v>23008507.4</v>
       </c>
       <c r="I59" s="6" t="n">
-        <v>34763026110</v>
+        <v>34512761100</v>
       </c>
       <c r="J59" s="7" t="n">
-        <v>4692191.48</v>
+        <v>4626594.59</v>
       </c>
       <c r="K59" s="7" t="n">
-        <v>18483159.41</v>
+        <v>18381912.97</v>
       </c>
       <c r="L59" s="6" t="n">
         <v>1031680000</v>
@@ -3262,7 +3262,7 @@
         <v>687786.67</v>
       </c>
       <c r="N59" s="6" t="n">
-        <v>33731346110</v>
+        <v>33481081100</v>
       </c>
     </row>
     <row r="60">
@@ -3331,7 +3331,7 @@
         <v>18270.18</v>
       </c>
       <c r="E61" s="7" t="n">
-        <v>4194</v>
+        <v>2399.86</v>
       </c>
       <c r="F61" s="7" t="n">
         <v>211.24</v>
@@ -3340,16 +3340,16 @@
         <v>5481.04</v>
       </c>
       <c r="H61" s="7" t="n">
-        <v>28156.5</v>
+        <v>26362.36</v>
       </c>
       <c r="I61" s="6" t="n">
-        <v>42234750</v>
+        <v>39543540</v>
       </c>
       <c r="J61" s="7" t="n">
-        <v>18260.35</v>
+        <v>17947.26</v>
       </c>
       <c r="K61" s="7" t="n">
-        <v>9896.219999999999</v>
+        <v>8415.18</v>
       </c>
       <c r="L61" s="6" t="n">
         <v>131040000</v>
@@ -3358,7 +3358,7 @@
         <v>87360</v>
       </c>
       <c r="N61" s="6" t="n">
-        <v>-88805250</v>
+        <v>-91496460</v>
       </c>
     </row>
     <row r="62">
@@ -3379,7 +3379,7 @@
         <v>11850520.38</v>
       </c>
       <c r="E62" s="7" t="n">
-        <v>7631315.2</v>
+        <v>7327606.83</v>
       </c>
       <c r="F62" s="7" t="n">
         <v>237674.94</v>
@@ -3388,16 +3388,16 @@
         <v>3555156.21</v>
       </c>
       <c r="H62" s="7" t="n">
-        <v>23274666.79</v>
+        <v>22970958.5</v>
       </c>
       <c r="I62" s="6" t="n">
-        <v>34912000185</v>
+        <v>34456437750</v>
       </c>
       <c r="J62" s="7" t="n">
-        <v>4774270.2</v>
+        <v>4730002.66</v>
       </c>
       <c r="K62" s="7" t="n">
-        <v>18500396.57</v>
+        <v>18240955.78</v>
       </c>
       <c r="L62" s="6" t="n">
         <v>1044160000</v>
@@ -3406,7 +3406,7 @@
         <v>696106.67</v>
       </c>
       <c r="N62" s="6" t="n">
-        <v>33867840185</v>
+        <v>33412277750</v>
       </c>
     </row>
     <row r="63">
@@ -3427,7 +3427,7 @@
         <v>2913889.95</v>
       </c>
       <c r="E63" s="7" t="n">
-        <v>1244797.46</v>
+        <v>1222164.2</v>
       </c>
       <c r="F63" s="7" t="n">
         <v>35864.78</v>
@@ -3436,16 +3436,16 @@
         <v>874166.98</v>
       </c>
       <c r="H63" s="7" t="n">
-        <v>5068719.15</v>
+        <v>5046085.9</v>
       </c>
       <c r="I63" s="6" t="n">
-        <v>7603078725</v>
+        <v>7569128850</v>
       </c>
       <c r="J63" s="7" t="n">
-        <v>589364</v>
+        <v>587387.05</v>
       </c>
       <c r="K63" s="7" t="n">
-        <v>4479355.17</v>
+        <v>4458698.85</v>
       </c>
       <c r="L63" s="6" t="n">
         <v>235040000</v>
@@ -3454,7 +3454,7 @@
         <v>156693.33</v>
       </c>
       <c r="N63" s="6" t="n">
-        <v>7368038725</v>
+        <v>7334088850</v>
       </c>
     </row>
     <row r="64">
@@ -3475,7 +3475,7 @@
         <v>18350.59</v>
       </c>
       <c r="E64" s="7" t="n">
-        <v>4194</v>
+        <v>2327.11</v>
       </c>
       <c r="F64" s="7" t="n">
         <v>213.12</v>
@@ -3484,16 +3484,16 @@
         <v>5505.19</v>
       </c>
       <c r="H64" s="7" t="n">
-        <v>28262.9</v>
+        <v>26396.01</v>
       </c>
       <c r="I64" s="6" t="n">
-        <v>42394350</v>
+        <v>39594015</v>
       </c>
       <c r="J64" s="7" t="n">
-        <v>17218.12</v>
+        <v>16894.39</v>
       </c>
       <c r="K64" s="7" t="n">
-        <v>11044.75</v>
+        <v>9501.59</v>
       </c>
       <c r="L64" s="6" t="n">
         <v>143520000</v>
@@ -3502,7 +3502,7 @@
         <v>95680</v>
       </c>
       <c r="N64" s="6" t="n">
-        <v>-101125650</v>
+        <v>-103925985</v>
       </c>
     </row>
     <row r="65">
@@ -3523,7 +3523,7 @@
         <v>13194146.48</v>
       </c>
       <c r="E65" s="7" t="n">
-        <v>8291318.81</v>
+        <v>8679051.300000001</v>
       </c>
       <c r="F65" s="7" t="n">
         <v>243618.46</v>
@@ -3532,16 +3532,16 @@
         <v>3958244</v>
       </c>
       <c r="H65" s="7" t="n">
-        <v>25687327.53</v>
+        <v>26075060.12</v>
       </c>
       <c r="I65" s="6" t="n">
-        <v>38530991295</v>
+        <v>39112590180</v>
       </c>
       <c r="J65" s="7" t="n">
-        <v>6432925.12</v>
+        <v>6536787.13</v>
       </c>
       <c r="K65" s="7" t="n">
-        <v>19254402.53</v>
+        <v>19538273.08</v>
       </c>
       <c r="L65" s="6" t="n">
         <v>1058720000</v>
@@ -3550,7 +3550,7 @@
         <v>705813.33</v>
       </c>
       <c r="N65" s="6" t="n">
-        <v>37472271295</v>
+        <v>38053870180</v>
       </c>
     </row>
     <row r="66">
@@ -3571,7 +3571,7 @@
         <v>3040159.31</v>
       </c>
       <c r="E66" s="7" t="n">
-        <v>1278214.65</v>
+        <v>1185044.24</v>
       </c>
       <c r="F66" s="7" t="n">
         <v>36607.29</v>
@@ -3580,16 +3580,16 @@
         <v>912047.78</v>
       </c>
       <c r="H66" s="7" t="n">
-        <v>5267029.11</v>
+        <v>5173858.67</v>
       </c>
       <c r="I66" s="6" t="n">
-        <v>7900543665</v>
+        <v>7760788005</v>
       </c>
       <c r="J66" s="7" t="n">
-        <v>832518.2</v>
+        <v>807425.25</v>
       </c>
       <c r="K66" s="7" t="n">
-        <v>4434510.92</v>
+        <v>4366433.45</v>
       </c>
       <c r="L66" s="6" t="n">
         <v>237120000</v>
@@ -3598,7 +3598,7 @@
         <v>158080</v>
       </c>
       <c r="N66" s="6" t="n">
-        <v>7663423665</v>
+        <v>7523668005</v>
       </c>
     </row>
     <row r="67">
@@ -3619,7 +3619,7 @@
         <v>25170.04</v>
       </c>
       <c r="E67" s="7" t="n">
-        <v>4194</v>
+        <v>2254.36</v>
       </c>
       <c r="F67" s="7" t="n">
         <v>214.47</v>
@@ -3628,16 +3628,16 @@
         <v>7551.02</v>
       </c>
       <c r="H67" s="7" t="n">
-        <v>37129.56</v>
+        <v>35189.92</v>
       </c>
       <c r="I67" s="6" t="n">
-        <v>55694340</v>
+        <v>52784880</v>
       </c>
       <c r="J67" s="7" t="n">
-        <v>20712.55</v>
+        <v>20299.56</v>
       </c>
       <c r="K67" s="7" t="n">
-        <v>16417.02</v>
+        <v>14890.37</v>
       </c>
       <c r="L67" s="6" t="n">
         <v>143520000</v>
@@ -3646,7 +3646,7 @@
         <v>95680</v>
       </c>
       <c r="N67" s="6" t="n">
-        <v>-87825660</v>
+        <v>-90735120</v>
       </c>
     </row>
     <row r="68">
@@ -3667,7 +3667,7 @@
         <v>13260604.91</v>
       </c>
       <c r="E68" s="7" t="n">
-        <v>10717223.78</v>
+        <v>10277820.09</v>
       </c>
       <c r="F68" s="7" t="n">
         <v>249498.18</v>
@@ -3676,16 +3676,16 @@
         <v>3978181.47</v>
       </c>
       <c r="H68" s="7" t="n">
-        <v>28205508.57</v>
+        <v>27766104.85</v>
       </c>
       <c r="I68" s="6" t="n">
-        <v>42308262855</v>
+        <v>41649157275</v>
       </c>
       <c r="J68" s="7" t="n">
-        <v>7964790.86</v>
+        <v>7812160.74</v>
       </c>
       <c r="K68" s="7" t="n">
-        <v>20240717.64</v>
+        <v>19953944.14</v>
       </c>
       <c r="L68" s="6" t="n">
         <v>1062880000</v>
@@ -3694,7 +3694,7 @@
         <v>708586.67</v>
       </c>
       <c r="N68" s="6" t="n">
-        <v>41245382855</v>
+        <v>40586277275</v>
       </c>
     </row>
     <row r="69">
@@ -3715,7 +3715,7 @@
         <v>4203926.92</v>
       </c>
       <c r="E69" s="7" t="n">
-        <v>1585771.77</v>
+        <v>1303598.5</v>
       </c>
       <c r="F69" s="7" t="n">
         <v>37322.83</v>
@@ -3724,16 +3724,16 @@
         <v>1261178.07</v>
       </c>
       <c r="H69" s="7" t="n">
-        <v>7088199.66</v>
+        <v>6806026.38</v>
       </c>
       <c r="I69" s="6" t="n">
-        <v>10632299490</v>
+        <v>10209039570</v>
       </c>
       <c r="J69" s="7" t="n">
-        <v>916223.87</v>
+        <v>853836.95</v>
       </c>
       <c r="K69" s="7" t="n">
-        <v>6171975.79</v>
+        <v>5952189.41</v>
       </c>
       <c r="L69" s="6" t="n">
         <v>237120000</v>
@@ -3742,7 +3742,7 @@
         <v>158080</v>
       </c>
       <c r="N69" s="6" t="n">
-        <v>10395179490</v>
+        <v>9971919570</v>
       </c>
     </row>
     <row r="70">
@@ -3763,7 +3763,7 @@
         <v>26528.96</v>
       </c>
       <c r="E70" s="7" t="n">
-        <v>4720.09</v>
+        <v>2713.24</v>
       </c>
       <c r="F70" s="7" t="n">
         <v>216.14</v>
@@ -3772,16 +3772,16 @@
         <v>7958.67</v>
       </c>
       <c r="H70" s="7" t="n">
-        <v>39423.82</v>
+        <v>37416.98</v>
       </c>
       <c r="I70" s="6" t="n">
-        <v>59135730</v>
+        <v>56125470</v>
       </c>
       <c r="J70" s="7" t="n">
-        <v>20720.87</v>
+        <v>20292.99</v>
       </c>
       <c r="K70" s="7" t="n">
-        <v>18702.97</v>
+        <v>17124.03</v>
       </c>
       <c r="L70" s="6" t="n">
         <v>147680000</v>
@@ -3790,7 +3790,7 @@
         <v>98453.33</v>
       </c>
       <c r="N70" s="6" t="n">
-        <v>-88544270</v>
+        <v>-91554530</v>
       </c>
     </row>
     <row r="71">
@@ -3811,7 +3811,7 @@
         <v>14151253.03</v>
       </c>
       <c r="E71" s="7" t="n">
-        <v>10375971.28</v>
+        <v>10133341.01</v>
       </c>
       <c r="F71" s="7" t="n">
         <v>252130.39</v>
@@ -3820,16 +3820,16 @@
         <v>4245375.88</v>
       </c>
       <c r="H71" s="7" t="n">
-        <v>29024730.8</v>
+        <v>28782100.56</v>
       </c>
       <c r="I71" s="6" t="n">
-        <v>43537096200</v>
+        <v>43173150840</v>
       </c>
       <c r="J71" s="7" t="n">
-        <v>9455708.109999999</v>
+        <v>9357626.460000001</v>
       </c>
       <c r="K71" s="7" t="n">
-        <v>19569022.74</v>
+        <v>19424474.23</v>
       </c>
       <c r="L71" s="6" t="n">
         <v>1067040000</v>
@@ -3838,7 +3838,7 @@
         <v>711360</v>
       </c>
       <c r="N71" s="6" t="n">
-        <v>42470056200</v>
+        <v>42106110840</v>
       </c>
     </row>
     <row r="72">
@@ -3859,7 +3859,7 @@
         <v>4113507.56</v>
       </c>
       <c r="E72" s="7" t="n">
-        <v>1381734.02</v>
+        <v>1363179.23</v>
       </c>
       <c r="F72" s="7" t="n">
         <v>38061.11</v>
@@ -3868,16 +3868,16 @@
         <v>1234052.25</v>
       </c>
       <c r="H72" s="7" t="n">
-        <v>6767354.96</v>
+        <v>6748800.19</v>
       </c>
       <c r="I72" s="6" t="n">
-        <v>10151032440</v>
+        <v>10123200285</v>
       </c>
       <c r="J72" s="7" t="n">
-        <v>1156457.29</v>
+        <v>1150549.38</v>
       </c>
       <c r="K72" s="7" t="n">
-        <v>5610897.73</v>
+        <v>5598250.86</v>
       </c>
       <c r="L72" s="6" t="n">
         <v>243360000</v>
@@ -3886,7 +3886,7 @@
         <v>162240</v>
       </c>
       <c r="N72" s="6" t="n">
-        <v>9907672440</v>
+        <v>9879840285</v>
       </c>
     </row>
     <row r="73">
@@ -3907,7 +3907,7 @@
         <v>34885.37</v>
       </c>
       <c r="E73" s="7" t="n">
-        <v>4879.59</v>
+        <v>2791.35</v>
       </c>
       <c r="F73" s="7" t="n">
         <v>217.47</v>
@@ -3916,16 +3916,16 @@
         <v>10465.58</v>
       </c>
       <c r="H73" s="7" t="n">
-        <v>50448.01</v>
+        <v>48359.78</v>
       </c>
       <c r="I73" s="6" t="n">
-        <v>75672015</v>
+        <v>72539670</v>
       </c>
       <c r="J73" s="7" t="n">
-        <v>28144.33</v>
+        <v>27542.82</v>
       </c>
       <c r="K73" s="7" t="n">
-        <v>22303.73</v>
+        <v>20817.03</v>
       </c>
       <c r="L73" s="6" t="n">
         <v>149760000</v>
@@ -3934,7 +3934,7 @@
         <v>99840</v>
       </c>
       <c r="N73" s="6" t="n">
-        <v>-74087985</v>
+        <v>-77220330</v>
       </c>
     </row>
     <row r="74">
@@ -3955,7 +3955,7 @@
         <v>13118835.33</v>
       </c>
       <c r="E74" s="7" t="n">
-        <v>9413014.25</v>
+        <v>9316369.52</v>
       </c>
       <c r="F74" s="7" t="n">
         <v>260117.63</v>
@@ -3964,16 +3964,16 @@
         <v>3935650.6</v>
       </c>
       <c r="H74" s="7" t="n">
-        <v>26727617.69</v>
+        <v>26630972.96</v>
       </c>
       <c r="I74" s="6" t="n">
-        <v>40091426535</v>
+        <v>39946459440</v>
       </c>
       <c r="J74" s="7" t="n">
-        <v>10016790.61</v>
+        <v>9980310.609999999</v>
       </c>
       <c r="K74" s="7" t="n">
-        <v>16710827.2</v>
+        <v>16650662.49</v>
       </c>
       <c r="L74" s="6" t="n">
         <v>1071200000</v>
@@ -3982,7 +3982,7 @@
         <v>714133.33</v>
       </c>
       <c r="N74" s="6" t="n">
-        <v>39020226535</v>
+        <v>38875259440</v>
       </c>
     </row>
     <row r="75">
@@ -4003,7 +4003,7 @@
         <v>3909212.81</v>
       </c>
       <c r="E75" s="7" t="n">
-        <v>1507711.54</v>
+        <v>1485949.65</v>
       </c>
       <c r="F75" s="7" t="n">
         <v>38903.52</v>
@@ -4012,16 +4012,16 @@
         <v>1172763.82</v>
       </c>
       <c r="H75" s="7" t="n">
-        <v>6628591.74</v>
+        <v>6606829.85</v>
       </c>
       <c r="I75" s="6" t="n">
-        <v>9942887610</v>
+        <v>9910244775</v>
       </c>
       <c r="J75" s="7" t="n">
-        <v>1245902.37</v>
+        <v>1243904.72</v>
       </c>
       <c r="K75" s="7" t="n">
-        <v>5382689.34</v>
+        <v>5362925.09</v>
       </c>
       <c r="L75" s="6" t="n">
         <v>245440000</v>
@@ -4030,7 +4030,7 @@
         <v>163626.67</v>
       </c>
       <c r="N75" s="6" t="n">
-        <v>9697447610</v>
+        <v>9664804775</v>
       </c>
     </row>
     <row r="76">
@@ -4051,7 +4051,7 @@
         <v>27331.39</v>
       </c>
       <c r="E76" s="7" t="n">
-        <v>5245.66</v>
+        <v>3097.41</v>
       </c>
       <c r="F76" s="7" t="n">
         <v>218.73</v>
@@ -4060,16 +4060,16 @@
         <v>8199.379999999999</v>
       </c>
       <c r="H76" s="7" t="n">
-        <v>40995.11</v>
+        <v>38846.86</v>
       </c>
       <c r="I76" s="6" t="n">
-        <v>61492665</v>
+        <v>58270290</v>
       </c>
       <c r="J76" s="7" t="n">
-        <v>26148.27</v>
+        <v>25457.67</v>
       </c>
       <c r="K76" s="7" t="n">
-        <v>14846.87</v>
+        <v>13389.22</v>
       </c>
       <c r="L76" s="6" t="n">
         <v>153920000</v>
@@ -4078,7 +4078,7 @@
         <v>102613.33</v>
       </c>
       <c r="N76" s="6" t="n">
-        <v>-92427335</v>
+        <v>-95649710</v>
       </c>
     </row>
     <row r="77">
@@ -4099,7 +4099,7 @@
         <v>15182768.98</v>
       </c>
       <c r="E77" s="7" t="n">
-        <v>10814981.08</v>
+        <v>10714984.38</v>
       </c>
       <c r="F77" s="7" t="n">
         <v>256445.55</v>
@@ -4108,16 +4108,16 @@
         <v>4554830.77</v>
       </c>
       <c r="H77" s="7" t="n">
-        <v>30809026.17</v>
+        <v>30709029.49</v>
       </c>
       <c r="I77" s="6" t="n">
-        <v>46213539255</v>
+        <v>46063544235</v>
       </c>
       <c r="J77" s="7" t="n">
-        <v>11812007.17</v>
+        <v>11741976.06</v>
       </c>
       <c r="K77" s="7" t="n">
-        <v>18997018.88</v>
+        <v>18967053.26</v>
       </c>
       <c r="L77" s="6" t="n">
         <v>1081600000</v>
@@ -4126,7 +4126,7 @@
         <v>721066.67</v>
       </c>
       <c r="N77" s="6" t="n">
-        <v>45131939255</v>
+        <v>44981944235</v>
       </c>
     </row>
     <row r="78">
@@ -4147,7 +4147,7 @@
         <v>4299541.82</v>
       </c>
       <c r="E78" s="7" t="n">
-        <v>1672610.71</v>
+        <v>1659119.47</v>
       </c>
       <c r="F78" s="7" t="n">
         <v>39844.21</v>
@@ -4156,16 +4156,16 @@
         <v>1289862.59</v>
       </c>
       <c r="H78" s="7" t="n">
-        <v>7301859.25</v>
+        <v>7288367.98</v>
       </c>
       <c r="I78" s="6" t="n">
-        <v>10952788875</v>
+        <v>10932551970</v>
       </c>
       <c r="J78" s="7" t="n">
-        <v>1600983.14</v>
+        <v>1596319.77</v>
       </c>
       <c r="K78" s="7" t="n">
-        <v>5700876.11</v>
+        <v>5692048.21</v>
       </c>
       <c r="L78" s="6" t="n">
         <v>247520000</v>
@@ -4174,7 +4174,7 @@
         <v>165013.33</v>
       </c>
       <c r="N78" s="6" t="n">
-        <v>10705268875</v>
+        <v>10685031970</v>
       </c>
     </row>
     <row r="79">
@@ -4195,7 +4195,7 @@
         <v>35517.73</v>
       </c>
       <c r="E79" s="7" t="n">
-        <v>1489.68</v>
+        <v>1520.38</v>
       </c>
       <c r="F79" s="7" t="n">
         <v>220.28</v>
@@ -4204,16 +4204,16 @@
         <v>10655.35</v>
       </c>
       <c r="H79" s="7" t="n">
-        <v>47883.06</v>
+        <v>47913.76</v>
       </c>
       <c r="I79" s="6" t="n">
-        <v>71824590</v>
+        <v>71870640</v>
       </c>
       <c r="J79" s="7" t="n">
-        <v>32775.53</v>
+        <v>32801.14</v>
       </c>
       <c r="K79" s="7" t="n">
-        <v>15107.54</v>
+        <v>15112.64</v>
       </c>
       <c r="L79" s="6" t="n">
         <v>160160000</v>
@@ -4222,7 +4222,7 @@
         <v>106773.33</v>
       </c>
       <c r="N79" s="6" t="n">
-        <v>-88335410</v>
+        <v>-88289360</v>
       </c>
     </row>
     <row r="80">
@@ -4243,7 +4243,7 @@
         <v>15309950.01</v>
       </c>
       <c r="E80" s="7" t="n">
-        <v>11079605.01</v>
+        <v>10681031.89</v>
       </c>
       <c r="F80" s="7" t="n">
         <v>261005.57</v>
@@ -4252,16 +4252,16 @@
         <v>4592984.88</v>
       </c>
       <c r="H80" s="7" t="n">
-        <v>31243545.35</v>
+        <v>30844972.27</v>
       </c>
       <c r="I80" s="6" t="n">
-        <v>46865318025</v>
+        <v>46267458405</v>
       </c>
       <c r="J80" s="7" t="n">
-        <v>12101706.85</v>
+        <v>11901885.46</v>
       </c>
       <c r="K80" s="7" t="n">
-        <v>19141838.48</v>
+        <v>18943086.71</v>
       </c>
       <c r="L80" s="6" t="n">
         <v>1085760000</v>
@@ -4270,7 +4270,7 @@
         <v>723840</v>
       </c>
       <c r="N80" s="6" t="n">
-        <v>45779558025</v>
+        <v>45181698405</v>
       </c>
     </row>
     <row r="81">
@@ -4291,7 +4291,7 @@
         <v>4218312.56</v>
       </c>
       <c r="E81" s="7" t="n">
-        <v>1456067.77</v>
+        <v>1446463.38</v>
       </c>
       <c r="F81" s="7" t="n">
         <v>41013.07</v>
@@ -4300,16 +4300,16 @@
         <v>1265493.79</v>
       </c>
       <c r="H81" s="7" t="n">
-        <v>6980887.23</v>
+        <v>6971282.87</v>
       </c>
       <c r="I81" s="6" t="n">
-        <v>10471330845</v>
+        <v>10456924305</v>
       </c>
       <c r="J81" s="7" t="n">
-        <v>1432474.88</v>
+        <v>1427403.07</v>
       </c>
       <c r="K81" s="7" t="n">
-        <v>5548412.36</v>
+        <v>5543879.79</v>
       </c>
       <c r="L81" s="6" t="n">
         <v>249600000</v>
@@ -4318,7 +4318,7 @@
         <v>166400</v>
       </c>
       <c r="N81" s="6" t="n">
-        <v>10221730845</v>
+        <v>10207324305</v>
       </c>
     </row>
     <row r="82">
@@ -4339,7 +4339,7 @@
         <v>48506.32</v>
       </c>
       <c r="E82" s="7" t="n">
-        <v>2273.09</v>
+        <v>2218.14</v>
       </c>
       <c r="F82" s="7" t="n">
         <v>222.54</v>
@@ -4348,16 +4348,16 @@
         <v>14551.91</v>
       </c>
       <c r="H82" s="7" t="n">
-        <v>65553.89</v>
+        <v>65498.93</v>
       </c>
       <c r="I82" s="6" t="n">
-        <v>98330835</v>
+        <v>98248395</v>
       </c>
       <c r="J82" s="7" t="n">
-        <v>38709.21</v>
+        <v>38698.44</v>
       </c>
       <c r="K82" s="7" t="n">
-        <v>26844.79</v>
+        <v>26800.56</v>
       </c>
       <c r="L82" s="6" t="n">
         <v>162240000</v>
@@ -4366,7 +4366,7 @@
         <v>108160</v>
       </c>
       <c r="N82" s="6" t="n">
-        <v>-63909165</v>
+        <v>-63991605</v>
       </c>
     </row>
     <row r="83">
@@ -4387,7 +4387,7 @@
         <v>16355772.25</v>
       </c>
       <c r="E83" s="7" t="n">
-        <v>10828323.47</v>
+        <v>10760430.31</v>
       </c>
       <c r="F83" s="7" t="n">
         <v>231584.72</v>
@@ -4396,16 +4396,16 @@
         <v>4906731.66</v>
       </c>
       <c r="H83" s="7" t="n">
-        <v>32322412.13</v>
+        <v>32254518.96</v>
       </c>
       <c r="I83" s="6" t="n">
-        <v>48483618195</v>
+        <v>48381778440</v>
       </c>
       <c r="J83" s="7" t="n">
-        <v>13708469.17</v>
+        <v>13662343.9</v>
       </c>
       <c r="K83" s="7" t="n">
-        <v>18613943.09</v>
+        <v>18592175.13</v>
       </c>
       <c r="L83" s="6" t="n">
         <v>1087840000</v>
@@ -4414,7 +4414,7 @@
         <v>725226.67</v>
       </c>
       <c r="N83" s="6" t="n">
-        <v>47395778195</v>
+        <v>47293938440</v>
       </c>
     </row>
     <row r="84">
@@ -4435,7 +4435,7 @@
         <v>4528391.73</v>
       </c>
       <c r="E84" s="7" t="n">
-        <v>1374573</v>
+        <v>1377570.58</v>
       </c>
       <c r="F84" s="7" t="n">
         <v>42071.49</v>
@@ -4444,16 +4444,16 @@
         <v>1358517.5</v>
       </c>
       <c r="H84" s="7" t="n">
-        <v>7303553.79</v>
+        <v>7306551.37</v>
       </c>
       <c r="I84" s="6" t="n">
-        <v>10955330685</v>
+        <v>10959827055</v>
       </c>
       <c r="J84" s="7" t="n">
-        <v>1859108.97</v>
+        <v>1868399.85</v>
       </c>
       <c r="K84" s="7" t="n">
-        <v>5444444.76</v>
+        <v>5438151.44</v>
       </c>
       <c r="L84" s="6" t="n">
         <v>249600000</v>
@@ -4462,7 +4462,7 @@
         <v>166400</v>
       </c>
       <c r="N84" s="6" t="n">
-        <v>10705730685</v>
+        <v>10710227055</v>
       </c>
     </row>
     <row r="85">
@@ -4483,7 +4483,7 @@
         <v>159336.18</v>
       </c>
       <c r="E85" s="7" t="n">
-        <v>10864.46</v>
+        <v>5987.7</v>
       </c>
       <c r="F85" s="7" t="n">
         <v>224.99</v>
@@ -4492,16 +4492,16 @@
         <v>47800.89</v>
       </c>
       <c r="H85" s="7" t="n">
-        <v>218226.46</v>
+        <v>213349.69</v>
       </c>
       <c r="I85" s="6" t="n">
-        <v>327339690</v>
+        <v>320024535</v>
       </c>
       <c r="J85" s="7" t="n">
-        <v>107552.08</v>
+        <v>102908.87</v>
       </c>
       <c r="K85" s="7" t="n">
-        <v>110674.31</v>
+        <v>110440.76</v>
       </c>
       <c r="L85" s="6" t="n">
         <v>164320000</v>
@@ -4510,7 +4510,7 @@
         <v>109546.67</v>
       </c>
       <c r="N85" s="6" t="n">
-        <v>163019690</v>
+        <v>155704535</v>
       </c>
     </row>
     <row r="86">
@@ -4531,7 +4531,7 @@
         <v>17584131.8</v>
       </c>
       <c r="E86" s="7" t="n">
-        <v>9892007.66</v>
+        <v>9453002.59</v>
       </c>
       <c r="F86" s="7" t="n">
         <v>234917.91</v>
@@ -4540,16 +4540,16 @@
         <v>5275239.43</v>
       </c>
       <c r="H86" s="7" t="n">
-        <v>32986296.91</v>
+        <v>32547291.89</v>
       </c>
       <c r="I86" s="6" t="n">
-        <v>49479445365</v>
+        <v>48820937835</v>
       </c>
       <c r="J86" s="7" t="n">
-        <v>13605442.1</v>
+        <v>13396757.02</v>
       </c>
       <c r="K86" s="7" t="n">
-        <v>19380854.73</v>
+        <v>19150534.85</v>
       </c>
       <c r="L86" s="6" t="n">
         <v>1089920000</v>
@@ -4558,7 +4558,7 @@
         <v>726613.33</v>
       </c>
       <c r="N86" s="6" t="n">
-        <v>48389525365</v>
+        <v>47731017835</v>
       </c>
     </row>
     <row r="87">
@@ -4579,7 +4579,7 @@
         <v>4996053.88</v>
       </c>
       <c r="E87" s="7" t="n">
-        <v>1355487.69</v>
+        <v>1342740.34</v>
       </c>
       <c r="F87" s="7" t="n">
         <v>42956.71</v>
@@ -4588,16 +4588,16 @@
         <v>1498816.15</v>
       </c>
       <c r="H87" s="7" t="n">
-        <v>7893314.4</v>
+        <v>7880567.06</v>
       </c>
       <c r="I87" s="6" t="n">
-        <v>11839971600</v>
+        <v>11820850590</v>
       </c>
       <c r="J87" s="7" t="n">
-        <v>2078246.77</v>
+        <v>2074775.33</v>
       </c>
       <c r="K87" s="7" t="n">
-        <v>5815067.68</v>
+        <v>5805791.78</v>
       </c>
       <c r="L87" s="6" t="n">
         <v>251680000</v>
@@ -4606,7 +4606,7 @@
         <v>167786.67</v>
       </c>
       <c r="N87" s="6" t="n">
-        <v>11588291600</v>
+        <v>11569170590</v>
       </c>
     </row>
     <row r="88">
@@ -4627,7 +4627,7 @@
         <v>155305.4</v>
       </c>
       <c r="E88" s="7" t="n">
-        <v>2767.87</v>
+        <v>7110.47</v>
       </c>
       <c r="F88" s="7" t="n">
         <v>228.8</v>
@@ -4636,16 +4636,16 @@
         <v>46591.62</v>
       </c>
       <c r="H88" s="7" t="n">
-        <v>204893.69</v>
+        <v>209236.29</v>
       </c>
       <c r="I88" s="6" t="n">
-        <v>307340535</v>
+        <v>313854435</v>
       </c>
       <c r="J88" s="7" t="n">
-        <v>96083.57000000001</v>
+        <v>97783.02</v>
       </c>
       <c r="K88" s="7" t="n">
-        <v>108810.15</v>
+        <v>111453.29</v>
       </c>
       <c r="L88" s="6" t="n">
         <v>166400000</v>
@@ -4654,7 +4654,7 @@
         <v>110933.33</v>
       </c>
       <c r="N88" s="6" t="n">
-        <v>140940535</v>
+        <v>147454435</v>
       </c>
     </row>
     <row r="89">
@@ -4675,7 +4675,7 @@
         <v>20096219.7</v>
       </c>
       <c r="E89" s="7" t="n">
-        <v>10423694.54</v>
+        <v>10344810.47</v>
       </c>
       <c r="F89" s="7" t="n">
         <v>278845.02</v>
@@ -4684,16 +4684,16 @@
         <v>6028865.88</v>
       </c>
       <c r="H89" s="7" t="n">
-        <v>36827625.03</v>
+        <v>36748740.92</v>
       </c>
       <c r="I89" s="6" t="n">
-        <v>55241437545</v>
+        <v>55123111380</v>
       </c>
       <c r="J89" s="7" t="n">
-        <v>14967718.59</v>
+        <v>14905940.6</v>
       </c>
       <c r="K89" s="7" t="n">
-        <v>21859906.46</v>
+        <v>21842800.39</v>
       </c>
       <c r="L89" s="6" t="n">
         <v>1089920000</v>
@@ -4702,7 +4702,7 @@
         <v>726613.33</v>
       </c>
       <c r="N89" s="6" t="n">
-        <v>54151517545</v>
+        <v>54033191380</v>
       </c>
     </row>
     <row r="90">
@@ -4723,7 +4723,7 @@
         <v>5422294.97</v>
       </c>
       <c r="E90" s="7" t="n">
-        <v>1363401.41</v>
+        <v>1338738.95</v>
       </c>
       <c r="F90" s="7" t="n">
         <v>43801.23</v>
@@ -4732,16 +4732,16 @@
         <v>1626688.46</v>
       </c>
       <c r="H90" s="7" t="n">
-        <v>8456186.039999999</v>
+        <v>8431523.57</v>
       </c>
       <c r="I90" s="6" t="n">
-        <v>12684279060</v>
+        <v>12647285355</v>
       </c>
       <c r="J90" s="7" t="n">
-        <v>2070905.94</v>
+        <v>2061215.89</v>
       </c>
       <c r="K90" s="7" t="n">
-        <v>6385280.1</v>
+        <v>6370307.69</v>
       </c>
       <c r="L90" s="6" t="n">
         <v>251680000</v>
@@ -4750,7 +4750,7 @@
         <v>167786.67</v>
       </c>
       <c r="N90" s="6" t="n">
-        <v>12432599060</v>
+        <v>12395605355</v>
       </c>
     </row>
     <row r="91">
@@ -4771,7 +4771,7 @@
         <v>140860.71</v>
       </c>
       <c r="E91" s="7" t="n">
-        <v>42254.51</v>
+        <v>42263.1</v>
       </c>
       <c r="F91" s="7" t="n">
         <v>237.96</v>
@@ -4780,16 +4780,16 @@
         <v>42258.21</v>
       </c>
       <c r="H91" s="7" t="n">
-        <v>225611.39</v>
+        <v>225619.98</v>
       </c>
       <c r="I91" s="6" t="n">
-        <v>338417085</v>
+        <v>338429970</v>
       </c>
       <c r="J91" s="7" t="n">
-        <v>90905.56</v>
+        <v>90911.62</v>
       </c>
       <c r="K91" s="7" t="n">
-        <v>134705.83</v>
+        <v>134708.36</v>
       </c>
       <c r="L91" s="6" t="n">
         <v>170560000</v>
@@ -4798,7 +4798,7 @@
         <v>113706.67</v>
       </c>
       <c r="N91" s="6" t="n">
-        <v>167857085</v>
+        <v>167869970</v>
       </c>
     </row>
     <row r="92">
@@ -4819,7 +4819,7 @@
         <v>20967697.37</v>
       </c>
       <c r="E92" s="7" t="n">
-        <v>5575295.55</v>
+        <v>10235251.46</v>
       </c>
       <c r="F92" s="7" t="n">
         <v>280694.12</v>
@@ -4828,16 +4828,16 @@
         <v>6290309.18</v>
       </c>
       <c r="H92" s="7" t="n">
-        <v>33113996.21</v>
+        <v>37773952.17</v>
       </c>
       <c r="I92" s="6" t="n">
-        <v>49670994315</v>
+        <v>56660928255</v>
       </c>
       <c r="J92" s="7" t="n">
-        <v>13447287.91</v>
+        <v>15781339.4</v>
       </c>
       <c r="K92" s="7" t="n">
-        <v>19666708.15</v>
+        <v>21992612.76</v>
       </c>
       <c r="L92" s="6" t="n">
         <v>1089920000</v>
@@ -4846,7 +4846,7 @@
         <v>726613.33</v>
       </c>
       <c r="N92" s="6" t="n">
-        <v>48581074315</v>
+        <v>55571008255</v>
       </c>
     </row>
     <row r="93">
@@ -4867,7 +4867,7 @@
         <v>5393736.03</v>
       </c>
       <c r="E93" s="7" t="n">
-        <v>725499.25</v>
+        <v>898586.08</v>
       </c>
       <c r="F93" s="7" t="n">
         <v>44130.18</v>
@@ -4876,16 +4876,16 @@
         <v>1618120.81</v>
       </c>
       <c r="H93" s="7" t="n">
-        <v>7781486.27</v>
+        <v>7954573.08</v>
       </c>
       <c r="I93" s="6" t="n">
-        <v>11672229405</v>
+        <v>11931859620</v>
       </c>
       <c r="J93" s="7" t="n">
-        <v>1328476.22</v>
+        <v>1322596.74</v>
       </c>
       <c r="K93" s="7" t="n">
-        <v>6453010.11</v>
+        <v>6631976.37</v>
       </c>
       <c r="L93" s="6" t="n">
         <v>251680000</v>
@@ -4894,7 +4894,7 @@
         <v>167786.67</v>
       </c>
       <c r="N93" s="6" t="n">
-        <v>11420549405</v>
+        <v>11680179620</v>
       </c>
     </row>
     <row r="94">
@@ -4915,7 +4915,7 @@
         <v>130921.78</v>
       </c>
       <c r="E94" s="7" t="n">
-        <v>10217.81</v>
+        <v>10760.01</v>
       </c>
       <c r="F94" s="7" t="n">
         <v>241.48</v>
@@ -4924,16 +4924,16 @@
         <v>39276.53</v>
       </c>
       <c r="H94" s="7" t="n">
-        <v>180657.67</v>
+        <v>181199.87</v>
       </c>
       <c r="I94" s="6" t="n">
-        <v>270986505</v>
+        <v>271799805</v>
       </c>
       <c r="J94" s="7" t="n">
-        <v>78002.34</v>
+        <v>78354.06</v>
       </c>
       <c r="K94" s="7" t="n">
-        <v>102655.4</v>
+        <v>102845.84</v>
       </c>
       <c r="L94" s="6" t="n">
         <v>170560000</v>
@@ -4942,7 +4942,7 @@
         <v>113706.67</v>
       </c>
       <c r="N94" s="6" t="n">
-        <v>100426505</v>
+        <v>101239805</v>
       </c>
     </row>
   </sheetData>

--- a/NBS FINAL delivery/03_Excel_Deliveries/9_NBS_Accounts_Domestic_and_GNI.xlsx
+++ b/NBS FINAL delivery/03_Excel_Deliveries/9_NBS_Accounts_Domestic_and_GNI.xlsx
@@ -512,7 +512,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28T18:49:53.220713+00:00</t>
+          <t>2026-08-28T20:13:47.903954+00:00</t>
         </is>
       </c>
     </row>
@@ -637,34 +637,34 @@
         </is>
       </c>
       <c r="C2" s="6" t="n">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D2" s="7" t="n">
-        <v>0</v>
+        <v>785823.08</v>
       </c>
       <c r="E2" s="7" t="n">
-        <v>996128.98</v>
+        <v>1286501.64</v>
       </c>
       <c r="F2" s="7" t="n">
         <v>39968.25</v>
       </c>
       <c r="G2" s="7" t="n">
-        <v>0</v>
+        <v>235746.91</v>
       </c>
       <c r="H2" s="7" t="n">
-        <v>1036097.22</v>
+        <v>2348039.94</v>
       </c>
       <c r="I2" s="6" t="n">
-        <v>1554145830</v>
+        <v>3522059910</v>
       </c>
       <c r="L2" s="6" t="n">
-        <v>465920000</v>
+        <v>470080000</v>
       </c>
       <c r="M2" s="7" t="n">
-        <v>310613.33</v>
+        <v>313386.67</v>
       </c>
       <c r="N2" s="6" t="n">
-        <v>1088225830</v>
+        <v>3051979910</v>
       </c>
     </row>
     <row r="3">
@@ -679,34 +679,34 @@
         </is>
       </c>
       <c r="C3" s="6" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D3" s="7" t="n">
-        <v>0</v>
+        <v>328694.8</v>
       </c>
       <c r="E3" s="7" t="n">
-        <v>150047.27</v>
+        <v>218017.95</v>
       </c>
       <c r="F3" s="7" t="n">
         <v>18481.94</v>
       </c>
       <c r="G3" s="7" t="n">
-        <v>0</v>
+        <v>98608.42999999999</v>
       </c>
       <c r="H3" s="7" t="n">
-        <v>168529.23</v>
+        <v>663803.16</v>
       </c>
       <c r="I3" s="6" t="n">
-        <v>252793845</v>
+        <v>995704740</v>
       </c>
       <c r="L3" s="6" t="n">
-        <v>81120000</v>
+        <v>83200000</v>
       </c>
       <c r="M3" s="7" t="n">
-        <v>54080</v>
+        <v>55466.67</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>171673845</v>
+        <v>912504740</v>
       </c>
     </row>
     <row r="4">
@@ -721,10 +721,10 @@
         </is>
       </c>
       <c r="C4" s="6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D4" s="7" t="n">
-        <v>0</v>
+        <v>909.79</v>
       </c>
       <c r="E4" s="7" t="n">
         <v>2719.41</v>
@@ -733,22 +733,22 @@
         <v>31.93</v>
       </c>
       <c r="G4" s="7" t="n">
-        <v>0</v>
+        <v>272.95</v>
       </c>
       <c r="H4" s="7" t="n">
-        <v>2751.34</v>
+        <v>3934.07</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>4127010</v>
+        <v>5901105</v>
       </c>
       <c r="L4" s="6" t="n">
-        <v>33280000</v>
+        <v>35360000</v>
       </c>
       <c r="M4" s="7" t="n">
-        <v>22186.67</v>
+        <v>23573.33</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>-29152990</v>
+        <v>-29458895</v>
       </c>
     </row>
     <row r="5">
@@ -769,7 +769,7 @@
         <v>1158908.69</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>1087027.9</v>
+        <v>1393734.89</v>
       </c>
       <c r="F5" s="7" t="n">
         <v>42745.73</v>
@@ -778,10 +778,10 @@
         <v>347672.68</v>
       </c>
       <c r="H5" s="7" t="n">
-        <v>2636354.87</v>
+        <v>2943061.87</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>3954532305</v>
+        <v>4414592805</v>
       </c>
       <c r="L5" s="6" t="n">
         <v>659360000</v>
@@ -790,7 +790,7 @@
         <v>439573.33</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>3295172305</v>
+        <v>3755232805</v>
       </c>
     </row>
     <row r="6">
@@ -811,7 +811,7 @@
         <v>448918.99</v>
       </c>
       <c r="E6" s="7" t="n">
-        <v>248766.49</v>
+        <v>301263.81</v>
       </c>
       <c r="F6" s="7" t="n">
         <v>18974.45</v>
@@ -820,10 +820,10 @@
         <v>134675.71</v>
       </c>
       <c r="H6" s="7" t="n">
-        <v>851335.59</v>
+        <v>903832.91</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>1277003385</v>
+        <v>1355749365</v>
       </c>
       <c r="L6" s="6" t="n">
         <v>147680000</v>
@@ -832,7 +832,7 @@
         <v>98453.33</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>1129323385</v>
+        <v>1208069365</v>
       </c>
     </row>
     <row r="7">
@@ -895,7 +895,7 @@
         <v>1648929.32</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>1172961.73</v>
+        <v>1666672.98</v>
       </c>
       <c r="F8" s="7" t="n">
         <v>55865.5</v>
@@ -904,10 +904,10 @@
         <v>494678.84</v>
       </c>
       <c r="H8" s="7" t="n">
-        <v>3372435.46</v>
+        <v>3866146.69</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>5058653190</v>
+        <v>5799220035</v>
       </c>
       <c r="L8" s="6" t="n">
         <v>723840000</v>
@@ -916,7 +916,7 @@
         <v>482560</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>4334813190</v>
+        <v>5075380035</v>
       </c>
     </row>
     <row r="9">
@@ -937,7 +937,7 @@
         <v>476500.37</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>254389.76</v>
+        <v>335648.64</v>
       </c>
       <c r="F9" s="7" t="n">
         <v>19688.62</v>
@@ -946,10 +946,10 @@
         <v>142950.09</v>
       </c>
       <c r="H9" s="7" t="n">
-        <v>893528.8</v>
+        <v>974787.67</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>1340293200</v>
+        <v>1462181505</v>
       </c>
       <c r="L9" s="6" t="n">
         <v>174720000</v>
@@ -958,7 +958,7 @@
         <v>116480</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>1165573200</v>
+        <v>1287461505</v>
       </c>
     </row>
     <row r="10">
@@ -1021,7 +1021,7 @@
         <v>1979440.3</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>1610658.32</v>
+        <v>2248340.15</v>
       </c>
       <c r="F11" s="7" t="n">
         <v>66819.48</v>
@@ -1030,10 +1030,10 @@
         <v>593831.9300000001</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>4250750.22</v>
+        <v>4888432.06</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>6376125330</v>
+        <v>7332648090</v>
       </c>
       <c r="L11" s="6" t="n">
         <v>736320000</v>
@@ -1042,7 +1042,7 @@
         <v>490880</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>5639805330</v>
+        <v>6596328090</v>
       </c>
     </row>
     <row r="12">
@@ -1063,7 +1063,7 @@
         <v>532221.88</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>260676.75</v>
+        <v>333264.07</v>
       </c>
       <c r="F12" s="7" t="n">
         <v>20756.08</v>
@@ -1072,10 +1072,10 @@
         <v>159666.63</v>
       </c>
       <c r="H12" s="7" t="n">
-        <v>973321.28</v>
+        <v>1045908.6</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>1459981920</v>
+        <v>1568862900</v>
       </c>
       <c r="L12" s="6" t="n">
         <v>176800000</v>
@@ -1084,7 +1084,7 @@
         <v>117866.67</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>1283181920</v>
+        <v>1392062900</v>
       </c>
     </row>
     <row r="13">
@@ -1147,7 +1147,7 @@
         <v>1927024.69</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>1723303.26</v>
+        <v>2077791.17</v>
       </c>
       <c r="F14" s="7" t="n">
         <v>77246.02</v>
@@ -1156,10 +1156,10 @@
         <v>578107.4399999999</v>
       </c>
       <c r="H14" s="7" t="n">
-        <v>4305681.34</v>
+        <v>4660169.26</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>6458522010</v>
+        <v>6990253890</v>
       </c>
       <c r="L14" s="6" t="n">
         <v>750880000</v>
@@ -1168,7 +1168,7 @@
         <v>500586.67</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>5707642010</v>
+        <v>6239373890</v>
       </c>
     </row>
     <row r="15">
@@ -1189,7 +1189,7 @@
         <v>630712.8199999999</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>264940.94</v>
+        <v>330334.7</v>
       </c>
       <c r="F15" s="7" t="n">
         <v>21736.2</v>
@@ -1198,10 +1198,10 @@
         <v>189213.84</v>
       </c>
       <c r="H15" s="7" t="n">
-        <v>1106603.78</v>
+        <v>1171997.54</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>1659905670</v>
+        <v>1757996310</v>
       </c>
       <c r="L15" s="6" t="n">
         <v>178880000</v>
@@ -1210,7 +1210,7 @@
         <v>119253.33</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>1481025670</v>
+        <v>1579116310</v>
       </c>
     </row>
     <row r="16">
@@ -1273,7 +1273,7 @@
         <v>2265971.02</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>1886501.7</v>
+        <v>2286773.03</v>
       </c>
       <c r="F17" s="7" t="n">
         <v>89097.19</v>
@@ -1282,10 +1282,10 @@
         <v>679791.3</v>
       </c>
       <c r="H17" s="7" t="n">
-        <v>4921361.17</v>
+        <v>5321632.5</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>7382041755</v>
+        <v>7982448750</v>
       </c>
       <c r="L17" s="6" t="n">
         <v>802880000</v>
@@ -1294,7 +1294,7 @@
         <v>535253.33</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>6579161755</v>
+        <v>7179568750</v>
       </c>
     </row>
     <row r="18">
@@ -1315,7 +1315,7 @@
         <v>707531.3199999999</v>
       </c>
       <c r="E18" s="7" t="n">
-        <v>271755.52</v>
+        <v>325861.7</v>
       </c>
       <c r="F18" s="7" t="n">
         <v>22720.03</v>
@@ -1324,10 +1324,10 @@
         <v>212259.44</v>
       </c>
       <c r="H18" s="7" t="n">
-        <v>1214266.36</v>
+        <v>1268372.55</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>1821399540</v>
+        <v>1902558825</v>
       </c>
       <c r="L18" s="6" t="n">
         <v>193440000</v>
@@ -1336,7 +1336,7 @@
         <v>128960</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>1627959540</v>
+        <v>1709118825</v>
       </c>
     </row>
     <row r="19">
@@ -1399,7 +1399,7 @@
         <v>2581135.11</v>
       </c>
       <c r="E20" s="7" t="n">
-        <v>2334856.21</v>
+        <v>2685417.57</v>
       </c>
       <c r="F20" s="7" t="n">
         <v>104788.44</v>
@@ -1408,10 +1408,10 @@
         <v>774340.54</v>
       </c>
       <c r="H20" s="7" t="n">
-        <v>5795120.34</v>
+        <v>6145681.66</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>8692680510</v>
+        <v>9218522490</v>
       </c>
       <c r="L20" s="6" t="n">
         <v>848640000</v>
@@ -1420,7 +1420,7 @@
         <v>565760</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>7844040510</v>
+        <v>8369882490</v>
       </c>
     </row>
     <row r="21">
@@ -1441,7 +1441,7 @@
         <v>728865.5699999999</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>283366.77</v>
+        <v>334441.37</v>
       </c>
       <c r="F21" s="7" t="n">
         <v>23878.73</v>
@@ -1450,10 +1450,10 @@
         <v>218659.68</v>
       </c>
       <c r="H21" s="7" t="n">
-        <v>1254770.84</v>
+        <v>1305845.43</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>1882156260</v>
+        <v>1958768145</v>
       </c>
       <c r="L21" s="6" t="n">
         <v>197600000</v>
@@ -1462,7 +1462,7 @@
         <v>131733.33</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>1684556260</v>
+        <v>1761168145</v>
       </c>
     </row>
     <row r="22">
@@ -1525,7 +1525,7 @@
         <v>2279842.09</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>2676644.25</v>
+        <v>3312261.02</v>
       </c>
       <c r="F23" s="7" t="n">
         <v>120783.98</v>
@@ -1534,10 +1534,10 @@
         <v>683952.67</v>
       </c>
       <c r="H23" s="7" t="n">
-        <v>5761223.06</v>
+        <v>6396839.84</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>8641834590</v>
+        <v>9595259760</v>
       </c>
       <c r="L23" s="6" t="n">
         <v>873600000</v>
@@ -1546,7 +1546,7 @@
         <v>582400</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>7768234590</v>
+        <v>8721659760</v>
       </c>
     </row>
     <row r="24">
@@ -1567,7 +1567,7 @@
         <v>1017953.85</v>
       </c>
       <c r="E24" s="7" t="n">
-        <v>336609.85</v>
+        <v>381423.59</v>
       </c>
       <c r="F24" s="7" t="n">
         <v>24846.67</v>
@@ -1576,10 +1576,10 @@
         <v>305386.13</v>
       </c>
       <c r="H24" s="7" t="n">
-        <v>1684796.48</v>
+        <v>1729610.2</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>2527194720</v>
+        <v>2594415300</v>
       </c>
       <c r="L24" s="6" t="n">
         <v>203840000</v>
@@ -1588,7 +1588,7 @@
         <v>135893.33</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>2323354720</v>
+        <v>2390575300</v>
       </c>
     </row>
     <row r="25">
@@ -1651,7 +1651,7 @@
         <v>2698296.15</v>
       </c>
       <c r="E26" s="7" t="n">
-        <v>3139439.22</v>
+        <v>3334436.3</v>
       </c>
       <c r="F26" s="7" t="n">
         <v>135947.53</v>
@@ -1660,16 +1660,16 @@
         <v>809489.02</v>
       </c>
       <c r="H26" s="7" t="n">
-        <v>6783171.76</v>
+        <v>6978168.86</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>10174757640</v>
+        <v>10467253290</v>
       </c>
       <c r="J26" s="7" t="n">
-        <v>283506.52</v>
+        <v>290110.74</v>
       </c>
       <c r="K26" s="7" t="n">
-        <v>6499665.28</v>
+        <v>6688058.17</v>
       </c>
       <c r="L26" s="6" t="n">
         <v>886080000</v>
@@ -1678,7 +1678,7 @@
         <v>590720</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>9288677640</v>
+        <v>9581173290</v>
       </c>
     </row>
     <row r="27">
@@ -1699,7 +1699,7 @@
         <v>958995.3199999999</v>
       </c>
       <c r="E27" s="7" t="n">
-        <v>340604.64</v>
+        <v>391613.19</v>
       </c>
       <c r="F27" s="7" t="n">
         <v>25717.39</v>
@@ -1708,16 +1708,16 @@
         <v>287698.63</v>
       </c>
       <c r="H27" s="7" t="n">
-        <v>1613016.02</v>
+        <v>1664024.57</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>2419524030</v>
+        <v>2496036855</v>
       </c>
       <c r="J27" s="7" t="n">
-        <v>42680.65</v>
+        <v>44691.39</v>
       </c>
       <c r="K27" s="7" t="n">
-        <v>1570335.38</v>
+        <v>1619333.19</v>
       </c>
       <c r="L27" s="6" t="n">
         <v>210080000</v>
@@ -1726,7 +1726,7 @@
         <v>140053.33</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>2209444030</v>
+        <v>2285956855</v>
       </c>
     </row>
     <row r="28">
@@ -1795,7 +1795,7 @@
         <v>2896002.93</v>
       </c>
       <c r="E29" s="7" t="n">
-        <v>3574925.78</v>
+        <v>3710377.41</v>
       </c>
       <c r="F29" s="7" t="n">
         <v>150010.07</v>
@@ -1804,16 +1804,16 @@
         <v>868800.98</v>
       </c>
       <c r="H29" s="7" t="n">
-        <v>7489739.84</v>
+        <v>7625191.47</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>11234609760</v>
+        <v>11437787205</v>
       </c>
       <c r="J29" s="7" t="n">
-        <v>301869.36</v>
+        <v>305605.32</v>
       </c>
       <c r="K29" s="7" t="n">
-        <v>7187870.59</v>
+        <v>7319586.27</v>
       </c>
       <c r="L29" s="6" t="n">
         <v>904800000</v>
@@ -1822,7 +1822,7 @@
         <v>603200</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>10329809760</v>
+        <v>10532987205</v>
       </c>
     </row>
     <row r="30">
@@ -1843,7 +1843,7 @@
         <v>1563473.58</v>
       </c>
       <c r="E30" s="7" t="n">
-        <v>342527.37</v>
+        <v>411657.78</v>
       </c>
       <c r="F30" s="7" t="n">
         <v>26624.46</v>
@@ -1852,16 +1852,16 @@
         <v>469042.06</v>
       </c>
       <c r="H30" s="7" t="n">
-        <v>2401667.52</v>
+        <v>2470797.93</v>
       </c>
       <c r="I30" s="6" t="n">
-        <v>3602501280</v>
+        <v>3706196895</v>
       </c>
       <c r="J30" s="7" t="n">
-        <v>31526.46</v>
+        <v>33319.28</v>
       </c>
       <c r="K30" s="7" t="n">
-        <v>2370141.02</v>
+        <v>2437478.61</v>
       </c>
       <c r="L30" s="6" t="n">
         <v>212160000</v>
@@ -1870,7 +1870,7 @@
         <v>141440</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>3390341280</v>
+        <v>3494036895</v>
       </c>
     </row>
     <row r="31">
@@ -1939,7 +1939,7 @@
         <v>4526301.09</v>
       </c>
       <c r="E32" s="7" t="n">
-        <v>3922000.16</v>
+        <v>4074651.28</v>
       </c>
       <c r="F32" s="7" t="n">
         <v>164363.14</v>
@@ -1948,16 +1948,16 @@
         <v>1357890.32</v>
       </c>
       <c r="H32" s="7" t="n">
-        <v>9970554.699999999</v>
+        <v>10123205.83</v>
       </c>
       <c r="I32" s="6" t="n">
-        <v>14955832050</v>
+        <v>15184808745</v>
       </c>
       <c r="J32" s="7" t="n">
-        <v>432005.99</v>
+        <v>437614.49</v>
       </c>
       <c r="K32" s="7" t="n">
-        <v>9538548.76</v>
+        <v>9685591.42</v>
       </c>
       <c r="L32" s="6" t="n">
         <v>911040000</v>
@@ -1966,7 +1966,7 @@
         <v>607360</v>
       </c>
       <c r="N32" s="6" t="n">
-        <v>14044792050</v>
+        <v>14273768745</v>
       </c>
     </row>
     <row r="33">
@@ -1987,7 +1987,7 @@
         <v>1337179.69</v>
       </c>
       <c r="E33" s="7" t="n">
-        <v>347325.59</v>
+        <v>477628.47</v>
       </c>
       <c r="F33" s="7" t="n">
         <v>27589.82</v>
@@ -1996,16 +1996,16 @@
         <v>401153.89</v>
       </c>
       <c r="H33" s="7" t="n">
-        <v>2113248.95</v>
+        <v>2243551.83</v>
       </c>
       <c r="I33" s="6" t="n">
-        <v>3169873425</v>
+        <v>3365327745</v>
       </c>
       <c r="J33" s="7" t="n">
-        <v>48727.13</v>
+        <v>52531.94</v>
       </c>
       <c r="K33" s="7" t="n">
-        <v>2064521.83</v>
+        <v>2191019.89</v>
       </c>
       <c r="L33" s="6" t="n">
         <v>218400000</v>
@@ -2014,7 +2014,7 @@
         <v>145600</v>
       </c>
       <c r="N33" s="6" t="n">
-        <v>2951473425</v>
+        <v>3146927745</v>
       </c>
     </row>
     <row r="34">
@@ -2083,7 +2083,7 @@
         <v>5167783.04</v>
       </c>
       <c r="E35" s="7" t="n">
-        <v>6025842.92</v>
+        <v>6120897.06</v>
       </c>
       <c r="F35" s="7" t="n">
         <v>179743.67</v>
@@ -2092,16 +2092,16 @@
         <v>1550334.92</v>
       </c>
       <c r="H35" s="7" t="n">
-        <v>12923704.55</v>
+        <v>13018758.65</v>
       </c>
       <c r="I35" s="6" t="n">
-        <v>19385556825</v>
+        <v>19528137975</v>
       </c>
       <c r="J35" s="7" t="n">
-        <v>795675.61</v>
+        <v>803532.39</v>
       </c>
       <c r="K35" s="7" t="n">
-        <v>12128028.8</v>
+        <v>12215226.14</v>
       </c>
       <c r="L35" s="6" t="n">
         <v>938080000</v>
@@ -2110,7 +2110,7 @@
         <v>625386.67</v>
       </c>
       <c r="N35" s="6" t="n">
-        <v>18447476825</v>
+        <v>18590057975</v>
       </c>
     </row>
     <row r="36">
@@ -2131,7 +2131,7 @@
         <v>1649056.45</v>
       </c>
       <c r="E36" s="7" t="n">
-        <v>516517.11</v>
+        <v>521716.09</v>
       </c>
       <c r="F36" s="7" t="n">
         <v>28516.67</v>
@@ -2140,16 +2140,16 @@
         <v>494716.91</v>
       </c>
       <c r="H36" s="7" t="n">
-        <v>2688807.14</v>
+        <v>2694006.12</v>
       </c>
       <c r="I36" s="6" t="n">
-        <v>4033210710</v>
+        <v>4041009180</v>
       </c>
       <c r="J36" s="7" t="n">
-        <v>61076.62</v>
+        <v>61636.71</v>
       </c>
       <c r="K36" s="7" t="n">
-        <v>2627730.51</v>
+        <v>2632369.41</v>
       </c>
       <c r="L36" s="6" t="n">
         <v>218400000</v>
@@ -2158,7 +2158,7 @@
         <v>145600</v>
       </c>
       <c r="N36" s="6" t="n">
-        <v>3814810710</v>
+        <v>3822609180</v>
       </c>
     </row>
     <row r="37">
@@ -2227,7 +2227,7 @@
         <v>5990704.91</v>
       </c>
       <c r="E38" s="7" t="n">
-        <v>5205248.74</v>
+        <v>5398930.72</v>
       </c>
       <c r="F38" s="7" t="n">
         <v>194162.12</v>
@@ -2236,16 +2236,16 @@
         <v>1797211.59</v>
       </c>
       <c r="H38" s="7" t="n">
-        <v>13187327.41</v>
+        <v>13381009.4</v>
       </c>
       <c r="I38" s="6" t="n">
-        <v>19780991115</v>
+        <v>20071514100</v>
       </c>
       <c r="J38" s="7" t="n">
-        <v>783885.59</v>
+        <v>784624.74</v>
       </c>
       <c r="K38" s="7" t="n">
-        <v>12403441.6</v>
+        <v>12596384.45</v>
       </c>
       <c r="L38" s="6" t="n">
         <v>950560000</v>
@@ -2254,7 +2254,7 @@
         <v>633706.67</v>
       </c>
       <c r="N38" s="6" t="n">
-        <v>18830431115</v>
+        <v>19120954100</v>
       </c>
     </row>
     <row r="39">
@@ -2275,7 +2275,7 @@
         <v>1526592.02</v>
       </c>
       <c r="E39" s="7" t="n">
-        <v>682820.25</v>
+        <v>690705.9399999999</v>
       </c>
       <c r="F39" s="7" t="n">
         <v>29730.81</v>
@@ -2284,16 +2284,16 @@
         <v>457977.63</v>
       </c>
       <c r="H39" s="7" t="n">
-        <v>2697120.75</v>
+        <v>2705006.45</v>
       </c>
       <c r="I39" s="6" t="n">
-        <v>4045681125</v>
+        <v>4057509675</v>
       </c>
       <c r="J39" s="7" t="n">
-        <v>85588.31</v>
+        <v>86535.99000000001</v>
       </c>
       <c r="K39" s="7" t="n">
-        <v>2611532.4</v>
+        <v>2618470.41</v>
       </c>
       <c r="L39" s="6" t="n">
         <v>222560000</v>
@@ -2302,7 +2302,7 @@
         <v>148373.33</v>
       </c>
       <c r="N39" s="6" t="n">
-        <v>3823121125</v>
+        <v>3834949675</v>
       </c>
     </row>
     <row r="40">
@@ -2371,7 +2371,7 @@
         <v>6787044.27</v>
       </c>
       <c r="E41" s="7" t="n">
-        <v>5745823.71</v>
+        <v>5783265.17</v>
       </c>
       <c r="F41" s="7" t="n">
         <v>201947.05</v>
@@ -2380,16 +2380,16 @@
         <v>2036113.31</v>
       </c>
       <c r="H41" s="7" t="n">
-        <v>14770928.4</v>
+        <v>14808369.87</v>
       </c>
       <c r="I41" s="6" t="n">
-        <v>22156392600</v>
+        <v>22212554805</v>
       </c>
       <c r="J41" s="7" t="n">
-        <v>922799.16</v>
+        <v>924903.63</v>
       </c>
       <c r="K41" s="7" t="n">
-        <v>13848129.18</v>
+        <v>13883466.15</v>
       </c>
       <c r="L41" s="6" t="n">
         <v>958880000</v>
@@ -2398,7 +2398,7 @@
         <v>639253.33</v>
       </c>
       <c r="N41" s="6" t="n">
-        <v>21197512600</v>
+        <v>21253674805</v>
       </c>
     </row>
     <row r="42">
@@ -2419,7 +2419,7 @@
         <v>1510912.47</v>
       </c>
       <c r="E42" s="7" t="n">
-        <v>692126.26</v>
+        <v>604806.99</v>
       </c>
       <c r="F42" s="7" t="n">
         <v>30670.68</v>
@@ -2428,16 +2428,16 @@
         <v>453273.77</v>
       </c>
       <c r="H42" s="7" t="n">
-        <v>2686983.19</v>
+        <v>2599663.92</v>
       </c>
       <c r="I42" s="6" t="n">
-        <v>4030474785</v>
+        <v>3899495880</v>
       </c>
       <c r="J42" s="7" t="n">
-        <v>122563.74</v>
+        <v>118882.04</v>
       </c>
       <c r="K42" s="7" t="n">
-        <v>2564419.51</v>
+        <v>2480781.95</v>
       </c>
       <c r="L42" s="6" t="n">
         <v>222560000</v>
@@ -2446,7 +2446,7 @@
         <v>148373.33</v>
       </c>
       <c r="N42" s="6" t="n">
-        <v>3807914785</v>
+        <v>3676935880</v>
       </c>
     </row>
     <row r="43">
@@ -2515,7 +2515,7 @@
         <v>7910499.2</v>
       </c>
       <c r="E44" s="7" t="n">
-        <v>7416785.27</v>
+        <v>7479496.73</v>
       </c>
       <c r="F44" s="7" t="n">
         <v>208194.32</v>
@@ -2524,16 +2524,16 @@
         <v>2373149.74</v>
       </c>
       <c r="H44" s="7" t="n">
-        <v>17908628.58</v>
+        <v>17971340.03</v>
       </c>
       <c r="I44" s="6" t="n">
-        <v>26862942870</v>
+        <v>26957010045</v>
       </c>
       <c r="J44" s="7" t="n">
-        <v>1022202.52</v>
+        <v>1025380.55</v>
       </c>
       <c r="K44" s="7" t="n">
-        <v>16886426.07</v>
+        <v>16945959.49</v>
       </c>
       <c r="L44" s="6" t="n">
         <v>981760000</v>
@@ -2542,7 +2542,7 @@
         <v>654506.67</v>
       </c>
       <c r="N44" s="6" t="n">
-        <v>25881182870</v>
+        <v>25975250045</v>
       </c>
     </row>
     <row r="45">
@@ -2563,7 +2563,7 @@
         <v>1798208.88</v>
       </c>
       <c r="E45" s="7" t="n">
-        <v>773565.98</v>
+        <v>789224.41</v>
       </c>
       <c r="F45" s="7" t="n">
         <v>31487.49</v>
@@ -2572,16 +2572,16 @@
         <v>539462.67</v>
       </c>
       <c r="H45" s="7" t="n">
-        <v>3142724.98</v>
+        <v>3158383.42</v>
       </c>
       <c r="I45" s="6" t="n">
-        <v>4714087470</v>
+        <v>4737575130</v>
       </c>
       <c r="J45" s="7" t="n">
-        <v>122286.86</v>
+        <v>124276.8</v>
       </c>
       <c r="K45" s="7" t="n">
-        <v>3020438.11</v>
+        <v>3034106.6</v>
       </c>
       <c r="L45" s="6" t="n">
         <v>226720000</v>
@@ -2590,7 +2590,7 @@
         <v>151146.67</v>
       </c>
       <c r="N45" s="6" t="n">
-        <v>4487367470</v>
+        <v>4510855130</v>
       </c>
     </row>
     <row r="46">
@@ -2659,7 +2659,7 @@
         <v>8820132.970000001</v>
       </c>
       <c r="E47" s="7" t="n">
-        <v>7369801.54</v>
+        <v>7530257.12</v>
       </c>
       <c r="F47" s="7" t="n">
         <v>213439.62</v>
@@ -2668,16 +2668,16 @@
         <v>2646039.91</v>
       </c>
       <c r="H47" s="7" t="n">
-        <v>19049414.09</v>
+        <v>19209869.69</v>
       </c>
       <c r="I47" s="6" t="n">
-        <v>28574121135</v>
+        <v>28814804535</v>
       </c>
       <c r="J47" s="7" t="n">
-        <v>1353247.79</v>
+        <v>1374258.37</v>
       </c>
       <c r="K47" s="7" t="n">
-        <v>17696166.33</v>
+        <v>17835611.33</v>
       </c>
       <c r="L47" s="6" t="n">
         <v>994240000</v>
@@ -2686,7 +2686,7 @@
         <v>662826.67</v>
       </c>
       <c r="N47" s="6" t="n">
-        <v>27579881135</v>
+        <v>27820564535</v>
       </c>
     </row>
     <row r="48">
@@ -2707,7 +2707,7 @@
         <v>1806877.16</v>
       </c>
       <c r="E48" s="7" t="n">
-        <v>902640.3100000001</v>
+        <v>889563.61</v>
       </c>
       <c r="F48" s="7" t="n">
         <v>32203.02</v>
@@ -2716,16 +2716,16 @@
         <v>542063.13</v>
       </c>
       <c r="H48" s="7" t="n">
-        <v>3283783.72</v>
+        <v>3270707.02</v>
       </c>
       <c r="I48" s="6" t="n">
-        <v>4925675580</v>
+        <v>4906060530</v>
       </c>
       <c r="J48" s="7" t="n">
-        <v>178565.3</v>
+        <v>173189.5</v>
       </c>
       <c r="K48" s="7" t="n">
-        <v>3105218.27</v>
+        <v>3097517.37</v>
       </c>
       <c r="L48" s="6" t="n">
         <v>230880000</v>
@@ -2734,7 +2734,7 @@
         <v>153920</v>
       </c>
       <c r="N48" s="6" t="n">
-        <v>4694795580</v>
+        <v>4675180530</v>
       </c>
     </row>
     <row r="49">
@@ -2803,7 +2803,7 @@
         <v>10242978.78</v>
       </c>
       <c r="E50" s="7" t="n">
-        <v>7113309.54</v>
+        <v>7051877.6</v>
       </c>
       <c r="F50" s="7" t="n">
         <v>218092</v>
@@ -2812,16 +2812,16 @@
         <v>3072893.64</v>
       </c>
       <c r="H50" s="7" t="n">
-        <v>20647274.01</v>
+        <v>20585842.07</v>
       </c>
       <c r="I50" s="6" t="n">
-        <v>30970911015</v>
+        <v>30878763105</v>
       </c>
       <c r="J50" s="7" t="n">
-        <v>1973748.86</v>
+        <v>1941506.83</v>
       </c>
       <c r="K50" s="7" t="n">
-        <v>18673525.17</v>
+        <v>18644335.28</v>
       </c>
       <c r="L50" s="6" t="n">
         <v>1006720000</v>
@@ -2830,7 +2830,7 @@
         <v>671146.67</v>
       </c>
       <c r="N50" s="6" t="n">
-        <v>29964191015</v>
+        <v>29872043105</v>
       </c>
     </row>
     <row r="51">
@@ -2851,7 +2851,7 @@
         <v>2368422.53</v>
       </c>
       <c r="E51" s="7" t="n">
-        <v>783464.6800000001</v>
+        <v>779838.72</v>
       </c>
       <c r="F51" s="7" t="n">
         <v>32825.93</v>
@@ -2860,16 +2860,16 @@
         <v>710526.73</v>
       </c>
       <c r="H51" s="7" t="n">
-        <v>3895239.9</v>
+        <v>3891613.95</v>
       </c>
       <c r="I51" s="6" t="n">
-        <v>5842859850</v>
+        <v>5837420925</v>
       </c>
       <c r="J51" s="7" t="n">
-        <v>225279.8</v>
+        <v>225014.05</v>
       </c>
       <c r="K51" s="7" t="n">
-        <v>3669960.02</v>
+        <v>3666599.82</v>
       </c>
       <c r="L51" s="6" t="n">
         <v>228800000</v>
@@ -2878,7 +2878,7 @@
         <v>152533.33</v>
       </c>
       <c r="N51" s="6" t="n">
-        <v>5614059850</v>
+        <v>5608620925</v>
       </c>
     </row>
     <row r="52">
@@ -2947,7 +2947,7 @@
         <v>12253435.18</v>
       </c>
       <c r="E53" s="7" t="n">
-        <v>8523117.140000001</v>
+        <v>7877503.91</v>
       </c>
       <c r="F53" s="7" t="n">
         <v>222615.46</v>
@@ -2956,16 +2956,16 @@
         <v>3676030.57</v>
       </c>
       <c r="H53" s="7" t="n">
-        <v>24675198.18</v>
+        <v>24029584.93</v>
       </c>
       <c r="I53" s="6" t="n">
-        <v>37012797270</v>
+        <v>36044377395</v>
       </c>
       <c r="J53" s="7" t="n">
-        <v>2904548.75</v>
+        <v>2711494.59</v>
       </c>
       <c r="K53" s="7" t="n">
-        <v>21770649.48</v>
+        <v>21318090.42</v>
       </c>
       <c r="L53" s="6" t="n">
         <v>1027520000</v>
@@ -2974,7 +2974,7 @@
         <v>685013.33</v>
       </c>
       <c r="N53" s="6" t="n">
-        <v>35985277270</v>
+        <v>35016857395</v>
       </c>
     </row>
     <row r="54">
@@ -2995,7 +2995,7 @@
         <v>2837075.09</v>
       </c>
       <c r="E54" s="7" t="n">
-        <v>1397796.47</v>
+        <v>1391262.79</v>
       </c>
       <c r="F54" s="7" t="n">
         <v>33473.33</v>
@@ -3004,16 +3004,16 @@
         <v>851122.53</v>
       </c>
       <c r="H54" s="7" t="n">
-        <v>5119467.45</v>
+        <v>5112933.77</v>
       </c>
       <c r="I54" s="6" t="n">
-        <v>7679201175</v>
+        <v>7669400655</v>
       </c>
       <c r="J54" s="7" t="n">
-        <v>277785.15</v>
+        <v>276675.37</v>
       </c>
       <c r="K54" s="7" t="n">
-        <v>4841682.38</v>
+        <v>4836258.47</v>
       </c>
       <c r="L54" s="6" t="n">
         <v>235040000</v>
@@ -3022,7 +3022,7 @@
         <v>156693.33</v>
       </c>
       <c r="N54" s="6" t="n">
-        <v>7444161175</v>
+        <v>7434360655</v>
       </c>
     </row>
     <row r="55">
@@ -3091,7 +3091,7 @@
         <v>11573147.47</v>
       </c>
       <c r="E56" s="7" t="n">
-        <v>7121667.29</v>
+        <v>7133093.46</v>
       </c>
       <c r="F56" s="7" t="n">
         <v>227250.03</v>
@@ -3100,16 +3100,16 @@
         <v>3471944.24</v>
       </c>
       <c r="H56" s="7" t="n">
-        <v>22394009.16</v>
+        <v>22405435.29</v>
       </c>
       <c r="I56" s="6" t="n">
-        <v>33591013740</v>
+        <v>33608152935</v>
       </c>
       <c r="J56" s="7" t="n">
-        <v>3355142.06</v>
+        <v>3338859.78</v>
       </c>
       <c r="K56" s="7" t="n">
-        <v>19038866.91</v>
+        <v>19066575.34</v>
       </c>
       <c r="L56" s="6" t="n">
         <v>1025440000</v>
@@ -3118,7 +3118,7 @@
         <v>683626.67</v>
       </c>
       <c r="N56" s="6" t="n">
-        <v>32565573740</v>
+        <v>32582712935</v>
       </c>
     </row>
     <row r="57">
@@ -3139,7 +3139,7 @@
         <v>2736178.63</v>
       </c>
       <c r="E57" s="7" t="n">
-        <v>1274189.45</v>
+        <v>1254148.88</v>
       </c>
       <c r="F57" s="7" t="n">
         <v>34184.81</v>
@@ -3148,16 +3148,16 @@
         <v>820853.59</v>
       </c>
       <c r="H57" s="7" t="n">
-        <v>4865406.41</v>
+        <v>4845365.83</v>
       </c>
       <c r="I57" s="6" t="n">
-        <v>7298109615</v>
+        <v>7268048745</v>
       </c>
       <c r="J57" s="7" t="n">
-        <v>375943.42</v>
+        <v>373950.84</v>
       </c>
       <c r="K57" s="7" t="n">
-        <v>4489462.98</v>
+        <v>4471415</v>
       </c>
       <c r="L57" s="6" t="n">
         <v>235040000</v>
@@ -3166,7 +3166,7 @@
         <v>156693.33</v>
       </c>
       <c r="N57" s="6" t="n">
-        <v>7063069615</v>
+        <v>7033008745</v>
       </c>
     </row>
     <row r="58">
@@ -3235,7 +3235,7 @@
         <v>12081945.7</v>
       </c>
       <c r="E59" s="7" t="n">
-        <v>7069903.73</v>
+        <v>7166542.4</v>
       </c>
       <c r="F59" s="7" t="n">
         <v>232074.24</v>
@@ -3244,16 +3244,16 @@
         <v>3624583.79</v>
       </c>
       <c r="H59" s="7" t="n">
-        <v>23008507.4</v>
+        <v>23105146.04</v>
       </c>
       <c r="I59" s="6" t="n">
-        <v>34512761100</v>
+        <v>34657719060</v>
       </c>
       <c r="J59" s="7" t="n">
-        <v>4626594.59</v>
+        <v>4652166.29</v>
       </c>
       <c r="K59" s="7" t="n">
-        <v>18381912.97</v>
+        <v>18452979.89</v>
       </c>
       <c r="L59" s="6" t="n">
         <v>1031680000</v>
@@ -3262,7 +3262,7 @@
         <v>687786.67</v>
       </c>
       <c r="N59" s="6" t="n">
-        <v>33481081100</v>
+        <v>33626039060</v>
       </c>
     </row>
     <row r="60">
@@ -3283,7 +3283,7 @@
         <v>2570965.9</v>
       </c>
       <c r="E60" s="7" t="n">
-        <v>1123256.37</v>
+        <v>1124822.11</v>
       </c>
       <c r="F60" s="7" t="n">
         <v>35024.24</v>
@@ -3292,16 +3292,16 @@
         <v>771289.75</v>
       </c>
       <c r="H60" s="7" t="n">
-        <v>4500536.27</v>
+        <v>4502102.01</v>
       </c>
       <c r="I60" s="6" t="n">
-        <v>6750804405</v>
+        <v>6753153015</v>
       </c>
       <c r="J60" s="7" t="n">
-        <v>495886.43</v>
+        <v>496430.87</v>
       </c>
       <c r="K60" s="7" t="n">
-        <v>4004649.78</v>
+        <v>4005671.08</v>
       </c>
       <c r="L60" s="6" t="n">
         <v>235040000</v>
@@ -3310,7 +3310,7 @@
         <v>156693.33</v>
       </c>
       <c r="N60" s="6" t="n">
-        <v>6515764405</v>
+        <v>6518113015</v>
       </c>
     </row>
     <row r="61">
@@ -3379,7 +3379,7 @@
         <v>11850520.38</v>
       </c>
       <c r="E62" s="7" t="n">
-        <v>7327606.83</v>
+        <v>7423596.49</v>
       </c>
       <c r="F62" s="7" t="n">
         <v>237674.94</v>
@@ -3388,16 +3388,16 @@
         <v>3555156.21</v>
       </c>
       <c r="H62" s="7" t="n">
-        <v>22970958.5</v>
+        <v>23066948.14</v>
       </c>
       <c r="I62" s="6" t="n">
-        <v>34456437750</v>
+        <v>34600422210</v>
       </c>
       <c r="J62" s="7" t="n">
-        <v>4730002.66</v>
+        <v>4768382.19</v>
       </c>
       <c r="K62" s="7" t="n">
-        <v>18240955.78</v>
+        <v>18298565.86</v>
       </c>
       <c r="L62" s="6" t="n">
         <v>1044160000</v>
@@ -3406,7 +3406,7 @@
         <v>696106.67</v>
       </c>
       <c r="N62" s="6" t="n">
-        <v>33412277750</v>
+        <v>33556262210</v>
       </c>
     </row>
     <row r="63">
@@ -3427,7 +3427,7 @@
         <v>2913889.95</v>
       </c>
       <c r="E63" s="7" t="n">
-        <v>1222164.2</v>
+        <v>1224206.63</v>
       </c>
       <c r="F63" s="7" t="n">
         <v>35864.78</v>
@@ -3436,16 +3436,16 @@
         <v>874166.98</v>
       </c>
       <c r="H63" s="7" t="n">
-        <v>5046085.9</v>
+        <v>5048128.32</v>
       </c>
       <c r="I63" s="6" t="n">
-        <v>7569128850</v>
+        <v>7572192480</v>
       </c>
       <c r="J63" s="7" t="n">
-        <v>587387.05</v>
+        <v>588085.6</v>
       </c>
       <c r="K63" s="7" t="n">
-        <v>4458698.85</v>
+        <v>4460042.73</v>
       </c>
       <c r="L63" s="6" t="n">
         <v>235040000</v>
@@ -3454,7 +3454,7 @@
         <v>156693.33</v>
       </c>
       <c r="N63" s="6" t="n">
-        <v>7334088850</v>
+        <v>7337152480</v>
       </c>
     </row>
     <row r="64">
@@ -3523,7 +3523,7 @@
         <v>13194146.48</v>
       </c>
       <c r="E65" s="7" t="n">
-        <v>8679051.300000001</v>
+        <v>8666427.699999999</v>
       </c>
       <c r="F65" s="7" t="n">
         <v>243618.46</v>
@@ -3532,16 +3532,16 @@
         <v>3958244</v>
       </c>
       <c r="H65" s="7" t="n">
-        <v>26075060.12</v>
+        <v>26062436.52</v>
       </c>
       <c r="I65" s="6" t="n">
-        <v>39112590180</v>
+        <v>39093654780</v>
       </c>
       <c r="J65" s="7" t="n">
-        <v>6536787.13</v>
+        <v>6524379.07</v>
       </c>
       <c r="K65" s="7" t="n">
-        <v>19538273.08</v>
+        <v>19538057.56</v>
       </c>
       <c r="L65" s="6" t="n">
         <v>1058720000</v>
@@ -3550,7 +3550,7 @@
         <v>705813.33</v>
       </c>
       <c r="N65" s="6" t="n">
-        <v>38053870180</v>
+        <v>38034934780</v>
       </c>
     </row>
     <row r="66">
@@ -3571,7 +3571,7 @@
         <v>3040159.31</v>
       </c>
       <c r="E66" s="7" t="n">
-        <v>1185044.24</v>
+        <v>1187199.7</v>
       </c>
       <c r="F66" s="7" t="n">
         <v>36607.29</v>
@@ -3580,16 +3580,16 @@
         <v>912047.78</v>
       </c>
       <c r="H66" s="7" t="n">
-        <v>5173858.67</v>
+        <v>5176014.14</v>
       </c>
       <c r="I66" s="6" t="n">
-        <v>7760788005</v>
+        <v>7764021210</v>
       </c>
       <c r="J66" s="7" t="n">
-        <v>807425.25</v>
+        <v>808298.6800000001</v>
       </c>
       <c r="K66" s="7" t="n">
-        <v>4366433.45</v>
+        <v>4367715.46</v>
       </c>
       <c r="L66" s="6" t="n">
         <v>237120000</v>
@@ -3598,7 +3598,7 @@
         <v>158080</v>
       </c>
       <c r="N66" s="6" t="n">
-        <v>7523668005</v>
+        <v>7526901210</v>
       </c>
     </row>
     <row r="67">
@@ -3619,7 +3619,7 @@
         <v>25170.04</v>
       </c>
       <c r="E67" s="7" t="n">
-        <v>2254.36</v>
+        <v>2289.25</v>
       </c>
       <c r="F67" s="7" t="n">
         <v>214.47</v>
@@ -3628,16 +3628,16 @@
         <v>7551.02</v>
       </c>
       <c r="H67" s="7" t="n">
-        <v>35189.92</v>
+        <v>35224.81</v>
       </c>
       <c r="I67" s="6" t="n">
-        <v>52784880</v>
+        <v>52837215</v>
       </c>
       <c r="J67" s="7" t="n">
-        <v>20299.56</v>
+        <v>20301.78</v>
       </c>
       <c r="K67" s="7" t="n">
-        <v>14890.37</v>
+        <v>14923.04</v>
       </c>
       <c r="L67" s="6" t="n">
         <v>143520000</v>
@@ -3646,7 +3646,7 @@
         <v>95680</v>
       </c>
       <c r="N67" s="6" t="n">
-        <v>-90735120</v>
+        <v>-90682785</v>
       </c>
     </row>
     <row r="68">
@@ -3667,7 +3667,7 @@
         <v>13260604.91</v>
       </c>
       <c r="E68" s="7" t="n">
-        <v>10277820.09</v>
+        <v>10181784.93</v>
       </c>
       <c r="F68" s="7" t="n">
         <v>249498.18</v>
@@ -3676,16 +3676,16 @@
         <v>3978181.47</v>
       </c>
       <c r="H68" s="7" t="n">
-        <v>27766104.85</v>
+        <v>27670069.7</v>
       </c>
       <c r="I68" s="6" t="n">
-        <v>41649157275</v>
+        <v>41505104550</v>
       </c>
       <c r="J68" s="7" t="n">
-        <v>7812160.74</v>
+        <v>7771578.58</v>
       </c>
       <c r="K68" s="7" t="n">
-        <v>19953944.14</v>
+        <v>19898491.14</v>
       </c>
       <c r="L68" s="6" t="n">
         <v>1062880000</v>
@@ -3694,7 +3694,7 @@
         <v>708586.67</v>
       </c>
       <c r="N68" s="6" t="n">
-        <v>40586277275</v>
+        <v>40442224550</v>
       </c>
     </row>
     <row r="69">
@@ -3715,7 +3715,7 @@
         <v>4203926.92</v>
       </c>
       <c r="E69" s="7" t="n">
-        <v>1303598.5</v>
+        <v>1305734.53</v>
       </c>
       <c r="F69" s="7" t="n">
         <v>37322.83</v>
@@ -3724,16 +3724,16 @@
         <v>1261178.07</v>
       </c>
       <c r="H69" s="7" t="n">
-        <v>6806026.38</v>
+        <v>6808162.41</v>
       </c>
       <c r="I69" s="6" t="n">
-        <v>10209039570</v>
+        <v>10212243615</v>
       </c>
       <c r="J69" s="7" t="n">
-        <v>853836.95</v>
+        <v>854622.87</v>
       </c>
       <c r="K69" s="7" t="n">
-        <v>5952189.41</v>
+        <v>5953539.52</v>
       </c>
       <c r="L69" s="6" t="n">
         <v>237120000</v>
@@ -3742,7 +3742,7 @@
         <v>158080</v>
       </c>
       <c r="N69" s="6" t="n">
-        <v>9971919570</v>
+        <v>9975123615</v>
       </c>
     </row>
     <row r="70">
@@ -3763,7 +3763,7 @@
         <v>26528.96</v>
       </c>
       <c r="E70" s="7" t="n">
-        <v>2713.24</v>
+        <v>3379.37</v>
       </c>
       <c r="F70" s="7" t="n">
         <v>216.14</v>
@@ -3772,16 +3772,16 @@
         <v>7958.67</v>
       </c>
       <c r="H70" s="7" t="n">
-        <v>37416.98</v>
+        <v>38083.12</v>
       </c>
       <c r="I70" s="6" t="n">
-        <v>56125470</v>
+        <v>57124680</v>
       </c>
       <c r="J70" s="7" t="n">
-        <v>20292.99</v>
+        <v>20348.28</v>
       </c>
       <c r="K70" s="7" t="n">
-        <v>17124.03</v>
+        <v>17734.86</v>
       </c>
       <c r="L70" s="6" t="n">
         <v>147680000</v>
@@ -3790,7 +3790,7 @@
         <v>98453.33</v>
       </c>
       <c r="N70" s="6" t="n">
-        <v>-91554530</v>
+        <v>-90555320</v>
       </c>
     </row>
     <row r="71">
@@ -3811,7 +3811,7 @@
         <v>14151253.03</v>
       </c>
       <c r="E71" s="7" t="n">
-        <v>10133341.01</v>
+        <v>10084842.63</v>
       </c>
       <c r="F71" s="7" t="n">
         <v>252130.39</v>
@@ -3820,16 +3820,16 @@
         <v>4245375.88</v>
       </c>
       <c r="H71" s="7" t="n">
-        <v>28782100.56</v>
+        <v>28733602.18</v>
       </c>
       <c r="I71" s="6" t="n">
-        <v>43173150840</v>
+        <v>43100403270</v>
       </c>
       <c r="J71" s="7" t="n">
-        <v>9357626.460000001</v>
+        <v>9337782.35</v>
       </c>
       <c r="K71" s="7" t="n">
-        <v>19424474.23</v>
+        <v>19395819.93</v>
       </c>
       <c r="L71" s="6" t="n">
         <v>1067040000</v>
@@ -3838,7 +3838,7 @@
         <v>711360</v>
       </c>
       <c r="N71" s="6" t="n">
-        <v>42106110840</v>
+        <v>42033363270</v>
       </c>
     </row>
     <row r="72">
@@ -3859,7 +3859,7 @@
         <v>4113507.56</v>
       </c>
       <c r="E72" s="7" t="n">
-        <v>1363179.23</v>
+        <v>1299764.62</v>
       </c>
       <c r="F72" s="7" t="n">
         <v>38061.11</v>
@@ -3868,16 +3868,16 @@
         <v>1234052.25</v>
       </c>
       <c r="H72" s="7" t="n">
-        <v>6748800.19</v>
+        <v>6685385.58</v>
       </c>
       <c r="I72" s="6" t="n">
-        <v>10123200285</v>
+        <v>10028078370</v>
       </c>
       <c r="J72" s="7" t="n">
-        <v>1150549.38</v>
+        <v>1151247.75</v>
       </c>
       <c r="K72" s="7" t="n">
-        <v>5598250.86</v>
+        <v>5534137.87</v>
       </c>
       <c r="L72" s="6" t="n">
         <v>243360000</v>
@@ -3886,7 +3886,7 @@
         <v>162240</v>
       </c>
       <c r="N72" s="6" t="n">
-        <v>9879840285</v>
+        <v>9784718370</v>
       </c>
     </row>
     <row r="73">
@@ -3907,7 +3907,7 @@
         <v>34885.37</v>
       </c>
       <c r="E73" s="7" t="n">
-        <v>2791.35</v>
+        <v>4011.15</v>
       </c>
       <c r="F73" s="7" t="n">
         <v>217.47</v>
@@ -3916,16 +3916,16 @@
         <v>10465.58</v>
       </c>
       <c r="H73" s="7" t="n">
-        <v>48359.78</v>
+        <v>49579.57</v>
       </c>
       <c r="I73" s="6" t="n">
-        <v>72539670</v>
+        <v>74369355</v>
       </c>
       <c r="J73" s="7" t="n">
-        <v>27542.82</v>
+        <v>27649.47</v>
       </c>
       <c r="K73" s="7" t="n">
-        <v>20817.03</v>
+        <v>21930.17</v>
       </c>
       <c r="L73" s="6" t="n">
         <v>149760000</v>
@@ -3934,7 +3934,7 @@
         <v>99840</v>
       </c>
       <c r="N73" s="6" t="n">
-        <v>-77220330</v>
+        <v>-75390645</v>
       </c>
     </row>
     <row r="74">
@@ -3955,7 +3955,7 @@
         <v>13118835.33</v>
       </c>
       <c r="E74" s="7" t="n">
-        <v>9316369.52</v>
+        <v>9162908.83</v>
       </c>
       <c r="F74" s="7" t="n">
         <v>260117.63</v>
@@ -3964,16 +3964,16 @@
         <v>3935650.6</v>
       </c>
       <c r="H74" s="7" t="n">
-        <v>26630972.96</v>
+        <v>26477512.28</v>
       </c>
       <c r="I74" s="6" t="n">
-        <v>39946459440</v>
+        <v>39716268420</v>
       </c>
       <c r="J74" s="7" t="n">
-        <v>9980310.609999999</v>
+        <v>9882329.619999999</v>
       </c>
       <c r="K74" s="7" t="n">
-        <v>16650662.49</v>
+        <v>16595182.78</v>
       </c>
       <c r="L74" s="6" t="n">
         <v>1071200000</v>
@@ -3982,7 +3982,7 @@
         <v>714133.33</v>
       </c>
       <c r="N74" s="6" t="n">
-        <v>38875259440</v>
+        <v>38645068420</v>
       </c>
     </row>
     <row r="75">
@@ -4003,7 +4003,7 @@
         <v>3909212.81</v>
       </c>
       <c r="E75" s="7" t="n">
-        <v>1485949.65</v>
+        <v>1490845.31</v>
       </c>
       <c r="F75" s="7" t="n">
         <v>38903.52</v>
@@ -4012,16 +4012,16 @@
         <v>1172763.82</v>
       </c>
       <c r="H75" s="7" t="n">
-        <v>6606829.85</v>
+        <v>6611725.51</v>
       </c>
       <c r="I75" s="6" t="n">
-        <v>9910244775</v>
+        <v>9917588265</v>
       </c>
       <c r="J75" s="7" t="n">
-        <v>1243904.72</v>
+        <v>1246606.24</v>
       </c>
       <c r="K75" s="7" t="n">
-        <v>5362925.09</v>
+        <v>5365119.23</v>
       </c>
       <c r="L75" s="6" t="n">
         <v>245440000</v>
@@ -4030,7 +4030,7 @@
         <v>163626.67</v>
       </c>
       <c r="N75" s="6" t="n">
-        <v>9664804775</v>
+        <v>9672148265</v>
       </c>
     </row>
     <row r="76">
@@ -4051,7 +4051,7 @@
         <v>27331.39</v>
       </c>
       <c r="E76" s="7" t="n">
-        <v>3097.41</v>
+        <v>3881.98</v>
       </c>
       <c r="F76" s="7" t="n">
         <v>218.73</v>
@@ -4060,16 +4060,16 @@
         <v>8199.379999999999</v>
       </c>
       <c r="H76" s="7" t="n">
-        <v>38846.86</v>
+        <v>39631.44</v>
       </c>
       <c r="I76" s="6" t="n">
-        <v>58270290</v>
+        <v>59447160</v>
       </c>
       <c r="J76" s="7" t="n">
-        <v>25457.67</v>
+        <v>25557.43</v>
       </c>
       <c r="K76" s="7" t="n">
-        <v>13389.22</v>
+        <v>14074.05</v>
       </c>
       <c r="L76" s="6" t="n">
         <v>153920000</v>
@@ -4078,7 +4078,7 @@
         <v>102613.33</v>
       </c>
       <c r="N76" s="6" t="n">
-        <v>-95649710</v>
+        <v>-94472840</v>
       </c>
     </row>
     <row r="77">
@@ -4099,7 +4099,7 @@
         <v>15182768.98</v>
       </c>
       <c r="E77" s="7" t="n">
-        <v>10714984.38</v>
+        <v>10702629.96</v>
       </c>
       <c r="F77" s="7" t="n">
         <v>256445.55</v>
@@ -4108,16 +4108,16 @@
         <v>4554830.77</v>
       </c>
       <c r="H77" s="7" t="n">
-        <v>30709029.49</v>
+        <v>30696675.07</v>
       </c>
       <c r="I77" s="6" t="n">
-        <v>46063544235</v>
+        <v>46045012605</v>
       </c>
       <c r="J77" s="7" t="n">
-        <v>11741976.06</v>
+        <v>11733287.67</v>
       </c>
       <c r="K77" s="7" t="n">
-        <v>18967053.26</v>
+        <v>18963387.24</v>
       </c>
       <c r="L77" s="6" t="n">
         <v>1081600000</v>
@@ -4126,7 +4126,7 @@
         <v>721066.67</v>
       </c>
       <c r="N77" s="6" t="n">
-        <v>44981944235</v>
+        <v>44963412605</v>
       </c>
     </row>
     <row r="78">
@@ -4147,7 +4147,7 @@
         <v>4299541.82</v>
       </c>
       <c r="E78" s="7" t="n">
-        <v>1659119.47</v>
+        <v>1662044.95</v>
       </c>
       <c r="F78" s="7" t="n">
         <v>39844.21</v>
@@ -4156,16 +4156,16 @@
         <v>1289862.59</v>
       </c>
       <c r="H78" s="7" t="n">
-        <v>7288367.98</v>
+        <v>7291293.46</v>
       </c>
       <c r="I78" s="6" t="n">
-        <v>10932551970</v>
+        <v>10936940190</v>
       </c>
       <c r="J78" s="7" t="n">
-        <v>1596319.77</v>
+        <v>1597112.66</v>
       </c>
       <c r="K78" s="7" t="n">
-        <v>5692048.21</v>
+        <v>5694180.81</v>
       </c>
       <c r="L78" s="6" t="n">
         <v>247520000</v>
@@ -4174,7 +4174,7 @@
         <v>165013.33</v>
       </c>
       <c r="N78" s="6" t="n">
-        <v>10685031970</v>
+        <v>10689420190</v>
       </c>
     </row>
     <row r="79">
@@ -4195,7 +4195,7 @@
         <v>35517.73</v>
       </c>
       <c r="E79" s="7" t="n">
-        <v>1520.38</v>
+        <v>2197.3</v>
       </c>
       <c r="F79" s="7" t="n">
         <v>220.28</v>
@@ -4204,16 +4204,16 @@
         <v>10655.35</v>
       </c>
       <c r="H79" s="7" t="n">
-        <v>47913.76</v>
+        <v>48590.68</v>
       </c>
       <c r="I79" s="6" t="n">
-        <v>71870640</v>
+        <v>72886020</v>
       </c>
       <c r="J79" s="7" t="n">
-        <v>32801.14</v>
+        <v>32925.87</v>
       </c>
       <c r="K79" s="7" t="n">
-        <v>15112.64</v>
+        <v>15664.83</v>
       </c>
       <c r="L79" s="6" t="n">
         <v>160160000</v>
@@ -4222,7 +4222,7 @@
         <v>106773.33</v>
       </c>
       <c r="N79" s="6" t="n">
-        <v>-88289360</v>
+        <v>-87273980</v>
       </c>
     </row>
     <row r="80">
@@ -4243,7 +4243,7 @@
         <v>15309950.01</v>
       </c>
       <c r="E80" s="7" t="n">
-        <v>10681031.89</v>
+        <v>10604938.5</v>
       </c>
       <c r="F80" s="7" t="n">
         <v>261005.57</v>
@@ -4252,16 +4252,16 @@
         <v>4592984.88</v>
       </c>
       <c r="H80" s="7" t="n">
-        <v>30844972.27</v>
+        <v>30768878.87</v>
       </c>
       <c r="I80" s="6" t="n">
-        <v>46267458405</v>
+        <v>46153318305</v>
       </c>
       <c r="J80" s="7" t="n">
-        <v>11901885.46</v>
+        <v>11836190.56</v>
       </c>
       <c r="K80" s="7" t="n">
-        <v>18943086.71</v>
+        <v>18932688.24</v>
       </c>
       <c r="L80" s="6" t="n">
         <v>1085760000</v>
@@ -4270,7 +4270,7 @@
         <v>723840</v>
       </c>
       <c r="N80" s="6" t="n">
-        <v>45181698405</v>
+        <v>45067558305</v>
       </c>
     </row>
     <row r="81">
@@ -4291,7 +4291,7 @@
         <v>4218312.56</v>
       </c>
       <c r="E81" s="7" t="n">
-        <v>1446463.38</v>
+        <v>1459284.32</v>
       </c>
       <c r="F81" s="7" t="n">
         <v>41013.07</v>
@@ -4300,16 +4300,16 @@
         <v>1265493.79</v>
       </c>
       <c r="H81" s="7" t="n">
-        <v>6971282.87</v>
+        <v>6984103.82</v>
       </c>
       <c r="I81" s="6" t="n">
-        <v>10456924305</v>
+        <v>10476155730</v>
       </c>
       <c r="J81" s="7" t="n">
-        <v>1427403.07</v>
+        <v>1431567.43</v>
       </c>
       <c r="K81" s="7" t="n">
-        <v>5543879.79</v>
+        <v>5552536.39</v>
       </c>
       <c r="L81" s="6" t="n">
         <v>249600000</v>
@@ -4318,7 +4318,7 @@
         <v>166400</v>
       </c>
       <c r="N81" s="6" t="n">
-        <v>10207324305</v>
+        <v>10226555730</v>
       </c>
     </row>
     <row r="82">
@@ -4339,7 +4339,7 @@
         <v>48506.32</v>
       </c>
       <c r="E82" s="7" t="n">
-        <v>2218.14</v>
+        <v>6474.02</v>
       </c>
       <c r="F82" s="7" t="n">
         <v>222.54</v>
@@ -4348,16 +4348,16 @@
         <v>14551.91</v>
       </c>
       <c r="H82" s="7" t="n">
-        <v>65498.93</v>
+        <v>69754.81</v>
       </c>
       <c r="I82" s="6" t="n">
-        <v>98248395</v>
+        <v>104632215</v>
       </c>
       <c r="J82" s="7" t="n">
-        <v>38698.44</v>
+        <v>40157.45</v>
       </c>
       <c r="K82" s="7" t="n">
-        <v>26800.56</v>
+        <v>29597.44</v>
       </c>
       <c r="L82" s="6" t="n">
         <v>162240000</v>
@@ -4366,7 +4366,7 @@
         <v>108160</v>
       </c>
       <c r="N82" s="6" t="n">
-        <v>-63991605</v>
+        <v>-57607785</v>
       </c>
     </row>
     <row r="83">
@@ -4387,7 +4387,7 @@
         <v>16355772.25</v>
       </c>
       <c r="E83" s="7" t="n">
-        <v>10760430.31</v>
+        <v>10821972.18</v>
       </c>
       <c r="F83" s="7" t="n">
         <v>231584.72</v>
@@ -4396,16 +4396,16 @@
         <v>4906731.66</v>
       </c>
       <c r="H83" s="7" t="n">
-        <v>32254518.96</v>
+        <v>32316060.81</v>
       </c>
       <c r="I83" s="6" t="n">
-        <v>48381778440</v>
+        <v>48474091215</v>
       </c>
       <c r="J83" s="7" t="n">
-        <v>13662343.9</v>
+        <v>13710103.21</v>
       </c>
       <c r="K83" s="7" t="n">
-        <v>18592175.13</v>
+        <v>18605957.69</v>
       </c>
       <c r="L83" s="6" t="n">
         <v>1087840000</v>
@@ -4414,7 +4414,7 @@
         <v>725226.67</v>
       </c>
       <c r="N83" s="6" t="n">
-        <v>47293938440</v>
+        <v>47386251215</v>
       </c>
     </row>
     <row r="84">
@@ -4435,7 +4435,7 @@
         <v>4528391.73</v>
       </c>
       <c r="E84" s="7" t="n">
-        <v>1377570.58</v>
+        <v>1292148.66</v>
       </c>
       <c r="F84" s="7" t="n">
         <v>42071.49</v>
@@ -4444,16 +4444,16 @@
         <v>1358517.5</v>
       </c>
       <c r="H84" s="7" t="n">
-        <v>7306551.37</v>
+        <v>7221129.45</v>
       </c>
       <c r="I84" s="6" t="n">
-        <v>10959827055</v>
+        <v>10831694175</v>
       </c>
       <c r="J84" s="7" t="n">
-        <v>1868399.85</v>
+        <v>1814303.22</v>
       </c>
       <c r="K84" s="7" t="n">
-        <v>5438151.44</v>
+        <v>5406826.14</v>
       </c>
       <c r="L84" s="6" t="n">
         <v>249600000</v>
@@ -4462,7 +4462,7 @@
         <v>166400</v>
       </c>
       <c r="N84" s="6" t="n">
-        <v>10710227055</v>
+        <v>10582094175</v>
       </c>
     </row>
     <row r="85">
@@ -4483,7 +4483,7 @@
         <v>159336.18</v>
       </c>
       <c r="E85" s="7" t="n">
-        <v>5987.7</v>
+        <v>154374.85</v>
       </c>
       <c r="F85" s="7" t="n">
         <v>224.99</v>
@@ -4492,16 +4492,16 @@
         <v>47800.89</v>
       </c>
       <c r="H85" s="7" t="n">
-        <v>213349.69</v>
+        <v>361736.84</v>
       </c>
       <c r="I85" s="6" t="n">
-        <v>320024535</v>
+        <v>542605260</v>
       </c>
       <c r="J85" s="7" t="n">
-        <v>102908.87</v>
+        <v>160578.96</v>
       </c>
       <c r="K85" s="7" t="n">
-        <v>110440.76</v>
+        <v>201157.82</v>
       </c>
       <c r="L85" s="6" t="n">
         <v>164320000</v>
@@ -4510,7 +4510,7 @@
         <v>109546.67</v>
       </c>
       <c r="N85" s="6" t="n">
-        <v>155704535</v>
+        <v>378285260</v>
       </c>
     </row>
     <row r="86">
@@ -4531,7 +4531,7 @@
         <v>17584131.8</v>
       </c>
       <c r="E86" s="7" t="n">
-        <v>9453002.59</v>
+        <v>9459190.35</v>
       </c>
       <c r="F86" s="7" t="n">
         <v>234917.91</v>
@@ -4540,16 +4540,16 @@
         <v>5275239.43</v>
       </c>
       <c r="H86" s="7" t="n">
-        <v>32547291.89</v>
+        <v>32553479.61</v>
       </c>
       <c r="I86" s="6" t="n">
-        <v>48820937835</v>
+        <v>48830219415</v>
       </c>
       <c r="J86" s="7" t="n">
-        <v>13396757.02</v>
+        <v>13401718.02</v>
       </c>
       <c r="K86" s="7" t="n">
-        <v>19150534.85</v>
+        <v>19151761.65</v>
       </c>
       <c r="L86" s="6" t="n">
         <v>1089920000</v>
@@ -4558,7 +4558,7 @@
         <v>726613.33</v>
       </c>
       <c r="N86" s="6" t="n">
-        <v>47731017835</v>
+        <v>47740299415</v>
       </c>
     </row>
     <row r="87">
@@ -4579,7 +4579,7 @@
         <v>4996053.88</v>
       </c>
       <c r="E87" s="7" t="n">
-        <v>1342740.34</v>
+        <v>1337116.86</v>
       </c>
       <c r="F87" s="7" t="n">
         <v>42956.71</v>
@@ -4588,16 +4588,16 @@
         <v>1498816.15</v>
       </c>
       <c r="H87" s="7" t="n">
-        <v>7880567.06</v>
+        <v>7874943.6</v>
       </c>
       <c r="I87" s="6" t="n">
-        <v>11820850590</v>
+        <v>11812415400</v>
       </c>
       <c r="J87" s="7" t="n">
-        <v>2074775.33</v>
+        <v>2070384.73</v>
       </c>
       <c r="K87" s="7" t="n">
-        <v>5805791.78</v>
+        <v>5804558.9</v>
       </c>
       <c r="L87" s="6" t="n">
         <v>251680000</v>
@@ -4606,7 +4606,7 @@
         <v>167786.67</v>
       </c>
       <c r="N87" s="6" t="n">
-        <v>11569170590</v>
+        <v>11560735400</v>
       </c>
     </row>
     <row r="88">
@@ -4675,7 +4675,7 @@
         <v>20096219.7</v>
       </c>
       <c r="E89" s="7" t="n">
-        <v>10344810.47</v>
+        <v>10418257.28</v>
       </c>
       <c r="F89" s="7" t="n">
         <v>278845.02</v>
@@ -4684,16 +4684,16 @@
         <v>6028865.88</v>
       </c>
       <c r="H89" s="7" t="n">
-        <v>36748740.92</v>
+        <v>36822187.7</v>
       </c>
       <c r="I89" s="6" t="n">
-        <v>55123111380</v>
+        <v>55233281550</v>
       </c>
       <c r="J89" s="7" t="n">
-        <v>14905940.6</v>
+        <v>14953161.69</v>
       </c>
       <c r="K89" s="7" t="n">
-        <v>21842800.39</v>
+        <v>21869026.12</v>
       </c>
       <c r="L89" s="6" t="n">
         <v>1089920000</v>
@@ -4702,7 +4702,7 @@
         <v>726613.33</v>
       </c>
       <c r="N89" s="6" t="n">
-        <v>54033191380</v>
+        <v>54143361550</v>
       </c>
     </row>
     <row r="90">
@@ -4723,7 +4723,7 @@
         <v>5422294.97</v>
       </c>
       <c r="E90" s="7" t="n">
-        <v>1338738.95</v>
+        <v>1340662.25</v>
       </c>
       <c r="F90" s="7" t="n">
         <v>43801.23</v>
@@ -4732,16 +4732,16 @@
         <v>1626688.46</v>
       </c>
       <c r="H90" s="7" t="n">
-        <v>8431523.57</v>
+        <v>8433446.859999999</v>
       </c>
       <c r="I90" s="6" t="n">
-        <v>12647285355</v>
+        <v>12650170290</v>
       </c>
       <c r="J90" s="7" t="n">
-        <v>2061215.89</v>
+        <v>2061822.67</v>
       </c>
       <c r="K90" s="7" t="n">
-        <v>6370307.69</v>
+        <v>6371624.18</v>
       </c>
       <c r="L90" s="6" t="n">
         <v>251680000</v>
@@ -4750,7 +4750,7 @@
         <v>167786.67</v>
       </c>
       <c r="N90" s="6" t="n">
-        <v>12395605355</v>
+        <v>12398490290</v>
       </c>
     </row>
     <row r="91">
@@ -4819,7 +4819,7 @@
         <v>20967697.37</v>
       </c>
       <c r="E92" s="7" t="n">
-        <v>10235251.46</v>
+        <v>10319142.07</v>
       </c>
       <c r="F92" s="7" t="n">
         <v>280694.12</v>
@@ -4828,16 +4828,16 @@
         <v>6290309.18</v>
       </c>
       <c r="H92" s="7" t="n">
-        <v>37773952.17</v>
+        <v>37857842.78</v>
       </c>
       <c r="I92" s="6" t="n">
-        <v>56660928255</v>
+        <v>56786764170</v>
       </c>
       <c r="J92" s="7" t="n">
-        <v>15781339.4</v>
+        <v>15833263.7</v>
       </c>
       <c r="K92" s="7" t="n">
-        <v>21992612.76</v>
+        <v>22024579.09</v>
       </c>
       <c r="L92" s="6" t="n">
         <v>1089920000</v>
@@ -4846,7 +4846,7 @@
         <v>726613.33</v>
       </c>
       <c r="N92" s="6" t="n">
-        <v>55571008255</v>
+        <v>55696844170</v>
       </c>
     </row>
     <row r="93">
@@ -4867,7 +4867,7 @@
         <v>5393736.03</v>
       </c>
       <c r="E93" s="7" t="n">
-        <v>898586.08</v>
+        <v>900761.65</v>
       </c>
       <c r="F93" s="7" t="n">
         <v>44130.18</v>
@@ -4876,16 +4876,16 @@
         <v>1618120.81</v>
       </c>
       <c r="H93" s="7" t="n">
-        <v>7954573.08</v>
+        <v>7956748.65</v>
       </c>
       <c r="I93" s="6" t="n">
-        <v>11931859620</v>
+        <v>11935122975</v>
       </c>
       <c r="J93" s="7" t="n">
-        <v>1322596.74</v>
+        <v>1323273.88</v>
       </c>
       <c r="K93" s="7" t="n">
-        <v>6631976.37</v>
+        <v>6633474.81</v>
       </c>
       <c r="L93" s="6" t="n">
         <v>251680000</v>
@@ -4894,7 +4894,7 @@
         <v>167786.67</v>
       </c>
       <c r="N93" s="6" t="n">
-        <v>11680179620</v>
+        <v>11683442975</v>
       </c>
     </row>
     <row r="94">

--- a/NBS FINAL delivery/03_Excel_Deliveries/9_NBS_Accounts_Domestic_and_GNI.xlsx
+++ b/NBS FINAL delivery/03_Excel_Deliveries/9_NBS_Accounts_Domestic_and_GNI.xlsx
@@ -512,7 +512,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28T20:13:47.903954+00:00</t>
+          <t>2026-08-31T23:48:51.976270+00:00</t>
         </is>
       </c>
     </row>
@@ -640,7 +640,7 @@
         <v>226</v>
       </c>
       <c r="D2" s="7" t="n">
-        <v>785823.08</v>
+        <v>785823.21</v>
       </c>
       <c r="E2" s="7" t="n">
         <v>1286501.64</v>
@@ -649,13 +649,13 @@
         <v>39968.25</v>
       </c>
       <c r="G2" s="7" t="n">
-        <v>235746.91</v>
+        <v>235746.99</v>
       </c>
       <c r="H2" s="7" t="n">
-        <v>2348039.94</v>
+        <v>2348040.15</v>
       </c>
       <c r="I2" s="6" t="n">
-        <v>3522059910</v>
+        <v>3522060225</v>
       </c>
       <c r="L2" s="6" t="n">
         <v>470080000</v>
@@ -664,7 +664,7 @@
         <v>313386.67</v>
       </c>
       <c r="N2" s="6" t="n">
-        <v>3051979910</v>
+        <v>3051980225</v>
       </c>
     </row>
     <row r="3">
@@ -682,7 +682,7 @@
         <v>40</v>
       </c>
       <c r="D3" s="7" t="n">
-        <v>328694.8</v>
+        <v>328694.85</v>
       </c>
       <c r="E3" s="7" t="n">
         <v>218017.95</v>
@@ -691,13 +691,13 @@
         <v>18481.94</v>
       </c>
       <c r="G3" s="7" t="n">
-        <v>98608.42999999999</v>
+        <v>98608.46000000001</v>
       </c>
       <c r="H3" s="7" t="n">
-        <v>663803.16</v>
+        <v>663803.24</v>
       </c>
       <c r="I3" s="6" t="n">
-        <v>995704740</v>
+        <v>995704860</v>
       </c>
       <c r="L3" s="6" t="n">
         <v>83200000</v>
@@ -706,7 +706,7 @@
         <v>55466.67</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>912504740</v>
+        <v>912504860</v>
       </c>
     </row>
     <row r="4">
@@ -724,7 +724,7 @@
         <v>17</v>
       </c>
       <c r="D4" s="7" t="n">
-        <v>909.79</v>
+        <v>909.8099999999999</v>
       </c>
       <c r="E4" s="7" t="n">
         <v>2719.41</v>
@@ -733,13 +733,13 @@
         <v>31.93</v>
       </c>
       <c r="G4" s="7" t="n">
-        <v>272.95</v>
+        <v>272.94</v>
       </c>
       <c r="H4" s="7" t="n">
-        <v>3934.07</v>
+        <v>3934.09</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>5901105</v>
+        <v>5901135</v>
       </c>
       <c r="L4" s="6" t="n">
         <v>35360000</v>
@@ -748,7 +748,7 @@
         <v>23573.33</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>-29458895</v>
+        <v>-29458865</v>
       </c>
     </row>
     <row r="5">

--- a/NBS FINAL delivery/03_Excel_Deliveries/9_NBS_Accounts_Domestic_and_GNI.xlsx
+++ b/NBS FINAL delivery/03_Excel_Deliveries/9_NBS_Accounts_Domestic_and_GNI.xlsx
@@ -512,7 +512,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>2026-08-31T23:48:51.976270+00:00</t>
+          <t>2026-09-01T00:10:26.191025+00:00</t>
         </is>
       </c>
     </row>
@@ -1150,16 +1150,16 @@
         <v>2077791.17</v>
       </c>
       <c r="F14" s="7" t="n">
-        <v>77246.02</v>
+        <v>77213.86</v>
       </c>
       <c r="G14" s="7" t="n">
         <v>578107.4399999999</v>
       </c>
       <c r="H14" s="7" t="n">
-        <v>4660169.26</v>
+        <v>4660137.1</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>6990253890</v>
+        <v>6990205650</v>
       </c>
       <c r="L14" s="6" t="n">
         <v>750880000</v>
@@ -1168,7 +1168,7 @@
         <v>500586.67</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>6239373890</v>
+        <v>6239325650</v>
       </c>
     </row>
     <row r="15">
@@ -1225,7 +1225,7 @@
         </is>
       </c>
       <c r="C16" s="6" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D16" s="7" t="n">
         <v>1225.57</v>
@@ -1234,25 +1234,25 @@
         <v>2951.74</v>
       </c>
       <c r="F16" s="7" t="n">
-        <v>99.13</v>
+        <v>98.91</v>
       </c>
       <c r="G16" s="7" t="n">
         <v>367.67</v>
       </c>
       <c r="H16" s="7" t="n">
-        <v>4644.12</v>
+        <v>4643.9</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>6966180</v>
+        <v>6965850</v>
       </c>
       <c r="L16" s="6" t="n">
-        <v>87360000</v>
+        <v>85280000</v>
       </c>
       <c r="M16" s="7" t="n">
-        <v>58240</v>
+        <v>56853.33</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>-80393820</v>
+        <v>-78314150</v>
       </c>
     </row>
     <row r="17">
@@ -1276,16 +1276,16 @@
         <v>2286773.03</v>
       </c>
       <c r="F17" s="7" t="n">
-        <v>89097.19</v>
+        <v>89043.5</v>
       </c>
       <c r="G17" s="7" t="n">
         <v>679791.3</v>
       </c>
       <c r="H17" s="7" t="n">
-        <v>5321632.5</v>
+        <v>5321578.81</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>7982448750</v>
+        <v>7982368215</v>
       </c>
       <c r="L17" s="6" t="n">
         <v>802880000</v>
@@ -1294,7 +1294,7 @@
         <v>535253.33</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>7179568750</v>
+        <v>7179488215</v>
       </c>
     </row>
     <row r="18">
@@ -1351,7 +1351,7 @@
         </is>
       </c>
       <c r="C19" s="6" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D19" s="7" t="n">
         <v>1596.1</v>
@@ -1360,25 +1360,25 @@
         <v>2992.92</v>
       </c>
       <c r="F19" s="7" t="n">
-        <v>123.07</v>
+        <v>122.83</v>
       </c>
       <c r="G19" s="7" t="n">
         <v>478.78</v>
       </c>
       <c r="H19" s="7" t="n">
-        <v>5190.91</v>
+        <v>5190.67</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>7786365</v>
+        <v>7786005</v>
       </c>
       <c r="L19" s="6" t="n">
-        <v>91520000</v>
+        <v>89440000</v>
       </c>
       <c r="M19" s="7" t="n">
-        <v>61013.33</v>
+        <v>59626.67</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>-83733635</v>
+        <v>-81653995</v>
       </c>
     </row>
     <row r="20">
@@ -1402,16 +1402,16 @@
         <v>2685417.57</v>
       </c>
       <c r="F20" s="7" t="n">
-        <v>104788.44</v>
+        <v>104719.51</v>
       </c>
       <c r="G20" s="7" t="n">
         <v>774340.54</v>
       </c>
       <c r="H20" s="7" t="n">
-        <v>6145681.66</v>
+        <v>6145612.73</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>9218522490</v>
+        <v>9218419095</v>
       </c>
       <c r="L20" s="6" t="n">
         <v>848640000</v>
@@ -1420,7 +1420,7 @@
         <v>565760</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>8369882490</v>
+        <v>8369779095</v>
       </c>
     </row>
     <row r="21">
@@ -1477,7 +1477,7 @@
         </is>
       </c>
       <c r="C22" s="6" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D22" s="7" t="n">
         <v>1283.81</v>
@@ -1486,25 +1486,25 @@
         <v>3029.74</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>140.97</v>
+        <v>140.71</v>
       </c>
       <c r="G22" s="7" t="n">
         <v>385.17</v>
       </c>
       <c r="H22" s="7" t="n">
-        <v>4839.69</v>
+        <v>4839.43</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>7259535</v>
+        <v>7259145</v>
       </c>
       <c r="L22" s="6" t="n">
-        <v>97760000</v>
+        <v>95680000</v>
       </c>
       <c r="M22" s="7" t="n">
-        <v>65173.33</v>
+        <v>63786.67</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>-90500465</v>
+        <v>-88420855</v>
       </c>
     </row>
     <row r="23">
@@ -1528,16 +1528,16 @@
         <v>3312261.02</v>
       </c>
       <c r="F23" s="7" t="n">
-        <v>120783.98</v>
+        <v>120704.49</v>
       </c>
       <c r="G23" s="7" t="n">
         <v>683952.67</v>
       </c>
       <c r="H23" s="7" t="n">
-        <v>6396839.84</v>
+        <v>6396760.35</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>9595259760</v>
+        <v>9595140525</v>
       </c>
       <c r="L23" s="6" t="n">
         <v>873600000</v>
@@ -1546,7 +1546,7 @@
         <v>582400</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>8721659760</v>
+        <v>8721540525</v>
       </c>
     </row>
     <row r="24">
@@ -1603,7 +1603,7 @@
         </is>
       </c>
       <c r="C25" s="6" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D25" s="7" t="n">
         <v>1385.46</v>
@@ -1612,25 +1612,25 @@
         <v>3048.14</v>
       </c>
       <c r="F25" s="7" t="n">
-        <v>151.16</v>
+        <v>150.9</v>
       </c>
       <c r="G25" s="7" t="n">
         <v>415.66</v>
       </c>
       <c r="H25" s="7" t="n">
-        <v>5000.37</v>
+        <v>5000.11</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>7500555</v>
+        <v>7500165</v>
       </c>
       <c r="L25" s="6" t="n">
-        <v>97760000</v>
+        <v>95680000</v>
       </c>
       <c r="M25" s="7" t="n">
-        <v>65173.33</v>
+        <v>63786.67</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>-90259445</v>
+        <v>-88179835</v>
       </c>
     </row>
     <row r="26">
@@ -1654,22 +1654,22 @@
         <v>3334436.3</v>
       </c>
       <c r="F26" s="7" t="n">
-        <v>135947.53</v>
+        <v>135857.72</v>
       </c>
       <c r="G26" s="7" t="n">
         <v>809489.02</v>
       </c>
       <c r="H26" s="7" t="n">
-        <v>6978168.86</v>
+        <v>6978079.05</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>10467253290</v>
+        <v>10467118575</v>
       </c>
       <c r="J26" s="7" t="n">
-        <v>290110.74</v>
+        <v>290108.6</v>
       </c>
       <c r="K26" s="7" t="n">
-        <v>6688058.17</v>
+        <v>6687970.5</v>
       </c>
       <c r="L26" s="6" t="n">
         <v>886080000</v>
@@ -1678,7 +1678,7 @@
         <v>590720</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>9581173290</v>
+        <v>9581038575</v>
       </c>
     </row>
     <row r="27">
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="C28" s="6" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D28" s="7" t="n">
         <v>1884.11</v>
@@ -1750,31 +1750,31 @@
         <v>3049.05</v>
       </c>
       <c r="F28" s="7" t="n">
-        <v>162.62</v>
+        <v>162.36</v>
       </c>
       <c r="G28" s="7" t="n">
         <v>565.21</v>
       </c>
       <c r="H28" s="7" t="n">
-        <v>5661.04</v>
+        <v>5660.78</v>
       </c>
       <c r="I28" s="6" t="n">
-        <v>8491560</v>
+        <v>8491170</v>
       </c>
       <c r="J28" s="7" t="n">
-        <v>420.29</v>
+        <v>420.28</v>
       </c>
       <c r="K28" s="7" t="n">
-        <v>5240.73</v>
+        <v>5240.47</v>
       </c>
       <c r="L28" s="6" t="n">
-        <v>99840000</v>
+        <v>97760000</v>
       </c>
       <c r="M28" s="7" t="n">
-        <v>66560</v>
+        <v>65173.33</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>-91348440</v>
+        <v>-89268830</v>
       </c>
     </row>
     <row r="29">
@@ -1798,22 +1798,22 @@
         <v>3710377.41</v>
       </c>
       <c r="F29" s="7" t="n">
-        <v>150010.07</v>
+        <v>149911.98</v>
       </c>
       <c r="G29" s="7" t="n">
         <v>868800.98</v>
       </c>
       <c r="H29" s="7" t="n">
-        <v>7625191.47</v>
+        <v>7625093.38</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>11437787205</v>
+        <v>11437640070</v>
       </c>
       <c r="J29" s="7" t="n">
-        <v>305605.32</v>
+        <v>305603.41</v>
       </c>
       <c r="K29" s="7" t="n">
-        <v>7319586.27</v>
+        <v>7319490.09</v>
       </c>
       <c r="L29" s="6" t="n">
         <v>904800000</v>
@@ -1822,7 +1822,7 @@
         <v>603200</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>10532987205</v>
+        <v>10532840070</v>
       </c>
     </row>
     <row r="30">
@@ -1885,7 +1885,7 @@
         </is>
       </c>
       <c r="C31" s="6" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D31" s="7" t="n">
         <v>1768.15</v>
@@ -1894,31 +1894,31 @@
         <v>3046.85</v>
       </c>
       <c r="F31" s="7" t="n">
-        <v>172.48</v>
+        <v>172.22</v>
       </c>
       <c r="G31" s="7" t="n">
         <v>530.4400000000001</v>
       </c>
       <c r="H31" s="7" t="n">
-        <v>5517.91</v>
+        <v>5517.65</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>8276865</v>
+        <v>8276475</v>
       </c>
       <c r="J31" s="7" t="n">
-        <v>484.55</v>
+        <v>484.54</v>
       </c>
       <c r="K31" s="7" t="n">
-        <v>5033.38</v>
+        <v>5033.12</v>
       </c>
       <c r="L31" s="6" t="n">
-        <v>104000000</v>
+        <v>101920000</v>
       </c>
       <c r="M31" s="7" t="n">
-        <v>69333.33</v>
+        <v>67946.67</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>-95723135</v>
+        <v>-93643525</v>
       </c>
     </row>
     <row r="32">
@@ -1942,22 +1942,22 @@
         <v>4074651.28</v>
       </c>
       <c r="F32" s="7" t="n">
-        <v>164363.14</v>
+        <v>164256.94</v>
       </c>
       <c r="G32" s="7" t="n">
         <v>1357890.32</v>
       </c>
       <c r="H32" s="7" t="n">
-        <v>10123205.83</v>
+        <v>10123099.63</v>
       </c>
       <c r="I32" s="6" t="n">
-        <v>15184808745</v>
+        <v>15184649445</v>
       </c>
       <c r="J32" s="7" t="n">
-        <v>437614.49</v>
+        <v>437611.87</v>
       </c>
       <c r="K32" s="7" t="n">
-        <v>9685591.42</v>
+        <v>9685487.85</v>
       </c>
       <c r="L32" s="6" t="n">
         <v>911040000</v>
@@ -1966,7 +1966,7 @@
         <v>607360</v>
       </c>
       <c r="N32" s="6" t="n">
-        <v>14273768745</v>
+        <v>14273609445</v>
       </c>
     </row>
     <row r="33">
@@ -2029,7 +2029,7 @@
         </is>
       </c>
       <c r="C34" s="6" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D34" s="7" t="n">
         <v>2230.37</v>
@@ -2038,31 +2038,31 @@
         <v>3054.63</v>
       </c>
       <c r="F34" s="7" t="n">
-        <v>182.61</v>
+        <v>182.32</v>
       </c>
       <c r="G34" s="7" t="n">
         <v>669.12</v>
       </c>
       <c r="H34" s="7" t="n">
-        <v>6136.78</v>
+        <v>6136.49</v>
       </c>
       <c r="I34" s="6" t="n">
-        <v>9205170</v>
+        <v>9204735</v>
       </c>
       <c r="J34" s="7" t="n">
-        <v>2048</v>
+        <v>2047.99</v>
       </c>
       <c r="K34" s="7" t="n">
-        <v>4088.78</v>
+        <v>4088.5</v>
       </c>
       <c r="L34" s="6" t="n">
-        <v>108160000</v>
+        <v>106080000</v>
       </c>
       <c r="M34" s="7" t="n">
-        <v>72106.67</v>
+        <v>70720</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>-98954830</v>
+        <v>-96875265</v>
       </c>
     </row>
     <row r="35">
@@ -2086,22 +2086,22 @@
         <v>6120897.06</v>
       </c>
       <c r="F35" s="7" t="n">
-        <v>179743.67</v>
+        <v>179631.52</v>
       </c>
       <c r="G35" s="7" t="n">
         <v>1550334.92</v>
       </c>
       <c r="H35" s="7" t="n">
-        <v>13018758.65</v>
+        <v>13018646.5</v>
       </c>
       <c r="I35" s="6" t="n">
-        <v>19528137975</v>
+        <v>19527969750</v>
       </c>
       <c r="J35" s="7" t="n">
-        <v>803532.39</v>
+        <v>803529.27</v>
       </c>
       <c r="K35" s="7" t="n">
-        <v>12215226.14</v>
+        <v>12215117.11</v>
       </c>
       <c r="L35" s="6" t="n">
         <v>938080000</v>
@@ -2110,7 +2110,7 @@
         <v>625386.67</v>
       </c>
       <c r="N35" s="6" t="n">
-        <v>18590057975</v>
+        <v>18589889750</v>
       </c>
     </row>
     <row r="36">
@@ -2173,7 +2173,7 @@
         </is>
       </c>
       <c r="C37" s="6" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D37" s="7" t="n">
         <v>5664.88</v>
@@ -2182,31 +2182,31 @@
         <v>220.09</v>
       </c>
       <c r="F37" s="7" t="n">
-        <v>189.54</v>
+        <v>189.23</v>
       </c>
       <c r="G37" s="7" t="n">
         <v>1699.47</v>
       </c>
       <c r="H37" s="7" t="n">
-        <v>7773.97</v>
+        <v>7773.66</v>
       </c>
       <c r="I37" s="6" t="n">
-        <v>11660955</v>
+        <v>11660490</v>
       </c>
       <c r="J37" s="7" t="n">
-        <v>2920.18</v>
+        <v>2920.17</v>
       </c>
       <c r="K37" s="7" t="n">
-        <v>4853.82</v>
+        <v>4853.52</v>
       </c>
       <c r="L37" s="6" t="n">
-        <v>114400000</v>
+        <v>112320000</v>
       </c>
       <c r="M37" s="7" t="n">
-        <v>76266.67</v>
+        <v>74880</v>
       </c>
       <c r="N37" s="6" t="n">
-        <v>-102739045</v>
+        <v>-100659510</v>
       </c>
     </row>
     <row r="38">
@@ -2230,22 +2230,22 @@
         <v>5398930.72</v>
       </c>
       <c r="F38" s="7" t="n">
-        <v>194162.12</v>
+        <v>194044.06</v>
       </c>
       <c r="G38" s="7" t="n">
         <v>1797211.59</v>
       </c>
       <c r="H38" s="7" t="n">
-        <v>13381009.4</v>
+        <v>13380891.34</v>
       </c>
       <c r="I38" s="6" t="n">
-        <v>20071514100</v>
+        <v>20071337010</v>
       </c>
       <c r="J38" s="7" t="n">
-        <v>784624.74</v>
+        <v>784622.03</v>
       </c>
       <c r="K38" s="7" t="n">
-        <v>12596384.45</v>
+        <v>12596269.1</v>
       </c>
       <c r="L38" s="6" t="n">
         <v>950560000</v>
@@ -2254,7 +2254,7 @@
         <v>633706.67</v>
       </c>
       <c r="N38" s="6" t="n">
-        <v>19120954100</v>
+        <v>19120777010</v>
       </c>
     </row>
     <row r="39">
@@ -2317,7 +2317,7 @@
         </is>
       </c>
       <c r="C40" s="6" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D40" s="7" t="n">
         <v>5977.23</v>
@@ -2326,31 +2326,31 @@
         <v>2946.58</v>
       </c>
       <c r="F40" s="7" t="n">
-        <v>196.3</v>
+        <v>195.99</v>
       </c>
       <c r="G40" s="7" t="n">
         <v>1793.2</v>
       </c>
       <c r="H40" s="7" t="n">
-        <v>10913.28</v>
+        <v>10912.97</v>
       </c>
       <c r="I40" s="6" t="n">
-        <v>16369920</v>
+        <v>16369455</v>
       </c>
       <c r="J40" s="7" t="n">
-        <v>2202.57</v>
+        <v>2202.56</v>
       </c>
       <c r="K40" s="7" t="n">
-        <v>8710.77</v>
+        <v>8710.469999999999</v>
       </c>
       <c r="L40" s="6" t="n">
-        <v>114400000</v>
+        <v>112320000</v>
       </c>
       <c r="M40" s="7" t="n">
-        <v>76266.67</v>
+        <v>74880</v>
       </c>
       <c r="N40" s="6" t="n">
-        <v>-98030080</v>
+        <v>-95950545</v>
       </c>
     </row>
     <row r="41">
@@ -2374,22 +2374,22 @@
         <v>5783265.17</v>
       </c>
       <c r="F41" s="7" t="n">
-        <v>201947.05</v>
+        <v>201825.15</v>
       </c>
       <c r="G41" s="7" t="n">
         <v>2036113.31</v>
       </c>
       <c r="H41" s="7" t="n">
-        <v>14808369.87</v>
+        <v>14808247.97</v>
       </c>
       <c r="I41" s="6" t="n">
-        <v>22212554805</v>
+        <v>22212371955</v>
       </c>
       <c r="J41" s="7" t="n">
-        <v>924903.63</v>
+        <v>924900.54</v>
       </c>
       <c r="K41" s="7" t="n">
-        <v>13883466.15</v>
+        <v>13883347.35</v>
       </c>
       <c r="L41" s="6" t="n">
         <v>958880000</v>
@@ -2398,7 +2398,7 @@
         <v>639253.33</v>
       </c>
       <c r="N41" s="6" t="n">
-        <v>21253674805</v>
+        <v>21253491955</v>
       </c>
     </row>
     <row r="42">
@@ -2461,7 +2461,7 @@
         </is>
       </c>
       <c r="C43" s="6" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D43" s="7" t="n">
         <v>5727.34</v>
@@ -2470,31 +2470,31 @@
         <v>2872.89</v>
       </c>
       <c r="F43" s="7" t="n">
-        <v>200.19</v>
+        <v>199.88</v>
       </c>
       <c r="G43" s="7" t="n">
         <v>1718.23</v>
       </c>
       <c r="H43" s="7" t="n">
-        <v>10518.59</v>
+        <v>10518.28</v>
       </c>
       <c r="I43" s="6" t="n">
-        <v>15777885</v>
+        <v>15777420</v>
       </c>
       <c r="J43" s="7" t="n">
-        <v>2092.9</v>
+        <v>2092.88</v>
       </c>
       <c r="K43" s="7" t="n">
-        <v>8425.709999999999</v>
+        <v>8425.41</v>
       </c>
       <c r="L43" s="6" t="n">
-        <v>122720000</v>
+        <v>120640000</v>
       </c>
       <c r="M43" s="7" t="n">
-        <v>81813.33</v>
+        <v>80426.67</v>
       </c>
       <c r="N43" s="6" t="n">
-        <v>-106942115</v>
+        <v>-104862580</v>
       </c>
     </row>
     <row r="44">
@@ -2518,22 +2518,22 @@
         <v>7479496.73</v>
       </c>
       <c r="F44" s="7" t="n">
-        <v>208194.32</v>
+        <v>208070.53</v>
       </c>
       <c r="G44" s="7" t="n">
         <v>2373149.74</v>
       </c>
       <c r="H44" s="7" t="n">
-        <v>17971340.03</v>
+        <v>17971216.23</v>
       </c>
       <c r="I44" s="6" t="n">
-        <v>26957010045</v>
+        <v>26956824345</v>
       </c>
       <c r="J44" s="7" t="n">
-        <v>1025380.55</v>
+        <v>1025376.23</v>
       </c>
       <c r="K44" s="7" t="n">
-        <v>16945959.49</v>
+        <v>16945840.03</v>
       </c>
       <c r="L44" s="6" t="n">
         <v>981760000</v>
@@ -2542,7 +2542,7 @@
         <v>654506.67</v>
       </c>
       <c r="N44" s="6" t="n">
-        <v>25975250045</v>
+        <v>25975064345</v>
       </c>
     </row>
     <row r="45">
@@ -2605,7 +2605,7 @@
         </is>
       </c>
       <c r="C46" s="6" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D46" s="7" t="n">
         <v>6173.38</v>
@@ -2614,31 +2614,31 @@
         <v>2787.34</v>
       </c>
       <c r="F46" s="7" t="n">
-        <v>202.26</v>
+        <v>201.95</v>
       </c>
       <c r="G46" s="7" t="n">
         <v>1851.98</v>
       </c>
       <c r="H46" s="7" t="n">
-        <v>11015</v>
+        <v>11014.69</v>
       </c>
       <c r="I46" s="6" t="n">
-        <v>16522500</v>
+        <v>16522035</v>
       </c>
       <c r="J46" s="7" t="n">
-        <v>2089.69</v>
+        <v>2089.68</v>
       </c>
       <c r="K46" s="7" t="n">
-        <v>8925.360000000001</v>
+        <v>8925.059999999999</v>
       </c>
       <c r="L46" s="6" t="n">
-        <v>122720000</v>
+        <v>120640000</v>
       </c>
       <c r="M46" s="7" t="n">
-        <v>81813.33</v>
+        <v>80426.67</v>
       </c>
       <c r="N46" s="6" t="n">
-        <v>-106197500</v>
+        <v>-104117965</v>
       </c>
     </row>
     <row r="47">
@@ -2662,22 +2662,22 @@
         <v>7530257.12</v>
       </c>
       <c r="F47" s="7" t="n">
-        <v>213439.62</v>
+        <v>213314.1</v>
       </c>
       <c r="G47" s="7" t="n">
         <v>2646039.91</v>
       </c>
       <c r="H47" s="7" t="n">
-        <v>19209869.69</v>
+        <v>19209744.17</v>
       </c>
       <c r="I47" s="6" t="n">
-        <v>28814804535</v>
+        <v>28814616255</v>
       </c>
       <c r="J47" s="7" t="n">
-        <v>1374258.37</v>
+        <v>1374252.33</v>
       </c>
       <c r="K47" s="7" t="n">
-        <v>17835611.33</v>
+        <v>17835491.85</v>
       </c>
       <c r="L47" s="6" t="n">
         <v>994240000</v>
@@ -2686,7 +2686,7 @@
         <v>662826.67</v>
       </c>
       <c r="N47" s="6" t="n">
-        <v>27820564535</v>
+        <v>27820376255</v>
       </c>
     </row>
     <row r="48">
@@ -2749,7 +2749,7 @@
         </is>
       </c>
       <c r="C49" s="6" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D49" s="7" t="n">
         <v>5401.29</v>
@@ -2758,31 +2758,31 @@
         <v>2713.97</v>
       </c>
       <c r="F49" s="7" t="n">
-        <v>204.05</v>
+        <v>203.74</v>
       </c>
       <c r="G49" s="7" t="n">
         <v>1620.41</v>
       </c>
       <c r="H49" s="7" t="n">
-        <v>9939.67</v>
+        <v>9939.360000000001</v>
       </c>
       <c r="I49" s="6" t="n">
-        <v>14909505</v>
+        <v>14909040</v>
       </c>
       <c r="J49" s="7" t="n">
-        <v>2473.64</v>
+        <v>2473.62</v>
       </c>
       <c r="K49" s="7" t="n">
-        <v>7466.01</v>
+        <v>7465.72</v>
       </c>
       <c r="L49" s="6" t="n">
-        <v>120640000</v>
+        <v>118560000</v>
       </c>
       <c r="M49" s="7" t="n">
-        <v>80426.67</v>
+        <v>79040</v>
       </c>
       <c r="N49" s="6" t="n">
-        <v>-105730495</v>
+        <v>-103650960</v>
       </c>
     </row>
     <row r="50">
@@ -2806,22 +2806,22 @@
         <v>7051877.6</v>
       </c>
       <c r="F50" s="7" t="n">
-        <v>218092</v>
+        <v>217965.21</v>
       </c>
       <c r="G50" s="7" t="n">
         <v>3072893.64</v>
       </c>
       <c r="H50" s="7" t="n">
-        <v>20585842.07</v>
+        <v>20585715.28</v>
       </c>
       <c r="I50" s="6" t="n">
-        <v>30878763105</v>
+        <v>30878572920</v>
       </c>
       <c r="J50" s="7" t="n">
-        <v>1941506.83</v>
+        <v>1941498.16</v>
       </c>
       <c r="K50" s="7" t="n">
-        <v>18644335.28</v>
+        <v>18644217.16</v>
       </c>
       <c r="L50" s="6" t="n">
         <v>1006720000</v>
@@ -2830,7 +2830,7 @@
         <v>671146.67</v>
       </c>
       <c r="N50" s="6" t="n">
-        <v>29872043105</v>
+        <v>29871852920</v>
       </c>
     </row>
     <row r="51">
@@ -2893,7 +2893,7 @@
         </is>
       </c>
       <c r="C52" s="6" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D52" s="7" t="n">
         <v>7092.08</v>
@@ -2902,31 +2902,31 @@
         <v>2640.59</v>
       </c>
       <c r="F52" s="7" t="n">
-        <v>205.87</v>
+        <v>205.56</v>
       </c>
       <c r="G52" s="7" t="n">
         <v>2127.64</v>
       </c>
       <c r="H52" s="7" t="n">
-        <v>12066.14</v>
+        <v>12065.83</v>
       </c>
       <c r="I52" s="6" t="n">
-        <v>18099210</v>
+        <v>18098745</v>
       </c>
       <c r="J52" s="7" t="n">
-        <v>4253.35</v>
+        <v>4253.33</v>
       </c>
       <c r="K52" s="7" t="n">
-        <v>7812.74</v>
+        <v>7812.45</v>
       </c>
       <c r="L52" s="6" t="n">
-        <v>126880000</v>
+        <v>124800000</v>
       </c>
       <c r="M52" s="7" t="n">
-        <v>84586.67</v>
+        <v>83200</v>
       </c>
       <c r="N52" s="6" t="n">
-        <v>-108780790</v>
+        <v>-106701255</v>
       </c>
     </row>
     <row r="53">
@@ -2950,22 +2950,22 @@
         <v>7877503.91</v>
       </c>
       <c r="F53" s="7" t="n">
-        <v>222615.46</v>
+        <v>222487.97</v>
       </c>
       <c r="G53" s="7" t="n">
         <v>3676030.57</v>
       </c>
       <c r="H53" s="7" t="n">
-        <v>24029584.93</v>
+        <v>24029457.45</v>
       </c>
       <c r="I53" s="6" t="n">
-        <v>36044377395</v>
+        <v>36044186175</v>
       </c>
       <c r="J53" s="7" t="n">
-        <v>2711494.59</v>
+        <v>2711483.82</v>
       </c>
       <c r="K53" s="7" t="n">
-        <v>21318090.42</v>
+        <v>21317973.7</v>
       </c>
       <c r="L53" s="6" t="n">
         <v>1027520000</v>
@@ -2974,7 +2974,7 @@
         <v>685013.33</v>
       </c>
       <c r="N53" s="6" t="n">
-        <v>35016857395</v>
+        <v>35016666175</v>
       </c>
     </row>
     <row r="54">
@@ -3037,7 +3037,7 @@
         </is>
       </c>
       <c r="C55" s="6" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D55" s="7" t="n">
         <v>8940.93</v>
@@ -3046,31 +3046,31 @@
         <v>2556.29</v>
       </c>
       <c r="F55" s="7" t="n">
-        <v>207.36</v>
+        <v>207.05</v>
       </c>
       <c r="G55" s="7" t="n">
         <v>2682.28</v>
       </c>
       <c r="H55" s="7" t="n">
-        <v>14386.84</v>
+        <v>14386.53</v>
       </c>
       <c r="I55" s="6" t="n">
-        <v>21580260</v>
+        <v>21579795</v>
       </c>
       <c r="J55" s="7" t="n">
-        <v>6433.68</v>
+        <v>6433.65</v>
       </c>
       <c r="K55" s="7" t="n">
-        <v>7953.1</v>
+        <v>7952.82</v>
       </c>
       <c r="L55" s="6" t="n">
-        <v>131040000</v>
+        <v>128960000</v>
       </c>
       <c r="M55" s="7" t="n">
-        <v>87360</v>
+        <v>85973.33</v>
       </c>
       <c r="N55" s="6" t="n">
-        <v>-109459740</v>
+        <v>-107380205</v>
       </c>
     </row>
     <row r="56">
@@ -3094,22 +3094,22 @@
         <v>7133093.46</v>
       </c>
       <c r="F56" s="7" t="n">
-        <v>227250.03</v>
+        <v>227121.99</v>
       </c>
       <c r="G56" s="7" t="n">
         <v>3471944.24</v>
       </c>
       <c r="H56" s="7" t="n">
-        <v>22405435.29</v>
+        <v>22405307.25</v>
       </c>
       <c r="I56" s="6" t="n">
-        <v>33608152935</v>
+        <v>33607960875</v>
       </c>
       <c r="J56" s="7" t="n">
-        <v>3338859.78</v>
+        <v>3338847.75</v>
       </c>
       <c r="K56" s="7" t="n">
-        <v>19066575.34</v>
+        <v>19066459.33</v>
       </c>
       <c r="L56" s="6" t="n">
         <v>1025440000</v>
@@ -3118,7 +3118,7 @@
         <v>683626.67</v>
       </c>
       <c r="N56" s="6" t="n">
-        <v>32582712935</v>
+        <v>32582520875</v>
       </c>
     </row>
     <row r="57">
@@ -3181,7 +3181,7 @@
         </is>
       </c>
       <c r="C58" s="6" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D58" s="7" t="n">
         <v>11249.43</v>
@@ -3190,31 +3190,31 @@
         <v>2483.23</v>
       </c>
       <c r="F58" s="7" t="n">
-        <v>209.38</v>
+        <v>209.07</v>
       </c>
       <c r="G58" s="7" t="n">
         <v>3374.82</v>
       </c>
       <c r="H58" s="7" t="n">
-        <v>17316.83</v>
+        <v>17316.52</v>
       </c>
       <c r="I58" s="6" t="n">
-        <v>25975245</v>
+        <v>25974780</v>
       </c>
       <c r="J58" s="7" t="n">
-        <v>10091.24</v>
+        <v>10091.2</v>
       </c>
       <c r="K58" s="7" t="n">
-        <v>7225.56</v>
+        <v>7225.29</v>
       </c>
       <c r="L58" s="6" t="n">
-        <v>131040000</v>
+        <v>128960000</v>
       </c>
       <c r="M58" s="7" t="n">
-        <v>87360</v>
+        <v>85973.33</v>
       </c>
       <c r="N58" s="6" t="n">
-        <v>-105064755</v>
+        <v>-102985220</v>
       </c>
     </row>
     <row r="59">
@@ -3238,22 +3238,22 @@
         <v>7166542.4</v>
       </c>
       <c r="F59" s="7" t="n">
-        <v>232074.24</v>
+        <v>231945.65</v>
       </c>
       <c r="G59" s="7" t="n">
         <v>3624583.79</v>
       </c>
       <c r="H59" s="7" t="n">
-        <v>23105146.04</v>
+        <v>23105017.44</v>
       </c>
       <c r="I59" s="6" t="n">
-        <v>34657719060</v>
+        <v>34657526160</v>
       </c>
       <c r="J59" s="7" t="n">
-        <v>4652166.29</v>
+        <v>4652146.15</v>
       </c>
       <c r="K59" s="7" t="n">
-        <v>18452979.89</v>
+        <v>18452871.44</v>
       </c>
       <c r="L59" s="6" t="n">
         <v>1031680000</v>
@@ -3262,7 +3262,7 @@
         <v>687786.67</v>
       </c>
       <c r="N59" s="6" t="n">
-        <v>33626039060</v>
+        <v>33625846160</v>
       </c>
     </row>
     <row r="60">
@@ -3325,7 +3325,7 @@
         </is>
       </c>
       <c r="C61" s="6" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D61" s="7" t="n">
         <v>18270.18</v>
@@ -3334,31 +3334,31 @@
         <v>2399.86</v>
       </c>
       <c r="F61" s="7" t="n">
-        <v>211.24</v>
+        <v>210.93</v>
       </c>
       <c r="G61" s="7" t="n">
         <v>5481.04</v>
       </c>
       <c r="H61" s="7" t="n">
-        <v>26362.36</v>
+        <v>26362.05</v>
       </c>
       <c r="I61" s="6" t="n">
-        <v>39543540</v>
+        <v>39543075</v>
       </c>
       <c r="J61" s="7" t="n">
-        <v>17947.26</v>
+        <v>17947.21</v>
       </c>
       <c r="K61" s="7" t="n">
-        <v>8415.18</v>
+        <v>8414.92</v>
       </c>
       <c r="L61" s="6" t="n">
-        <v>131040000</v>
+        <v>128960000</v>
       </c>
       <c r="M61" s="7" t="n">
-        <v>87360</v>
+        <v>85973.33</v>
       </c>
       <c r="N61" s="6" t="n">
-        <v>-91496460</v>
+        <v>-89416925</v>
       </c>
     </row>
     <row r="62">
@@ -3382,22 +3382,22 @@
         <v>7423596.49</v>
       </c>
       <c r="F62" s="7" t="n">
-        <v>237674.94</v>
+        <v>237545.84</v>
       </c>
       <c r="G62" s="7" t="n">
         <v>3555156.21</v>
       </c>
       <c r="H62" s="7" t="n">
-        <v>23066948.14</v>
+        <v>23066819.05</v>
       </c>
       <c r="I62" s="6" t="n">
-        <v>34600422210</v>
+        <v>34600228575</v>
       </c>
       <c r="J62" s="7" t="n">
-        <v>4768382.19</v>
+        <v>4768362.71</v>
       </c>
       <c r="K62" s="7" t="n">
-        <v>18298565.86</v>
+        <v>18298456.24</v>
       </c>
       <c r="L62" s="6" t="n">
         <v>1044160000</v>
@@ -3406,7 +3406,7 @@
         <v>696106.67</v>
       </c>
       <c r="N62" s="6" t="n">
-        <v>33556262210</v>
+        <v>33556068575</v>
       </c>
     </row>
     <row r="63">
@@ -3469,7 +3469,7 @@
         </is>
       </c>
       <c r="C64" s="6" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D64" s="7" t="n">
         <v>18350.59</v>
@@ -3478,31 +3478,31 @@
         <v>2327.11</v>
       </c>
       <c r="F64" s="7" t="n">
-        <v>213.12</v>
+        <v>212.81</v>
       </c>
       <c r="G64" s="7" t="n">
         <v>5505.19</v>
       </c>
       <c r="H64" s="7" t="n">
-        <v>26396.01</v>
+        <v>26395.7</v>
       </c>
       <c r="I64" s="6" t="n">
-        <v>39594015</v>
+        <v>39593550</v>
       </c>
       <c r="J64" s="7" t="n">
-        <v>16894.39</v>
+        <v>16894.34</v>
       </c>
       <c r="K64" s="7" t="n">
-        <v>9501.59</v>
+        <v>9501.33</v>
       </c>
       <c r="L64" s="6" t="n">
-        <v>143520000</v>
+        <v>141440000</v>
       </c>
       <c r="M64" s="7" t="n">
-        <v>95680</v>
+        <v>94293.33</v>
       </c>
       <c r="N64" s="6" t="n">
-        <v>-103925985</v>
+        <v>-101846450</v>
       </c>
     </row>
     <row r="65">
@@ -3526,22 +3526,22 @@
         <v>8666427.699999999</v>
       </c>
       <c r="F65" s="7" t="n">
-        <v>243618.46</v>
+        <v>243488.88</v>
       </c>
       <c r="G65" s="7" t="n">
         <v>3958244</v>
       </c>
       <c r="H65" s="7" t="n">
-        <v>26062436.52</v>
+        <v>26062306.94</v>
       </c>
       <c r="I65" s="6" t="n">
-        <v>39093654780</v>
+        <v>39093460410</v>
       </c>
       <c r="J65" s="7" t="n">
-        <v>6524379.07</v>
+        <v>6524355.28</v>
       </c>
       <c r="K65" s="7" t="n">
-        <v>19538057.56</v>
+        <v>19537951.78</v>
       </c>
       <c r="L65" s="6" t="n">
         <v>1058720000</v>
@@ -3550,7 +3550,7 @@
         <v>705813.33</v>
       </c>
       <c r="N65" s="6" t="n">
-        <v>38034934780</v>
+        <v>38034740410</v>
       </c>
     </row>
     <row r="66">
@@ -3613,7 +3613,7 @@
         </is>
       </c>
       <c r="C67" s="6" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D67" s="7" t="n">
         <v>25170.04</v>
@@ -3622,31 +3622,31 @@
         <v>2289.25</v>
       </c>
       <c r="F67" s="7" t="n">
-        <v>214.47</v>
+        <v>214.16</v>
       </c>
       <c r="G67" s="7" t="n">
         <v>7551.02</v>
       </c>
       <c r="H67" s="7" t="n">
-        <v>35224.81</v>
+        <v>35224.5</v>
       </c>
       <c r="I67" s="6" t="n">
-        <v>52837215</v>
+        <v>52836750</v>
       </c>
       <c r="J67" s="7" t="n">
-        <v>20301.78</v>
+        <v>20301.71</v>
       </c>
       <c r="K67" s="7" t="n">
-        <v>14923.04</v>
+        <v>14922.79</v>
       </c>
       <c r="L67" s="6" t="n">
-        <v>143520000</v>
+        <v>141440000</v>
       </c>
       <c r="M67" s="7" t="n">
-        <v>95680</v>
+        <v>94293.33</v>
       </c>
       <c r="N67" s="6" t="n">
-        <v>-90682785</v>
+        <v>-88603250</v>
       </c>
     </row>
     <row r="68">
@@ -3757,7 +3757,7 @@
         </is>
       </c>
       <c r="C70" s="6" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D70" s="7" t="n">
         <v>26528.96</v>
@@ -3766,31 +3766,31 @@
         <v>3379.37</v>
       </c>
       <c r="F70" s="7" t="n">
-        <v>216.14</v>
+        <v>215.83</v>
       </c>
       <c r="G70" s="7" t="n">
         <v>7958.67</v>
       </c>
       <c r="H70" s="7" t="n">
-        <v>38083.12</v>
+        <v>38082.81</v>
       </c>
       <c r="I70" s="6" t="n">
-        <v>57124680</v>
+        <v>57124215</v>
       </c>
       <c r="J70" s="7" t="n">
-        <v>20348.28</v>
+        <v>20348.21</v>
       </c>
       <c r="K70" s="7" t="n">
-        <v>17734.86</v>
+        <v>17734.62</v>
       </c>
       <c r="L70" s="6" t="n">
-        <v>147680000</v>
+        <v>145600000</v>
       </c>
       <c r="M70" s="7" t="n">
-        <v>98453.33</v>
+        <v>97066.67</v>
       </c>
       <c r="N70" s="6" t="n">
-        <v>-90555320</v>
+        <v>-88475785</v>
       </c>
     </row>
     <row r="71">
@@ -3901,7 +3901,7 @@
         </is>
       </c>
       <c r="C73" s="6" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D73" s="7" t="n">
         <v>34885.37</v>
@@ -3910,31 +3910,31 @@
         <v>4011.15</v>
       </c>
       <c r="F73" s="7" t="n">
-        <v>217.47</v>
+        <v>217.16</v>
       </c>
       <c r="G73" s="7" t="n">
         <v>10465.58</v>
       </c>
       <c r="H73" s="7" t="n">
-        <v>49579.57</v>
+        <v>49579.26</v>
       </c>
       <c r="I73" s="6" t="n">
-        <v>74369355</v>
+        <v>74368890</v>
       </c>
       <c r="J73" s="7" t="n">
-        <v>27649.47</v>
+        <v>27649.38</v>
       </c>
       <c r="K73" s="7" t="n">
-        <v>21930.17</v>
+        <v>21929.95</v>
       </c>
       <c r="L73" s="6" t="n">
-        <v>149760000</v>
+        <v>147680000</v>
       </c>
       <c r="M73" s="7" t="n">
-        <v>99840</v>
+        <v>98453.33</v>
       </c>
       <c r="N73" s="6" t="n">
-        <v>-75390645</v>
+        <v>-73311110</v>
       </c>
     </row>
     <row r="74">
@@ -4045,7 +4045,7 @@
         </is>
       </c>
       <c r="C76" s="6" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D76" s="7" t="n">
         <v>27331.39</v>
@@ -4054,31 +4054,31 @@
         <v>3881.98</v>
       </c>
       <c r="F76" s="7" t="n">
-        <v>218.73</v>
+        <v>218.42</v>
       </c>
       <c r="G76" s="7" t="n">
         <v>8199.379999999999</v>
       </c>
       <c r="H76" s="7" t="n">
-        <v>39631.44</v>
+        <v>39631.13</v>
       </c>
       <c r="I76" s="6" t="n">
-        <v>59447160</v>
+        <v>59446695</v>
       </c>
       <c r="J76" s="7" t="n">
-        <v>25557.43</v>
+        <v>25557.33</v>
       </c>
       <c r="K76" s="7" t="n">
-        <v>14074.05</v>
+        <v>14073.84</v>
       </c>
       <c r="L76" s="6" t="n">
-        <v>153920000</v>
+        <v>151840000</v>
       </c>
       <c r="M76" s="7" t="n">
-        <v>102613.33</v>
+        <v>101226.67</v>
       </c>
       <c r="N76" s="6" t="n">
-        <v>-94472840</v>
+        <v>-92393305</v>
       </c>
     </row>
     <row r="77">
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="C79" s="6" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D79" s="7" t="n">
         <v>35517.73</v>
@@ -4198,31 +4198,31 @@
         <v>2197.3</v>
       </c>
       <c r="F79" s="7" t="n">
-        <v>220.28</v>
+        <v>219.97</v>
       </c>
       <c r="G79" s="7" t="n">
         <v>10655.35</v>
       </c>
       <c r="H79" s="7" t="n">
-        <v>48590.68</v>
+        <v>48590.37</v>
       </c>
       <c r="I79" s="6" t="n">
-        <v>72886020</v>
+        <v>72885555</v>
       </c>
       <c r="J79" s="7" t="n">
-        <v>32925.87</v>
+        <v>32925.77</v>
       </c>
       <c r="K79" s="7" t="n">
-        <v>15664.83</v>
+        <v>15664.62</v>
       </c>
       <c r="L79" s="6" t="n">
-        <v>160160000</v>
+        <v>158080000</v>
       </c>
       <c r="M79" s="7" t="n">
-        <v>106773.33</v>
+        <v>105386.67</v>
       </c>
       <c r="N79" s="6" t="n">
-        <v>-87273980</v>
+        <v>-85194445</v>
       </c>
     </row>
     <row r="80">
@@ -4333,7 +4333,7 @@
         </is>
       </c>
       <c r="C82" s="6" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D82" s="7" t="n">
         <v>48506.32</v>
@@ -4342,31 +4342,31 @@
         <v>6474.02</v>
       </c>
       <c r="F82" s="7" t="n">
-        <v>222.54</v>
+        <v>222.23</v>
       </c>
       <c r="G82" s="7" t="n">
         <v>14551.91</v>
       </c>
       <c r="H82" s="7" t="n">
-        <v>69754.81</v>
+        <v>69754.5</v>
       </c>
       <c r="I82" s="6" t="n">
-        <v>104632215</v>
+        <v>104631750</v>
       </c>
       <c r="J82" s="7" t="n">
-        <v>40157.45</v>
+        <v>40157.34</v>
       </c>
       <c r="K82" s="7" t="n">
-        <v>29597.44</v>
+        <v>29597.24</v>
       </c>
       <c r="L82" s="6" t="n">
-        <v>162240000</v>
+        <v>160160000</v>
       </c>
       <c r="M82" s="7" t="n">
-        <v>108160</v>
+        <v>106773.33</v>
       </c>
       <c r="N82" s="6" t="n">
-        <v>-57607785</v>
+        <v>-55528250</v>
       </c>
     </row>
     <row r="83">
@@ -4477,7 +4477,7 @@
         </is>
       </c>
       <c r="C85" s="6" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D85" s="7" t="n">
         <v>159336.18</v>
@@ -4486,31 +4486,31 @@
         <v>154374.85</v>
       </c>
       <c r="F85" s="7" t="n">
-        <v>224.99</v>
+        <v>224.68</v>
       </c>
       <c r="G85" s="7" t="n">
         <v>47800.89</v>
       </c>
       <c r="H85" s="7" t="n">
-        <v>361736.84</v>
+        <v>361736.53</v>
       </c>
       <c r="I85" s="6" t="n">
-        <v>542605260</v>
+        <v>542604795</v>
       </c>
       <c r="J85" s="7" t="n">
-        <v>160578.96</v>
+        <v>160578.84</v>
       </c>
       <c r="K85" s="7" t="n">
-        <v>201157.82</v>
+        <v>201157.63</v>
       </c>
       <c r="L85" s="6" t="n">
-        <v>164320000</v>
+        <v>162240000</v>
       </c>
       <c r="M85" s="7" t="n">
-        <v>109546.67</v>
+        <v>108160</v>
       </c>
       <c r="N85" s="6" t="n">
-        <v>378285260</v>
+        <v>380364795</v>
       </c>
     </row>
     <row r="86">
@@ -4621,7 +4621,7 @@
         </is>
       </c>
       <c r="C88" s="6" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D88" s="7" t="n">
         <v>155305.4</v>
@@ -4630,31 +4630,31 @@
         <v>7110.47</v>
       </c>
       <c r="F88" s="7" t="n">
-        <v>228.8</v>
+        <v>228.49</v>
       </c>
       <c r="G88" s="7" t="n">
         <v>46591.62</v>
       </c>
       <c r="H88" s="7" t="n">
-        <v>209236.29</v>
+        <v>209235.98</v>
       </c>
       <c r="I88" s="6" t="n">
-        <v>313854435</v>
+        <v>313853970</v>
       </c>
       <c r="J88" s="7" t="n">
-        <v>97783.02</v>
+        <v>97782.89</v>
       </c>
       <c r="K88" s="7" t="n">
-        <v>111453.29</v>
+        <v>111453.1</v>
       </c>
       <c r="L88" s="6" t="n">
-        <v>166400000</v>
+        <v>164320000</v>
       </c>
       <c r="M88" s="7" t="n">
-        <v>110933.33</v>
+        <v>109546.67</v>
       </c>
       <c r="N88" s="6" t="n">
-        <v>147454435</v>
+        <v>149533970</v>
       </c>
     </row>
     <row r="89">
@@ -4678,22 +4678,22 @@
         <v>10418257.28</v>
       </c>
       <c r="F89" s="7" t="n">
-        <v>278845.02</v>
+        <v>278708.03</v>
       </c>
       <c r="G89" s="7" t="n">
         <v>6028865.88</v>
       </c>
       <c r="H89" s="7" t="n">
-        <v>36822187.7</v>
+        <v>36822050.71</v>
       </c>
       <c r="I89" s="6" t="n">
-        <v>55233281550</v>
+        <v>55233076065</v>
       </c>
       <c r="J89" s="7" t="n">
-        <v>14953161.69</v>
+        <v>14953126.95</v>
       </c>
       <c r="K89" s="7" t="n">
-        <v>21869026.12</v>
+        <v>21868923.86</v>
       </c>
       <c r="L89" s="6" t="n">
         <v>1089920000</v>
@@ -4702,7 +4702,7 @@
         <v>726613.33</v>
       </c>
       <c r="N89" s="6" t="n">
-        <v>54143361550</v>
+        <v>54143156065</v>
       </c>
     </row>
     <row r="90">
@@ -4765,7 +4765,7 @@
         </is>
       </c>
       <c r="C91" s="6" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D91" s="7" t="n">
         <v>140860.71</v>
@@ -4774,31 +4774,31 @@
         <v>42263.1</v>
       </c>
       <c r="F91" s="7" t="n">
-        <v>237.96</v>
+        <v>237.65</v>
       </c>
       <c r="G91" s="7" t="n">
         <v>42258.21</v>
       </c>
       <c r="H91" s="7" t="n">
-        <v>225619.98</v>
+        <v>225619.67</v>
       </c>
       <c r="I91" s="6" t="n">
-        <v>338429970</v>
+        <v>338429505</v>
       </c>
       <c r="J91" s="7" t="n">
-        <v>90911.62</v>
+        <v>90911.49000000001</v>
       </c>
       <c r="K91" s="7" t="n">
-        <v>134708.36</v>
+        <v>134708.17</v>
       </c>
       <c r="L91" s="6" t="n">
-        <v>170560000</v>
+        <v>168480000</v>
       </c>
       <c r="M91" s="7" t="n">
-        <v>113706.67</v>
+        <v>112320</v>
       </c>
       <c r="N91" s="6" t="n">
-        <v>167869970</v>
+        <v>169949505</v>
       </c>
     </row>
     <row r="92">
@@ -4822,22 +4822,22 @@
         <v>10319142.07</v>
       </c>
       <c r="F92" s="7" t="n">
-        <v>280694.12</v>
+        <v>280556.17</v>
       </c>
       <c r="G92" s="7" t="n">
         <v>6290309.18</v>
       </c>
       <c r="H92" s="7" t="n">
-        <v>37857842.78</v>
+        <v>37857704.83</v>
       </c>
       <c r="I92" s="6" t="n">
-        <v>56786764170</v>
+        <v>56786557245</v>
       </c>
       <c r="J92" s="7" t="n">
-        <v>15833263.7</v>
+        <v>15833230.11</v>
       </c>
       <c r="K92" s="7" t="n">
-        <v>22024579.09</v>
+        <v>22024474.74</v>
       </c>
       <c r="L92" s="6" t="n">
         <v>1089920000</v>
@@ -4846,7 +4846,7 @@
         <v>726613.33</v>
       </c>
       <c r="N92" s="6" t="n">
-        <v>55696844170</v>
+        <v>55696637245</v>
       </c>
     </row>
     <row r="93">
@@ -4909,7 +4909,7 @@
         </is>
       </c>
       <c r="C94" s="6" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D94" s="7" t="n">
         <v>130921.78</v>
@@ -4918,31 +4918,31 @@
         <v>10760.01</v>
       </c>
       <c r="F94" s="7" t="n">
-        <v>241.48</v>
+        <v>241.17</v>
       </c>
       <c r="G94" s="7" t="n">
         <v>39276.53</v>
       </c>
       <c r="H94" s="7" t="n">
-        <v>181199.87</v>
+        <v>181199.56</v>
       </c>
       <c r="I94" s="6" t="n">
-        <v>271799805</v>
+        <v>271799340</v>
       </c>
       <c r="J94" s="7" t="n">
-        <v>78354.06</v>
+        <v>78353.92999999999</v>
       </c>
       <c r="K94" s="7" t="n">
-        <v>102845.84</v>
+        <v>102845.65</v>
       </c>
       <c r="L94" s="6" t="n">
-        <v>170560000</v>
+        <v>168480000</v>
       </c>
       <c r="M94" s="7" t="n">
-        <v>113706.67</v>
+        <v>112320</v>
       </c>
       <c r="N94" s="6" t="n">
-        <v>101239805</v>
+        <v>103319340</v>
       </c>
     </row>
   </sheetData>

--- a/NBS FINAL delivery/03_Excel_Deliveries/9_NBS_Accounts_Domestic_and_GNI.xlsx
+++ b/NBS FINAL delivery/03_Excel_Deliveries/9_NBS_Accounts_Domestic_and_GNI.xlsx
@@ -512,7 +512,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01T00:10:26.191025+00:00</t>
+          <t>2026-09-01T00:38:12.797681+00:00</t>
         </is>
       </c>
     </row>
@@ -1150,16 +1150,16 @@
         <v>2077791.17</v>
       </c>
       <c r="F14" s="7" t="n">
-        <v>77213.86</v>
+        <v>77246.02</v>
       </c>
       <c r="G14" s="7" t="n">
         <v>578107.4399999999</v>
       </c>
       <c r="H14" s="7" t="n">
-        <v>4660137.1</v>
+        <v>4660169.26</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>6990205650</v>
+        <v>6990253890</v>
       </c>
       <c r="L14" s="6" t="n">
         <v>750880000</v>
@@ -1168,7 +1168,7 @@
         <v>500586.67</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>6239325650</v>
+        <v>6239373890</v>
       </c>
     </row>
     <row r="15">
@@ -1276,16 +1276,16 @@
         <v>2286773.03</v>
       </c>
       <c r="F17" s="7" t="n">
-        <v>89043.5</v>
+        <v>89097.19</v>
       </c>
       <c r="G17" s="7" t="n">
         <v>679791.3</v>
       </c>
       <c r="H17" s="7" t="n">
-        <v>5321578.81</v>
+        <v>5321632.5</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>7982368215</v>
+        <v>7982448750</v>
       </c>
       <c r="L17" s="6" t="n">
         <v>802880000</v>
@@ -1294,7 +1294,7 @@
         <v>535253.33</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>7179488215</v>
+        <v>7179568750</v>
       </c>
     </row>
     <row r="18">
@@ -1402,16 +1402,16 @@
         <v>2685417.57</v>
       </c>
       <c r="F20" s="7" t="n">
-        <v>104719.51</v>
+        <v>104788.44</v>
       </c>
       <c r="G20" s="7" t="n">
         <v>774340.54</v>
       </c>
       <c r="H20" s="7" t="n">
-        <v>6145612.73</v>
+        <v>6145681.66</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>9218419095</v>
+        <v>9218522490</v>
       </c>
       <c r="L20" s="6" t="n">
         <v>848640000</v>
@@ -1420,7 +1420,7 @@
         <v>565760</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>8369779095</v>
+        <v>8369882490</v>
       </c>
     </row>
     <row r="21">
@@ -1522,22 +1522,22 @@
         <v>420</v>
       </c>
       <c r="D23" s="7" t="n">
-        <v>2279842.09</v>
+        <v>2294029.02</v>
       </c>
       <c r="E23" s="7" t="n">
         <v>3312261.02</v>
       </c>
       <c r="F23" s="7" t="n">
-        <v>120704.49</v>
+        <v>120783.98</v>
       </c>
       <c r="G23" s="7" t="n">
-        <v>683952.67</v>
+        <v>688208.75</v>
       </c>
       <c r="H23" s="7" t="n">
-        <v>6396760.35</v>
+        <v>6415282.85</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>9595140525</v>
+        <v>9622924275</v>
       </c>
       <c r="L23" s="6" t="n">
         <v>873600000</v>
@@ -1546,7 +1546,7 @@
         <v>582400</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>8721540525</v>
+        <v>8749324275</v>
       </c>
     </row>
     <row r="24">
@@ -1654,22 +1654,22 @@
         <v>3334436.3</v>
       </c>
       <c r="F26" s="7" t="n">
-        <v>135857.72</v>
+        <v>135947.53</v>
       </c>
       <c r="G26" s="7" t="n">
         <v>809489.02</v>
       </c>
       <c r="H26" s="7" t="n">
-        <v>6978079.05</v>
+        <v>6978168.86</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>10467118575</v>
+        <v>10467253290</v>
       </c>
       <c r="J26" s="7" t="n">
-        <v>290108.6</v>
+        <v>290110.74</v>
       </c>
       <c r="K26" s="7" t="n">
-        <v>6687970.5</v>
+        <v>6688058.17</v>
       </c>
       <c r="L26" s="6" t="n">
         <v>886080000</v>
@@ -1678,7 +1678,7 @@
         <v>590720</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>9581038575</v>
+        <v>9581173290</v>
       </c>
     </row>
     <row r="27">
@@ -1798,22 +1798,22 @@
         <v>3710377.41</v>
       </c>
       <c r="F29" s="7" t="n">
-        <v>149911.98</v>
+        <v>150010.07</v>
       </c>
       <c r="G29" s="7" t="n">
         <v>868800.98</v>
       </c>
       <c r="H29" s="7" t="n">
-        <v>7625093.38</v>
+        <v>7625191.47</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>11437640070</v>
+        <v>11437787205</v>
       </c>
       <c r="J29" s="7" t="n">
-        <v>305603.41</v>
+        <v>305605.32</v>
       </c>
       <c r="K29" s="7" t="n">
-        <v>7319490.09</v>
+        <v>7319586.27</v>
       </c>
       <c r="L29" s="6" t="n">
         <v>904800000</v>
@@ -1822,7 +1822,7 @@
         <v>603200</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>10532840070</v>
+        <v>10532987205</v>
       </c>
     </row>
     <row r="30">
@@ -1942,22 +1942,22 @@
         <v>4074651.28</v>
       </c>
       <c r="F32" s="7" t="n">
-        <v>164256.94</v>
+        <v>164363.14</v>
       </c>
       <c r="G32" s="7" t="n">
         <v>1357890.32</v>
       </c>
       <c r="H32" s="7" t="n">
-        <v>10123099.63</v>
+        <v>10123205.83</v>
       </c>
       <c r="I32" s="6" t="n">
-        <v>15184649445</v>
+        <v>15184808745</v>
       </c>
       <c r="J32" s="7" t="n">
-        <v>437611.87</v>
+        <v>445839.47</v>
       </c>
       <c r="K32" s="7" t="n">
-        <v>9685487.85</v>
+        <v>9677366.449999999</v>
       </c>
       <c r="L32" s="6" t="n">
         <v>911040000</v>
@@ -1966,7 +1966,7 @@
         <v>607360</v>
       </c>
       <c r="N32" s="6" t="n">
-        <v>14273609445</v>
+        <v>14273768745</v>
       </c>
     </row>
     <row r="33">
@@ -2002,10 +2002,10 @@
         <v>3365327745</v>
       </c>
       <c r="J33" s="7" t="n">
-        <v>52531.94</v>
+        <v>52589.58</v>
       </c>
       <c r="K33" s="7" t="n">
-        <v>2191019.89</v>
+        <v>2190962.31</v>
       </c>
       <c r="L33" s="6" t="n">
         <v>218400000</v>
@@ -2050,10 +2050,10 @@
         <v>9204735</v>
       </c>
       <c r="J34" s="7" t="n">
-        <v>2047.99</v>
+        <v>2048.03</v>
       </c>
       <c r="K34" s="7" t="n">
-        <v>4088.5</v>
+        <v>4088.47</v>
       </c>
       <c r="L34" s="6" t="n">
         <v>106080000</v>
@@ -2086,22 +2086,22 @@
         <v>6120897.06</v>
       </c>
       <c r="F35" s="7" t="n">
-        <v>179631.52</v>
+        <v>179743.67</v>
       </c>
       <c r="G35" s="7" t="n">
         <v>1550334.92</v>
       </c>
       <c r="H35" s="7" t="n">
-        <v>13018646.5</v>
+        <v>13018758.65</v>
       </c>
       <c r="I35" s="6" t="n">
-        <v>19527969750</v>
+        <v>19528137975</v>
       </c>
       <c r="J35" s="7" t="n">
-        <v>803529.27</v>
+        <v>803532.39</v>
       </c>
       <c r="K35" s="7" t="n">
-        <v>12215117.11</v>
+        <v>12215226.14</v>
       </c>
       <c r="L35" s="6" t="n">
         <v>938080000</v>
@@ -2110,7 +2110,7 @@
         <v>625386.67</v>
       </c>
       <c r="N35" s="6" t="n">
-        <v>18589889750</v>
+        <v>18590057975</v>
       </c>
     </row>
     <row r="36">
@@ -2224,28 +2224,28 @@
         <v>457</v>
       </c>
       <c r="D38" s="7" t="n">
-        <v>5990704.91</v>
+        <v>6011403.56</v>
       </c>
       <c r="E38" s="7" t="n">
         <v>5398930.72</v>
       </c>
       <c r="F38" s="7" t="n">
-        <v>194044.06</v>
+        <v>194162.12</v>
       </c>
       <c r="G38" s="7" t="n">
-        <v>1797211.59</v>
+        <v>1803421.18</v>
       </c>
       <c r="H38" s="7" t="n">
-        <v>13380891.34</v>
+        <v>13407917.64</v>
       </c>
       <c r="I38" s="6" t="n">
-        <v>20071337010</v>
+        <v>20111876460</v>
       </c>
       <c r="J38" s="7" t="n">
-        <v>784622.03</v>
+        <v>787421.37</v>
       </c>
       <c r="K38" s="7" t="n">
-        <v>12596269.1</v>
+        <v>12620496.06</v>
       </c>
       <c r="L38" s="6" t="n">
         <v>950560000</v>
@@ -2254,7 +2254,7 @@
         <v>633706.67</v>
       </c>
       <c r="N38" s="6" t="n">
-        <v>19120777010</v>
+        <v>19161316460</v>
       </c>
     </row>
     <row r="39">
@@ -2374,22 +2374,22 @@
         <v>5783265.17</v>
       </c>
       <c r="F41" s="7" t="n">
-        <v>201825.15</v>
+        <v>201947.05</v>
       </c>
       <c r="G41" s="7" t="n">
         <v>2036113.31</v>
       </c>
       <c r="H41" s="7" t="n">
-        <v>14808247.97</v>
+        <v>14808369.87</v>
       </c>
       <c r="I41" s="6" t="n">
-        <v>22212371955</v>
+        <v>22212554805</v>
       </c>
       <c r="J41" s="7" t="n">
-        <v>924900.54</v>
+        <v>924903.63</v>
       </c>
       <c r="K41" s="7" t="n">
-        <v>13883347.35</v>
+        <v>13883466.15</v>
       </c>
       <c r="L41" s="6" t="n">
         <v>958880000</v>
@@ -2398,7 +2398,7 @@
         <v>639253.33</v>
       </c>
       <c r="N41" s="6" t="n">
-        <v>21253491955</v>
+        <v>21253674805</v>
       </c>
     </row>
     <row r="42">
@@ -2518,22 +2518,22 @@
         <v>7479496.73</v>
       </c>
       <c r="F44" s="7" t="n">
-        <v>208070.53</v>
+        <v>208194.32</v>
       </c>
       <c r="G44" s="7" t="n">
         <v>2373149.74</v>
       </c>
       <c r="H44" s="7" t="n">
-        <v>17971216.23</v>
+        <v>17971340.03</v>
       </c>
       <c r="I44" s="6" t="n">
-        <v>26956824345</v>
+        <v>26957010045</v>
       </c>
       <c r="J44" s="7" t="n">
-        <v>1025376.23</v>
+        <v>1025380.55</v>
       </c>
       <c r="K44" s="7" t="n">
-        <v>16945840.03</v>
+        <v>16945959.49</v>
       </c>
       <c r="L44" s="6" t="n">
         <v>981760000</v>
@@ -2542,7 +2542,7 @@
         <v>654506.67</v>
       </c>
       <c r="N44" s="6" t="n">
-        <v>25975064345</v>
+        <v>25975250045</v>
       </c>
     </row>
     <row r="45">
@@ -2662,22 +2662,22 @@
         <v>7530257.12</v>
       </c>
       <c r="F47" s="7" t="n">
-        <v>213314.1</v>
+        <v>213439.62</v>
       </c>
       <c r="G47" s="7" t="n">
         <v>2646039.91</v>
       </c>
       <c r="H47" s="7" t="n">
-        <v>19209744.17</v>
+        <v>19209869.69</v>
       </c>
       <c r="I47" s="6" t="n">
-        <v>28814616255</v>
+        <v>28814804535</v>
       </c>
       <c r="J47" s="7" t="n">
-        <v>1374252.33</v>
+        <v>1374258.37</v>
       </c>
       <c r="K47" s="7" t="n">
-        <v>17835491.85</v>
+        <v>17835611.33</v>
       </c>
       <c r="L47" s="6" t="n">
         <v>994240000</v>
@@ -2686,7 +2686,7 @@
         <v>662826.67</v>
       </c>
       <c r="N47" s="6" t="n">
-        <v>27820376255</v>
+        <v>27820564535</v>
       </c>
     </row>
     <row r="48">
@@ -2806,22 +2806,22 @@
         <v>7051877.6</v>
       </c>
       <c r="F50" s="7" t="n">
-        <v>217965.21</v>
+        <v>218092</v>
       </c>
       <c r="G50" s="7" t="n">
         <v>3072893.64</v>
       </c>
       <c r="H50" s="7" t="n">
-        <v>20585715.28</v>
+        <v>20585842.07</v>
       </c>
       <c r="I50" s="6" t="n">
-        <v>30878572920</v>
+        <v>30878763105</v>
       </c>
       <c r="J50" s="7" t="n">
-        <v>1941498.16</v>
+        <v>1941506.83</v>
       </c>
       <c r="K50" s="7" t="n">
-        <v>18644217.16</v>
+        <v>18644335.28</v>
       </c>
       <c r="L50" s="6" t="n">
         <v>1006720000</v>
@@ -2830,7 +2830,7 @@
         <v>671146.67</v>
       </c>
       <c r="N50" s="6" t="n">
-        <v>29871852920</v>
+        <v>29872043105</v>
       </c>
     </row>
     <row r="51">
@@ -2950,22 +2950,22 @@
         <v>7877503.91</v>
       </c>
       <c r="F53" s="7" t="n">
-        <v>222487.97</v>
+        <v>222615.46</v>
       </c>
       <c r="G53" s="7" t="n">
         <v>3676030.57</v>
       </c>
       <c r="H53" s="7" t="n">
-        <v>24029457.45</v>
+        <v>24029584.93</v>
       </c>
       <c r="I53" s="6" t="n">
-        <v>36044186175</v>
+        <v>36044377395</v>
       </c>
       <c r="J53" s="7" t="n">
-        <v>2711483.82</v>
+        <v>2711494.59</v>
       </c>
       <c r="K53" s="7" t="n">
-        <v>21317973.7</v>
+        <v>21318090.42</v>
       </c>
       <c r="L53" s="6" t="n">
         <v>1027520000</v>
@@ -2974,7 +2974,7 @@
         <v>685013.33</v>
       </c>
       <c r="N53" s="6" t="n">
-        <v>35016666175</v>
+        <v>35016857395</v>
       </c>
     </row>
     <row r="54">
@@ -3094,22 +3094,22 @@
         <v>7133093.46</v>
       </c>
       <c r="F56" s="7" t="n">
-        <v>227121.99</v>
+        <v>227250.03</v>
       </c>
       <c r="G56" s="7" t="n">
         <v>3471944.24</v>
       </c>
       <c r="H56" s="7" t="n">
-        <v>22405307.25</v>
+        <v>22405435.29</v>
       </c>
       <c r="I56" s="6" t="n">
-        <v>33607960875</v>
+        <v>33608152935</v>
       </c>
       <c r="J56" s="7" t="n">
-        <v>3338847.75</v>
+        <v>3394595.02</v>
       </c>
       <c r="K56" s="7" t="n">
-        <v>19066459.33</v>
+        <v>19010840.05</v>
       </c>
       <c r="L56" s="6" t="n">
         <v>1025440000</v>
@@ -3118,7 +3118,7 @@
         <v>683626.67</v>
       </c>
       <c r="N56" s="6" t="n">
-        <v>32582520875</v>
+        <v>32582712935</v>
       </c>
     </row>
     <row r="57">
@@ -3154,10 +3154,10 @@
         <v>7268048745</v>
       </c>
       <c r="J57" s="7" t="n">
-        <v>373950.84</v>
+        <v>375036.99</v>
       </c>
       <c r="K57" s="7" t="n">
-        <v>4471415</v>
+        <v>4470328.89</v>
       </c>
       <c r="L57" s="6" t="n">
         <v>235040000</v>
@@ -3202,10 +3202,10 @@
         <v>25974780</v>
       </c>
       <c r="J58" s="7" t="n">
-        <v>10091.2</v>
+        <v>10093.83</v>
       </c>
       <c r="K58" s="7" t="n">
-        <v>7225.29</v>
+        <v>7222.64</v>
       </c>
       <c r="L58" s="6" t="n">
         <v>128960000</v>
@@ -3238,22 +3238,22 @@
         <v>7166542.4</v>
       </c>
       <c r="F59" s="7" t="n">
-        <v>231945.65</v>
+        <v>232074.24</v>
       </c>
       <c r="G59" s="7" t="n">
         <v>3624583.79</v>
       </c>
       <c r="H59" s="7" t="n">
-        <v>23105017.44</v>
+        <v>23105146.04</v>
       </c>
       <c r="I59" s="6" t="n">
-        <v>34657526160</v>
+        <v>34657719060</v>
       </c>
       <c r="J59" s="7" t="n">
-        <v>4652146.15</v>
+        <v>4652166.29</v>
       </c>
       <c r="K59" s="7" t="n">
-        <v>18452871.44</v>
+        <v>18452979.89</v>
       </c>
       <c r="L59" s="6" t="n">
         <v>1031680000</v>
@@ -3262,7 +3262,7 @@
         <v>687786.67</v>
       </c>
       <c r="N59" s="6" t="n">
-        <v>33625846160</v>
+        <v>33626039060</v>
       </c>
     </row>
     <row r="60">
@@ -3382,22 +3382,22 @@
         <v>7423596.49</v>
       </c>
       <c r="F62" s="7" t="n">
-        <v>237545.84</v>
+        <v>237674.94</v>
       </c>
       <c r="G62" s="7" t="n">
         <v>3555156.21</v>
       </c>
       <c r="H62" s="7" t="n">
-        <v>23066819.05</v>
+        <v>23066948.14</v>
       </c>
       <c r="I62" s="6" t="n">
-        <v>34600228575</v>
+        <v>34600422210</v>
       </c>
       <c r="J62" s="7" t="n">
-        <v>4768362.71</v>
+        <v>4768382.19</v>
       </c>
       <c r="K62" s="7" t="n">
-        <v>18298456.24</v>
+        <v>18298565.86</v>
       </c>
       <c r="L62" s="6" t="n">
         <v>1044160000</v>
@@ -3406,7 +3406,7 @@
         <v>696106.67</v>
       </c>
       <c r="N62" s="6" t="n">
-        <v>33556068575</v>
+        <v>33556262210</v>
       </c>
     </row>
     <row r="63">
@@ -3526,22 +3526,22 @@
         <v>8666427.699999999</v>
       </c>
       <c r="F65" s="7" t="n">
-        <v>243488.88</v>
+        <v>243618.46</v>
       </c>
       <c r="G65" s="7" t="n">
         <v>3958244</v>
       </c>
       <c r="H65" s="7" t="n">
-        <v>26062306.94</v>
+        <v>26062436.52</v>
       </c>
       <c r="I65" s="6" t="n">
-        <v>39093460410</v>
+        <v>39093654780</v>
       </c>
       <c r="J65" s="7" t="n">
-        <v>6524355.28</v>
+        <v>6524379.07</v>
       </c>
       <c r="K65" s="7" t="n">
-        <v>19537951.78</v>
+        <v>19538057.56</v>
       </c>
       <c r="L65" s="6" t="n">
         <v>1058720000</v>
@@ -3550,7 +3550,7 @@
         <v>705813.33</v>
       </c>
       <c r="N65" s="6" t="n">
-        <v>38034740410</v>
+        <v>38034934780</v>
       </c>
     </row>
     <row r="66">
@@ -3814,22 +3814,22 @@
         <v>10084842.63</v>
       </c>
       <c r="F71" s="7" t="n">
-        <v>252130.39</v>
+        <v>254096.32</v>
       </c>
       <c r="G71" s="7" t="n">
         <v>4245375.88</v>
       </c>
       <c r="H71" s="7" t="n">
-        <v>28733602.18</v>
+        <v>28735568.11</v>
       </c>
       <c r="I71" s="6" t="n">
-        <v>43100403270</v>
+        <v>43103352165</v>
       </c>
       <c r="J71" s="7" t="n">
-        <v>9337782.35</v>
+        <v>9338726.949999999</v>
       </c>
       <c r="K71" s="7" t="n">
-        <v>19395819.93</v>
+        <v>19396841.28</v>
       </c>
       <c r="L71" s="6" t="n">
         <v>1067040000</v>
@@ -3838,7 +3838,7 @@
         <v>711360</v>
       </c>
       <c r="N71" s="6" t="n">
-        <v>42033363270</v>
+        <v>42036312165</v>
       </c>
     </row>
     <row r="72">
@@ -4387,7 +4387,7 @@
         <v>16355772.25</v>
       </c>
       <c r="E83" s="7" t="n">
-        <v>10821972.18</v>
+        <v>10728852.39</v>
       </c>
       <c r="F83" s="7" t="n">
         <v>231584.72</v>
@@ -4396,16 +4396,16 @@
         <v>4906731.66</v>
       </c>
       <c r="H83" s="7" t="n">
-        <v>32316060.81</v>
+        <v>32222941.02</v>
       </c>
       <c r="I83" s="6" t="n">
-        <v>48474091215</v>
+        <v>48334411530</v>
       </c>
       <c r="J83" s="7" t="n">
-        <v>13710103.21</v>
+        <v>13652707.54</v>
       </c>
       <c r="K83" s="7" t="n">
-        <v>18605957.69</v>
+        <v>18570233.57</v>
       </c>
       <c r="L83" s="6" t="n">
         <v>1087840000</v>
@@ -4414,7 +4414,7 @@
         <v>725226.67</v>
       </c>
       <c r="N83" s="6" t="n">
-        <v>47386251215</v>
+        <v>47246571530</v>
       </c>
     </row>
     <row r="84">
@@ -4678,22 +4678,22 @@
         <v>10418257.28</v>
       </c>
       <c r="F89" s="7" t="n">
-        <v>278708.03</v>
+        <v>278845.02</v>
       </c>
       <c r="G89" s="7" t="n">
         <v>6028865.88</v>
       </c>
       <c r="H89" s="7" t="n">
-        <v>36822050.71</v>
+        <v>36822187.7</v>
       </c>
       <c r="I89" s="6" t="n">
-        <v>55233076065</v>
+        <v>55233281550</v>
       </c>
       <c r="J89" s="7" t="n">
-        <v>14953126.95</v>
+        <v>14953161.69</v>
       </c>
       <c r="K89" s="7" t="n">
-        <v>21868923.86</v>
+        <v>21869026.12</v>
       </c>
       <c r="L89" s="6" t="n">
         <v>1089920000</v>
@@ -4702,7 +4702,7 @@
         <v>726613.33</v>
       </c>
       <c r="N89" s="6" t="n">
-        <v>54143156065</v>
+        <v>54143361550</v>
       </c>
     </row>
     <row r="90">
@@ -4822,22 +4822,22 @@
         <v>10319142.07</v>
       </c>
       <c r="F92" s="7" t="n">
-        <v>280556.17</v>
+        <v>280694.12</v>
       </c>
       <c r="G92" s="7" t="n">
         <v>6290309.18</v>
       </c>
       <c r="H92" s="7" t="n">
-        <v>37857704.83</v>
+        <v>37857842.78</v>
       </c>
       <c r="I92" s="6" t="n">
-        <v>56786557245</v>
+        <v>56786764170</v>
       </c>
       <c r="J92" s="7" t="n">
-        <v>15833230.11</v>
+        <v>15833263.7</v>
       </c>
       <c r="K92" s="7" t="n">
-        <v>22024474.74</v>
+        <v>22024579.09</v>
       </c>
       <c r="L92" s="6" t="n">
         <v>1089920000</v>
@@ -4846,7 +4846,7 @@
         <v>726613.33</v>
       </c>
       <c r="N92" s="6" t="n">
-        <v>55696637245</v>
+        <v>55696844170</v>
       </c>
     </row>
     <row r="93">

--- a/NBS FINAL delivery/03_Excel_Deliveries/9_NBS_Accounts_Domestic_and_GNI.xlsx
+++ b/NBS FINAL delivery/03_Excel_Deliveries/9_NBS_Accounts_Domestic_and_GNI.xlsx
@@ -512,7 +512,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01T00:38:12.797681+00:00</t>
+          <t>2026-09-01T01:12:21.685661+00:00</t>
         </is>
       </c>
     </row>
@@ -655,16 +655,16 @@
         <v>2348040.15</v>
       </c>
       <c r="I2" s="6" t="n">
-        <v>3522060225</v>
+        <v>720660482.84</v>
       </c>
       <c r="L2" s="6" t="n">
         <v>470080000</v>
       </c>
       <c r="M2" s="7" t="n">
-        <v>313386.67</v>
+        <v>1531604.33</v>
       </c>
       <c r="N2" s="6" t="n">
-        <v>3051980225</v>
+        <v>250580482.84</v>
       </c>
     </row>
     <row r="3">
@@ -697,16 +697,16 @@
         <v>663803.24</v>
       </c>
       <c r="I3" s="6" t="n">
-        <v>995704860</v>
+        <v>203734490.42</v>
       </c>
       <c r="L3" s="6" t="n">
         <v>83200000</v>
       </c>
       <c r="M3" s="7" t="n">
-        <v>55466.67</v>
+        <v>271080.41</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>912504860</v>
+        <v>120534490.42</v>
       </c>
     </row>
     <row r="4">
@@ -739,16 +739,16 @@
         <v>3934.09</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>5901135</v>
+        <v>1207450.9</v>
       </c>
       <c r="L4" s="6" t="n">
         <v>35360000</v>
       </c>
       <c r="M4" s="7" t="n">
-        <v>23573.33</v>
+        <v>115209.18</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>-29458865</v>
+        <v>-34152549.1</v>
       </c>
     </row>
     <row r="5">
@@ -766,31 +766,31 @@
         <v>317</v>
       </c>
       <c r="D5" s="7" t="n">
-        <v>1158908.69</v>
+        <v>1126603.53</v>
       </c>
       <c r="E5" s="7" t="n">
         <v>1393734.89</v>
       </c>
       <c r="F5" s="7" t="n">
-        <v>42745.73</v>
+        <v>41658.63</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>347672.68</v>
+        <v>337981</v>
       </c>
       <c r="H5" s="7" t="n">
-        <v>2943061.87</v>
+        <v>2899978.06</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>4414592805</v>
+        <v>890061266.1799999</v>
       </c>
       <c r="L5" s="6" t="n">
         <v>659360000</v>
       </c>
       <c r="M5" s="7" t="n">
-        <v>439573.33</v>
+        <v>2148312.26</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>3755232805</v>
+        <v>230701266.18</v>
       </c>
     </row>
     <row r="6">
@@ -808,31 +808,31 @@
         <v>71</v>
       </c>
       <c r="D6" s="7" t="n">
-        <v>448918.99</v>
+        <v>426859.33</v>
       </c>
       <c r="E6" s="7" t="n">
         <v>301263.81</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>18974.45</v>
+        <v>18783.87</v>
       </c>
       <c r="G6" s="7" t="n">
-        <v>134675.71</v>
+        <v>128057.79</v>
       </c>
       <c r="H6" s="7" t="n">
-        <v>903832.91</v>
+        <v>874964.87</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>1355749365</v>
+        <v>268544217.9</v>
       </c>
       <c r="L6" s="6" t="n">
         <v>147680000</v>
       </c>
       <c r="M6" s="7" t="n">
-        <v>98453.33</v>
+        <v>481167.73</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>1208069365</v>
+        <v>120864217.9</v>
       </c>
     </row>
     <row r="7">
@@ -850,31 +850,31 @@
         <v>34</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>1829.85</v>
+        <v>1966.78</v>
       </c>
       <c r="E7" s="7" t="n">
         <v>2768.99</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>32.55</v>
+        <v>32.32</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>548.96</v>
+        <v>590</v>
       </c>
       <c r="H7" s="7" t="n">
-        <v>5180.35</v>
+        <v>5358.14</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>7770525</v>
+        <v>1644520.33</v>
       </c>
       <c r="L7" s="6" t="n">
         <v>70720000</v>
       </c>
       <c r="M7" s="7" t="n">
-        <v>47146.67</v>
+        <v>230418.35</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>-62949475</v>
+        <v>-69075479.67</v>
       </c>
     </row>
     <row r="8">
@@ -892,31 +892,31 @@
         <v>348</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>1648929.32</v>
+        <v>1657304.07</v>
       </c>
       <c r="E8" s="7" t="n">
         <v>1666672.98</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>55865.5</v>
+        <v>53621.03</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>494678.84</v>
+        <v>497191.19</v>
       </c>
       <c r="H8" s="7" t="n">
-        <v>3866146.69</v>
+        <v>3874789.37</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>5799220035</v>
+        <v>1189250353.44</v>
       </c>
       <c r="L8" s="6" t="n">
         <v>723840000</v>
       </c>
       <c r="M8" s="7" t="n">
-        <v>482560</v>
+        <v>2358399.58</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>5075380035</v>
+        <v>465410353.44</v>
       </c>
     </row>
     <row r="9">
@@ -934,31 +934,31 @@
         <v>84</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>476500.37</v>
+        <v>470683.28</v>
       </c>
       <c r="E9" s="7" t="n">
         <v>335648.64</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>19688.62</v>
+        <v>19451.01</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>142950.09</v>
+        <v>141204.93</v>
       </c>
       <c r="H9" s="7" t="n">
-        <v>974787.67</v>
+        <v>966987.9</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>1462181505</v>
+        <v>296787926.27</v>
       </c>
       <c r="L9" s="6" t="n">
         <v>174720000</v>
       </c>
       <c r="M9" s="7" t="n">
-        <v>116480</v>
+        <v>569268.86</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>1287461505</v>
+        <v>122067926.27</v>
       </c>
     </row>
     <row r="10">
@@ -976,31 +976,31 @@
         <v>39</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>1292.33</v>
+        <v>1366.05</v>
       </c>
       <c r="E10" s="7" t="n">
         <v>2825.03</v>
       </c>
       <c r="F10" s="7" t="n">
-        <v>59.64</v>
+        <v>59.23</v>
       </c>
       <c r="G10" s="7" t="n">
-        <v>387.68</v>
+        <v>409.83</v>
       </c>
       <c r="H10" s="7" t="n">
-        <v>4564.73</v>
+        <v>4660.14</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>6847095</v>
+        <v>1430290.17</v>
       </c>
       <c r="L10" s="6" t="n">
         <v>81120000</v>
       </c>
       <c r="M10" s="7" t="n">
-        <v>54080</v>
+        <v>264303.4</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>-74272905</v>
+        <v>-79689709.83</v>
       </c>
     </row>
     <row r="11">
@@ -1018,31 +1018,31 @@
         <v>354</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>1979440.3</v>
+        <v>1757342.62</v>
       </c>
       <c r="E11" s="7" t="n">
         <v>2248340.15</v>
       </c>
       <c r="F11" s="7" t="n">
-        <v>66819.48</v>
+        <v>62927.47</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>593831.9300000001</v>
+        <v>527202.84</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>4888432.06</v>
+        <v>4595813.2</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>7332648090</v>
+        <v>1410546987.34</v>
       </c>
       <c r="L11" s="6" t="n">
         <v>736320000</v>
       </c>
       <c r="M11" s="7" t="n">
-        <v>490880</v>
+        <v>2399061.64</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>6596328090</v>
+        <v>674226987.34</v>
       </c>
     </row>
     <row r="12">
@@ -1060,31 +1060,31 @@
         <v>85</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>532221.88</v>
+        <v>525128.17</v>
       </c>
       <c r="E12" s="7" t="n">
         <v>333264.07</v>
       </c>
       <c r="F12" s="7" t="n">
-        <v>20756.08</v>
+        <v>20371.04</v>
       </c>
       <c r="G12" s="7" t="n">
-        <v>159666.63</v>
+        <v>157538.44</v>
       </c>
       <c r="H12" s="7" t="n">
-        <v>1045908.6</v>
+        <v>1036301.69</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>1568862900</v>
+        <v>318061714.69</v>
       </c>
       <c r="L12" s="6" t="n">
         <v>176800000</v>
       </c>
       <c r="M12" s="7" t="n">
-        <v>117866.67</v>
+        <v>576045.88</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>1392062900</v>
+        <v>141261714.69</v>
       </c>
     </row>
     <row r="13">
@@ -1102,31 +1102,31 @@
         <v>41</v>
       </c>
       <c r="D13" s="7" t="n">
-        <v>1391.37</v>
+        <v>1352.62</v>
       </c>
       <c r="E13" s="7" t="n">
         <v>2906.18</v>
       </c>
       <c r="F13" s="7" t="n">
-        <v>75.93000000000001</v>
+        <v>70.79000000000001</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>417.45</v>
+        <v>405.77</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>4790.89</v>
+        <v>4735.33</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>7186335</v>
+        <v>1453367.48</v>
       </c>
       <c r="L13" s="6" t="n">
         <v>85280000</v>
       </c>
       <c r="M13" s="7" t="n">
-        <v>56853.33</v>
+        <v>277857.42</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>-78093665</v>
+        <v>-83826632.52</v>
       </c>
     </row>
     <row r="14">
@@ -1144,31 +1144,31 @@
         <v>361</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>1927024.69</v>
+        <v>1970142.51</v>
       </c>
       <c r="E14" s="7" t="n">
         <v>2077791.17</v>
       </c>
       <c r="F14" s="7" t="n">
-        <v>77246.02</v>
+        <v>73625.13</v>
       </c>
       <c r="G14" s="7" t="n">
-        <v>578107.4399999999</v>
+        <v>591042.75</v>
       </c>
       <c r="H14" s="7" t="n">
-        <v>4660169.26</v>
+        <v>4712601.59</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>6990253890</v>
+        <v>1690928576.51</v>
       </c>
       <c r="L14" s="6" t="n">
         <v>750880000</v>
       </c>
       <c r="M14" s="7" t="n">
-        <v>500586.67</v>
+        <v>2092695.3</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>6239373890</v>
+        <v>940048576.51</v>
       </c>
     </row>
     <row r="15">
@@ -1186,31 +1186,31 @@
         <v>86</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>630712.8199999999</v>
+        <v>584312.71</v>
       </c>
       <c r="E15" s="7" t="n">
         <v>330334.7</v>
       </c>
       <c r="F15" s="7" t="n">
-        <v>21736.2</v>
+        <v>21405.78</v>
       </c>
       <c r="G15" s="7" t="n">
-        <v>189213.84</v>
+        <v>175293.81</v>
       </c>
       <c r="H15" s="7" t="n">
-        <v>1171997.54</v>
+        <v>1111347.06</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>1757996310</v>
+        <v>398762438.6</v>
       </c>
       <c r="L15" s="6" t="n">
         <v>178880000</v>
       </c>
       <c r="M15" s="7" t="n">
-        <v>119253.33</v>
+        <v>498536.83</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>1579116310</v>
+        <v>219882438.6</v>
       </c>
     </row>
     <row r="16">
@@ -1228,31 +1228,31 @@
         <v>41</v>
       </c>
       <c r="D16" s="7" t="n">
-        <v>1225.57</v>
+        <v>1253.72</v>
       </c>
       <c r="E16" s="7" t="n">
         <v>2951.74</v>
       </c>
       <c r="F16" s="7" t="n">
-        <v>98.91</v>
+        <v>93</v>
       </c>
       <c r="G16" s="7" t="n">
-        <v>367.67</v>
+        <v>376.11</v>
       </c>
       <c r="H16" s="7" t="n">
-        <v>4643.9</v>
+        <v>4674.57</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>6965850</v>
+        <v>1677282.46</v>
       </c>
       <c r="L16" s="6" t="n">
         <v>85280000</v>
       </c>
       <c r="M16" s="7" t="n">
-        <v>56853.33</v>
+        <v>237674.54</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>-78314150</v>
+        <v>-83602717.54000001</v>
       </c>
     </row>
     <row r="17">
@@ -1270,31 +1270,31 @@
         <v>386</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>2265971.02</v>
+        <v>2099170.99</v>
       </c>
       <c r="E17" s="7" t="n">
         <v>2286773.03</v>
       </c>
       <c r="F17" s="7" t="n">
-        <v>89097.19</v>
+        <v>84930.64</v>
       </c>
       <c r="G17" s="7" t="n">
-        <v>679791.3</v>
+        <v>629751.38</v>
       </c>
       <c r="H17" s="7" t="n">
-        <v>5321632.5</v>
+        <v>5100625.99</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>7982448750</v>
+        <v>1830155611.47</v>
       </c>
       <c r="L17" s="6" t="n">
         <v>802880000</v>
       </c>
       <c r="M17" s="7" t="n">
-        <v>535253.33</v>
+        <v>2237618.8</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>7179568750</v>
+        <v>1027275611.47</v>
       </c>
     </row>
     <row r="18">
@@ -1312,31 +1312,31 @@
         <v>93</v>
       </c>
       <c r="D18" s="7" t="n">
-        <v>707531.3199999999</v>
+        <v>702181.35</v>
       </c>
       <c r="E18" s="7" t="n">
         <v>325861.7</v>
       </c>
       <c r="F18" s="7" t="n">
-        <v>22720.03</v>
+        <v>22396.88</v>
       </c>
       <c r="G18" s="7" t="n">
-        <v>212259.44</v>
+        <v>210654.43</v>
       </c>
       <c r="H18" s="7" t="n">
-        <v>1268372.55</v>
+        <v>1261094.36</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>1902558825</v>
+        <v>452493267.31</v>
       </c>
       <c r="L18" s="6" t="n">
         <v>193440000</v>
       </c>
       <c r="M18" s="7" t="n">
-        <v>128960</v>
+        <v>539115.41</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>1709118825</v>
+        <v>259053267.31</v>
       </c>
     </row>
     <row r="19">
@@ -1354,31 +1354,31 @@
         <v>43</v>
       </c>
       <c r="D19" s="7" t="n">
-        <v>1596.1</v>
+        <v>1633.58</v>
       </c>
       <c r="E19" s="7" t="n">
         <v>2992.92</v>
       </c>
       <c r="F19" s="7" t="n">
-        <v>122.83</v>
+        <v>117.64</v>
       </c>
       <c r="G19" s="7" t="n">
-        <v>478.78</v>
+        <v>490.06</v>
       </c>
       <c r="H19" s="7" t="n">
-        <v>5190.67</v>
+        <v>5234.2</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>7786005</v>
+        <v>1878083.3</v>
       </c>
       <c r="L19" s="6" t="n">
         <v>89440000</v>
       </c>
       <c r="M19" s="7" t="n">
-        <v>59626.67</v>
+        <v>249268.42</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>-81653995</v>
+        <v>-87561916.7</v>
       </c>
     </row>
     <row r="20">
@@ -1396,31 +1396,31 @@
         <v>408</v>
       </c>
       <c r="D20" s="7" t="n">
-        <v>2581135.11</v>
+        <v>2528800.16</v>
       </c>
       <c r="E20" s="7" t="n">
         <v>2685417.57</v>
       </c>
       <c r="F20" s="7" t="n">
-        <v>104788.44</v>
+        <v>99452.98</v>
       </c>
       <c r="G20" s="7" t="n">
-        <v>774340.54</v>
+        <v>758640.03</v>
       </c>
       <c r="H20" s="7" t="n">
-        <v>6145681.66</v>
+        <v>6072310.76</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>9218522490</v>
+        <v>2178805823.8</v>
       </c>
       <c r="L20" s="6" t="n">
         <v>848640000</v>
       </c>
       <c r="M20" s="7" t="n">
-        <v>565760</v>
+        <v>2365151.47</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>8369882490</v>
+        <v>1330165823.8</v>
       </c>
     </row>
     <row r="21">
@@ -1438,31 +1438,31 @@
         <v>95</v>
       </c>
       <c r="D21" s="7" t="n">
-        <v>728865.5699999999</v>
+        <v>708010.51</v>
       </c>
       <c r="E21" s="7" t="n">
         <v>334441.37</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>23878.73</v>
+        <v>23547.37</v>
       </c>
       <c r="G21" s="7" t="n">
-        <v>218659.68</v>
+        <v>212403.13</v>
       </c>
       <c r="H21" s="7" t="n">
-        <v>1305845.43</v>
+        <v>1278402.33</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>1958768145</v>
+        <v>458703540.03</v>
       </c>
       <c r="L21" s="6" t="n">
         <v>197600000</v>
       </c>
       <c r="M21" s="7" t="n">
-        <v>131733.33</v>
+        <v>550709.29</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>1761168145</v>
+        <v>261103540.03</v>
       </c>
     </row>
     <row r="22">
@@ -1480,31 +1480,31 @@
         <v>46</v>
       </c>
       <c r="D22" s="7" t="n">
-        <v>1283.81</v>
+        <v>1402.2</v>
       </c>
       <c r="E22" s="7" t="n">
         <v>3029.74</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>140.71</v>
+        <v>135.19</v>
       </c>
       <c r="G22" s="7" t="n">
-        <v>385.17</v>
+        <v>420.69</v>
       </c>
       <c r="H22" s="7" t="n">
-        <v>4839.43</v>
+        <v>4987.8</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>7259145</v>
+        <v>1789672.52</v>
       </c>
       <c r="L22" s="6" t="n">
         <v>95680000</v>
       </c>
       <c r="M22" s="7" t="n">
-        <v>63786.67</v>
+        <v>266659.23</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>-88420855</v>
+        <v>-93890327.48</v>
       </c>
     </row>
     <row r="23">
@@ -1519,34 +1519,34 @@
         </is>
       </c>
       <c r="C23" s="6" t="n">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="D23" s="7" t="n">
-        <v>2294029.02</v>
+        <v>2291185.9</v>
       </c>
       <c r="E23" s="7" t="n">
         <v>3312261.02</v>
       </c>
       <c r="F23" s="7" t="n">
-        <v>120783.98</v>
+        <v>115183.38</v>
       </c>
       <c r="G23" s="7" t="n">
-        <v>688208.75</v>
+        <v>687355.89</v>
       </c>
       <c r="H23" s="7" t="n">
-        <v>6415282.85</v>
+        <v>6405986.04</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>9622924275</v>
+        <v>2298531851.01</v>
       </c>
       <c r="L23" s="6" t="n">
-        <v>873600000</v>
+        <v>871520000</v>
       </c>
       <c r="M23" s="7" t="n">
-        <v>582400</v>
+        <v>2428917.81</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>8749324275</v>
+        <v>1427011851.01</v>
       </c>
     </row>
     <row r="24">
@@ -1564,31 +1564,31 @@
         <v>98</v>
       </c>
       <c r="D24" s="7" t="n">
-        <v>1017953.85</v>
+        <v>887504.38</v>
       </c>
       <c r="E24" s="7" t="n">
         <v>381423.59</v>
       </c>
       <c r="F24" s="7" t="n">
-        <v>24846.67</v>
+        <v>24525.58</v>
       </c>
       <c r="G24" s="7" t="n">
-        <v>305386.13</v>
+        <v>266251.29</v>
       </c>
       <c r="H24" s="7" t="n">
-        <v>1729610.2</v>
+        <v>1559705.04</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>2594415300</v>
+        <v>559637765.4</v>
       </c>
       <c r="L24" s="6" t="n">
         <v>203840000</v>
       </c>
       <c r="M24" s="7" t="n">
-        <v>135893.33</v>
+        <v>568100.11</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>2390575300</v>
+        <v>355797765.4</v>
       </c>
     </row>
     <row r="25">
@@ -1606,31 +1606,31 @@
         <v>46</v>
       </c>
       <c r="D25" s="7" t="n">
-        <v>1385.46</v>
+        <v>1357.53</v>
       </c>
       <c r="E25" s="7" t="n">
         <v>3048.14</v>
       </c>
       <c r="F25" s="7" t="n">
-        <v>150.9</v>
+        <v>147.63</v>
       </c>
       <c r="G25" s="7" t="n">
-        <v>415.66</v>
+        <v>407.26</v>
       </c>
       <c r="H25" s="7" t="n">
-        <v>5000.11</v>
+        <v>4960.57</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>7500165</v>
+        <v>1779902.12</v>
       </c>
       <c r="L25" s="6" t="n">
         <v>95680000</v>
       </c>
       <c r="M25" s="7" t="n">
-        <v>63786.67</v>
+        <v>266659.23</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>-88179835</v>
+        <v>-93900097.88</v>
       </c>
     </row>
     <row r="26">
@@ -1648,37 +1648,37 @@
         <v>426</v>
       </c>
       <c r="D26" s="7" t="n">
-        <v>2698296.15</v>
+        <v>2435024.52</v>
       </c>
       <c r="E26" s="7" t="n">
         <v>3334436.3</v>
       </c>
       <c r="F26" s="7" t="n">
-        <v>135947.53</v>
+        <v>130927.19</v>
       </c>
       <c r="G26" s="7" t="n">
-        <v>809489.02</v>
+        <v>730507.36</v>
       </c>
       <c r="H26" s="7" t="n">
-        <v>6978168.86</v>
+        <v>6630895.57</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>10467253290</v>
+        <v>2659983757.91</v>
       </c>
       <c r="J26" s="7" t="n">
-        <v>290110.74</v>
+        <v>273480.9</v>
       </c>
       <c r="K26" s="7" t="n">
-        <v>6688058.17</v>
+        <v>6357414.57</v>
       </c>
       <c r="L26" s="6" t="n">
         <v>886080000</v>
       </c>
       <c r="M26" s="7" t="n">
-        <v>590720</v>
+        <v>2208849.56</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>9581173290</v>
+        <v>1773903757.91</v>
       </c>
     </row>
     <row r="27">
@@ -1696,37 +1696,37 @@
         <v>101</v>
       </c>
       <c r="D27" s="7" t="n">
-        <v>958995.3199999999</v>
+        <v>963956.24</v>
       </c>
       <c r="E27" s="7" t="n">
         <v>391613.19</v>
       </c>
       <c r="F27" s="7" t="n">
-        <v>25717.39</v>
+        <v>25433.58</v>
       </c>
       <c r="G27" s="7" t="n">
-        <v>287698.63</v>
+        <v>289186.85</v>
       </c>
       <c r="H27" s="7" t="n">
-        <v>1664024.57</v>
+        <v>1670189.88</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>2496036855</v>
+        <v>669996670.36</v>
       </c>
       <c r="J27" s="7" t="n">
-        <v>44691.39</v>
+        <v>44921.05</v>
       </c>
       <c r="K27" s="7" t="n">
-        <v>1619333.19</v>
+        <v>1625268.8</v>
       </c>
       <c r="L27" s="6" t="n">
         <v>210080000</v>
       </c>
       <c r="M27" s="7" t="n">
-        <v>140053.33</v>
+        <v>523694.38</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>2285956855</v>
+        <v>459916670.36</v>
       </c>
     </row>
     <row r="28">
@@ -1744,37 +1744,37 @@
         <v>47</v>
       </c>
       <c r="D28" s="7" t="n">
-        <v>1884.11</v>
+        <v>1784.74</v>
       </c>
       <c r="E28" s="7" t="n">
         <v>3049.05</v>
       </c>
       <c r="F28" s="7" t="n">
-        <v>162.36</v>
+        <v>158.87</v>
       </c>
       <c r="G28" s="7" t="n">
-        <v>565.21</v>
+        <v>535.45</v>
       </c>
       <c r="H28" s="7" t="n">
-        <v>5660.78</v>
+        <v>5528.11</v>
       </c>
       <c r="I28" s="6" t="n">
-        <v>8491170</v>
+        <v>2217601.33</v>
       </c>
       <c r="J28" s="7" t="n">
-        <v>420.28</v>
+        <v>397.43</v>
       </c>
       <c r="K28" s="7" t="n">
-        <v>5240.47</v>
+        <v>5130.67</v>
       </c>
       <c r="L28" s="6" t="n">
         <v>97760000</v>
       </c>
       <c r="M28" s="7" t="n">
-        <v>65173.33</v>
+        <v>243699.36</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>-89268830</v>
+        <v>-95542398.67</v>
       </c>
     </row>
     <row r="29">
@@ -1792,37 +1792,37 @@
         <v>435</v>
       </c>
       <c r="D29" s="7" t="n">
-        <v>2896002.93</v>
+        <v>2856262.01</v>
       </c>
       <c r="E29" s="7" t="n">
         <v>3710377.41</v>
       </c>
       <c r="F29" s="7" t="n">
-        <v>150010.07</v>
+        <v>145273.88</v>
       </c>
       <c r="G29" s="7" t="n">
-        <v>868800.98</v>
+        <v>856878.46</v>
       </c>
       <c r="H29" s="7" t="n">
-        <v>7625191.47</v>
+        <v>7568791.9</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>11437787205</v>
+        <v>3036220870.68</v>
       </c>
       <c r="J29" s="7" t="n">
-        <v>305605.32</v>
+        <v>297718.76</v>
       </c>
       <c r="K29" s="7" t="n">
-        <v>7319586.27</v>
+        <v>7271073.09</v>
       </c>
       <c r="L29" s="6" t="n">
         <v>904800000</v>
       </c>
       <c r="M29" s="7" t="n">
-        <v>603200</v>
+        <v>2255515.39</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>10532987205</v>
+        <v>2131420870.68</v>
       </c>
     </row>
     <row r="30">
@@ -1840,37 +1840,37 @@
         <v>102</v>
       </c>
       <c r="D30" s="7" t="n">
-        <v>1563473.58</v>
+        <v>1389227.84</v>
       </c>
       <c r="E30" s="7" t="n">
         <v>411657.78</v>
       </c>
       <c r="F30" s="7" t="n">
-        <v>26624.46</v>
+        <v>26305.51</v>
       </c>
       <c r="G30" s="7" t="n">
-        <v>469042.06</v>
+        <v>416768.37</v>
       </c>
       <c r="H30" s="7" t="n">
-        <v>2470797.93</v>
+        <v>2243959.53</v>
       </c>
       <c r="I30" s="6" t="n">
-        <v>3706196895</v>
+        <v>900164365.46</v>
       </c>
       <c r="J30" s="7" t="n">
-        <v>33319.28</v>
+        <v>31302.54</v>
       </c>
       <c r="K30" s="7" t="n">
-        <v>2437478.61</v>
+        <v>2212656.93</v>
       </c>
       <c r="L30" s="6" t="n">
         <v>212160000</v>
       </c>
       <c r="M30" s="7" t="n">
-        <v>141440</v>
+        <v>528879.47</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>3494036895</v>
+        <v>688004365.46</v>
       </c>
     </row>
     <row r="31">
@@ -1888,37 +1888,37 @@
         <v>49</v>
       </c>
       <c r="D31" s="7" t="n">
-        <v>1768.15</v>
+        <v>2601.76</v>
       </c>
       <c r="E31" s="7" t="n">
         <v>3046.85</v>
       </c>
       <c r="F31" s="7" t="n">
-        <v>172.22</v>
+        <v>169.09</v>
       </c>
       <c r="G31" s="7" t="n">
-        <v>530.4400000000001</v>
+        <v>780.53</v>
       </c>
       <c r="H31" s="7" t="n">
-        <v>5517.65</v>
+        <v>6598.24</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>8276475</v>
+        <v>2646883.98</v>
       </c>
       <c r="J31" s="7" t="n">
-        <v>484.54</v>
+        <v>493.83</v>
       </c>
       <c r="K31" s="7" t="n">
-        <v>5033.12</v>
+        <v>6104.41</v>
       </c>
       <c r="L31" s="6" t="n">
         <v>101920000</v>
       </c>
       <c r="M31" s="7" t="n">
-        <v>67946.67</v>
+        <v>254069.55</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>-93643525</v>
+        <v>-99273116.02</v>
       </c>
     </row>
     <row r="32">
@@ -1936,37 +1936,37 @@
         <v>438</v>
       </c>
       <c r="D32" s="7" t="n">
-        <v>4526301.09</v>
+        <v>3707812.64</v>
       </c>
       <c r="E32" s="7" t="n">
         <v>4074651.28</v>
       </c>
       <c r="F32" s="7" t="n">
-        <v>164363.14</v>
+        <v>159594.43</v>
       </c>
       <c r="G32" s="7" t="n">
-        <v>1357890.32</v>
+        <v>1112343.77</v>
       </c>
       <c r="H32" s="7" t="n">
-        <v>10123205.83</v>
+        <v>9054402.279999999</v>
       </c>
       <c r="I32" s="6" t="n">
-        <v>15184808745</v>
+        <v>3632173474.62</v>
       </c>
       <c r="J32" s="7" t="n">
-        <v>445839.47</v>
+        <v>427325.98</v>
       </c>
       <c r="K32" s="7" t="n">
-        <v>9677366.449999999</v>
+        <v>8627076.32</v>
       </c>
       <c r="L32" s="6" t="n">
         <v>911040000</v>
       </c>
       <c r="M32" s="7" t="n">
-        <v>607360</v>
+        <v>2271070.67</v>
       </c>
       <c r="N32" s="6" t="n">
-        <v>14273768745</v>
+        <v>2721133474.62</v>
       </c>
     </row>
     <row r="33">
@@ -1984,37 +1984,37 @@
         <v>105</v>
       </c>
       <c r="D33" s="7" t="n">
-        <v>1337179.69</v>
+        <v>1336907.17</v>
       </c>
       <c r="E33" s="7" t="n">
         <v>477628.47</v>
       </c>
       <c r="F33" s="7" t="n">
-        <v>27589.82</v>
+        <v>27264.2</v>
       </c>
       <c r="G33" s="7" t="n">
-        <v>401153.89</v>
+        <v>401072.22</v>
       </c>
       <c r="H33" s="7" t="n">
-        <v>2243551.83</v>
+        <v>2242871.99</v>
       </c>
       <c r="I33" s="6" t="n">
-        <v>3365327745</v>
+        <v>899728098.79</v>
       </c>
       <c r="J33" s="7" t="n">
-        <v>52589.58</v>
+        <v>52115.06</v>
       </c>
       <c r="K33" s="7" t="n">
-        <v>2190962.31</v>
+        <v>2190756.93</v>
       </c>
       <c r="L33" s="6" t="n">
         <v>218400000</v>
       </c>
       <c r="M33" s="7" t="n">
-        <v>145600</v>
+        <v>544434.75</v>
       </c>
       <c r="N33" s="6" t="n">
-        <v>3146927745</v>
+        <v>681328098.79</v>
       </c>
     </row>
     <row r="34">
@@ -2032,37 +2032,37 @@
         <v>51</v>
       </c>
       <c r="D34" s="7" t="n">
-        <v>2230.37</v>
+        <v>2195.53</v>
       </c>
       <c r="E34" s="7" t="n">
         <v>3054.63</v>
       </c>
       <c r="F34" s="7" t="n">
-        <v>182.32</v>
+        <v>179.91</v>
       </c>
       <c r="G34" s="7" t="n">
-        <v>669.12</v>
+        <v>658.6900000000001</v>
       </c>
       <c r="H34" s="7" t="n">
-        <v>6136.49</v>
+        <v>6088.76</v>
       </c>
       <c r="I34" s="6" t="n">
-        <v>9204735</v>
+        <v>2442506.07</v>
       </c>
       <c r="J34" s="7" t="n">
-        <v>2048.03</v>
+        <v>2036.92</v>
       </c>
       <c r="K34" s="7" t="n">
-        <v>4088.47</v>
+        <v>4051.88</v>
       </c>
       <c r="L34" s="6" t="n">
         <v>106080000</v>
       </c>
       <c r="M34" s="7" t="n">
-        <v>70720</v>
+        <v>264439.74</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>-96875265</v>
+        <v>-103637493.93</v>
       </c>
     </row>
     <row r="35">
@@ -2080,37 +2080,37 @@
         <v>451</v>
       </c>
       <c r="D35" s="7" t="n">
-        <v>5167783.04</v>
+        <v>5112784.92</v>
       </c>
       <c r="E35" s="7" t="n">
         <v>6120897.06</v>
       </c>
       <c r="F35" s="7" t="n">
-        <v>179743.67</v>
+        <v>174629.17</v>
       </c>
       <c r="G35" s="7" t="n">
-        <v>1550334.92</v>
+        <v>1533835.43</v>
       </c>
       <c r="H35" s="7" t="n">
-        <v>13018758.65</v>
+        <v>12942146.53</v>
       </c>
       <c r="I35" s="6" t="n">
-        <v>19528137975</v>
+        <v>5191742080.51</v>
       </c>
       <c r="J35" s="7" t="n">
-        <v>803532.39</v>
+        <v>781788.71</v>
       </c>
       <c r="K35" s="7" t="n">
-        <v>12215226.14</v>
+        <v>12160357.73</v>
       </c>
       <c r="L35" s="6" t="n">
         <v>938080000</v>
       </c>
       <c r="M35" s="7" t="n">
-        <v>625386.67</v>
+        <v>2338476.88</v>
       </c>
       <c r="N35" s="6" t="n">
-        <v>18590057975</v>
+        <v>4253662080.51</v>
       </c>
     </row>
     <row r="36">
@@ -2128,37 +2128,37 @@
         <v>105</v>
       </c>
       <c r="D36" s="7" t="n">
-        <v>1649056.45</v>
+        <v>1520665.93</v>
       </c>
       <c r="E36" s="7" t="n">
         <v>521716.09</v>
       </c>
       <c r="F36" s="7" t="n">
-        <v>28516.67</v>
+        <v>28190.77</v>
       </c>
       <c r="G36" s="7" t="n">
-        <v>494716.91</v>
+        <v>456199.79</v>
       </c>
       <c r="H36" s="7" t="n">
-        <v>2694006.12</v>
+        <v>2526772.6</v>
       </c>
       <c r="I36" s="6" t="n">
-        <v>4041009180</v>
+        <v>1013614828.49</v>
       </c>
       <c r="J36" s="7" t="n">
-        <v>61636.71</v>
+        <v>59488.07</v>
       </c>
       <c r="K36" s="7" t="n">
-        <v>2632369.41</v>
+        <v>2467284.38</v>
       </c>
       <c r="L36" s="6" t="n">
         <v>218400000</v>
       </c>
       <c r="M36" s="7" t="n">
-        <v>145600</v>
+        <v>544434.75</v>
       </c>
       <c r="N36" s="6" t="n">
-        <v>3822609180</v>
+        <v>795214828.49</v>
       </c>
     </row>
     <row r="37">
@@ -2176,37 +2176,37 @@
         <v>54</v>
       </c>
       <c r="D37" s="7" t="n">
-        <v>5664.88</v>
+        <v>4481</v>
       </c>
       <c r="E37" s="7" t="n">
         <v>220.09</v>
       </c>
       <c r="F37" s="7" t="n">
-        <v>189.23</v>
+        <v>187.08</v>
       </c>
       <c r="G37" s="7" t="n">
-        <v>1699.47</v>
+        <v>1344.32</v>
       </c>
       <c r="H37" s="7" t="n">
-        <v>7773.66</v>
+        <v>6232.52</v>
       </c>
       <c r="I37" s="6" t="n">
-        <v>11660490</v>
+        <v>2500175.4</v>
       </c>
       <c r="J37" s="7" t="n">
-        <v>2920.17</v>
+        <v>2122.05</v>
       </c>
       <c r="K37" s="7" t="n">
-        <v>4853.52</v>
+        <v>4110.45</v>
       </c>
       <c r="L37" s="6" t="n">
         <v>112320000</v>
       </c>
       <c r="M37" s="7" t="n">
-        <v>74880</v>
+        <v>279995.01</v>
       </c>
       <c r="N37" s="6" t="n">
-        <v>-100659510</v>
+        <v>-109819824.6</v>
       </c>
     </row>
     <row r="38">
@@ -2224,37 +2224,37 @@
         <v>457</v>
       </c>
       <c r="D38" s="7" t="n">
-        <v>6011403.56</v>
+        <v>5639162.09</v>
       </c>
       <c r="E38" s="7" t="n">
         <v>5398930.72</v>
       </c>
       <c r="F38" s="7" t="n">
-        <v>194162.12</v>
+        <v>189159.28</v>
       </c>
       <c r="G38" s="7" t="n">
-        <v>1803421.18</v>
+        <v>1691748.64</v>
       </c>
       <c r="H38" s="7" t="n">
-        <v>13407917.64</v>
+        <v>12919000.72</v>
       </c>
       <c r="I38" s="6" t="n">
-        <v>20111876460</v>
+        <v>5503235926.71</v>
       </c>
       <c r="J38" s="7" t="n">
-        <v>787421.37</v>
+        <v>744299.16</v>
       </c>
       <c r="K38" s="7" t="n">
-        <v>12620496.06</v>
+        <v>12174701.66</v>
       </c>
       <c r="L38" s="6" t="n">
         <v>950560000</v>
       </c>
       <c r="M38" s="7" t="n">
-        <v>633706.67</v>
+        <v>2231466.27</v>
       </c>
       <c r="N38" s="6" t="n">
-        <v>19161316460</v>
+        <v>4552675926.71</v>
       </c>
     </row>
     <row r="39">
@@ -2272,37 +2272,37 @@
         <v>107</v>
       </c>
       <c r="D39" s="7" t="n">
-        <v>1526592.02</v>
+        <v>1567914.97</v>
       </c>
       <c r="E39" s="7" t="n">
         <v>690705.9399999999</v>
       </c>
       <c r="F39" s="7" t="n">
-        <v>29730.81</v>
+        <v>29283.09</v>
       </c>
       <c r="G39" s="7" t="n">
-        <v>457977.63</v>
+        <v>470374.51</v>
       </c>
       <c r="H39" s="7" t="n">
-        <v>2705006.45</v>
+        <v>2758278.44</v>
       </c>
       <c r="I39" s="6" t="n">
-        <v>4057509675</v>
+        <v>1174971449.87</v>
       </c>
       <c r="J39" s="7" t="n">
-        <v>86535.99000000001</v>
+        <v>82865.13</v>
       </c>
       <c r="K39" s="7" t="n">
-        <v>2618470.41</v>
+        <v>2675413.33</v>
       </c>
       <c r="L39" s="6" t="n">
         <v>222560000</v>
       </c>
       <c r="M39" s="7" t="n">
-        <v>148373.33</v>
+        <v>522465.84</v>
       </c>
       <c r="N39" s="6" t="n">
-        <v>3834949675</v>
+        <v>952411449.87</v>
       </c>
     </row>
     <row r="40">
@@ -2320,37 +2320,37 @@
         <v>54</v>
       </c>
       <c r="D40" s="7" t="n">
-        <v>5977.23</v>
+        <v>6202.42</v>
       </c>
       <c r="E40" s="7" t="n">
         <v>2946.58</v>
       </c>
       <c r="F40" s="7" t="n">
-        <v>195.99</v>
+        <v>193.73</v>
       </c>
       <c r="G40" s="7" t="n">
-        <v>1793.2</v>
+        <v>1860.72</v>
       </c>
       <c r="H40" s="7" t="n">
-        <v>10912.97</v>
+        <v>11203.44</v>
       </c>
       <c r="I40" s="6" t="n">
-        <v>16369455</v>
+        <v>4772441.37</v>
       </c>
       <c r="J40" s="7" t="n">
-        <v>2202.56</v>
+        <v>2324.24</v>
       </c>
       <c r="K40" s="7" t="n">
-        <v>8710.469999999999</v>
+        <v>8879.23</v>
       </c>
       <c r="L40" s="6" t="n">
         <v>112320000</v>
       </c>
       <c r="M40" s="7" t="n">
-        <v>74880</v>
+        <v>263674.35</v>
       </c>
       <c r="N40" s="6" t="n">
-        <v>-95950545</v>
+        <v>-107547558.63</v>
       </c>
     </row>
     <row r="41">
@@ -2368,37 +2368,37 @@
         <v>461</v>
       </c>
       <c r="D41" s="7" t="n">
-        <v>6787044.27</v>
+        <v>6403958.82</v>
       </c>
       <c r="E41" s="7" t="n">
         <v>5783265.17</v>
       </c>
       <c r="F41" s="7" t="n">
-        <v>201947.05</v>
+        <v>200112.7</v>
       </c>
       <c r="G41" s="7" t="n">
-        <v>2036113.31</v>
+        <v>1921187.59</v>
       </c>
       <c r="H41" s="7" t="n">
-        <v>14808369.87</v>
+        <v>14308524.48</v>
       </c>
       <c r="I41" s="6" t="n">
-        <v>22212554805</v>
+        <v>6095145257.99</v>
       </c>
       <c r="J41" s="7" t="n">
-        <v>924903.63</v>
+        <v>897650.3</v>
       </c>
       <c r="K41" s="7" t="n">
-        <v>13883466.15</v>
+        <v>13410874.07</v>
       </c>
       <c r="L41" s="6" t="n">
         <v>958880000</v>
       </c>
       <c r="M41" s="7" t="n">
-        <v>639253.33</v>
+        <v>2250997.7</v>
       </c>
       <c r="N41" s="6" t="n">
-        <v>21253674805</v>
+        <v>5136265257.99</v>
       </c>
     </row>
     <row r="42">
@@ -2416,37 +2416,37 @@
         <v>107</v>
       </c>
       <c r="D42" s="7" t="n">
-        <v>1510912.47</v>
+        <v>1489346.82</v>
       </c>
       <c r="E42" s="7" t="n">
         <v>604806.99</v>
       </c>
       <c r="F42" s="7" t="n">
-        <v>30670.68</v>
+        <v>30413.06</v>
       </c>
       <c r="G42" s="7" t="n">
-        <v>453273.77</v>
+        <v>446804.04</v>
       </c>
       <c r="H42" s="7" t="n">
-        <v>2599663.92</v>
+        <v>2571370.95</v>
       </c>
       <c r="I42" s="6" t="n">
-        <v>3899495880</v>
+        <v>1095352597.28</v>
       </c>
       <c r="J42" s="7" t="n">
-        <v>118882.04</v>
+        <v>114022.78</v>
       </c>
       <c r="K42" s="7" t="n">
-        <v>2480781.95</v>
+        <v>2457348.13</v>
       </c>
       <c r="L42" s="6" t="n">
         <v>222560000</v>
       </c>
       <c r="M42" s="7" t="n">
-        <v>148373.33</v>
+        <v>522465.84</v>
       </c>
       <c r="N42" s="6" t="n">
-        <v>3676935880</v>
+        <v>872792597.28</v>
       </c>
     </row>
     <row r="43">
@@ -2464,37 +2464,37 @@
         <v>58</v>
       </c>
       <c r="D43" s="7" t="n">
-        <v>5727.34</v>
+        <v>6132.47</v>
       </c>
       <c r="E43" s="7" t="n">
         <v>2872.89</v>
       </c>
       <c r="F43" s="7" t="n">
-        <v>199.88</v>
+        <v>199.36</v>
       </c>
       <c r="G43" s="7" t="n">
-        <v>1718.23</v>
+        <v>1839.74</v>
       </c>
       <c r="H43" s="7" t="n">
-        <v>10518.28</v>
+        <v>11044.43</v>
       </c>
       <c r="I43" s="6" t="n">
-        <v>15777420</v>
+        <v>4704706.29</v>
       </c>
       <c r="J43" s="7" t="n">
-        <v>2092.88</v>
+        <v>2227.88</v>
       </c>
       <c r="K43" s="7" t="n">
-        <v>8425.41</v>
+        <v>8816.65</v>
       </c>
       <c r="L43" s="6" t="n">
         <v>120640000</v>
       </c>
       <c r="M43" s="7" t="n">
-        <v>80426.67</v>
+        <v>283205.78</v>
       </c>
       <c r="N43" s="6" t="n">
-        <v>-104862580</v>
+        <v>-115935293.71</v>
       </c>
     </row>
     <row r="44">
@@ -2509,40 +2509,40 @@
         </is>
       </c>
       <c r="C44" s="6" t="n">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="D44" s="7" t="n">
-        <v>7910499.2</v>
+        <v>7403054.32</v>
       </c>
       <c r="E44" s="7" t="n">
         <v>7479496.73</v>
       </c>
       <c r="F44" s="7" t="n">
-        <v>208194.32</v>
+        <v>206239.71</v>
       </c>
       <c r="G44" s="7" t="n">
-        <v>2373149.74</v>
+        <v>2220916.32</v>
       </c>
       <c r="H44" s="7" t="n">
-        <v>17971340.03</v>
+        <v>17309707.06</v>
       </c>
       <c r="I44" s="6" t="n">
-        <v>26957010045</v>
+        <v>7373589013.42</v>
       </c>
       <c r="J44" s="7" t="n">
-        <v>1025380.55</v>
+        <v>1006523.75</v>
       </c>
       <c r="K44" s="7" t="n">
-        <v>16945959.49</v>
+        <v>16303183.23</v>
       </c>
       <c r="L44" s="6" t="n">
-        <v>981760000</v>
+        <v>979680000</v>
       </c>
       <c r="M44" s="7" t="n">
-        <v>654506.67</v>
+        <v>2299826.28</v>
       </c>
       <c r="N44" s="6" t="n">
-        <v>25975250045</v>
+        <v>6393909013.42</v>
       </c>
     </row>
     <row r="45">
@@ -2560,37 +2560,37 @@
         <v>109</v>
       </c>
       <c r="D45" s="7" t="n">
-        <v>1798208.88</v>
+        <v>1645127.67</v>
       </c>
       <c r="E45" s="7" t="n">
         <v>789224.41</v>
       </c>
       <c r="F45" s="7" t="n">
-        <v>31487.49</v>
+        <v>31197.15</v>
       </c>
       <c r="G45" s="7" t="n">
-        <v>539462.67</v>
+        <v>493538.34</v>
       </c>
       <c r="H45" s="7" t="n">
-        <v>3158383.42</v>
+        <v>2959087.58</v>
       </c>
       <c r="I45" s="6" t="n">
-        <v>4737575130</v>
+        <v>1260512127.33</v>
       </c>
       <c r="J45" s="7" t="n">
-        <v>124276.8</v>
+        <v>113217.85</v>
       </c>
       <c r="K45" s="7" t="n">
-        <v>3034106.6</v>
+        <v>2845869.67</v>
       </c>
       <c r="L45" s="6" t="n">
         <v>226720000</v>
       </c>
       <c r="M45" s="7" t="n">
-        <v>151146.67</v>
+        <v>532231.5600000001</v>
       </c>
       <c r="N45" s="6" t="n">
-        <v>4510855130</v>
+        <v>1033792127.33</v>
       </c>
     </row>
     <row r="46">
@@ -2608,37 +2608,37 @@
         <v>58</v>
       </c>
       <c r="D46" s="7" t="n">
-        <v>6173.38</v>
+        <v>5800.93</v>
       </c>
       <c r="E46" s="7" t="n">
         <v>2787.34</v>
       </c>
       <c r="F46" s="7" t="n">
-        <v>201.95</v>
+        <v>201.35</v>
       </c>
       <c r="G46" s="7" t="n">
-        <v>1851.98</v>
+        <v>1740.29</v>
       </c>
       <c r="H46" s="7" t="n">
-        <v>11014.69</v>
+        <v>10529.93</v>
       </c>
       <c r="I46" s="6" t="n">
-        <v>16522035</v>
+        <v>4485539.58</v>
       </c>
       <c r="J46" s="7" t="n">
-        <v>2089.68</v>
+        <v>1966.25</v>
       </c>
       <c r="K46" s="7" t="n">
-        <v>8925.059999999999</v>
+        <v>8563.65</v>
       </c>
       <c r="L46" s="6" t="n">
         <v>120640000</v>
       </c>
       <c r="M46" s="7" t="n">
-        <v>80426.67</v>
+        <v>283205.78</v>
       </c>
       <c r="N46" s="6" t="n">
-        <v>-104117965</v>
+        <v>-116154460.42</v>
       </c>
     </row>
     <row r="47">
@@ -2653,40 +2653,40 @@
         </is>
       </c>
       <c r="C47" s="6" t="n">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="D47" s="7" t="n">
-        <v>8820132.970000001</v>
+        <v>8383512.28</v>
       </c>
       <c r="E47" s="7" t="n">
         <v>7530257.12</v>
       </c>
       <c r="F47" s="7" t="n">
-        <v>213439.62</v>
+        <v>211631.32</v>
       </c>
       <c r="G47" s="7" t="n">
-        <v>2646039.91</v>
+        <v>2515053.71</v>
       </c>
       <c r="H47" s="7" t="n">
-        <v>19209869.69</v>
+        <v>18640454.62</v>
       </c>
       <c r="I47" s="6" t="n">
-        <v>28814804535</v>
+        <v>7940460859.03</v>
       </c>
       <c r="J47" s="7" t="n">
-        <v>1374258.37</v>
+        <v>1304550.38</v>
       </c>
       <c r="K47" s="7" t="n">
-        <v>17835611.33</v>
+        <v>17335904.2</v>
       </c>
       <c r="L47" s="6" t="n">
-        <v>994240000</v>
+        <v>992160000</v>
       </c>
       <c r="M47" s="7" t="n">
-        <v>662826.67</v>
+        <v>2329123.43</v>
       </c>
       <c r="N47" s="6" t="n">
-        <v>27820564535</v>
+        <v>6948300859.03</v>
       </c>
     </row>
     <row r="48">
@@ -2704,37 +2704,37 @@
         <v>111</v>
       </c>
       <c r="D48" s="7" t="n">
-        <v>1806877.16</v>
+        <v>1765476.54</v>
       </c>
       <c r="E48" s="7" t="n">
         <v>889563.61</v>
       </c>
       <c r="F48" s="7" t="n">
-        <v>32203.02</v>
+        <v>31968</v>
       </c>
       <c r="G48" s="7" t="n">
-        <v>542063.13</v>
+        <v>529643</v>
       </c>
       <c r="H48" s="7" t="n">
-        <v>3270707.02</v>
+        <v>3216651.07</v>
       </c>
       <c r="I48" s="6" t="n">
-        <v>4906060530</v>
+        <v>1370229022.8</v>
       </c>
       <c r="J48" s="7" t="n">
-        <v>173189.5</v>
+        <v>170248.41</v>
       </c>
       <c r="K48" s="7" t="n">
-        <v>3097517.37</v>
+        <v>3046402.6</v>
       </c>
       <c r="L48" s="6" t="n">
         <v>230880000</v>
       </c>
       <c r="M48" s="7" t="n">
-        <v>153920</v>
+        <v>541997.28</v>
       </c>
       <c r="N48" s="6" t="n">
-        <v>4675180530</v>
+        <v>1139349022.8</v>
       </c>
     </row>
     <row r="49">
@@ -2752,37 +2752,37 @@
         <v>57</v>
       </c>
       <c r="D49" s="7" t="n">
-        <v>5401.29</v>
+        <v>5200.38</v>
       </c>
       <c r="E49" s="7" t="n">
         <v>2713.97</v>
       </c>
       <c r="F49" s="7" t="n">
-        <v>203.74</v>
+        <v>203.04</v>
       </c>
       <c r="G49" s="7" t="n">
-        <v>1620.41</v>
+        <v>1560.15</v>
       </c>
       <c r="H49" s="7" t="n">
-        <v>9939.360000000001</v>
+        <v>9677.52</v>
       </c>
       <c r="I49" s="6" t="n">
-        <v>14909040</v>
+        <v>4122429.97</v>
       </c>
       <c r="J49" s="7" t="n">
-        <v>2473.62</v>
+        <v>2232.03</v>
       </c>
       <c r="K49" s="7" t="n">
-        <v>7465.72</v>
+        <v>7445.47</v>
       </c>
       <c r="L49" s="6" t="n">
         <v>118560000</v>
       </c>
       <c r="M49" s="7" t="n">
-        <v>79040</v>
+        <v>278322.93</v>
       </c>
       <c r="N49" s="6" t="n">
-        <v>-103650960</v>
+        <v>-114437570.03</v>
       </c>
     </row>
     <row r="50">
@@ -2800,37 +2800,37 @@
         <v>484</v>
       </c>
       <c r="D50" s="7" t="n">
-        <v>10242978.78</v>
+        <v>9898798.23</v>
       </c>
       <c r="E50" s="7" t="n">
         <v>7051877.6</v>
       </c>
       <c r="F50" s="7" t="n">
-        <v>218092</v>
+        <v>216623.37</v>
       </c>
       <c r="G50" s="7" t="n">
-        <v>3072893.64</v>
+        <v>2969639.49</v>
       </c>
       <c r="H50" s="7" t="n">
-        <v>20585842.07</v>
+        <v>20136938.68</v>
       </c>
       <c r="I50" s="6" t="n">
-        <v>30878763105</v>
+        <v>12988325448.6</v>
       </c>
       <c r="J50" s="7" t="n">
-        <v>1941506.83</v>
+        <v>1854488.39</v>
       </c>
       <c r="K50" s="7" t="n">
-        <v>18644335.28</v>
+        <v>18282450.36</v>
       </c>
       <c r="L50" s="6" t="n">
         <v>1006720000</v>
       </c>
       <c r="M50" s="7" t="n">
-        <v>671146.67</v>
+        <v>1560806.2</v>
       </c>
       <c r="N50" s="6" t="n">
-        <v>29872043105</v>
+        <v>11981605448.6</v>
       </c>
     </row>
     <row r="51">
@@ -2848,37 +2848,37 @@
         <v>110</v>
       </c>
       <c r="D51" s="7" t="n">
-        <v>2368422.53</v>
+        <v>2309231.39</v>
       </c>
       <c r="E51" s="7" t="n">
         <v>779838.72</v>
       </c>
       <c r="F51" s="7" t="n">
-        <v>32825.93</v>
+        <v>32625.05</v>
       </c>
       <c r="G51" s="7" t="n">
-        <v>710526.73</v>
+        <v>692769.39</v>
       </c>
       <c r="H51" s="7" t="n">
-        <v>3891613.95</v>
+        <v>3814464.59</v>
       </c>
       <c r="I51" s="6" t="n">
-        <v>5837420925</v>
+        <v>2460329660.55</v>
       </c>
       <c r="J51" s="7" t="n">
-        <v>225014.05</v>
+        <v>226516.36</v>
       </c>
       <c r="K51" s="7" t="n">
-        <v>3666599.82</v>
+        <v>3587948.27</v>
       </c>
       <c r="L51" s="6" t="n">
         <v>228800000</v>
       </c>
       <c r="M51" s="7" t="n">
-        <v>152533.33</v>
+        <v>354728.68</v>
       </c>
       <c r="N51" s="6" t="n">
-        <v>5608620925</v>
+        <v>2231529660.55</v>
       </c>
     </row>
     <row r="52">
@@ -2896,37 +2896,37 @@
         <v>60</v>
       </c>
       <c r="D52" s="7" t="n">
-        <v>7092.08</v>
+        <v>6977.78</v>
       </c>
       <c r="E52" s="7" t="n">
         <v>2640.59</v>
       </c>
       <c r="F52" s="7" t="n">
-        <v>205.56</v>
+        <v>204.95</v>
       </c>
       <c r="G52" s="7" t="n">
-        <v>2127.64</v>
+        <v>2093.31</v>
       </c>
       <c r="H52" s="7" t="n">
-        <v>12065.83</v>
+        <v>11916.68</v>
       </c>
       <c r="I52" s="6" t="n">
-        <v>18098745</v>
+        <v>7686258.6</v>
       </c>
       <c r="J52" s="7" t="n">
-        <v>4253.33</v>
+        <v>3878.72</v>
       </c>
       <c r="K52" s="7" t="n">
-        <v>7812.45</v>
+        <v>8037.96</v>
       </c>
       <c r="L52" s="6" t="n">
         <v>124800000</v>
       </c>
       <c r="M52" s="7" t="n">
-        <v>83200</v>
+        <v>193488.37</v>
       </c>
       <c r="N52" s="6" t="n">
-        <v>-106701255</v>
+        <v>-117113741.4</v>
       </c>
     </row>
     <row r="53">
@@ -2944,37 +2944,37 @@
         <v>494</v>
       </c>
       <c r="D53" s="7" t="n">
-        <v>12253435.18</v>
+        <v>11451063.92</v>
       </c>
       <c r="E53" s="7" t="n">
         <v>7877503.91</v>
       </c>
       <c r="F53" s="7" t="n">
-        <v>222615.46</v>
+        <v>221082.68</v>
       </c>
       <c r="G53" s="7" t="n">
-        <v>3676030.57</v>
+        <v>3435319.24</v>
       </c>
       <c r="H53" s="7" t="n">
-        <v>24029584.93</v>
+        <v>22984969.68</v>
       </c>
       <c r="I53" s="6" t="n">
-        <v>36044377395</v>
+        <v>14825305443.6</v>
       </c>
       <c r="J53" s="7" t="n">
-        <v>2711494.59</v>
+        <v>2607028.15</v>
       </c>
       <c r="K53" s="7" t="n">
-        <v>21318090.42</v>
+        <v>20377941.59</v>
       </c>
       <c r="L53" s="6" t="n">
         <v>1027520000</v>
       </c>
       <c r="M53" s="7" t="n">
-        <v>685013.33</v>
+        <v>1593054.26</v>
       </c>
       <c r="N53" s="6" t="n">
-        <v>35016857395</v>
+        <v>13797785443.6</v>
       </c>
     </row>
     <row r="54">
@@ -2992,37 +2992,37 @@
         <v>113</v>
       </c>
       <c r="D54" s="7" t="n">
-        <v>2837075.09</v>
+        <v>2698139.65</v>
       </c>
       <c r="E54" s="7" t="n">
         <v>1391262.79</v>
       </c>
       <c r="F54" s="7" t="n">
-        <v>33473.33</v>
+        <v>33253.78</v>
       </c>
       <c r="G54" s="7" t="n">
-        <v>851122.53</v>
+        <v>809441.89</v>
       </c>
       <c r="H54" s="7" t="n">
-        <v>5112933.77</v>
+        <v>4932098.13</v>
       </c>
       <c r="I54" s="6" t="n">
-        <v>7669400655</v>
+        <v>3181203293.85</v>
       </c>
       <c r="J54" s="7" t="n">
-        <v>276675.37</v>
+        <v>275670.47</v>
       </c>
       <c r="K54" s="7" t="n">
-        <v>4836258.47</v>
+        <v>4656427.61</v>
       </c>
       <c r="L54" s="6" t="n">
         <v>235040000</v>
       </c>
       <c r="M54" s="7" t="n">
-        <v>156693.33</v>
+        <v>364403.1</v>
       </c>
       <c r="N54" s="6" t="n">
-        <v>7434360655</v>
+        <v>2946163293.85</v>
       </c>
     </row>
     <row r="55">
@@ -3040,37 +3040,37 @@
         <v>62</v>
       </c>
       <c r="D55" s="7" t="n">
-        <v>8940.93</v>
+        <v>8271.4</v>
       </c>
       <c r="E55" s="7" t="n">
         <v>2556.29</v>
       </c>
       <c r="F55" s="7" t="n">
-        <v>207.05</v>
+        <v>206.65</v>
       </c>
       <c r="G55" s="7" t="n">
-        <v>2682.28</v>
+        <v>2481.38</v>
       </c>
       <c r="H55" s="7" t="n">
-        <v>14386.53</v>
+        <v>13515.75</v>
       </c>
       <c r="I55" s="6" t="n">
-        <v>21579795</v>
+        <v>8717658.75</v>
       </c>
       <c r="J55" s="7" t="n">
-        <v>6433.65</v>
+        <v>5809.4</v>
       </c>
       <c r="K55" s="7" t="n">
-        <v>7952.82</v>
+        <v>7706.31</v>
       </c>
       <c r="L55" s="6" t="n">
         <v>128960000</v>
       </c>
       <c r="M55" s="7" t="n">
-        <v>85973.33</v>
+        <v>199937.98</v>
       </c>
       <c r="N55" s="6" t="n">
-        <v>-107380205</v>
+        <v>-120242341.25</v>
       </c>
     </row>
     <row r="56">
@@ -3088,37 +3088,37 @@
         <v>493</v>
       </c>
       <c r="D56" s="7" t="n">
-        <v>11573147.47</v>
+        <v>11706350.26</v>
       </c>
       <c r="E56" s="7" t="n">
         <v>7133093.46</v>
       </c>
       <c r="F56" s="7" t="n">
-        <v>227250.03</v>
+        <v>225746.96</v>
       </c>
       <c r="G56" s="7" t="n">
-        <v>3471944.24</v>
+        <v>3511905.09</v>
       </c>
       <c r="H56" s="7" t="n">
-        <v>22405435.29</v>
+        <v>22577095.6</v>
       </c>
       <c r="I56" s="6" t="n">
-        <v>33608152935</v>
+        <v>14562226662</v>
       </c>
       <c r="J56" s="7" t="n">
-        <v>3394595.02</v>
+        <v>3343842.44</v>
       </c>
       <c r="K56" s="7" t="n">
-        <v>19010840.05</v>
+        <v>19233253.1</v>
       </c>
       <c r="L56" s="6" t="n">
         <v>1025440000</v>
       </c>
       <c r="M56" s="7" t="n">
-        <v>683626.67</v>
+        <v>1589829.46</v>
       </c>
       <c r="N56" s="6" t="n">
-        <v>32582712935</v>
+        <v>13536786662</v>
       </c>
     </row>
     <row r="57">
@@ -3136,37 +3136,37 @@
         <v>113</v>
       </c>
       <c r="D57" s="7" t="n">
-        <v>2736178.63</v>
+        <v>2720852.22</v>
       </c>
       <c r="E57" s="7" t="n">
         <v>1254148.88</v>
       </c>
       <c r="F57" s="7" t="n">
-        <v>34184.81</v>
+        <v>33943.17</v>
       </c>
       <c r="G57" s="7" t="n">
-        <v>820853.59</v>
+        <v>816255.6899999999</v>
       </c>
       <c r="H57" s="7" t="n">
-        <v>4845365.83</v>
+        <v>4825199.9</v>
       </c>
       <c r="I57" s="6" t="n">
-        <v>7268048745</v>
+        <v>3112253935.5</v>
       </c>
       <c r="J57" s="7" t="n">
-        <v>375036.99</v>
+        <v>367463.28</v>
       </c>
       <c r="K57" s="7" t="n">
-        <v>4470328.89</v>
+        <v>4457736.74</v>
       </c>
       <c r="L57" s="6" t="n">
         <v>235040000</v>
       </c>
       <c r="M57" s="7" t="n">
-        <v>156693.33</v>
+        <v>364403.1</v>
       </c>
       <c r="N57" s="6" t="n">
-        <v>7033008745</v>
+        <v>2877213935.5</v>
       </c>
     </row>
     <row r="58">
@@ -3184,37 +3184,37 @@
         <v>62</v>
       </c>
       <c r="D58" s="7" t="n">
-        <v>11249.43</v>
+        <v>10728.82</v>
       </c>
       <c r="E58" s="7" t="n">
         <v>2483.23</v>
       </c>
       <c r="F58" s="7" t="n">
-        <v>209.07</v>
+        <v>208.19</v>
       </c>
       <c r="G58" s="7" t="n">
-        <v>3374.82</v>
+        <v>3218.65</v>
       </c>
       <c r="H58" s="7" t="n">
-        <v>17316.52</v>
+        <v>16638.91</v>
       </c>
       <c r="I58" s="6" t="n">
-        <v>25974780</v>
+        <v>10732096.95</v>
       </c>
       <c r="J58" s="7" t="n">
-        <v>10093.83</v>
+        <v>9583.200000000001</v>
       </c>
       <c r="K58" s="7" t="n">
-        <v>7222.64</v>
+        <v>7055.72</v>
       </c>
       <c r="L58" s="6" t="n">
         <v>128960000</v>
       </c>
       <c r="M58" s="7" t="n">
-        <v>85973.33</v>
+        <v>199937.98</v>
       </c>
       <c r="N58" s="6" t="n">
-        <v>-102985220</v>
+        <v>-118227903.05</v>
       </c>
     </row>
     <row r="59">
@@ -3232,37 +3232,37 @@
         <v>496</v>
       </c>
       <c r="D59" s="7" t="n">
-        <v>12081945.7</v>
+        <v>11856064.63</v>
       </c>
       <c r="E59" s="7" t="n">
         <v>7166542.4</v>
       </c>
       <c r="F59" s="7" t="n">
-        <v>232074.24</v>
+        <v>230380.21</v>
       </c>
       <c r="G59" s="7" t="n">
-        <v>3624583.79</v>
+        <v>3556819.34</v>
       </c>
       <c r="H59" s="7" t="n">
-        <v>23105146.04</v>
+        <v>22809806.72</v>
       </c>
       <c r="I59" s="6" t="n">
-        <v>34657719060</v>
+        <v>14712325334.4</v>
       </c>
       <c r="J59" s="7" t="n">
-        <v>4652166.29</v>
+        <v>4487508.38</v>
       </c>
       <c r="K59" s="7" t="n">
-        <v>18452979.89</v>
+        <v>18322298.42</v>
       </c>
       <c r="L59" s="6" t="n">
         <v>1031680000</v>
       </c>
       <c r="M59" s="7" t="n">
-        <v>687786.67</v>
+        <v>1599503.88</v>
       </c>
       <c r="N59" s="6" t="n">
-        <v>33626039060</v>
+        <v>13680645334.4</v>
       </c>
     </row>
     <row r="60">
@@ -3280,37 +3280,37 @@
         <v>113</v>
       </c>
       <c r="D60" s="7" t="n">
-        <v>2570965.9</v>
+        <v>2576518.79</v>
       </c>
       <c r="E60" s="7" t="n">
         <v>1124822.11</v>
       </c>
       <c r="F60" s="7" t="n">
-        <v>35024.24</v>
+        <v>34733.31</v>
       </c>
       <c r="G60" s="7" t="n">
-        <v>771289.75</v>
+        <v>772955.63</v>
       </c>
       <c r="H60" s="7" t="n">
-        <v>4502102.01</v>
+        <v>4509029.91</v>
       </c>
       <c r="I60" s="6" t="n">
-        <v>6753153015</v>
+        <v>2908324291.95</v>
       </c>
       <c r="J60" s="7" t="n">
-        <v>496430.87</v>
+        <v>495148.72</v>
       </c>
       <c r="K60" s="7" t="n">
-        <v>4005671.08</v>
+        <v>4013881.2</v>
       </c>
       <c r="L60" s="6" t="n">
         <v>235040000</v>
       </c>
       <c r="M60" s="7" t="n">
-        <v>156693.33</v>
+        <v>364403.1</v>
       </c>
       <c r="N60" s="6" t="n">
-        <v>6518113015</v>
+        <v>2673284291.95</v>
       </c>
     </row>
     <row r="61">
@@ -3328,37 +3328,37 @@
         <v>62</v>
       </c>
       <c r="D61" s="7" t="n">
-        <v>18270.18</v>
+        <v>15879.21</v>
       </c>
       <c r="E61" s="7" t="n">
         <v>2399.86</v>
       </c>
       <c r="F61" s="7" t="n">
-        <v>210.93</v>
+        <v>210.34</v>
       </c>
       <c r="G61" s="7" t="n">
-        <v>5481.04</v>
+        <v>4763.8</v>
       </c>
       <c r="H61" s="7" t="n">
-        <v>26362.05</v>
+        <v>23253.22</v>
       </c>
       <c r="I61" s="6" t="n">
-        <v>39543075</v>
+        <v>14998326.9</v>
       </c>
       <c r="J61" s="7" t="n">
-        <v>17947.21</v>
+        <v>15443.02</v>
       </c>
       <c r="K61" s="7" t="n">
-        <v>8414.92</v>
+        <v>7810.21</v>
       </c>
       <c r="L61" s="6" t="n">
         <v>128960000</v>
       </c>
       <c r="M61" s="7" t="n">
-        <v>85973.33</v>
+        <v>199937.98</v>
       </c>
       <c r="N61" s="6" t="n">
-        <v>-89416925</v>
+        <v>-113961673.1</v>
       </c>
     </row>
     <row r="62">
@@ -3376,37 +3376,37 @@
         <v>502</v>
       </c>
       <c r="D62" s="7" t="n">
-        <v>11850520.38</v>
+        <v>11954336.46</v>
       </c>
       <c r="E62" s="7" t="n">
         <v>7423596.49</v>
       </c>
       <c r="F62" s="7" t="n">
-        <v>237674.94</v>
+        <v>235750.9</v>
       </c>
       <c r="G62" s="7" t="n">
-        <v>3555156.21</v>
+        <v>3586301.04</v>
       </c>
       <c r="H62" s="7" t="n">
-        <v>23066948.14</v>
+        <v>23199985.12</v>
       </c>
       <c r="I62" s="6" t="n">
-        <v>34600422210</v>
+        <v>34289578007.36</v>
       </c>
       <c r="J62" s="7" t="n">
-        <v>4768382.19</v>
+        <v>4717532.36</v>
       </c>
       <c r="K62" s="7" t="n">
-        <v>18298565.86</v>
+        <v>18482452.66</v>
       </c>
       <c r="L62" s="6" t="n">
         <v>1044160000</v>
       </c>
       <c r="M62" s="7" t="n">
-        <v>696106.67</v>
+        <v>706468.2</v>
       </c>
       <c r="N62" s="6" t="n">
-        <v>33556262210</v>
+        <v>33245418007.36</v>
       </c>
     </row>
     <row r="63">
@@ -3424,37 +3424,37 @@
         <v>113</v>
       </c>
       <c r="D63" s="7" t="n">
-        <v>2913889.95</v>
+        <v>2835438.17</v>
       </c>
       <c r="E63" s="7" t="n">
         <v>1224206.63</v>
       </c>
       <c r="F63" s="7" t="n">
-        <v>35864.78</v>
+        <v>35587.33</v>
       </c>
       <c r="G63" s="7" t="n">
-        <v>874166.98</v>
+        <v>850631.48</v>
       </c>
       <c r="H63" s="7" t="n">
-        <v>5048128.32</v>
+        <v>4945863.58</v>
       </c>
       <c r="I63" s="6" t="n">
-        <v>7572192480</v>
+        <v>7309986371.24</v>
       </c>
       <c r="J63" s="7" t="n">
-        <v>588085.6</v>
+        <v>576641.4300000001</v>
       </c>
       <c r="K63" s="7" t="n">
-        <v>4460042.73</v>
+        <v>4369222.22</v>
       </c>
       <c r="L63" s="6" t="n">
         <v>235040000</v>
       </c>
       <c r="M63" s="7" t="n">
-        <v>156693.33</v>
+        <v>159025.71</v>
       </c>
       <c r="N63" s="6" t="n">
-        <v>7337152480</v>
+        <v>7074946371.24</v>
       </c>
     </row>
     <row r="64">
@@ -3472,37 +3472,37 @@
         <v>68</v>
       </c>
       <c r="D64" s="7" t="n">
-        <v>18350.59</v>
+        <v>18750.71</v>
       </c>
       <c r="E64" s="7" t="n">
         <v>2327.11</v>
       </c>
       <c r="F64" s="7" t="n">
-        <v>212.81</v>
+        <v>212.35</v>
       </c>
       <c r="G64" s="7" t="n">
-        <v>5505.19</v>
+        <v>5625.25</v>
       </c>
       <c r="H64" s="7" t="n">
-        <v>26395.7</v>
+        <v>26915.39</v>
       </c>
       <c r="I64" s="6" t="n">
-        <v>39593550</v>
+        <v>39780946.42</v>
       </c>
       <c r="J64" s="7" t="n">
-        <v>16894.34</v>
+        <v>17296.72</v>
       </c>
       <c r="K64" s="7" t="n">
-        <v>9501.33</v>
+        <v>9618.75</v>
       </c>
       <c r="L64" s="6" t="n">
         <v>141440000</v>
       </c>
       <c r="M64" s="7" t="n">
-        <v>94293.33</v>
+        <v>95696.89</v>
       </c>
       <c r="N64" s="6" t="n">
-        <v>-101846450</v>
+        <v>-101659053.58</v>
       </c>
     </row>
     <row r="65">
@@ -3520,37 +3520,37 @@
         <v>509</v>
       </c>
       <c r="D65" s="7" t="n">
-        <v>13194146.48</v>
+        <v>12833821.99</v>
       </c>
       <c r="E65" s="7" t="n">
         <v>8666427.699999999</v>
       </c>
       <c r="F65" s="7" t="n">
-        <v>243618.46</v>
+        <v>241459.98</v>
       </c>
       <c r="G65" s="7" t="n">
-        <v>3958244</v>
+        <v>3850146.55</v>
       </c>
       <c r="H65" s="7" t="n">
-        <v>26062436.52</v>
+        <v>25591856.29</v>
       </c>
       <c r="I65" s="6" t="n">
-        <v>39093654780</v>
+        <v>37824763596.62</v>
       </c>
       <c r="J65" s="7" t="n">
-        <v>6524379.07</v>
+        <v>6430600.96</v>
       </c>
       <c r="K65" s="7" t="n">
-        <v>19538057.56</v>
+        <v>19161255.2</v>
       </c>
       <c r="L65" s="6" t="n">
         <v>1058720000</v>
       </c>
       <c r="M65" s="7" t="n">
-        <v>705813.33</v>
+        <v>716319.35</v>
       </c>
       <c r="N65" s="6" t="n">
-        <v>38034934780</v>
+        <v>36766043596.62</v>
       </c>
     </row>
     <row r="66">
@@ -3568,37 +3568,37 @@
         <v>114</v>
       </c>
       <c r="D66" s="7" t="n">
-        <v>3040159.31</v>
+        <v>3010624.48</v>
       </c>
       <c r="E66" s="7" t="n">
         <v>1187199.7</v>
       </c>
       <c r="F66" s="7" t="n">
-        <v>36607.29</v>
+        <v>36355.45</v>
       </c>
       <c r="G66" s="7" t="n">
-        <v>912047.78</v>
+        <v>903187.35</v>
       </c>
       <c r="H66" s="7" t="n">
-        <v>5176014.14</v>
+        <v>5137367.05</v>
       </c>
       <c r="I66" s="6" t="n">
-        <v>7764021210</v>
+        <v>7593028499.9</v>
       </c>
       <c r="J66" s="7" t="n">
-        <v>808298.6800000001</v>
+        <v>786179.33</v>
       </c>
       <c r="K66" s="7" t="n">
-        <v>4367715.46</v>
+        <v>4351187.75</v>
       </c>
       <c r="L66" s="6" t="n">
         <v>237120000</v>
       </c>
       <c r="M66" s="7" t="n">
-        <v>158080</v>
+        <v>160433.02</v>
       </c>
       <c r="N66" s="6" t="n">
-        <v>7526901210</v>
+        <v>7355908499.9</v>
       </c>
     </row>
     <row r="67">
@@ -3616,37 +3616,37 @@
         <v>68</v>
       </c>
       <c r="D67" s="7" t="n">
-        <v>25170.04</v>
+        <v>23058.3</v>
       </c>
       <c r="E67" s="7" t="n">
         <v>2289.25</v>
       </c>
       <c r="F67" s="7" t="n">
-        <v>214.16</v>
+        <v>213.73</v>
       </c>
       <c r="G67" s="7" t="n">
-        <v>7551.02</v>
+        <v>6917.47</v>
       </c>
       <c r="H67" s="7" t="n">
-        <v>35224.5</v>
+        <v>32478.82</v>
       </c>
       <c r="I67" s="6" t="n">
-        <v>52836750</v>
+        <v>48003695.96</v>
       </c>
       <c r="J67" s="7" t="n">
-        <v>20301.71</v>
+        <v>20050.88</v>
       </c>
       <c r="K67" s="7" t="n">
-        <v>14922.79</v>
+        <v>12427.91</v>
       </c>
       <c r="L67" s="6" t="n">
         <v>141440000</v>
       </c>
       <c r="M67" s="7" t="n">
-        <v>94293.33</v>
+        <v>95696.89</v>
       </c>
       <c r="N67" s="6" t="n">
-        <v>-88603250</v>
+        <v>-93436304.04000001</v>
       </c>
     </row>
     <row r="68">
@@ -3664,37 +3664,37 @@
         <v>511</v>
       </c>
       <c r="D68" s="7" t="n">
-        <v>13260604.91</v>
+        <v>13412754.53</v>
       </c>
       <c r="E68" s="7" t="n">
         <v>10181784.93</v>
       </c>
       <c r="F68" s="7" t="n">
-        <v>249498.18</v>
+        <v>247401.83</v>
       </c>
       <c r="G68" s="7" t="n">
-        <v>3978181.47</v>
+        <v>4023826.35</v>
       </c>
       <c r="H68" s="7" t="n">
-        <v>27670069.7</v>
+        <v>27865767.66</v>
       </c>
       <c r="I68" s="6" t="n">
-        <v>41505104550</v>
+        <v>41185604601.48</v>
       </c>
       <c r="J68" s="7" t="n">
-        <v>7771578.58</v>
+        <v>7728345.03</v>
       </c>
       <c r="K68" s="7" t="n">
-        <v>19898491.14</v>
+        <v>20137422.96</v>
       </c>
       <c r="L68" s="6" t="n">
         <v>1062880000</v>
       </c>
       <c r="M68" s="7" t="n">
-        <v>708586.67</v>
+        <v>719133.96</v>
       </c>
       <c r="N68" s="6" t="n">
-        <v>40442224550</v>
+        <v>40122724601.48</v>
       </c>
     </row>
     <row r="69">
@@ -3712,37 +3712,37 @@
         <v>114</v>
       </c>
       <c r="D69" s="7" t="n">
-        <v>4203926.92</v>
+        <v>3767567.59</v>
       </c>
       <c r="E69" s="7" t="n">
         <v>1305734.53</v>
       </c>
       <c r="F69" s="7" t="n">
-        <v>37322.83</v>
+        <v>37093.34</v>
       </c>
       <c r="G69" s="7" t="n">
-        <v>1261178.07</v>
+        <v>1130270.25</v>
       </c>
       <c r="H69" s="7" t="n">
-        <v>6808162.41</v>
+        <v>6240665.66</v>
       </c>
       <c r="I69" s="6" t="n">
-        <v>10212243615</v>
+        <v>9223703845.48</v>
       </c>
       <c r="J69" s="7" t="n">
-        <v>854622.87</v>
+        <v>847998.1</v>
       </c>
       <c r="K69" s="7" t="n">
-        <v>5953539.52</v>
+        <v>5392667.6</v>
       </c>
       <c r="L69" s="6" t="n">
         <v>237120000</v>
       </c>
       <c r="M69" s="7" t="n">
-        <v>158080</v>
+        <v>160433.02</v>
       </c>
       <c r="N69" s="6" t="n">
-        <v>9975123615</v>
+        <v>8986583845.48</v>
       </c>
     </row>
     <row r="70">
@@ -3760,37 +3760,37 @@
         <v>70</v>
       </c>
       <c r="D70" s="7" t="n">
-        <v>26528.96</v>
+        <v>25918.9</v>
       </c>
       <c r="E70" s="7" t="n">
         <v>3379.37</v>
       </c>
       <c r="F70" s="7" t="n">
-        <v>215.83</v>
+        <v>215.24</v>
       </c>
       <c r="G70" s="7" t="n">
-        <v>7958.67</v>
+        <v>7775.7</v>
       </c>
       <c r="H70" s="7" t="n">
-        <v>38082.81</v>
+        <v>37289.22</v>
       </c>
       <c r="I70" s="6" t="n">
-        <v>57124215</v>
+        <v>55113467.16</v>
       </c>
       <c r="J70" s="7" t="n">
-        <v>20348.21</v>
+        <v>20362.5</v>
       </c>
       <c r="K70" s="7" t="n">
-        <v>17734.62</v>
+        <v>16926.79</v>
       </c>
       <c r="L70" s="6" t="n">
         <v>145600000</v>
       </c>
       <c r="M70" s="7" t="n">
-        <v>97066.67</v>
+        <v>98511.5</v>
       </c>
       <c r="N70" s="6" t="n">
-        <v>-88475785</v>
+        <v>-90486532.84</v>
       </c>
     </row>
     <row r="71">
@@ -3808,37 +3808,37 @@
         <v>513</v>
       </c>
       <c r="D71" s="7" t="n">
-        <v>14151253.03</v>
+        <v>13644668.15</v>
       </c>
       <c r="E71" s="7" t="n">
         <v>10084842.63</v>
       </c>
       <c r="F71" s="7" t="n">
-        <v>254096.32</v>
+        <v>252490.26</v>
       </c>
       <c r="G71" s="7" t="n">
-        <v>4245375.88</v>
+        <v>4093400.35</v>
       </c>
       <c r="H71" s="7" t="n">
-        <v>28735568.11</v>
+        <v>28075401.52</v>
       </c>
       <c r="I71" s="6" t="n">
-        <v>43103352165</v>
+        <v>41495443446.56</v>
       </c>
       <c r="J71" s="7" t="n">
-        <v>9338726.949999999</v>
+        <v>8974215.43</v>
       </c>
       <c r="K71" s="7" t="n">
-        <v>19396841.28</v>
+        <v>19101186.14</v>
       </c>
       <c r="L71" s="6" t="n">
         <v>1067040000</v>
       </c>
       <c r="M71" s="7" t="n">
-        <v>711360</v>
+        <v>721948.58</v>
       </c>
       <c r="N71" s="6" t="n">
-        <v>42036312165</v>
+        <v>40428403446.56</v>
       </c>
     </row>
     <row r="72">
@@ -3856,37 +3856,37 @@
         <v>117</v>
       </c>
       <c r="D72" s="7" t="n">
-        <v>4113507.56</v>
+        <v>4276245.02</v>
       </c>
       <c r="E72" s="7" t="n">
         <v>1299764.62</v>
       </c>
       <c r="F72" s="7" t="n">
-        <v>38061.11</v>
+        <v>37810.28</v>
       </c>
       <c r="G72" s="7" t="n">
-        <v>1234052.25</v>
+        <v>1282873.54</v>
       </c>
       <c r="H72" s="7" t="n">
-        <v>6685385.58</v>
+        <v>6896693.43</v>
       </c>
       <c r="I72" s="6" t="n">
-        <v>10028078370</v>
+        <v>10193312889.54</v>
       </c>
       <c r="J72" s="7" t="n">
-        <v>1151247.75</v>
+        <v>1152955.11</v>
       </c>
       <c r="K72" s="7" t="n">
-        <v>5534137.87</v>
+        <v>5743738.37</v>
       </c>
       <c r="L72" s="6" t="n">
         <v>243360000</v>
       </c>
       <c r="M72" s="7" t="n">
-        <v>162240</v>
+        <v>164654.94</v>
       </c>
       <c r="N72" s="6" t="n">
-        <v>9784718370</v>
+        <v>9949952889.540001</v>
       </c>
     </row>
     <row r="73">
@@ -3904,37 +3904,37 @@
         <v>71</v>
       </c>
       <c r="D73" s="7" t="n">
-        <v>34885.37</v>
+        <v>32197.22</v>
       </c>
       <c r="E73" s="7" t="n">
         <v>4011.15</v>
       </c>
       <c r="F73" s="7" t="n">
-        <v>217.16</v>
+        <v>216.74</v>
       </c>
       <c r="G73" s="7" t="n">
-        <v>10465.58</v>
+        <v>9659.18</v>
       </c>
       <c r="H73" s="7" t="n">
-        <v>49579.26</v>
+        <v>46084.28</v>
       </c>
       <c r="I73" s="6" t="n">
-        <v>74368890</v>
+        <v>68112565.84</v>
       </c>
       <c r="J73" s="7" t="n">
-        <v>27649.38</v>
+        <v>25320.54</v>
       </c>
       <c r="K73" s="7" t="n">
-        <v>21929.95</v>
+        <v>20763.77</v>
       </c>
       <c r="L73" s="6" t="n">
         <v>147680000</v>
       </c>
       <c r="M73" s="7" t="n">
-        <v>98453.33</v>
+        <v>99918.81</v>
       </c>
       <c r="N73" s="6" t="n">
-        <v>-73311110</v>
+        <v>-79567434.16</v>
       </c>
     </row>
     <row r="74">
@@ -3952,37 +3952,37 @@
         <v>515</v>
       </c>
       <c r="D74" s="7" t="n">
-        <v>13118835.33</v>
+        <v>13564523.31</v>
       </c>
       <c r="E74" s="7" t="n">
         <v>9162908.83</v>
       </c>
       <c r="F74" s="7" t="n">
-        <v>260117.63</v>
+        <v>257989.71</v>
       </c>
       <c r="G74" s="7" t="n">
-        <v>3935650.6</v>
+        <v>4069356.97</v>
       </c>
       <c r="H74" s="7" t="n">
-        <v>26477512.28</v>
+        <v>27054778.75</v>
       </c>
       <c r="I74" s="6" t="n">
-        <v>39716268420</v>
+        <v>41393811487.5</v>
       </c>
       <c r="J74" s="7" t="n">
-        <v>9882329.619999999</v>
+        <v>9995040.460000001</v>
       </c>
       <c r="K74" s="7" t="n">
-        <v>16595182.78</v>
+        <v>17059738.17</v>
       </c>
       <c r="L74" s="6" t="n">
         <v>1071200000</v>
       </c>
       <c r="M74" s="7" t="n">
-        <v>714133.33</v>
+        <v>700130.72</v>
       </c>
       <c r="N74" s="6" t="n">
-        <v>38645068420</v>
+        <v>40322611487.5</v>
       </c>
     </row>
     <row r="75">
@@ -4000,37 +4000,37 @@
         <v>118</v>
       </c>
       <c r="D75" s="7" t="n">
-        <v>3909212.81</v>
+        <v>3949063.95</v>
       </c>
       <c r="E75" s="7" t="n">
         <v>1490845.31</v>
       </c>
       <c r="F75" s="7" t="n">
-        <v>38903.52</v>
+        <v>38591.35</v>
       </c>
       <c r="G75" s="7" t="n">
-        <v>1172763.82</v>
+        <v>1184719.19</v>
       </c>
       <c r="H75" s="7" t="n">
-        <v>6611725.51</v>
+        <v>6663219.83</v>
       </c>
       <c r="I75" s="6" t="n">
-        <v>9917588265</v>
+        <v>10194726339.9</v>
       </c>
       <c r="J75" s="7" t="n">
-        <v>1246606.24</v>
+        <v>1251764.34</v>
       </c>
       <c r="K75" s="7" t="n">
-        <v>5365119.23</v>
+        <v>5411455.48</v>
       </c>
       <c r="L75" s="6" t="n">
         <v>245440000</v>
       </c>
       <c r="M75" s="7" t="n">
-        <v>163626.67</v>
+        <v>160418.3</v>
       </c>
       <c r="N75" s="6" t="n">
-        <v>9672148265</v>
+        <v>9949286339.9</v>
       </c>
     </row>
     <row r="76">
@@ -4048,37 +4048,37 @@
         <v>73</v>
       </c>
       <c r="D76" s="7" t="n">
-        <v>27331.39</v>
+        <v>29897.42</v>
       </c>
       <c r="E76" s="7" t="n">
         <v>3881.98</v>
       </c>
       <c r="F76" s="7" t="n">
-        <v>218.42</v>
+        <v>218.03</v>
       </c>
       <c r="G76" s="7" t="n">
-        <v>8199.379999999999</v>
+        <v>8969.23</v>
       </c>
       <c r="H76" s="7" t="n">
-        <v>39631.13</v>
+        <v>42966.63</v>
       </c>
       <c r="I76" s="6" t="n">
-        <v>59446695</v>
+        <v>65738943.9</v>
       </c>
       <c r="J76" s="7" t="n">
-        <v>25557.33</v>
+        <v>27480.52</v>
       </c>
       <c r="K76" s="7" t="n">
-        <v>14073.84</v>
+        <v>15486.07</v>
       </c>
       <c r="L76" s="6" t="n">
         <v>151840000</v>
       </c>
       <c r="M76" s="7" t="n">
-        <v>101226.67</v>
+        <v>99241.83</v>
       </c>
       <c r="N76" s="6" t="n">
-        <v>-92393305</v>
+        <v>-86101056.09999999</v>
       </c>
     </row>
     <row r="77">
@@ -4096,37 +4096,37 @@
         <v>520</v>
       </c>
       <c r="D77" s="7" t="n">
-        <v>15182768.98</v>
+        <v>14830600.83</v>
       </c>
       <c r="E77" s="7" t="n">
         <v>10702629.96</v>
       </c>
       <c r="F77" s="7" t="n">
-        <v>256445.55</v>
+        <v>260348.03</v>
       </c>
       <c r="G77" s="7" t="n">
-        <v>4554830.77</v>
+        <v>4449180.33</v>
       </c>
       <c r="H77" s="7" t="n">
-        <v>30696675.07</v>
+        <v>30242759.19</v>
       </c>
       <c r="I77" s="6" t="n">
-        <v>46045012605</v>
+        <v>46271421560.7</v>
       </c>
       <c r="J77" s="7" t="n">
-        <v>11733287.67</v>
+        <v>11434816.19</v>
       </c>
       <c r="K77" s="7" t="n">
-        <v>18963387.24</v>
+        <v>18807943.1</v>
       </c>
       <c r="L77" s="6" t="n">
         <v>1081600000</v>
       </c>
       <c r="M77" s="7" t="n">
-        <v>721066.67</v>
+        <v>706928.1</v>
       </c>
       <c r="N77" s="6" t="n">
-        <v>44963412605</v>
+        <v>45189821560.7</v>
       </c>
     </row>
     <row r="78">
@@ -4144,37 +4144,37 @@
         <v>119</v>
       </c>
       <c r="D78" s="7" t="n">
-        <v>4299541.82</v>
+        <v>4186404.92</v>
       </c>
       <c r="E78" s="7" t="n">
         <v>1662044.95</v>
       </c>
       <c r="F78" s="7" t="n">
-        <v>39844.21</v>
+        <v>39535.31</v>
       </c>
       <c r="G78" s="7" t="n">
-        <v>1289862.59</v>
+        <v>1255921.52</v>
       </c>
       <c r="H78" s="7" t="n">
-        <v>7291293.46</v>
+        <v>7143906.56</v>
       </c>
       <c r="I78" s="6" t="n">
-        <v>10936940190</v>
+        <v>10930177036.8</v>
       </c>
       <c r="J78" s="7" t="n">
-        <v>1597112.66</v>
+        <v>1567133.47</v>
       </c>
       <c r="K78" s="7" t="n">
-        <v>5694180.81</v>
+        <v>5576773.11</v>
       </c>
       <c r="L78" s="6" t="n">
         <v>247520000</v>
       </c>
       <c r="M78" s="7" t="n">
-        <v>165013.33</v>
+        <v>161777.78</v>
       </c>
       <c r="N78" s="6" t="n">
-        <v>10689420190</v>
+        <v>10682657036.8</v>
       </c>
     </row>
     <row r="79">
@@ -4192,37 +4192,37 @@
         <v>76</v>
       </c>
       <c r="D79" s="7" t="n">
-        <v>35517.73</v>
+        <v>33258.05</v>
       </c>
       <c r="E79" s="7" t="n">
         <v>2197.3</v>
       </c>
       <c r="F79" s="7" t="n">
-        <v>219.97</v>
+        <v>219.53</v>
       </c>
       <c r="G79" s="7" t="n">
-        <v>10655.35</v>
+        <v>9977.41</v>
       </c>
       <c r="H79" s="7" t="n">
-        <v>48590.37</v>
+        <v>45652.28</v>
       </c>
       <c r="I79" s="6" t="n">
-        <v>72885555</v>
+        <v>69847988.40000001</v>
       </c>
       <c r="J79" s="7" t="n">
-        <v>32925.77</v>
+        <v>30256.79</v>
       </c>
       <c r="K79" s="7" t="n">
-        <v>15664.62</v>
+        <v>15395.5</v>
       </c>
       <c r="L79" s="6" t="n">
         <v>158080000</v>
       </c>
       <c r="M79" s="7" t="n">
-        <v>105386.67</v>
+        <v>103320.26</v>
       </c>
       <c r="N79" s="6" t="n">
-        <v>-85194445</v>
+        <v>-88232011.59999999</v>
       </c>
     </row>
     <row r="80">
@@ -4240,37 +4240,37 @@
         <v>522</v>
       </c>
       <c r="D80" s="7" t="n">
-        <v>15309950.01</v>
+        <v>15331301.07</v>
       </c>
       <c r="E80" s="7" t="n">
         <v>10604938.5</v>
       </c>
       <c r="F80" s="7" t="n">
-        <v>261005.57</v>
+        <v>262305.52</v>
       </c>
       <c r="G80" s="7" t="n">
-        <v>4592984.88</v>
+        <v>4599390.37</v>
       </c>
       <c r="H80" s="7" t="n">
-        <v>30768878.87</v>
+        <v>30797935.42</v>
       </c>
       <c r="I80" s="6" t="n">
-        <v>46153318305</v>
+        <v>47120841192.6</v>
       </c>
       <c r="J80" s="7" t="n">
-        <v>11836190.56</v>
+        <v>11826151.95</v>
       </c>
       <c r="K80" s="7" t="n">
-        <v>18932688.24</v>
+        <v>18971783.33</v>
       </c>
       <c r="L80" s="6" t="n">
         <v>1085760000</v>
       </c>
       <c r="M80" s="7" t="n">
-        <v>723840</v>
+        <v>709647.0600000001</v>
       </c>
       <c r="N80" s="6" t="n">
-        <v>45067558305</v>
+        <v>46035081192.6</v>
       </c>
     </row>
     <row r="81">
@@ -4288,37 +4288,37 @@
         <v>120</v>
       </c>
       <c r="D81" s="7" t="n">
-        <v>4218312.56</v>
+        <v>4380790.66</v>
       </c>
       <c r="E81" s="7" t="n">
         <v>1459284.32</v>
       </c>
       <c r="F81" s="7" t="n">
-        <v>41013.07</v>
+        <v>40649.29</v>
       </c>
       <c r="G81" s="7" t="n">
-        <v>1265493.79</v>
+        <v>1314237.18</v>
       </c>
       <c r="H81" s="7" t="n">
-        <v>6984103.82</v>
+        <v>7194961.45</v>
       </c>
       <c r="I81" s="6" t="n">
-        <v>10476155730</v>
+        <v>11008291018.5</v>
       </c>
       <c r="J81" s="7" t="n">
-        <v>1431567.43</v>
+        <v>1416247.08</v>
       </c>
       <c r="K81" s="7" t="n">
-        <v>5552536.39</v>
+        <v>5778714.32</v>
       </c>
       <c r="L81" s="6" t="n">
         <v>249600000</v>
       </c>
       <c r="M81" s="7" t="n">
-        <v>166400</v>
+        <v>163137.25</v>
       </c>
       <c r="N81" s="6" t="n">
-        <v>10226555730</v>
+        <v>10758691018.5</v>
       </c>
     </row>
     <row r="82">
@@ -4336,37 +4336,37 @@
         <v>77</v>
       </c>
       <c r="D82" s="7" t="n">
-        <v>48506.32</v>
+        <v>37926.34</v>
       </c>
       <c r="E82" s="7" t="n">
         <v>6474.02</v>
       </c>
       <c r="F82" s="7" t="n">
-        <v>222.23</v>
+        <v>221.52</v>
       </c>
       <c r="G82" s="7" t="n">
-        <v>14551.91</v>
+        <v>11377.92</v>
       </c>
       <c r="H82" s="7" t="n">
-        <v>69754.5</v>
+        <v>55999.89</v>
       </c>
       <c r="I82" s="6" t="n">
-        <v>104631750</v>
+        <v>85679831.7</v>
       </c>
       <c r="J82" s="7" t="n">
-        <v>40157.34</v>
+        <v>34316.03</v>
       </c>
       <c r="K82" s="7" t="n">
-        <v>29597.24</v>
+        <v>21683.84</v>
       </c>
       <c r="L82" s="6" t="n">
         <v>160160000</v>
       </c>
       <c r="M82" s="7" t="n">
-        <v>106773.33</v>
+        <v>104679.74</v>
       </c>
       <c r="N82" s="6" t="n">
-        <v>-55528250</v>
+        <v>-74480168.3</v>
       </c>
     </row>
     <row r="83">
@@ -4384,37 +4384,37 @@
         <v>523</v>
       </c>
       <c r="D83" s="7" t="n">
-        <v>16355772.25</v>
+        <v>15997110.26</v>
       </c>
       <c r="E83" s="7" t="n">
         <v>10728852.39</v>
       </c>
       <c r="F83" s="7" t="n">
-        <v>231584.72</v>
+        <v>230332.99</v>
       </c>
       <c r="G83" s="7" t="n">
-        <v>4906731.66</v>
+        <v>4799133.1</v>
       </c>
       <c r="H83" s="7" t="n">
-        <v>32222941.02</v>
+        <v>31755428.82</v>
       </c>
       <c r="I83" s="6" t="n">
-        <v>48334411530</v>
+        <v>48585806094.6</v>
       </c>
       <c r="J83" s="7" t="n">
-        <v>13652707.54</v>
+        <v>13424505.84</v>
       </c>
       <c r="K83" s="7" t="n">
-        <v>18570233.57</v>
+        <v>18330923.03</v>
       </c>
       <c r="L83" s="6" t="n">
         <v>1087840000</v>
       </c>
       <c r="M83" s="7" t="n">
-        <v>725226.67</v>
+        <v>711006.54</v>
       </c>
       <c r="N83" s="6" t="n">
-        <v>47246571530</v>
+        <v>47497966094.6</v>
       </c>
     </row>
     <row r="84">
@@ -4432,37 +4432,37 @@
         <v>120</v>
       </c>
       <c r="D84" s="7" t="n">
-        <v>4528391.73</v>
+        <v>4382315.28</v>
       </c>
       <c r="E84" s="7" t="n">
         <v>1292148.66</v>
       </c>
       <c r="F84" s="7" t="n">
-        <v>42071.49</v>
+        <v>41699.35</v>
       </c>
       <c r="G84" s="7" t="n">
-        <v>1358517.5</v>
+        <v>1314694.6</v>
       </c>
       <c r="H84" s="7" t="n">
-        <v>7221129.45</v>
+        <v>7030857.89</v>
       </c>
       <c r="I84" s="6" t="n">
-        <v>10831694175</v>
+        <v>10757212571.7</v>
       </c>
       <c r="J84" s="7" t="n">
-        <v>1814303.22</v>
+        <v>1697810.32</v>
       </c>
       <c r="K84" s="7" t="n">
-        <v>5406826.14</v>
+        <v>5333047.43</v>
       </c>
       <c r="L84" s="6" t="n">
         <v>249600000</v>
       </c>
       <c r="M84" s="7" t="n">
-        <v>166400</v>
+        <v>163137.25</v>
       </c>
       <c r="N84" s="6" t="n">
-        <v>10582094175</v>
+        <v>10507612571.7</v>
       </c>
     </row>
     <row r="85">
@@ -4480,37 +4480,37 @@
         <v>78</v>
       </c>
       <c r="D85" s="7" t="n">
-        <v>159336.18</v>
+        <v>91382.89999999999</v>
       </c>
       <c r="E85" s="7" t="n">
         <v>154374.85</v>
       </c>
       <c r="F85" s="7" t="n">
-        <v>224.68</v>
+        <v>223.69</v>
       </c>
       <c r="G85" s="7" t="n">
-        <v>47800.89</v>
+        <v>27414.88</v>
       </c>
       <c r="H85" s="7" t="n">
-        <v>361736.53</v>
+        <v>273396.25</v>
       </c>
       <c r="I85" s="6" t="n">
-        <v>542604795</v>
+        <v>418296262.5</v>
       </c>
       <c r="J85" s="7" t="n">
-        <v>160578.84</v>
+        <v>126045.79</v>
       </c>
       <c r="K85" s="7" t="n">
-        <v>201157.63</v>
+        <v>147350.48</v>
       </c>
       <c r="L85" s="6" t="n">
         <v>162240000</v>
       </c>
       <c r="M85" s="7" t="n">
-        <v>108160</v>
+        <v>106039.22</v>
       </c>
       <c r="N85" s="6" t="n">
-        <v>380364795</v>
+        <v>256056262.5</v>
       </c>
     </row>
     <row r="86">
@@ -4528,37 +4528,37 @@
         <v>524</v>
       </c>
       <c r="D86" s="7" t="n">
-        <v>17584131.8</v>
+        <v>17209530.81</v>
       </c>
       <c r="E86" s="7" t="n">
         <v>9459190.35</v>
       </c>
       <c r="F86" s="7" t="n">
-        <v>234917.91</v>
+        <v>233834.04</v>
       </c>
       <c r="G86" s="7" t="n">
-        <v>5275239.43</v>
+        <v>5162859.35</v>
       </c>
       <c r="H86" s="7" t="n">
-        <v>32553479.61</v>
+        <v>32065414.61</v>
       </c>
       <c r="I86" s="6" t="n">
-        <v>48830219415</v>
+        <v>49060084353.3</v>
       </c>
       <c r="J86" s="7" t="n">
-        <v>13401718.02</v>
+        <v>13339943.11</v>
       </c>
       <c r="K86" s="7" t="n">
-        <v>19151761.65</v>
+        <v>18725471.36</v>
       </c>
       <c r="L86" s="6" t="n">
         <v>1089920000</v>
       </c>
       <c r="M86" s="7" t="n">
-        <v>726613.33</v>
+        <v>712366.01</v>
       </c>
       <c r="N86" s="6" t="n">
-        <v>47740299415</v>
+        <v>47970164353.3</v>
       </c>
     </row>
     <row r="87">
@@ -4576,37 +4576,37 @@
         <v>121</v>
       </c>
       <c r="D87" s="7" t="n">
-        <v>4996053.88</v>
+        <v>4762734.7</v>
       </c>
       <c r="E87" s="7" t="n">
         <v>1337116.86</v>
       </c>
       <c r="F87" s="7" t="n">
-        <v>42956.71</v>
+        <v>42667.92</v>
       </c>
       <c r="G87" s="7" t="n">
-        <v>1498816.15</v>
+        <v>1428820.37</v>
       </c>
       <c r="H87" s="7" t="n">
-        <v>7874943.6</v>
+        <v>7571339.84</v>
       </c>
       <c r="I87" s="6" t="n">
-        <v>11812415400</v>
+        <v>11584149955.2</v>
       </c>
       <c r="J87" s="7" t="n">
-        <v>2070384.73</v>
+        <v>1928382.61</v>
       </c>
       <c r="K87" s="7" t="n">
-        <v>5804558.9</v>
+        <v>5642957.19</v>
       </c>
       <c r="L87" s="6" t="n">
         <v>251680000</v>
       </c>
       <c r="M87" s="7" t="n">
-        <v>167786.67</v>
+        <v>164496.73</v>
       </c>
       <c r="N87" s="6" t="n">
-        <v>11560735400</v>
+        <v>11332469955.2</v>
       </c>
     </row>
     <row r="88">
@@ -4624,37 +4624,37 @@
         <v>79</v>
       </c>
       <c r="D88" s="7" t="n">
-        <v>155305.4</v>
+        <v>149227.44</v>
       </c>
       <c r="E88" s="7" t="n">
         <v>7110.47</v>
       </c>
       <c r="F88" s="7" t="n">
-        <v>228.49</v>
+        <v>227.08</v>
       </c>
       <c r="G88" s="7" t="n">
-        <v>46591.62</v>
+        <v>44768.21</v>
       </c>
       <c r="H88" s="7" t="n">
-        <v>209235.98</v>
+        <v>201333.25</v>
       </c>
       <c r="I88" s="6" t="n">
-        <v>313853970</v>
+        <v>308039872.5</v>
       </c>
       <c r="J88" s="7" t="n">
-        <v>97782.89</v>
+        <v>95584.66</v>
       </c>
       <c r="K88" s="7" t="n">
-        <v>111453.1</v>
+        <v>105748.6</v>
       </c>
       <c r="L88" s="6" t="n">
         <v>164320000</v>
       </c>
       <c r="M88" s="7" t="n">
-        <v>109546.67</v>
+        <v>107398.69</v>
       </c>
       <c r="N88" s="6" t="n">
-        <v>149533970</v>
+        <v>143719872.5</v>
       </c>
     </row>
     <row r="89">
@@ -4672,37 +4672,37 @@
         <v>524</v>
       </c>
       <c r="D89" s="7" t="n">
-        <v>20096219.7</v>
+        <v>19232003.8</v>
       </c>
       <c r="E89" s="7" t="n">
         <v>10418257.28</v>
       </c>
       <c r="F89" s="7" t="n">
-        <v>278845.02</v>
+        <v>277528.86</v>
       </c>
       <c r="G89" s="7" t="n">
-        <v>6028865.88</v>
+        <v>5769601.1</v>
       </c>
       <c r="H89" s="7" t="n">
-        <v>36822187.7</v>
+        <v>35697391.04</v>
       </c>
       <c r="I89" s="6" t="n">
-        <v>55233281550</v>
+        <v>54617008291.2</v>
       </c>
       <c r="J89" s="7" t="n">
-        <v>14953161.69</v>
+        <v>14700410.81</v>
       </c>
       <c r="K89" s="7" t="n">
-        <v>21869026.12</v>
+        <v>20996980.29</v>
       </c>
       <c r="L89" s="6" t="n">
         <v>1089920000</v>
       </c>
       <c r="M89" s="7" t="n">
-        <v>726613.33</v>
+        <v>712366.01</v>
       </c>
       <c r="N89" s="6" t="n">
-        <v>54143361550</v>
+        <v>53527088291.2</v>
       </c>
     </row>
     <row r="90">
@@ -4720,37 +4720,37 @@
         <v>121</v>
       </c>
       <c r="D90" s="7" t="n">
-        <v>5422294.97</v>
+        <v>5351710.27</v>
       </c>
       <c r="E90" s="7" t="n">
         <v>1340662.25</v>
       </c>
       <c r="F90" s="7" t="n">
-        <v>43801.23</v>
+        <v>43505.74</v>
       </c>
       <c r="G90" s="7" t="n">
-        <v>1626688.46</v>
+        <v>1605513.11</v>
       </c>
       <c r="H90" s="7" t="n">
-        <v>8433446.859999999</v>
+        <v>8341391.35</v>
       </c>
       <c r="I90" s="6" t="n">
-        <v>12650170290</v>
+        <v>12762328765.5</v>
       </c>
       <c r="J90" s="7" t="n">
-        <v>2061822.67</v>
+        <v>2070361.93</v>
       </c>
       <c r="K90" s="7" t="n">
-        <v>6371624.18</v>
+        <v>6271029.45</v>
       </c>
       <c r="L90" s="6" t="n">
         <v>251680000</v>
       </c>
       <c r="M90" s="7" t="n">
-        <v>167786.67</v>
+        <v>164496.73</v>
       </c>
       <c r="N90" s="6" t="n">
-        <v>12398490290</v>
+        <v>12510648765.5</v>
       </c>
     </row>
     <row r="91">
@@ -4768,37 +4768,37 @@
         <v>81</v>
       </c>
       <c r="D91" s="7" t="n">
-        <v>140860.71</v>
+        <v>149690.29</v>
       </c>
       <c r="E91" s="7" t="n">
         <v>42263.1</v>
       </c>
       <c r="F91" s="7" t="n">
-        <v>237.65</v>
+        <v>234.52</v>
       </c>
       <c r="G91" s="7" t="n">
-        <v>42258.21</v>
+        <v>44907.09</v>
       </c>
       <c r="H91" s="7" t="n">
-        <v>225619.67</v>
+        <v>237095.03</v>
       </c>
       <c r="I91" s="6" t="n">
-        <v>338429505</v>
+        <v>362755395.9</v>
       </c>
       <c r="J91" s="7" t="n">
-        <v>90911.49000000001</v>
+        <v>93033.81</v>
       </c>
       <c r="K91" s="7" t="n">
-        <v>134708.17</v>
+        <v>144061.23</v>
       </c>
       <c r="L91" s="6" t="n">
         <v>168480000</v>
       </c>
       <c r="M91" s="7" t="n">
-        <v>112320</v>
+        <v>110117.65</v>
       </c>
       <c r="N91" s="6" t="n">
-        <v>169949505</v>
+        <v>194275395.9</v>
       </c>
     </row>
     <row r="92">
@@ -4816,37 +4816,37 @@
         <v>524</v>
       </c>
       <c r="D92" s="7" t="n">
-        <v>20967697.37</v>
+        <v>20841440.64</v>
       </c>
       <c r="E92" s="7" t="n">
         <v>10319142.07</v>
       </c>
       <c r="F92" s="7" t="n">
-        <v>280694.12</v>
+        <v>280454.81</v>
       </c>
       <c r="G92" s="7" t="n">
-        <v>6290309.18</v>
+        <v>6252432.09</v>
       </c>
       <c r="H92" s="7" t="n">
-        <v>37857842.78</v>
+        <v>37693469.74</v>
       </c>
       <c r="I92" s="6" t="n">
-        <v>56786764170</v>
+        <v>57671008702.2</v>
       </c>
       <c r="J92" s="7" t="n">
-        <v>15833263.7</v>
+        <v>15737445.26</v>
       </c>
       <c r="K92" s="7" t="n">
-        <v>22024579.09</v>
+        <v>21956024.5</v>
       </c>
       <c r="L92" s="6" t="n">
         <v>1089920000</v>
       </c>
       <c r="M92" s="7" t="n">
-        <v>726613.33</v>
+        <v>712366.01</v>
       </c>
       <c r="N92" s="6" t="n">
-        <v>55696844170</v>
+        <v>56581088702.2</v>
       </c>
     </row>
     <row r="93">
@@ -4864,37 +4864,37 @@
         <v>121</v>
       </c>
       <c r="D93" s="7" t="n">
-        <v>5393736.03</v>
+        <v>5360683.89</v>
       </c>
       <c r="E93" s="7" t="n">
         <v>900761.65</v>
       </c>
       <c r="F93" s="7" t="n">
-        <v>44130.18</v>
+        <v>44086.39</v>
       </c>
       <c r="G93" s="7" t="n">
-        <v>1618120.81</v>
+        <v>1608205.19</v>
       </c>
       <c r="H93" s="7" t="n">
-        <v>7956748.65</v>
+        <v>7913736.99</v>
       </c>
       <c r="I93" s="6" t="n">
-        <v>11935122975</v>
+        <v>12108017594.7</v>
       </c>
       <c r="J93" s="7" t="n">
-        <v>1323273.88</v>
+        <v>1312746.23</v>
       </c>
       <c r="K93" s="7" t="n">
-        <v>6633474.81</v>
+        <v>6600990.82</v>
       </c>
       <c r="L93" s="6" t="n">
         <v>251680000</v>
       </c>
       <c r="M93" s="7" t="n">
-        <v>167786.67</v>
+        <v>164496.73</v>
       </c>
       <c r="N93" s="6" t="n">
-        <v>11683442975</v>
+        <v>11856337594.7</v>
       </c>
     </row>
     <row r="94">
@@ -4912,37 +4912,37 @@
         <v>81</v>
       </c>
       <c r="D94" s="7" t="n">
-        <v>130921.78</v>
+        <v>133559.32</v>
       </c>
       <c r="E94" s="7" t="n">
         <v>10760.01</v>
       </c>
       <c r="F94" s="7" t="n">
-        <v>241.17</v>
+        <v>240.68</v>
       </c>
       <c r="G94" s="7" t="n">
-        <v>39276.53</v>
+        <v>40067.79</v>
       </c>
       <c r="H94" s="7" t="n">
-        <v>181199.56</v>
+        <v>184627.92</v>
       </c>
       <c r="I94" s="6" t="n">
-        <v>271799340</v>
+        <v>282480717.6</v>
       </c>
       <c r="J94" s="7" t="n">
-        <v>78353.92999999999</v>
+        <v>79610.5</v>
       </c>
       <c r="K94" s="7" t="n">
-        <v>102845.65</v>
+        <v>105017.37</v>
       </c>
       <c r="L94" s="6" t="n">
         <v>168480000</v>
       </c>
       <c r="M94" s="7" t="n">
-        <v>112320</v>
+        <v>110117.65</v>
       </c>
       <c r="N94" s="6" t="n">
-        <v>103319340</v>
+        <v>114000717.6</v>
       </c>
     </row>
   </sheetData>
